--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>18/07/2026 a las 07:25:17</t>
+    <t>18/07/2026 a las 07:39:02</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -6182,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y27" s="4"/>
       <c r="Z27" s="4" t="s">
@@ -11332,7 +11332,7 @@
         <v>3</v>
       </c>
       <c r="X95" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y95" s="4"/>
       <c r="Z95" s="4" t="s">
@@ -21320,7 +21320,7 @@
         <v>2</v>
       </c>
       <c r="X227" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y227" s="4"/>
       <c r="Z227" s="4" t="s">
@@ -23264,7 +23264,7 @@
         <v>2</v>
       </c>
       <c r="X254" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y254" s="4"/>
       <c r="Z254" s="4" t="s">
@@ -23416,7 +23416,7 @@
         <v>1</v>
       </c>
       <c r="X256" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y256" s="4"/>
       <c r="Z256" s="4" t="s">
@@ -24762,7 +24762,7 @@
         <v>1</v>
       </c>
       <c r="X274" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y274" s="4"/>
       <c r="Z274" s="4" t="s">
@@ -25260,7 +25260,7 @@
         <v>1</v>
       </c>
       <c r="X281" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y281" s="4"/>
       <c r="Z281" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>18/07/2026 a las 07:39:02</t>
+    <t>18/07/2026 a las 08:01:10</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -10198,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="X80" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y80" s="4"/>
       <c r="Z80" s="4" t="s">
@@ -10354,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="X82" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y82" s="4"/>
       <c r="Z82" s="4" t="s">
@@ -10430,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="X83" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y83" s="4"/>
       <c r="Z83" s="4" t="s">
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="X84" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y84" s="4"/>
       <c r="Z84" s="4" t="s">
@@ -10578,7 +10578,7 @@
         <v>1</v>
       </c>
       <c r="X85" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y85" s="4"/>
       <c r="Z85" s="4" t="s">
@@ -12934,7 +12934,7 @@
         <v>3</v>
       </c>
       <c r="X116" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y116" s="4"/>
       <c r="Z116" s="4" t="s">
@@ -15256,7 +15256,7 @@
         <v>1000</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="C147" s="4">
         <v>161971161</v>
@@ -19022,7 +19022,7 @@
         <v>1</v>
       </c>
       <c r="X196" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y196" s="4"/>
       <c r="Z196" s="4" t="s">
@@ -19168,7 +19168,7 @@
         <v>2</v>
       </c>
       <c r="X198" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y198" s="4"/>
       <c r="Z198" s="4" t="s">
@@ -19242,7 +19242,7 @@
         <v>1</v>
       </c>
       <c r="X199" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y199" s="4"/>
       <c r="Z199" s="4" t="s">
@@ -19316,7 +19316,7 @@
         <v>1</v>
       </c>
       <c r="X200" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y200" s="4"/>
       <c r="Z200" s="4" t="s">
@@ -20262,7 +20262,7 @@
         <v>2</v>
       </c>
       <c r="X213" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y213" s="4"/>
       <c r="Z213" s="4" t="s">
@@ -20512,7 +20512,7 @@
         <v>1000</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="C217" s="4">
         <v>161844503</v>
@@ -21026,7 +21026,7 @@
         <v>3</v>
       </c>
       <c r="X223" s="4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="Y223" s="4"/>
       <c r="Z223" s="4" t="s">
@@ -25736,7 +25736,7 @@
         <v>1000</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>33</v>
+        <v>779</v>
       </c>
       <c r="C288" s="4">
         <v>162080256</v>
@@ -25788,7 +25788,7 @@
         <v>1</v>
       </c>
       <c r="X288" s="4" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="Y288" s="4"/>
       <c r="Z288" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1199">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>19/07/2026 a las 12:01:21</t>
+    <t>19/07/2026 a las 13:01:22</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -2916,18 +2916,6 @@
   </si>
   <si>
     <t>CR 33C</t>
-  </si>
-  <si>
-    <t>CR 33C # CL 19 - 70 APTO 08 AN6321</t>
-  </si>
-  <si>
-    <t>ROSADO  MAILYN</t>
-  </si>
-  <si>
-    <t>13093220-MCA55</t>
-  </si>
-  <si>
-    <t>Investigar Dano medidor yo acometida SUSPENSION EN TENDIDO. Jorge Curvelo -3014614016-jorgecurvelo1557hotmail.con - Tel Entrando por la universidad cum</t>
   </si>
   <si>
     <t>CL 21</t>
@@ -4017,7 +4005,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB248"/>
+  <dimension ref="A1:AB247"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -18414,13 +18402,13 @@
         <v>245</v>
       </c>
       <c r="C194" s="4">
-        <v>162072355</v>
+        <v>162099761</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>72</v>
       </c>
       <c r="E194" s="4">
-        <v>6808021</v>
+        <v>1015959</v>
       </c>
       <c r="F194" s="4" t="s">
         <v>61</v>
@@ -18442,18 +18430,20 @@
         <v>966</v>
       </c>
       <c r="M194" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N194" s="4"/>
+        <v>967</v>
+      </c>
+      <c r="N194" s="4">
+        <v>95</v>
+      </c>
       <c r="O194" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="P194" s="5"/>
       <c r="Q194" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="R194" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="S194" s="4">
         <v>0</v>
@@ -18462,7 +18452,7 @@
         <v>0</v>
       </c>
       <c r="U194" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="V194" s="4" t="s">
         <v>114</v>
@@ -18475,11 +18465,9 @@
       </c>
       <c r="Y194" s="4"/>
       <c r="Z194" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="AA194" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>971</v>
+      </c>
+      <c r="AA194" s="4"/>
       <c r="AB194" s="4" t="s">
         <v>46</v>
       </c>
@@ -18489,16 +18477,16 @@
         <v>1000</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>245</v>
+        <v>33</v>
       </c>
       <c r="C195" s="4">
-        <v>162099761</v>
+        <v>162088153</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>72</v>
+        <v>972</v>
       </c>
       <c r="E195" s="4">
-        <v>1015959</v>
+        <v>6944188</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>61</v>
@@ -18510,30 +18498,30 @@
         <v>223</v>
       </c>
       <c r="I195" s="4" t="s">
-        <v>223</v>
+        <v>973</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>951</v>
+        <v>973</v>
       </c>
       <c r="K195" s="4"/>
       <c r="L195" s="4" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="M195" s="4" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="N195" s="4">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O195" s="4" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="P195" s="5"/>
       <c r="Q195" s="4" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="R195" s="4" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="S195" s="4">
         <v>0</v>
@@ -18541,23 +18529,21 @@
       <c r="T195" s="4">
         <v>0</v>
       </c>
-      <c r="U195" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="V195" s="4" t="s">
-        <v>114</v>
-      </c>
+      <c r="U195" s="4"/>
+      <c r="V195" s="4"/>
       <c r="W195" s="4">
         <v>2</v>
       </c>
       <c r="X195" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y195" s="4"/>
       <c r="Z195" s="4" t="s">
-        <v>975</v>
-      </c>
-      <c r="AA195" s="4"/>
+        <v>978</v>
+      </c>
+      <c r="AA195" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="AB195" s="4" t="s">
         <v>46</v>
       </c>
@@ -18567,16 +18553,16 @@
         <v>1000</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>33</v>
+        <v>787</v>
       </c>
       <c r="C196" s="4">
-        <v>162088153</v>
+        <v>161842246</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>976</v>
+        <v>238</v>
       </c>
       <c r="E196" s="4">
-        <v>6944188</v>
+        <v>7715577</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>61</v>
@@ -18588,30 +18574,30 @@
         <v>223</v>
       </c>
       <c r="I196" s="4" t="s">
-        <v>977</v>
+        <v>223</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="K196" s="4"/>
       <c r="L196" s="4" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="M196" s="4" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="N196" s="4">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="O196" s="4" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="P196" s="5"/>
       <c r="Q196" s="4" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="R196" s="4" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="S196" s="4">
         <v>0</v>
@@ -18619,20 +18605,24 @@
       <c r="T196" s="4">
         <v>0</v>
       </c>
-      <c r="U196" s="4"/>
-      <c r="V196" s="4"/>
+      <c r="U196" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="V196" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="W196" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X196" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y196" s="4"/>
       <c r="Z196" s="4" t="s">
-        <v>982</v>
+        <v>546</v>
       </c>
       <c r="AA196" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AB196" s="4" t="s">
         <v>46</v>
@@ -18643,16 +18633,16 @@
         <v>1000</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>787</v>
+        <v>33</v>
       </c>
       <c r="C197" s="4">
-        <v>161842246</v>
+        <v>162145303</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="E197" s="4">
-        <v>7715577</v>
+        <v>8122394</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>61</v>
@@ -18664,30 +18654,24 @@
         <v>223</v>
       </c>
       <c r="I197" s="4" t="s">
-        <v>223</v>
+        <v>985</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="K197" s="4"/>
-      <c r="L197" s="4" t="s">
-        <v>984</v>
-      </c>
-      <c r="M197" s="4" t="s">
-        <v>985</v>
-      </c>
-      <c r="N197" s="4">
-        <v>55</v>
-      </c>
+      <c r="L197" s="4"/>
+      <c r="M197" s="4"/>
+      <c r="N197" s="4"/>
       <c r="O197" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="P197" s="5"/>
       <c r="Q197" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="R197" s="4" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="S197" s="4">
         <v>0</v>
@@ -18695,25 +18679,19 @@
       <c r="T197" s="4">
         <v>0</v>
       </c>
-      <c r="U197" s="4" t="s">
-        <v>988</v>
-      </c>
-      <c r="V197" s="4" t="s">
-        <v>436</v>
-      </c>
+      <c r="U197" s="4"/>
+      <c r="V197" s="4"/>
       <c r="W197" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X197" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y197" s="4"/>
       <c r="Z197" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="AA197" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>989</v>
+      </c>
+      <c r="AA197" s="4"/>
       <c r="AB197" s="4" t="s">
         <v>46</v>
       </c>
@@ -18726,13 +18704,13 @@
         <v>33</v>
       </c>
       <c r="C198" s="4">
-        <v>162145303</v>
+        <v>161825701</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E198" s="4">
-        <v>8122394</v>
+        <v>8375615</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>61</v>
@@ -18744,7 +18722,7 @@
         <v>223</v>
       </c>
       <c r="I198" s="4" t="s">
-        <v>989</v>
+        <v>223</v>
       </c>
       <c r="J198" s="4" t="s">
         <v>990</v>
@@ -18761,25 +18739,25 @@
         <v>992</v>
       </c>
       <c r="R198" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="S198" s="4">
-        <v>0</v>
+        <v>205205.43</v>
       </c>
       <c r="T198" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U198" s="4"/>
       <c r="V198" s="4"/>
       <c r="W198" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X198" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y198" s="4"/>
       <c r="Z198" s="4" t="s">
-        <v>993</v>
+        <v>317</v>
       </c>
       <c r="AA198" s="4"/>
       <c r="AB198" s="4" t="s">
@@ -18794,13 +18772,13 @@
         <v>33</v>
       </c>
       <c r="C199" s="4">
-        <v>161825701</v>
+        <v>161825906</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E199" s="4">
-        <v>8375615</v>
+        <v>8375616</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>61</v>
@@ -18815,18 +18793,18 @@
         <v>223</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="K199" s="4"/>
       <c r="L199" s="4"/>
       <c r="M199" s="4"/>
       <c r="N199" s="4"/>
       <c r="O199" s="4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="P199" s="5"/>
       <c r="Q199" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="R199" s="4" t="s">
         <v>52</v>
@@ -18862,13 +18840,13 @@
         <v>33</v>
       </c>
       <c r="C200" s="4">
-        <v>161825906</v>
+        <v>161826081</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E200" s="4">
-        <v>8375616</v>
+        <v>8375614</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>61</v>
@@ -18883,18 +18861,18 @@
         <v>223</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="K200" s="4"/>
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
       <c r="N200" s="4"/>
       <c r="O200" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="P200" s="5"/>
       <c r="Q200" s="4" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="R200" s="4" t="s">
         <v>52</v>
@@ -18930,13 +18908,13 @@
         <v>33</v>
       </c>
       <c r="C201" s="4">
-        <v>161826081</v>
+        <v>161826260</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E201" s="4">
-        <v>8375614</v>
+        <v>8375604</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>61</v>
@@ -18951,18 +18929,18 @@
         <v>223</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="K201" s="4"/>
       <c r="L201" s="4"/>
       <c r="M201" s="4"/>
       <c r="N201" s="4"/>
       <c r="O201" s="4" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="P201" s="5"/>
       <c r="Q201" s="4" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="R201" s="4" t="s">
         <v>52</v>
@@ -18983,7 +18961,7 @@
       </c>
       <c r="Y201" s="4"/>
       <c r="Z201" s="4" t="s">
-        <v>317</v>
+        <v>999</v>
       </c>
       <c r="AA201" s="4"/>
       <c r="AB201" s="4" t="s">
@@ -18998,13 +18976,13 @@
         <v>33</v>
       </c>
       <c r="C202" s="4">
-        <v>161826260</v>
+        <v>161826484</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E202" s="4">
-        <v>8375604</v>
+        <v>8375941</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>61</v>
@@ -19019,18 +18997,18 @@
         <v>223</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="K202" s="4"/>
       <c r="L202" s="4"/>
       <c r="M202" s="4"/>
       <c r="N202" s="4"/>
       <c r="O202" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="P202" s="5"/>
       <c r="Q202" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="R202" s="4" t="s">
         <v>52</v>
@@ -19051,7 +19029,7 @@
       </c>
       <c r="Y202" s="4"/>
       <c r="Z202" s="4" t="s">
-        <v>1003</v>
+        <v>317</v>
       </c>
       <c r="AA202" s="4"/>
       <c r="AB202" s="4" t="s">
@@ -19063,16 +19041,16 @@
         <v>1000</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>33</v>
+        <v>654</v>
       </c>
       <c r="C203" s="4">
-        <v>161826484</v>
+        <v>162002621</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="E203" s="4">
-        <v>8375941</v>
+        <v>6641364</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>61</v>
@@ -19087,41 +19065,49 @@
         <v>223</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="K203" s="4"/>
-      <c r="L203" s="4"/>
+      <c r="L203" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="M203" s="4"/>
       <c r="N203" s="4"/>
       <c r="O203" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="P203" s="5"/>
       <c r="Q203" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="R203" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="S203" s="4">
+        <v>0</v>
+      </c>
+      <c r="T203" s="4">
+        <v>0</v>
+      </c>
+      <c r="U203" s="4" t="s">
         <v>1005</v>
       </c>
-      <c r="R203" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="S203" s="4">
-        <v>205205.43</v>
-      </c>
-      <c r="T203" s="4">
-        <v>1</v>
-      </c>
-      <c r="U203" s="4"/>
-      <c r="V203" s="4"/>
+      <c r="V203" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="W203" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X203" s="4" t="s">
-        <v>44</v>
+        <v>1006</v>
       </c>
       <c r="Y203" s="4"/>
       <c r="Z203" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="AA203" s="4"/>
+        <v>1007</v>
+      </c>
+      <c r="AA203" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="AB203" s="4" t="s">
         <v>46</v>
       </c>
@@ -19131,16 +19117,16 @@
         <v>1000</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>654</v>
+        <v>946</v>
       </c>
       <c r="C204" s="4">
-        <v>162002621</v>
+        <v>162083641</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="E204" s="4">
-        <v>6641364</v>
+        <v>6639208</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>61</v>
@@ -19155,7 +19141,7 @@
         <v>223</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="K204" s="4"/>
       <c r="L204" s="4" t="s">
@@ -19164,11 +19150,11 @@
       <c r="M204" s="4"/>
       <c r="N204" s="4"/>
       <c r="O204" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="P204" s="5"/>
       <c r="Q204" s="4" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="R204" s="4" t="s">
         <v>132</v>
@@ -19179,24 +19165,20 @@
       <c r="T204" s="4">
         <v>0</v>
       </c>
-      <c r="U204" s="4" t="s">
-        <v>1009</v>
-      </c>
-      <c r="V204" s="4" t="s">
-        <v>204</v>
-      </c>
+      <c r="U204" s="4"/>
+      <c r="V204" s="4"/>
       <c r="W204" s="4">
         <v>2</v>
       </c>
       <c r="X204" s="4" t="s">
-        <v>1010</v>
+        <v>253</v>
       </c>
       <c r="Y204" s="4"/>
       <c r="Z204" s="4" t="s">
-        <v>1011</v>
+        <v>441</v>
       </c>
       <c r="AA204" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AB204" s="4" t="s">
         <v>46</v>
@@ -19207,16 +19189,16 @@
         <v>1000</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>946</v>
+        <v>33</v>
       </c>
       <c r="C205" s="4">
-        <v>162083641</v>
+        <v>162089713</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="E205" s="4">
-        <v>6639208</v>
+        <v>5911652</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>61</v>
@@ -19231,7 +19213,7 @@
         <v>223</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="K205" s="4"/>
       <c r="L205" s="4" t="s">
@@ -19240,36 +19222,38 @@
       <c r="M205" s="4"/>
       <c r="N205" s="4"/>
       <c r="O205" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="P205" s="5"/>
       <c r="Q205" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="R205" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S205" s="4">
+        <v>0</v>
+      </c>
+      <c r="T205" s="4">
+        <v>0</v>
+      </c>
+      <c r="U205" s="4" t="s">
         <v>1013</v>
       </c>
-      <c r="R205" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="S205" s="4">
-        <v>0</v>
-      </c>
-      <c r="T205" s="4">
-        <v>0</v>
-      </c>
-      <c r="U205" s="4"/>
-      <c r="V205" s="4"/>
+      <c r="V205" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="W205" s="4">
         <v>2</v>
       </c>
       <c r="X205" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y205" s="4"/>
       <c r="Z205" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="AA205" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>1014</v>
+      </c>
+      <c r="AA205" s="4"/>
       <c r="AB205" s="4" t="s">
         <v>46</v>
       </c>
@@ -19282,13 +19266,13 @@
         <v>33</v>
       </c>
       <c r="C206" s="4">
-        <v>162089713</v>
+        <v>162136391</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>72</v>
+        <v>287</v>
       </c>
       <c r="E206" s="4">
-        <v>5911652</v>
+        <v>7516302</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>61</v>
@@ -19303,7 +19287,7 @@
         <v>223</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="K206" s="4"/>
       <c r="L206" s="4" t="s">
@@ -19312,14 +19296,14 @@
       <c r="M206" s="4"/>
       <c r="N206" s="4"/>
       <c r="O206" s="4" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="P206" s="5"/>
       <c r="Q206" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="R206" s="4" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="S206" s="4">
         <v>0</v>
@@ -19328,22 +19312,24 @@
         <v>0</v>
       </c>
       <c r="U206" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="V206" s="4" t="s">
-        <v>436</v>
+        <v>114</v>
       </c>
       <c r="W206" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X206" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y206" s="4"/>
       <c r="Z206" s="4" t="s">
-        <v>1018</v>
-      </c>
-      <c r="AA206" s="4"/>
+        <v>1019</v>
+      </c>
+      <c r="AA206" s="4" t="s">
+        <v>84</v>
+      </c>
       <c r="AB206" s="4" t="s">
         <v>46</v>
       </c>
@@ -19353,16 +19339,16 @@
         <v>1000</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>33</v>
+        <v>268</v>
       </c>
       <c r="C207" s="4">
-        <v>162136391</v>
+        <v>161842254</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="E207" s="4">
-        <v>7516302</v>
+        <v>6502930</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>61</v>
@@ -19377,7 +19363,7 @@
         <v>223</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="K207" s="4"/>
       <c r="L207" s="4" t="s">
@@ -19386,14 +19372,14 @@
       <c r="M207" s="4"/>
       <c r="N207" s="4"/>
       <c r="O207" s="4" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="P207" s="5"/>
       <c r="Q207" s="4" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="R207" s="4" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="S207" s="4">
         <v>0</v>
@@ -19402,20 +19388,20 @@
         <v>0</v>
       </c>
       <c r="U207" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="V207" s="4" t="s">
-        <v>114</v>
+        <v>321</v>
       </c>
       <c r="W207" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X207" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y207" s="4"/>
       <c r="Z207" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AA207" s="4" t="s">
         <v>84</v>
@@ -19429,16 +19415,16 @@
         <v>1000</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>268</v>
+        <v>33</v>
       </c>
       <c r="C208" s="4">
-        <v>161842254</v>
+        <v>161842258</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E208" s="4">
-        <v>6502930</v>
+        <v>6915253</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>61</v>
@@ -19453,7 +19439,7 @@
         <v>223</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="K208" s="4"/>
       <c r="L208" s="4" t="s">
@@ -19477,24 +19463,20 @@
       <c r="T208" s="4">
         <v>0</v>
       </c>
-      <c r="U208" s="4" t="s">
-        <v>1027</v>
-      </c>
-      <c r="V208" s="4" t="s">
-        <v>321</v>
-      </c>
+      <c r="U208" s="4"/>
+      <c r="V208" s="4"/>
       <c r="W208" s="4">
         <v>4</v>
       </c>
       <c r="X208" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y208" s="4"/>
       <c r="Z208" s="4" t="s">
-        <v>1028</v>
+        <v>719</v>
       </c>
       <c r="AA208" s="4" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="AB208" s="4" t="s">
         <v>46</v>
@@ -19508,13 +19490,13 @@
         <v>33</v>
       </c>
       <c r="C209" s="4">
-        <v>161842258</v>
+        <v>161842259</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E209" s="4">
-        <v>6915253</v>
+        <v>7884056</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>61</v>
@@ -19529,7 +19511,7 @@
         <v>223</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="4" t="s">
@@ -19538,11 +19520,11 @@
       <c r="M209" s="4"/>
       <c r="N209" s="4"/>
       <c r="O209" s="4" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="P209" s="5"/>
       <c r="Q209" s="4" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="R209" s="4" t="s">
         <v>43</v>
@@ -19563,10 +19545,10 @@
       </c>
       <c r="Y209" s="4"/>
       <c r="Z209" s="4" t="s">
-        <v>719</v>
+        <v>546</v>
       </c>
       <c r="AA209" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AB209" s="4" t="s">
         <v>46</v>
@@ -19580,13 +19562,13 @@
         <v>33</v>
       </c>
       <c r="C210" s="4">
-        <v>161842259</v>
+        <v>162134784</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="E210" s="4">
-        <v>7884056</v>
+        <v>6865747</v>
       </c>
       <c r="F210" s="4" t="s">
         <v>61</v>
@@ -19601,7 +19583,7 @@
         <v>223</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="4" t="s">
@@ -19610,11 +19592,11 @@
       <c r="M210" s="4"/>
       <c r="N210" s="4"/>
       <c r="O210" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="P210" s="5"/>
       <c r="Q210" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="R210" s="4" t="s">
         <v>43</v>
@@ -19628,17 +19610,17 @@
       <c r="U210" s="4"/>
       <c r="V210" s="4"/>
       <c r="W210" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X210" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y210" s="4"/>
       <c r="Z210" s="4" t="s">
-        <v>546</v>
+        <v>1032</v>
       </c>
       <c r="AA210" s="4" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="AB210" s="4" t="s">
         <v>46</v>
@@ -19652,13 +19634,13 @@
         <v>33</v>
       </c>
       <c r="C211" s="4">
-        <v>162134784</v>
+        <v>161382504</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="E211" s="4">
-        <v>6865747</v>
+        <v>7531027</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>61</v>
@@ -19689,7 +19671,7 @@
         <v>1035</v>
       </c>
       <c r="R211" s="4" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="S211" s="4">
         <v>0</v>
@@ -19697,20 +19679,24 @@
       <c r="T211" s="4">
         <v>0</v>
       </c>
-      <c r="U211" s="4"/>
-      <c r="V211" s="4"/>
+      <c r="U211" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="V211" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="W211" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X211" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y211" s="4"/>
       <c r="Z211" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AA211" s="4" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="AB211" s="4" t="s">
         <v>46</v>
@@ -19721,16 +19707,16 @@
         <v>1000</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>33</v>
+        <v>1038</v>
       </c>
       <c r="C212" s="4">
-        <v>161382504</v>
+        <v>161843460</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E212" s="4">
-        <v>7531027</v>
+        <v>7859713</v>
       </c>
       <c r="F212" s="4" t="s">
         <v>61</v>
@@ -19745,7 +19731,7 @@
         <v>223</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="K212" s="4"/>
       <c r="L212" s="4" t="s">
@@ -19754,40 +19740,34 @@
       <c r="M212" s="4"/>
       <c r="N212" s="4"/>
       <c r="O212" s="4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="P212" s="5"/>
       <c r="Q212" s="4" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="R212" s="4" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="S212" s="4">
-        <v>0</v>
+        <v>55071.92</v>
       </c>
       <c r="T212" s="4">
-        <v>0</v>
-      </c>
-      <c r="U212" s="4" t="s">
-        <v>1040</v>
-      </c>
-      <c r="V212" s="4" t="s">
-        <v>436</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U212" s="4"/>
+      <c r="V212" s="4"/>
       <c r="W212" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X212" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y212" s="4"/>
       <c r="Z212" s="4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="AA212" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="AA212" s="4"/>
       <c r="AB212" s="4" t="s">
         <v>46</v>
       </c>
@@ -19797,16 +19777,16 @@
         <v>1000</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>1042</v>
+        <v>355</v>
       </c>
       <c r="C213" s="4">
-        <v>161843460</v>
+        <v>161842260</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E213" s="4">
-        <v>7859713</v>
+        <v>1345270</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>61</v>
@@ -19821,29 +19801,31 @@
         <v>223</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="K213" s="4"/>
       <c r="L213" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="M213" s="4"/>
+        <v>1043</v>
+      </c>
+      <c r="M213" s="4" t="s">
+        <v>1044</v>
+      </c>
       <c r="N213" s="4"/>
       <c r="O213" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="P213" s="5"/>
       <c r="Q213" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="R213" s="4" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="S213" s="4">
-        <v>55071.92</v>
+        <v>0</v>
       </c>
       <c r="T213" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U213" s="4"/>
       <c r="V213" s="4"/>
@@ -19855,9 +19837,11 @@
       </c>
       <c r="Y213" s="4"/>
       <c r="Z213" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="AA213" s="4"/>
+        <v>719</v>
+      </c>
+      <c r="AA213" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="AB213" s="4" t="s">
         <v>46</v>
       </c>
@@ -19867,16 +19851,16 @@
         <v>1000</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C214" s="4">
-        <v>161842260</v>
+        <v>161975057</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>238</v>
+        <v>34</v>
       </c>
       <c r="E214" s="4">
-        <v>1345270</v>
+        <v>8377162</v>
       </c>
       <c r="F214" s="4" t="s">
         <v>61</v>
@@ -19891,47 +19875,41 @@
         <v>223</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="K214" s="4"/>
-      <c r="L214" s="4" t="s">
-        <v>1047</v>
-      </c>
-      <c r="M214" s="4" t="s">
-        <v>1048</v>
-      </c>
+      <c r="L214" s="4"/>
+      <c r="M214" s="4"/>
       <c r="N214" s="4"/>
       <c r="O214" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P214" s="5"/>
       <c r="Q214" s="4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="R214" s="4" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="S214" s="4">
-        <v>0</v>
+        <v>96785.61</v>
       </c>
       <c r="T214" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U214" s="4"/>
       <c r="V214" s="4"/>
       <c r="W214" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X214" s="4" t="s">
         <v>253</v>
       </c>
       <c r="Y214" s="4"/>
       <c r="Z214" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="AA214" s="4" t="s">
-        <v>104</v>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="AA214" s="4"/>
       <c r="AB214" s="4" t="s">
         <v>46</v>
       </c>
@@ -19941,16 +19919,16 @@
         <v>1000</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>348</v>
+        <v>1051</v>
       </c>
       <c r="C215" s="4">
-        <v>161975057</v>
+        <v>161827825</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>34</v>
+        <v>644</v>
       </c>
       <c r="E215" s="4">
-        <v>8377162</v>
+        <v>6635531</v>
       </c>
       <c r="F215" s="4" t="s">
         <v>61</v>
@@ -19965,10 +19943,12 @@
         <v>223</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="K215" s="4"/>
-      <c r="L215" s="4"/>
+      <c r="L215" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="M215" s="4"/>
       <c r="N215" s="4"/>
       <c r="O215" s="4" t="s">
@@ -19979,18 +19959,18 @@
         <v>1053</v>
       </c>
       <c r="R215" s="4" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="S215" s="4">
-        <v>96785.61</v>
+        <v>0</v>
       </c>
       <c r="T215" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U215" s="4"/>
       <c r="V215" s="4"/>
       <c r="W215" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X215" s="4" t="s">
         <v>253</v>
@@ -19999,7 +19979,9 @@
       <c r="Z215" s="4" t="s">
         <v>1054</v>
       </c>
-      <c r="AA215" s="4"/>
+      <c r="AA215" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB215" s="4" t="s">
         <v>46</v>
       </c>
@@ -20009,16 +19991,16 @@
         <v>1000</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C216" s="4">
-        <v>161827825</v>
+        <v>161945294</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>644</v>
+        <v>287</v>
       </c>
       <c r="E216" s="4">
-        <v>6635531</v>
+        <v>5883262</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>61</v>
@@ -20033,7 +20015,7 @@
         <v>223</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="K216" s="4"/>
       <c r="L216" s="4" t="s">
@@ -20042,11 +20024,11 @@
       <c r="M216" s="4"/>
       <c r="N216" s="4"/>
       <c r="O216" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="P216" s="5"/>
       <c r="Q216" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="R216" s="4" t="s">
         <v>52</v>
@@ -20057,10 +20039,14 @@
       <c r="T216" s="4">
         <v>0</v>
       </c>
-      <c r="U216" s="4"/>
-      <c r="V216" s="4"/>
+      <c r="U216" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="V216" s="4" t="s">
+        <v>221</v>
+      </c>
       <c r="W216" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X216" s="4" t="s">
         <v>253</v>
@@ -20070,7 +20056,7 @@
         <v>1058</v>
       </c>
       <c r="AA216" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AB216" s="4" t="s">
         <v>46</v>
@@ -20081,16 +20067,16 @@
         <v>1000</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C217" s="4">
-        <v>161945294</v>
+        <v>162090749</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>287</v>
       </c>
       <c r="E217" s="4">
-        <v>5883262</v>
+        <v>8377244</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>61</v>
@@ -20105,23 +20091,27 @@
         <v>223</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="M217" s="4"/>
-      <c r="N217" s="4"/>
+        <v>1060</v>
+      </c>
+      <c r="M217" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="N217" s="4">
+        <v>8</v>
+      </c>
       <c r="O217" s="4" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="P217" s="5"/>
       <c r="Q217" s="4" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="R217" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="S217" s="4">
         <v>0</v>
@@ -20129,25 +20119,19 @@
       <c r="T217" s="4">
         <v>0</v>
       </c>
-      <c r="U217" s="4" t="s">
-        <v>1061</v>
-      </c>
-      <c r="V217" s="4" t="s">
-        <v>221</v>
-      </c>
+      <c r="U217" s="4"/>
+      <c r="V217" s="4"/>
       <c r="W217" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X217" s="4" t="s">
         <v>253</v>
       </c>
       <c r="Y217" s="4"/>
       <c r="Z217" s="4" t="s">
-        <v>1062</v>
-      </c>
-      <c r="AA217" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>1064</v>
+      </c>
+      <c r="AA217" s="4"/>
       <c r="AB217" s="4" t="s">
         <v>46</v>
       </c>
@@ -20157,16 +20141,16 @@
         <v>1000</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>1055</v>
+        <v>33</v>
       </c>
       <c r="C218" s="4">
-        <v>162090749</v>
+        <v>162145171</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>287</v>
+        <v>72</v>
       </c>
       <c r="E218" s="4">
-        <v>8377244</v>
+        <v>8322486</v>
       </c>
       <c r="F218" s="4" t="s">
         <v>61</v>
@@ -20181,18 +20165,12 @@
         <v>223</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="K218" s="4"/>
-      <c r="L218" s="4" t="s">
-        <v>1064</v>
-      </c>
-      <c r="M218" s="4" t="s">
-        <v>1065</v>
-      </c>
-      <c r="N218" s="4">
-        <v>8</v>
-      </c>
+      <c r="L218" s="4"/>
+      <c r="M218" s="4"/>
+      <c r="N218" s="4"/>
       <c r="O218" s="4" t="s">
         <v>1066</v>
       </c>
@@ -20212,10 +20190,10 @@
       <c r="U218" s="4"/>
       <c r="V218" s="4"/>
       <c r="W218" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X218" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y218" s="4"/>
       <c r="Z218" s="4" t="s">
@@ -20231,16 +20209,16 @@
         <v>1000</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>33</v>
+        <v>744</v>
       </c>
       <c r="C219" s="4">
-        <v>162145171</v>
+        <v>161842359</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="E219" s="4">
-        <v>8322486</v>
+        <v>7796628</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>61</v>
@@ -20255,18 +20233,20 @@
         <v>223</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="K219" s="4"/>
-      <c r="L219" s="4"/>
+      <c r="L219" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="M219" s="4"/>
       <c r="N219" s="4"/>
       <c r="O219" s="4" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P219" s="5"/>
       <c r="Q219" s="4" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="R219" s="4" t="s">
         <v>43</v>
@@ -20280,14 +20260,14 @@
       <c r="U219" s="4"/>
       <c r="V219" s="4"/>
       <c r="W219" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X219" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y219" s="4"/>
       <c r="Z219" s="4" t="s">
-        <v>1072</v>
+        <v>556</v>
       </c>
       <c r="AA219" s="4"/>
       <c r="AB219" s="4" t="s">
@@ -20299,16 +20279,16 @@
         <v>1000</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>744</v>
+        <v>872</v>
       </c>
       <c r="C220" s="4">
-        <v>161842359</v>
+        <v>161843461</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E220" s="4">
-        <v>7796628</v>
+        <v>4321843</v>
       </c>
       <c r="F220" s="4" t="s">
         <v>61</v>
@@ -20323,7 +20303,7 @@
         <v>223</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="K220" s="4"/>
       <c r="L220" s="4" t="s">
@@ -20332,20 +20312,20 @@
       <c r="M220" s="4"/>
       <c r="N220" s="4"/>
       <c r="O220" s="4" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="P220" s="5"/>
       <c r="Q220" s="4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="R220" s="4" t="s">
         <v>43</v>
       </c>
       <c r="S220" s="4">
-        <v>0</v>
+        <v>174533.3</v>
       </c>
       <c r="T220" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U220" s="4"/>
       <c r="V220" s="4"/>
@@ -20357,9 +20337,11 @@
       </c>
       <c r="Y220" s="4"/>
       <c r="Z220" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="AA220" s="4"/>
+        <v>559</v>
+      </c>
+      <c r="AA220" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="AB220" s="4" t="s">
         <v>46</v>
       </c>
@@ -20369,16 +20351,16 @@
         <v>1000</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C221" s="4">
-        <v>161843461</v>
+        <v>162083660</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E221" s="4">
-        <v>4321843</v>
+        <v>5903965</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>61</v>
@@ -20393,7 +20375,7 @@
         <v>223</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="K221" s="4"/>
       <c r="L221" s="4" t="s">
@@ -20402,36 +20384,38 @@
       <c r="M221" s="4"/>
       <c r="N221" s="4"/>
       <c r="O221" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="P221" s="5"/>
       <c r="Q221" s="4" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="R221" s="4" t="s">
         <v>43</v>
       </c>
       <c r="S221" s="4">
-        <v>174533.3</v>
+        <v>0</v>
       </c>
       <c r="T221" s="4">
-        <v>1</v>
-      </c>
-      <c r="U221" s="4"/>
-      <c r="V221" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U221" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="V221" s="4" t="s">
+        <v>221</v>
+      </c>
       <c r="W221" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X221" s="4" t="s">
         <v>253</v>
       </c>
       <c r="Y221" s="4"/>
       <c r="Z221" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="AA221" s="4" t="s">
-        <v>104</v>
-      </c>
+        <v>1075</v>
+      </c>
+      <c r="AA221" s="4"/>
       <c r="AB221" s="4" t="s">
         <v>46</v>
       </c>
@@ -20441,16 +20425,16 @@
         <v>1000</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>868</v>
+        <v>33</v>
       </c>
       <c r="C222" s="4">
-        <v>162083660</v>
+        <v>161842214</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E222" s="4">
-        <v>5903965</v>
+        <v>4327672</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>61</v>
@@ -20465,23 +20449,27 @@
         <v>223</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="K222" s="4"/>
       <c r="L222" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="M222" s="4"/>
-      <c r="N222" s="4"/>
+        <v>1077</v>
+      </c>
+      <c r="M222" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="N222" s="4">
+        <v>85</v>
+      </c>
       <c r="O222" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="P222" s="5"/>
       <c r="Q222" s="4" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="R222" s="4" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="S222" s="4">
         <v>0</v>
@@ -20490,22 +20478,24 @@
         <v>0</v>
       </c>
       <c r="U222" s="4" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="V222" s="4" t="s">
-        <v>221</v>
+        <v>321</v>
       </c>
       <c r="W222" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X222" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y222" s="4"/>
       <c r="Z222" s="4" t="s">
-        <v>1079</v>
-      </c>
-      <c r="AA222" s="4"/>
+        <v>1082</v>
+      </c>
+      <c r="AA222" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="AB222" s="4" t="s">
         <v>46</v>
       </c>
@@ -20515,16 +20505,16 @@
         <v>1000</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>33</v>
+        <v>725</v>
       </c>
       <c r="C223" s="4">
-        <v>161842214</v>
+        <v>162072072</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>238</v>
+        <v>670</v>
       </c>
       <c r="E223" s="4">
-        <v>4327672</v>
+        <v>7519952</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>61</v>
@@ -20539,24 +20529,20 @@
         <v>223</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="K223" s="4"/>
       <c r="L223" s="4" t="s">
-        <v>1081</v>
-      </c>
-      <c r="M223" s="4" t="s">
-        <v>1082</v>
-      </c>
-      <c r="N223" s="4">
-        <v>85</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="M223" s="4"/>
+      <c r="N223" s="4"/>
       <c r="O223" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="P223" s="5"/>
       <c r="Q223" s="4" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="R223" s="4" t="s">
         <v>132</v>
@@ -20567,24 +20553,20 @@
       <c r="T223" s="4">
         <v>0</v>
       </c>
-      <c r="U223" s="4" t="s">
-        <v>1085</v>
-      </c>
-      <c r="V223" s="4" t="s">
-        <v>321</v>
-      </c>
+      <c r="U223" s="4"/>
+      <c r="V223" s="4"/>
       <c r="W223" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X223" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y223" s="4"/>
       <c r="Z223" s="4" t="s">
         <v>1086</v>
       </c>
       <c r="AA223" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AB223" s="4" t="s">
         <v>46</v>
@@ -20595,16 +20577,16 @@
         <v>1000</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>725</v>
+        <v>868</v>
       </c>
       <c r="C224" s="4">
-        <v>162072072</v>
+        <v>162083668</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>670</v>
+        <v>238</v>
       </c>
       <c r="E224" s="4">
-        <v>7519952</v>
+        <v>7557348</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>61</v>
@@ -20623,25 +20605,29 @@
       </c>
       <c r="K224" s="4"/>
       <c r="L224" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="M224" s="4"/>
-      <c r="N224" s="4"/>
+        <v>231</v>
+      </c>
+      <c r="M224" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="N224" s="4">
+        <v>42</v>
+      </c>
       <c r="O224" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="P224" s="5"/>
       <c r="Q224" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="R224" s="4" t="s">
         <v>132</v>
       </c>
       <c r="S224" s="4">
-        <v>0</v>
+        <v>264958.77</v>
       </c>
       <c r="T224" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U224" s="4"/>
       <c r="V224" s="4"/>
@@ -20653,10 +20639,10 @@
       </c>
       <c r="Y224" s="4"/>
       <c r="Z224" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AA224" s="4" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AB224" s="4" t="s">
         <v>46</v>
@@ -20667,16 +20653,16 @@
         <v>1000</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>868</v>
+        <v>245</v>
       </c>
       <c r="C225" s="4">
-        <v>162083668</v>
+        <v>162085179</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="E225" s="4">
-        <v>7557348</v>
+        <v>6629549</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>61</v>
@@ -20691,18 +20677,14 @@
         <v>223</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="K225" s="4"/>
       <c r="L225" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="M225" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="N225" s="4">
-        <v>42</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="M225" s="4"/>
+      <c r="N225" s="4"/>
       <c r="O225" s="4" t="s">
         <v>1093</v>
       </c>
@@ -20711,16 +20693,20 @@
         <v>1094</v>
       </c>
       <c r="R225" s="4" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="S225" s="4">
-        <v>264958.77</v>
+        <v>0</v>
       </c>
       <c r="T225" s="4">
-        <v>1</v>
-      </c>
-      <c r="U225" s="4"/>
-      <c r="V225" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U225" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="V225" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="W225" s="4">
         <v>2</v>
       </c>
@@ -20729,10 +20715,10 @@
       </c>
       <c r="Y225" s="4"/>
       <c r="Z225" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AA225" s="4" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AB225" s="4" t="s">
         <v>46</v>
@@ -20743,16 +20729,16 @@
         <v>1000</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>245</v>
+        <v>33</v>
       </c>
       <c r="C226" s="4">
-        <v>162085179</v>
+        <v>162142455</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>72</v>
       </c>
       <c r="E226" s="4">
-        <v>6629549</v>
+        <v>1265794</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>61</v>
@@ -20767,7 +20753,7 @@
         <v>223</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="K226" s="4"/>
       <c r="L226" s="4" t="s">
@@ -20783,7 +20769,7 @@
         <v>1098</v>
       </c>
       <c r="R226" s="4" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="S226" s="4">
         <v>0</v>
@@ -20791,21 +20777,17 @@
       <c r="T226" s="4">
         <v>0</v>
       </c>
-      <c r="U226" s="4" t="s">
-        <v>1099</v>
-      </c>
-      <c r="V226" s="4" t="s">
-        <v>160</v>
-      </c>
+      <c r="U226" s="4"/>
+      <c r="V226" s="4"/>
       <c r="W226" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X226" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y226" s="4"/>
       <c r="Z226" s="4" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AA226" s="4" t="s">
         <v>79</v>
@@ -20822,13 +20804,13 @@
         <v>33</v>
       </c>
       <c r="C227" s="4">
-        <v>162142455</v>
+        <v>162133718</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>72</v>
+        <v>287</v>
       </c>
       <c r="E227" s="4">
-        <v>1265794</v>
+        <v>7545491</v>
       </c>
       <c r="F227" s="4" t="s">
         <v>61</v>
@@ -20843,7 +20825,7 @@
         <v>223</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="K227" s="4"/>
       <c r="L227" s="4" t="s">
@@ -20862,10 +20844,10 @@
         <v>132</v>
       </c>
       <c r="S227" s="4">
-        <v>0</v>
+        <v>75670</v>
       </c>
       <c r="T227" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U227" s="4"/>
       <c r="V227" s="4"/>
@@ -20891,16 +20873,16 @@
         <v>1000</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>33</v>
+        <v>706</v>
       </c>
       <c r="C228" s="4">
-        <v>162133718</v>
+        <v>162083680</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="E228" s="4">
-        <v>7545491</v>
+        <v>7667070</v>
       </c>
       <c r="F228" s="4" t="s">
         <v>61</v>
@@ -20915,13 +20897,15 @@
         <v>223</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="K228" s="4"/>
       <c r="L228" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="M228" s="4"/>
+      <c r="M228" s="4" t="s">
+        <v>1104</v>
+      </c>
       <c r="N228" s="4"/>
       <c r="O228" s="4" t="s">
         <v>1105</v>
@@ -20934,25 +20918,25 @@
         <v>132</v>
       </c>
       <c r="S228" s="4">
-        <v>75670</v>
+        <v>0</v>
       </c>
       <c r="T228" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U228" s="4"/>
       <c r="V228" s="4"/>
       <c r="W228" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X228" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y228" s="4"/>
       <c r="Z228" s="4" t="s">
         <v>1107</v>
       </c>
       <c r="AA228" s="4" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="AB228" s="4" t="s">
         <v>46</v>
@@ -20963,16 +20947,16 @@
         <v>1000</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>706</v>
+        <v>1051</v>
       </c>
       <c r="C229" s="4">
-        <v>162083680</v>
+        <v>162085219</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="E229" s="4">
-        <v>7667070</v>
+        <v>7691692</v>
       </c>
       <c r="F229" s="4" t="s">
         <v>61</v>
@@ -20987,15 +20971,11 @@
         <v>223</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="K229" s="4"/>
-      <c r="L229" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="M229" s="4" t="s">
-        <v>1108</v>
-      </c>
+      <c r="L229" s="4"/>
+      <c r="M229" s="4"/>
       <c r="N229" s="4"/>
       <c r="O229" s="4" t="s">
         <v>1109</v>
@@ -21005,16 +20985,20 @@
         <v>1110</v>
       </c>
       <c r="R229" s="4" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="S229" s="4">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="T229" s="4">
-        <v>0</v>
-      </c>
-      <c r="U229" s="4"/>
-      <c r="V229" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U229" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="V229" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="W229" s="4">
         <v>2</v>
       </c>
@@ -21023,7 +21007,7 @@
       </c>
       <c r="Y229" s="4"/>
       <c r="Z229" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="AA229" s="4" t="s">
         <v>104</v>
@@ -21037,16 +21021,16 @@
         <v>1000</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>1055</v>
+        <v>33</v>
       </c>
       <c r="C230" s="4">
-        <v>162085219</v>
+        <v>162136417</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>287</v>
       </c>
       <c r="E230" s="4">
-        <v>7691692</v>
+        <v>7716274</v>
       </c>
       <c r="F230" s="4" t="s">
         <v>61</v>
@@ -21061,7 +21045,7 @@
         <v>223</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="K230" s="4"/>
       <c r="L230" s="4"/>
@@ -21078,7 +21062,7 @@
         <v>52</v>
       </c>
       <c r="S230" s="4">
-        <v>294</v>
+        <v>302968.31</v>
       </c>
       <c r="T230" s="4">
         <v>1</v>
@@ -21087,17 +21071,17 @@
         <v>1115</v>
       </c>
       <c r="V230" s="4" t="s">
-        <v>321</v>
+        <v>1116</v>
       </c>
       <c r="W230" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X230" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y230" s="4"/>
       <c r="Z230" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="AA230" s="4" t="s">
         <v>104</v>
@@ -21111,16 +21095,16 @@
         <v>1000</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>33</v>
+        <v>245</v>
       </c>
       <c r="C231" s="4">
-        <v>162136417</v>
+        <v>162094076</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>287</v>
+        <v>72</v>
       </c>
       <c r="E231" s="4">
-        <v>7716274</v>
+        <v>1075231</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>61</v>
@@ -21135,46 +21119,50 @@
         <v>223</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="K231" s="4"/>
-      <c r="L231" s="4"/>
-      <c r="M231" s="4"/>
+      <c r="L231" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="M231" s="4" t="s">
+        <v>1119</v>
+      </c>
       <c r="N231" s="4"/>
       <c r="O231" s="4" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="P231" s="5"/>
       <c r="Q231" s="4" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="R231" s="4" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="S231" s="4">
-        <v>302968.31</v>
+        <v>68907.88</v>
       </c>
       <c r="T231" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="V231" s="4" t="s">
-        <v>1120</v>
+        <v>252</v>
       </c>
       <c r="W231" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X231" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y231" s="4"/>
       <c r="Z231" s="4" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="AA231" s="4" t="s">
-        <v>104</v>
+        <v>700</v>
       </c>
       <c r="AB231" s="4" t="s">
         <v>46</v>
@@ -21185,16 +21173,16 @@
         <v>1000</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>245</v>
+        <v>33</v>
       </c>
       <c r="C232" s="4">
-        <v>162094076</v>
+        <v>162143140</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>72</v>
       </c>
       <c r="E232" s="4">
-        <v>1075231</v>
+        <v>7621523</v>
       </c>
       <c r="F232" s="4" t="s">
         <v>61</v>
@@ -21209,50 +21197,44 @@
         <v>223</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
       <c r="K232" s="4"/>
       <c r="L232" s="4" t="s">
-        <v>1122</v>
-      </c>
-      <c r="M232" s="4" t="s">
-        <v>1123</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="M232" s="4"/>
       <c r="N232" s="4"/>
       <c r="O232" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="P232" s="5"/>
       <c r="Q232" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="R232" s="4" t="s">
         <v>132</v>
       </c>
       <c r="S232" s="4">
-        <v>68907.88</v>
+        <v>0</v>
       </c>
       <c r="T232" s="4">
-        <v>2</v>
-      </c>
-      <c r="U232" s="4" t="s">
-        <v>1126</v>
-      </c>
-      <c r="V232" s="4" t="s">
-        <v>252</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U232" s="4"/>
+      <c r="V232" s="4"/>
       <c r="W232" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X232" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y232" s="4"/>
       <c r="Z232" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="AA232" s="4" t="s">
-        <v>700</v>
+        <v>79</v>
       </c>
       <c r="AB232" s="4" t="s">
         <v>46</v>
@@ -21263,16 +21245,16 @@
         <v>1000</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>33</v>
+        <v>1128</v>
       </c>
       <c r="C233" s="4">
-        <v>162143140</v>
+        <v>162083691</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="E233" s="4">
-        <v>7621523</v>
+        <v>8037493</v>
       </c>
       <c r="F233" s="4" t="s">
         <v>61</v>
@@ -21287,44 +21269,42 @@
         <v>223</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K233" s="4"/>
-      <c r="L233" s="4" t="s">
-        <v>271</v>
-      </c>
+      <c r="L233" s="4"/>
       <c r="M233" s="4"/>
       <c r="N233" s="4"/>
       <c r="O233" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="P233" s="5"/>
       <c r="Q233" s="4" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="R233" s="4" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="S233" s="4">
-        <v>0</v>
+        <v>63841.15</v>
       </c>
       <c r="T233" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U233" s="4"/>
       <c r="V233" s="4"/>
       <c r="W233" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X233" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y233" s="4"/>
       <c r="Z233" s="4" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AA233" s="4" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="AB233" s="4" t="s">
         <v>46</v>
@@ -21335,16 +21315,16 @@
         <v>1000</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="C234" s="4">
-        <v>162083691</v>
+        <v>162083689</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E234" s="4">
-        <v>8037493</v>
+        <v>1142919</v>
       </c>
       <c r="F234" s="4" t="s">
         <v>61</v>
@@ -21359,30 +21339,36 @@
         <v>223</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="K234" s="4"/>
-      <c r="L234" s="4"/>
+      <c r="L234" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="M234" s="4"/>
       <c r="N234" s="4"/>
       <c r="O234" s="4" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="P234" s="5"/>
       <c r="Q234" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="R234" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="S234" s="4">
+        <v>0</v>
+      </c>
+      <c r="T234" s="4">
+        <v>0</v>
+      </c>
+      <c r="U234" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="R234" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="S234" s="4">
-        <v>63841.15</v>
-      </c>
-      <c r="T234" s="4">
-        <v>1</v>
-      </c>
-      <c r="U234" s="4"/>
-      <c r="V234" s="4"/>
+      <c r="V234" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="W234" s="4">
         <v>2</v>
       </c>
@@ -21391,7 +21377,7 @@
       </c>
       <c r="Y234" s="4"/>
       <c r="Z234" s="4" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="AA234" s="4" t="s">
         <v>104</v>
@@ -21405,16 +21391,16 @@
         <v>1000</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>1132</v>
+        <v>872</v>
       </c>
       <c r="C235" s="4">
-        <v>162083689</v>
+        <v>161842332</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E235" s="4">
-        <v>1142919</v>
+        <v>7746340</v>
       </c>
       <c r="F235" s="4" t="s">
         <v>61</v>
@@ -21429,12 +21415,10 @@
         <v>223</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="K235" s="4"/>
-      <c r="L235" s="4" t="s">
-        <v>271</v>
-      </c>
+      <c r="L235" s="4"/>
       <c r="M235" s="4"/>
       <c r="N235" s="4"/>
       <c r="O235" s="4" t="s">
@@ -21445,7 +21429,7 @@
         <v>1138</v>
       </c>
       <c r="R235" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="S235" s="4">
         <v>0</v>
@@ -21457,21 +21441,19 @@
         <v>1139</v>
       </c>
       <c r="V235" s="4" t="s">
-        <v>204</v>
+        <v>364</v>
       </c>
       <c r="W235" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X235" s="4" t="s">
         <v>253</v>
       </c>
       <c r="Y235" s="4"/>
       <c r="Z235" s="4" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AA235" s="4" t="s">
-        <v>104</v>
-      </c>
+        <v>1140</v>
+      </c>
+      <c r="AA235" s="4"/>
       <c r="AB235" s="4" t="s">
         <v>46</v>
       </c>
@@ -21481,16 +21463,16 @@
         <v>1000</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>872</v>
+        <v>308</v>
       </c>
       <c r="C236" s="4">
-        <v>161842332</v>
+        <v>161827057</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>238</v>
+        <v>34</v>
       </c>
       <c r="E236" s="4">
-        <v>7746340</v>
+        <v>8368972</v>
       </c>
       <c r="F236" s="4" t="s">
         <v>61</v>
@@ -21502,37 +21484,33 @@
         <v>223</v>
       </c>
       <c r="I236" s="4" t="s">
-        <v>223</v>
+        <v>309</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="K236" s="4"/>
       <c r="L236" s="4"/>
       <c r="M236" s="4"/>
       <c r="N236" s="4"/>
       <c r="O236" s="4" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="P236" s="5"/>
       <c r="Q236" s="4" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="R236" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="S236" s="4">
-        <v>0</v>
+        <v>570276.66</v>
       </c>
       <c r="T236" s="4">
-        <v>0</v>
-      </c>
-      <c r="U236" s="4" t="s">
-        <v>1143</v>
-      </c>
-      <c r="V236" s="4" t="s">
-        <v>364</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U236" s="4"/>
+      <c r="V236" s="4"/>
       <c r="W236" s="4">
         <v>4</v>
       </c>
@@ -21541,7 +21519,7 @@
       </c>
       <c r="Y236" s="4"/>
       <c r="Z236" s="4" t="s">
-        <v>1144</v>
+        <v>317</v>
       </c>
       <c r="AA236" s="4"/>
       <c r="AB236" s="4" t="s">
@@ -21553,16 +21531,16 @@
         <v>1000</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>308</v>
+        <v>33</v>
       </c>
       <c r="C237" s="4">
-        <v>161827057</v>
+        <v>162155831</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>34</v>
+        <v>287</v>
       </c>
       <c r="E237" s="4">
-        <v>8368972</v>
+        <v>7163768</v>
       </c>
       <c r="F237" s="4" t="s">
         <v>61</v>
@@ -21577,41 +21555,43 @@
         <v>309</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="K237" s="4"/>
       <c r="L237" s="4"/>
       <c r="M237" s="4"/>
       <c r="N237" s="4"/>
       <c r="O237" s="4" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="P237" s="5"/>
       <c r="Q237" s="4" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="R237" s="4" t="s">
         <v>52</v>
       </c>
       <c r="S237" s="4">
-        <v>570276.66</v>
+        <v>0</v>
       </c>
       <c r="T237" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U237" s="4"/>
       <c r="V237" s="4"/>
       <c r="W237" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X237" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y237" s="4"/>
       <c r="Z237" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="AA237" s="4"/>
+        <v>1146</v>
+      </c>
+      <c r="AA237" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB237" s="4" t="s">
         <v>46</v>
       </c>
@@ -21624,13 +21604,13 @@
         <v>33</v>
       </c>
       <c r="C238" s="4">
-        <v>162155831</v>
+        <v>162123948</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E238" s="4">
-        <v>7163768</v>
+        <v>7161032</v>
       </c>
       <c r="F238" s="4" t="s">
         <v>61</v>
@@ -21645,10 +21625,12 @@
         <v>309</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="K238" s="4"/>
-      <c r="L238" s="4"/>
+      <c r="L238" s="4" t="s">
+        <v>1147</v>
+      </c>
       <c r="M238" s="4"/>
       <c r="N238" s="4"/>
       <c r="O238" s="4" t="s">
@@ -21662,15 +21644,15 @@
         <v>52</v>
       </c>
       <c r="S238" s="4">
-        <v>0</v>
+        <v>38424.42</v>
       </c>
       <c r="T238" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U238" s="4"/>
       <c r="V238" s="4"/>
       <c r="W238" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X238" s="4" t="s">
         <v>44</v>
@@ -21691,16 +21673,16 @@
         <v>1000</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>33</v>
+        <v>872</v>
       </c>
       <c r="C239" s="4">
-        <v>162123948</v>
+        <v>161842353</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="E239" s="4">
-        <v>7161032</v>
+        <v>6816286</v>
       </c>
       <c r="F239" s="4" t="s">
         <v>61</v>
@@ -21712,14 +21694,14 @@
         <v>223</v>
       </c>
       <c r="I239" s="4" t="s">
-        <v>309</v>
+        <v>223</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="K239" s="4"/>
       <c r="L239" s="4" t="s">
-        <v>1151</v>
+        <v>271</v>
       </c>
       <c r="M239" s="4"/>
       <c r="N239" s="4"/>
@@ -21731,25 +21713,29 @@
         <v>1153</v>
       </c>
       <c r="R239" s="4" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="S239" s="4">
-        <v>38424.42</v>
+        <v>0</v>
       </c>
       <c r="T239" s="4">
-        <v>2</v>
-      </c>
-      <c r="U239" s="4"/>
-      <c r="V239" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U239" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="V239" s="4" t="s">
+        <v>1155</v>
+      </c>
       <c r="W239" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X239" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y239" s="4"/>
       <c r="Z239" s="4" t="s">
-        <v>1154</v>
+        <v>314</v>
       </c>
       <c r="AA239" s="4" t="s">
         <v>79</v>
@@ -21763,16 +21749,16 @@
         <v>1000</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>872</v>
+        <v>420</v>
       </c>
       <c r="C240" s="4">
-        <v>161842353</v>
+        <v>161842205</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E240" s="4">
-        <v>6816286</v>
+        <v>1012673</v>
       </c>
       <c r="F240" s="4" t="s">
         <v>61</v>
@@ -21787,23 +21773,27 @@
         <v>223</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="K240" s="4"/>
       <c r="L240" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="M240" s="4"/>
-      <c r="N240" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="M240" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="N240" s="4">
+        <v>10</v>
+      </c>
       <c r="O240" s="4" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="P240" s="5"/>
       <c r="Q240" s="4" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="R240" s="4" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="S240" s="4">
         <v>0</v>
@@ -21812,10 +21802,10 @@
         <v>0</v>
       </c>
       <c r="U240" s="4" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="V240" s="4" t="s">
-        <v>1159</v>
+        <v>498</v>
       </c>
       <c r="W240" s="4">
         <v>4</v>
@@ -21825,10 +21815,10 @@
       </c>
       <c r="Y240" s="4"/>
       <c r="Z240" s="4" t="s">
-        <v>314</v>
+        <v>1160</v>
       </c>
       <c r="AA240" s="4" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="AB240" s="4" t="s">
         <v>46</v>
@@ -21839,16 +21829,16 @@
         <v>1000</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>420</v>
+        <v>530</v>
       </c>
       <c r="C241" s="4">
-        <v>161842205</v>
+        <v>162083583</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E241" s="4">
-        <v>1012673</v>
+        <v>6309984</v>
       </c>
       <c r="F241" s="4" t="s">
         <v>61</v>
@@ -21863,27 +21853,27 @@
         <v>223</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="K241" s="4"/>
       <c r="L241" s="4" t="s">
-        <v>151</v>
+        <v>709</v>
       </c>
       <c r="M241" s="4" t="s">
-        <v>494</v>
+        <v>1162</v>
       </c>
       <c r="N241" s="4">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="O241" s="4" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="P241" s="5"/>
       <c r="Q241" s="4" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="R241" s="4" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="S241" s="4">
         <v>0</v>
@@ -21891,24 +21881,20 @@
       <c r="T241" s="4">
         <v>0</v>
       </c>
-      <c r="U241" s="4" t="s">
-        <v>1163</v>
-      </c>
-      <c r="V241" s="4" t="s">
-        <v>498</v>
-      </c>
+      <c r="U241" s="4"/>
+      <c r="V241" s="4"/>
       <c r="W241" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X241" s="4" t="s">
         <v>253</v>
       </c>
       <c r="Y241" s="4"/>
       <c r="Z241" s="4" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="AA241" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AB241" s="4" t="s">
         <v>46</v>
@@ -21919,16 +21905,16 @@
         <v>1000</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>530</v>
+        <v>33</v>
       </c>
       <c r="C242" s="4">
-        <v>162083583</v>
+        <v>161842213</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E242" s="4">
-        <v>6309984</v>
+        <v>8310303</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>61</v>
@@ -21943,24 +21929,24 @@
         <v>223</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="K242" s="4"/>
       <c r="L242" s="4" t="s">
-        <v>709</v>
+        <v>1166</v>
       </c>
       <c r="M242" s="4" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="N242" s="4">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="O242" s="4" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="P242" s="5"/>
       <c r="Q242" s="4" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="R242" s="4" t="s">
         <v>52</v>
@@ -21974,17 +21960,17 @@
       <c r="U242" s="4"/>
       <c r="V242" s="4"/>
       <c r="W242" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X242" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y242" s="4"/>
       <c r="Z242" s="4" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="AA242" s="4" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="AB242" s="4" t="s">
         <v>46</v>
@@ -21995,16 +21981,16 @@
         <v>1000</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>33</v>
+        <v>530</v>
       </c>
       <c r="C243" s="4">
-        <v>161842213</v>
+        <v>162083685</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E243" s="4">
-        <v>8310303</v>
+        <v>1334711</v>
       </c>
       <c r="F243" s="4" t="s">
         <v>61</v>
@@ -22019,27 +22005,25 @@
         <v>223</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="K243" s="4"/>
       <c r="L243" s="4" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="M243" s="4" t="s">
-        <v>1171</v>
-      </c>
-      <c r="N243" s="4">
-        <v>58</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="N243" s="4"/>
       <c r="O243" s="4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="P243" s="5"/>
       <c r="Q243" s="4" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="R243" s="4" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="S243" s="4">
         <v>0</v>
@@ -22047,20 +22031,24 @@
       <c r="T243" s="4">
         <v>0</v>
       </c>
-      <c r="U243" s="4"/>
-      <c r="V243" s="4"/>
+      <c r="U243" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="V243" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="W243" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X243" s="4" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="Y243" s="4"/>
       <c r="Z243" s="4" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="AA243" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="AB243" s="4" t="s">
         <v>46</v>
@@ -22071,16 +22059,16 @@
         <v>1000</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>530</v>
+        <v>706</v>
       </c>
       <c r="C244" s="4">
-        <v>162083685</v>
+        <v>162083675</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>238</v>
       </c>
       <c r="E244" s="4">
-        <v>1334711</v>
+        <v>6650968</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>61</v>
@@ -22095,25 +22083,23 @@
         <v>223</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="K244" s="4"/>
       <c r="L244" s="4" t="s">
-        <v>1176</v>
-      </c>
-      <c r="M244" s="4" t="s">
-        <v>716</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="M244" s="4"/>
       <c r="N244" s="4"/>
       <c r="O244" s="4" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="P244" s="5"/>
       <c r="Q244" s="4" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="R244" s="4" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="S244" s="4">
         <v>0</v>
@@ -22121,12 +22107,8 @@
       <c r="T244" s="4">
         <v>0</v>
       </c>
-      <c r="U244" s="4" t="s">
-        <v>1179</v>
-      </c>
-      <c r="V244" s="4" t="s">
-        <v>204</v>
-      </c>
+      <c r="U244" s="4"/>
+      <c r="V244" s="4"/>
       <c r="W244" s="4">
         <v>2</v>
       </c>
@@ -22149,16 +22131,16 @@
         <v>1000</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>706</v>
+        <v>281</v>
       </c>
       <c r="C245" s="4">
-        <v>162083675</v>
+        <v>162136490</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="E245" s="4">
-        <v>6650968</v>
+        <v>7199089</v>
       </c>
       <c r="F245" s="4" t="s">
         <v>61</v>
@@ -22177,41 +22159,43 @@
       </c>
       <c r="K245" s="4"/>
       <c r="L245" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="M245" s="4"/>
-      <c r="N245" s="4"/>
+        <v>1182</v>
+      </c>
+      <c r="M245" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="N245" s="4">
+        <v>12</v>
+      </c>
       <c r="O245" s="4" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="P245" s="5"/>
       <c r="Q245" s="4" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="R245" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="S245" s="4">
-        <v>0</v>
+        <v>41321.18</v>
       </c>
       <c r="T245" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U245" s="4"/>
       <c r="V245" s="4"/>
       <c r="W245" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X245" s="4" t="s">
         <v>253</v>
       </c>
       <c r="Y245" s="4"/>
       <c r="Z245" s="4" t="s">
-        <v>1184</v>
-      </c>
-      <c r="AA245" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>1186</v>
+      </c>
+      <c r="AA245" s="4"/>
       <c r="AB245" s="4" t="s">
         <v>46</v>
       </c>
@@ -22221,42 +22205,36 @@
         <v>1000</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="C246" s="4">
-        <v>162136490</v>
+        <v>162072743</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>282</v>
+        <v>72</v>
       </c>
       <c r="E246" s="4">
-        <v>7199089</v>
+        <v>3817523</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>223</v>
+        <v>1187</v>
       </c>
       <c r="I246" s="4" t="s">
-        <v>223</v>
+        <v>1187</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>1185</v>
+        <v>493</v>
       </c>
       <c r="K246" s="4"/>
-      <c r="L246" s="4" t="s">
-        <v>1186</v>
-      </c>
-      <c r="M246" s="4" t="s">
-        <v>1187</v>
-      </c>
-      <c r="N246" s="4">
-        <v>12</v>
-      </c>
+      <c r="L246" s="4"/>
+      <c r="M246" s="4"/>
+      <c r="N246" s="4"/>
       <c r="O246" s="4" t="s">
         <v>1188</v>
       </c>
@@ -22268,22 +22246,26 @@
         <v>52</v>
       </c>
       <c r="S246" s="4">
-        <v>41321.18</v>
+        <v>0</v>
       </c>
       <c r="T246" s="4">
+        <v>0</v>
+      </c>
+      <c r="U246" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="V246" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="W246" s="4">
         <v>2</v>
-      </c>
-      <c r="U246" s="4"/>
-      <c r="V246" s="4"/>
-      <c r="W246" s="4">
-        <v>1</v>
       </c>
       <c r="X246" s="4" t="s">
         <v>253</v>
       </c>
       <c r="Y246" s="4"/>
       <c r="Z246" s="4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="AA246" s="4"/>
       <c r="AB246" s="4" t="s">
@@ -22295,42 +22277,42 @@
         <v>1000</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>245</v>
+        <v>33</v>
       </c>
       <c r="C247" s="4">
-        <v>162072743</v>
+        <v>162077094</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>72</v>
       </c>
       <c r="E247" s="4">
-        <v>3817523</v>
+        <v>6204375</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H247" s="4" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="I247" s="4" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>493</v>
+        <v>1194</v>
       </c>
       <c r="K247" s="4"/>
       <c r="L247" s="4"/>
       <c r="M247" s="4"/>
       <c r="N247" s="4"/>
       <c r="O247" s="4" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="P247" s="5"/>
       <c r="Q247" s="4" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="R247" s="4" t="s">
         <v>52</v>
@@ -22342,95 +22324,23 @@
         <v>0</v>
       </c>
       <c r="U247" s="4" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="V247" s="4" t="s">
-        <v>160</v>
+        <v>293</v>
       </c>
       <c r="W247" s="4">
         <v>2</v>
       </c>
       <c r="X247" s="4" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="Y247" s="4"/>
       <c r="Z247" s="4" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="AA247" s="4"/>
       <c r="AB247" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="248" spans="1:28">
-      <c r="A248" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B248" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C248" s="4">
-        <v>162077094</v>
-      </c>
-      <c r="D248" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E248" s="4">
-        <v>6204375</v>
-      </c>
-      <c r="F248" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G248" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H248" s="4" t="s">
-        <v>1196</v>
-      </c>
-      <c r="I248" s="4" t="s">
-        <v>1197</v>
-      </c>
-      <c r="J248" s="4" t="s">
-        <v>1198</v>
-      </c>
-      <c r="K248" s="4"/>
-      <c r="L248" s="4"/>
-      <c r="M248" s="4"/>
-      <c r="N248" s="4"/>
-      <c r="O248" s="4" t="s">
-        <v>1199</v>
-      </c>
-      <c r="P248" s="5"/>
-      <c r="Q248" s="4" t="s">
-        <v>1200</v>
-      </c>
-      <c r="R248" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="S248" s="4">
-        <v>0</v>
-      </c>
-      <c r="T248" s="4">
-        <v>0</v>
-      </c>
-      <c r="U248" s="4" t="s">
-        <v>1201</v>
-      </c>
-      <c r="V248" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="W248" s="4">
-        <v>2</v>
-      </c>
-      <c r="X248" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y248" s="4"/>
-      <c r="Z248" s="4" t="s">
-        <v>1202</v>
-      </c>
-      <c r="AA248" s="4"/>
-      <c r="AB248" s="4" t="s">
         <v>46</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>28/07/2026 a las 08:01:42</t>
+    <t>28/07/2026 a las 08:02:48</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1512">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>28/07/2026 a las 10:01:12</t>
+    <t>28/07/2026 a las 10:02:16</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -3104,21 +3104,6 @@
     <t>RIASCOS</t>
   </si>
   <si>
-    <t>CR 18A</t>
-  </si>
-  <si>
-    <t>CL 11C CR 18A - 26 DPL AT8717</t>
-  </si>
-  <si>
-    <t>LIAN AROCA  CARMEN EDITH</t>
-  </si>
-  <si>
-    <t>259935-MC989</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION DE BORNERA. Senor a jorge ivan ujueta linan CC 1081911491 NIC 1041485  Dir.CL 11C CR 18A - 26 DPL AT8717, SANTA MARTA, MAGDALENA, COLOMBIA Tel.3015943075 validar estado del predio medidor y lectura</t>
-  </si>
-  <si>
     <t>CR 17</t>
   </si>
   <si>
@@ -3192,9 +3177,6 @@
   </si>
   <si>
     <t>19213671-MCA59</t>
-  </si>
-  <si>
-    <t>En Asignacion</t>
   </si>
   <si>
     <t>Investigar Dano medidor yo acometida Reportar incidencia en viviendA OSF  ALVARO SUARES   TEL3125595471 reporta predio sin energa punt</t>
@@ -4962,7 +4944,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB330"/>
+  <dimension ref="A1:AB329"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -20154,16 +20136,16 @@
         <v>1000</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>267</v>
+        <v>356</v>
       </c>
       <c r="C203" s="4">
-        <v>162674296</v>
+        <v>162817595</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="E203" s="4">
-        <v>1041485</v>
+        <v>1041482</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>48</v>
@@ -20182,14 +20164,12 @@
       </c>
       <c r="K203" s="4"/>
       <c r="L203" s="4" t="s">
-        <v>785</v>
+        <v>1029</v>
       </c>
       <c r="M203" s="4" t="s">
-        <v>1029</v>
-      </c>
-      <c r="N203" s="4">
-        <v>26</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="N203" s="4"/>
       <c r="O203" s="4" t="s">
         <v>1030</v>
       </c>
@@ -20201,29 +20181,25 @@
         <v>157</v>
       </c>
       <c r="S203" s="4">
-        <v>275149.7</v>
+        <v>0</v>
       </c>
       <c r="T203" s="4">
-        <v>1</v>
-      </c>
-      <c r="U203" s="4" t="s">
-        <v>1032</v>
-      </c>
-      <c r="V203" s="4" t="s">
-        <v>144</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U203" s="4"/>
+      <c r="V203" s="4"/>
       <c r="W203" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X203" s="4" t="s">
-        <v>483</v>
+        <v>121</v>
       </c>
       <c r="Y203" s="4"/>
       <c r="Z203" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AA203" s="4" t="s">
         <v>1033</v>
-      </c>
-      <c r="AA203" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="AB203" s="4" t="s">
         <v>46</v>
@@ -20234,16 +20210,16 @@
         <v>1000</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>356</v>
+        <v>686</v>
       </c>
       <c r="C204" s="4">
-        <v>162817595</v>
+        <v>162832695</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E204" s="4">
-        <v>1041482</v>
+        <v>1096065</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>48</v>
@@ -20258,14 +20234,14 @@
         <v>108</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="K204" s="4"/>
       <c r="L204" s="4" t="s">
-        <v>1034</v>
+        <v>677</v>
       </c>
       <c r="M204" s="4" t="s">
-        <v>776</v>
+        <v>841</v>
       </c>
       <c r="N204" s="4"/>
       <c r="O204" s="4" t="s">
@@ -20276,18 +20252,18 @@
         <v>1036</v>
       </c>
       <c r="R204" s="4" t="s">
-        <v>157</v>
+        <v>597</v>
       </c>
       <c r="S204" s="4">
-        <v>0</v>
+        <v>29667650.22</v>
       </c>
       <c r="T204" s="4">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="U204" s="4"/>
       <c r="V204" s="4"/>
       <c r="W204" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X204" s="4" t="s">
         <v>121</v>
@@ -20297,7 +20273,7 @@
         <v>1037</v>
       </c>
       <c r="AA204" s="4" t="s">
-        <v>1038</v>
+        <v>66</v>
       </c>
       <c r="AB204" s="4" t="s">
         <v>46</v>
@@ -20308,16 +20284,16 @@
         <v>1000</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>686</v>
+        <v>33</v>
       </c>
       <c r="C205" s="4">
-        <v>162832695</v>
+        <v>162848046</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E205" s="4">
-        <v>1096065</v>
+        <v>1061157</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>48</v>
@@ -20332,46 +20308,50 @@
         <v>108</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="K205" s="4"/>
       <c r="L205" s="4" t="s">
-        <v>677</v>
+        <v>554</v>
       </c>
       <c r="M205" s="4" t="s">
-        <v>841</v>
+        <v>254</v>
       </c>
       <c r="N205" s="4"/>
       <c r="O205" s="4" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="P205" s="5"/>
       <c r="Q205" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="R205" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="S205" s="4">
+        <v>0</v>
+      </c>
+      <c r="T205" s="4">
+        <v>0</v>
+      </c>
+      <c r="U205" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="V205" s="4" t="s">
         <v>1041</v>
       </c>
-      <c r="R205" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="S205" s="4">
-        <v>29667650.22</v>
-      </c>
-      <c r="T205" s="4">
-        <v>67</v>
-      </c>
-      <c r="U205" s="4"/>
-      <c r="V205" s="4"/>
       <c r="W205" s="4">
         <v>1</v>
       </c>
       <c r="X205" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y205" s="4"/>
       <c r="Z205" s="4" t="s">
         <v>1042</v>
       </c>
       <c r="AA205" s="4" t="s">
-        <v>66</v>
+        <v>210</v>
       </c>
       <c r="AB205" s="4" t="s">
         <v>46</v>
@@ -20382,16 +20362,16 @@
         <v>1000</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>33</v>
+        <v>681</v>
       </c>
       <c r="C206" s="4">
-        <v>162848046</v>
+        <v>162739277</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E206" s="4">
-        <v>1061157</v>
+        <v>1063262</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>48</v>
@@ -20406,14 +20386,14 @@
         <v>108</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="K206" s="4"/>
       <c r="L206" s="4" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="M206" s="4" t="s">
-        <v>254</v>
+        <v>540</v>
       </c>
       <c r="N206" s="4"/>
       <c r="O206" s="4" t="s">
@@ -20427,26 +20407,26 @@
         <v>272</v>
       </c>
       <c r="S206" s="4">
-        <v>0</v>
+        <v>127680.7</v>
       </c>
       <c r="T206" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U206" s="4" t="s">
         <v>1045</v>
       </c>
       <c r="V206" s="4" t="s">
-        <v>1046</v>
+        <v>294</v>
       </c>
       <c r="W206" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X206" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y206" s="4"/>
       <c r="Z206" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="AA206" s="4" t="s">
         <v>210</v>
@@ -20460,16 +20440,16 @@
         <v>1000</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>681</v>
+        <v>33</v>
       </c>
       <c r="C207" s="4">
-        <v>162739277</v>
+        <v>162849333</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="E207" s="4">
-        <v>1063262</v>
+        <v>8331144</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>48</v>
@@ -20484,15 +20464,11 @@
         <v>108</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="K207" s="4"/>
-      <c r="L207" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="M207" s="4" t="s">
-        <v>540</v>
-      </c>
+      <c r="L207" s="4"/>
+      <c r="M207" s="4"/>
       <c r="N207" s="4"/>
       <c r="O207" s="4" t="s">
         <v>1048</v>
@@ -20502,29 +20478,25 @@
         <v>1049</v>
       </c>
       <c r="R207" s="4" t="s">
-        <v>272</v>
+        <v>597</v>
       </c>
       <c r="S207" s="4">
-        <v>127680.7</v>
+        <v>0</v>
       </c>
       <c r="T207" s="4">
+        <v>0</v>
+      </c>
+      <c r="U207" s="4"/>
+      <c r="V207" s="4"/>
+      <c r="W207" s="4">
         <v>1</v>
       </c>
-      <c r="U207" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="V207" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="W207" s="4">
-        <v>3</v>
-      </c>
       <c r="X207" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y207" s="4"/>
       <c r="Z207" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="AA207" s="4" t="s">
         <v>210</v>
@@ -20538,16 +20510,16 @@
         <v>1000</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c r="C208" s="4">
-        <v>162849333</v>
+        <v>162864460</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E208" s="4">
-        <v>8331144</v>
+        <v>5905922</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>48</v>
@@ -20562,21 +20534,27 @@
         <v>108</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="K208" s="4"/>
-      <c r="L208" s="4"/>
-      <c r="M208" s="4"/>
-      <c r="N208" s="4"/>
+      <c r="L208" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="M208" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="N208" s="4">
+        <v>10</v>
+      </c>
       <c r="O208" s="4" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="P208" s="5"/>
       <c r="Q208" s="4" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="R208" s="4" t="s">
-        <v>597</v>
+        <v>200</v>
       </c>
       <c r="S208" s="4">
         <v>0</v>
@@ -20584,21 +20562,23 @@
       <c r="T208" s="4">
         <v>0</v>
       </c>
-      <c r="U208" s="4"/>
-      <c r="V208" s="4"/>
+      <c r="U208" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="V208" s="4" t="s">
+        <v>743</v>
+      </c>
       <c r="W208" s="4">
         <v>1</v>
       </c>
       <c r="X208" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y208" s="4"/>
       <c r="Z208" s="4" t="s">
-        <v>1055</v>
-      </c>
-      <c r="AA208" s="4" t="s">
-        <v>210</v>
-      </c>
+        <v>1054</v>
+      </c>
+      <c r="AA208" s="4"/>
       <c r="AB208" s="4" t="s">
         <v>46</v>
       </c>
@@ -20608,16 +20588,16 @@
         <v>1000</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>356</v>
+        <v>1055</v>
       </c>
       <c r="C209" s="4">
-        <v>162864460</v>
+        <v>162690430</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="E209" s="4">
-        <v>5905922</v>
+        <v>1043459</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>48</v>
@@ -20632,51 +20612,53 @@
         <v>108</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="K209" s="4"/>
       <c r="L209" s="4" t="s">
-        <v>548</v>
+        <v>1057</v>
       </c>
       <c r="M209" s="4" t="s">
-        <v>553</v>
+        <v>40</v>
       </c>
       <c r="N209" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O209" s="4" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="P209" s="5"/>
       <c r="Q209" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="R209" s="4" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="S209" s="4">
-        <v>0</v>
+        <v>2720235.58</v>
       </c>
       <c r="T209" s="4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U209" s="4" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="V209" s="4" t="s">
-        <v>743</v>
+        <v>137</v>
       </c>
       <c r="W209" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X209" s="4" t="s">
-        <v>1059</v>
+        <v>121</v>
       </c>
       <c r="Y209" s="4"/>
       <c r="Z209" s="4" t="s">
-        <v>1060</v>
-      </c>
-      <c r="AA209" s="4"/>
+        <v>1061</v>
+      </c>
+      <c r="AA209" s="4" t="s">
+        <v>247</v>
+      </c>
       <c r="AB209" s="4" t="s">
         <v>46</v>
       </c>
@@ -20686,16 +20668,16 @@
         <v>1000</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="C210" s="4">
-        <v>162690430</v>
+        <v>162690361</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E210" s="4">
-        <v>1043459</v>
+        <v>1042021</v>
       </c>
       <c r="F210" s="4" t="s">
         <v>48</v>
@@ -20714,35 +20696,33 @@
       </c>
       <c r="K210" s="4"/>
       <c r="L210" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="M210" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="N210" s="4"/>
+      <c r="O210" s="4" t="s">
         <v>1063</v>
-      </c>
-      <c r="M210" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N210" s="4">
-        <v>20</v>
-      </c>
-      <c r="O210" s="4" t="s">
-        <v>1064</v>
       </c>
       <c r="P210" s="5"/>
       <c r="Q210" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="R210" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S210" s="4">
+        <v>272704.5</v>
+      </c>
+      <c r="T210" s="4">
+        <v>2</v>
+      </c>
+      <c r="U210" s="4" t="s">
         <v>1065</v>
       </c>
-      <c r="R210" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="S210" s="4">
-        <v>2720235.58</v>
-      </c>
-      <c r="T210" s="4">
-        <v>32</v>
-      </c>
-      <c r="U210" s="4" t="s">
+      <c r="V210" s="4" t="s">
         <v>1066</v>
-      </c>
-      <c r="V210" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="W210" s="4">
         <v>4</v>
@@ -20752,10 +20732,10 @@
       </c>
       <c r="Y210" s="4"/>
       <c r="Z210" s="4" t="s">
-        <v>1067</v>
+        <v>203</v>
       </c>
       <c r="AA210" s="4" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="AB210" s="4" t="s">
         <v>46</v>
@@ -20766,16 +20746,16 @@
         <v>1000</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>1061</v>
+        <v>749</v>
       </c>
       <c r="C211" s="4">
-        <v>162690361</v>
+        <v>162583511</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E211" s="4">
-        <v>1042021</v>
+        <v>1049744</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>48</v>
@@ -20790,51 +20770,51 @@
         <v>108</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="K211" s="4"/>
       <c r="L211" s="4" t="s">
-        <v>766</v>
+        <v>1068</v>
       </c>
       <c r="M211" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="N211" s="4"/>
+        <v>1069</v>
+      </c>
+      <c r="N211" s="4">
+        <v>34</v>
+      </c>
       <c r="O211" s="4" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="P211" s="5"/>
       <c r="Q211" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="R211" s="4" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="S211" s="4">
-        <v>272704.5</v>
+        <v>0</v>
       </c>
       <c r="T211" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U211" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="V211" s="4" t="s">
-        <v>1072</v>
+        <v>195</v>
       </c>
       <c r="W211" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X211" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y211" s="4"/>
       <c r="Z211" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA211" s="4" t="s">
-        <v>190</v>
-      </c>
+        <v>1073</v>
+      </c>
+      <c r="AA211" s="4"/>
       <c r="AB211" s="4" t="s">
         <v>46</v>
       </c>
@@ -20847,13 +20827,13 @@
         <v>749</v>
       </c>
       <c r="C212" s="4">
-        <v>162583511</v>
+        <v>162583482</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E212" s="4">
-        <v>1049744</v>
+        <v>6529155</v>
       </c>
       <c r="F212" s="4" t="s">
         <v>48</v>
@@ -20868,27 +20848,27 @@
         <v>108</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="K212" s="4"/>
       <c r="L212" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="M212" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="N212" s="4">
+        <v>8</v>
+      </c>
+      <c r="O212" s="4" t="s">
         <v>1074</v>
-      </c>
-      <c r="M212" s="4" t="s">
-        <v>1075</v>
-      </c>
-      <c r="N212" s="4">
-        <v>34</v>
-      </c>
-      <c r="O212" s="4" t="s">
-        <v>1076</v>
       </c>
       <c r="P212" s="5"/>
       <c r="Q212" s="4" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="R212" s="4" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="S212" s="4">
         <v>0</v>
@@ -20896,12 +20876,8 @@
       <c r="T212" s="4">
         <v>0</v>
       </c>
-      <c r="U212" s="4" t="s">
-        <v>1078</v>
-      </c>
-      <c r="V212" s="4" t="s">
-        <v>195</v>
-      </c>
+      <c r="U212" s="4"/>
+      <c r="V212" s="4"/>
       <c r="W212" s="4">
         <v>5</v>
       </c>
@@ -20910,9 +20886,11 @@
       </c>
       <c r="Y212" s="4"/>
       <c r="Z212" s="4" t="s">
-        <v>1079</v>
-      </c>
-      <c r="AA212" s="4"/>
+        <v>1076</v>
+      </c>
+      <c r="AA212" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="AB212" s="4" t="s">
         <v>46</v>
       </c>
@@ -20925,13 +20903,13 @@
         <v>749</v>
       </c>
       <c r="C213" s="4">
-        <v>162583482</v>
+        <v>162583481</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E213" s="4">
-        <v>6529155</v>
+        <v>1049869</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>48</v>
@@ -20946,36 +20924,40 @@
         <v>108</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="K213" s="4"/>
       <c r="L213" s="4" t="s">
         <v>253</v>
       </c>
       <c r="M213" s="4" t="s">
-        <v>213</v>
+        <v>1077</v>
       </c>
       <c r="N213" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O213" s="4" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="P213" s="5"/>
       <c r="Q213" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="R213" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="S213" s="4">
+        <v>0</v>
+      </c>
+      <c r="T213" s="4">
+        <v>0</v>
+      </c>
+      <c r="U213" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="V213" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="R213" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="S213" s="4">
-        <v>0</v>
-      </c>
-      <c r="T213" s="4">
-        <v>0</v>
-      </c>
-      <c r="U213" s="4"/>
-      <c r="V213" s="4"/>
       <c r="W213" s="4">
         <v>5</v>
       </c>
@@ -20998,16 +20980,16 @@
         <v>1000</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>749</v>
+        <v>676</v>
       </c>
       <c r="C214" s="4">
-        <v>162583481</v>
+        <v>162831926</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E214" s="4">
-        <v>1049869</v>
+        <v>4322338</v>
       </c>
       <c r="F214" s="4" t="s">
         <v>48</v>
@@ -21022,18 +21004,14 @@
         <v>108</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
       <c r="K214" s="4"/>
       <c r="L214" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="M214" s="4" t="s">
-        <v>1083</v>
-      </c>
-      <c r="N214" s="4">
-        <v>3</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="M214" s="4"/>
+      <c r="N214" s="4"/>
       <c r="O214" s="4" t="s">
         <v>1084</v>
       </c>
@@ -21042,7 +21020,7 @@
         <v>1085</v>
       </c>
       <c r="R214" s="4" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="S214" s="4">
         <v>0</v>
@@ -21054,17 +21032,17 @@
         <v>1086</v>
       </c>
       <c r="V214" s="4" t="s">
-        <v>1087</v>
+        <v>387</v>
       </c>
       <c r="W214" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X214" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y214" s="4"/>
       <c r="Z214" s="4" t="s">
-        <v>1088</v>
+        <v>443</v>
       </c>
       <c r="AA214" s="4" t="s">
         <v>74</v>
@@ -21081,13 +21059,13 @@
         <v>676</v>
       </c>
       <c r="C215" s="4">
-        <v>162831926</v>
+        <v>162831946</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E215" s="4">
-        <v>4322338</v>
+        <v>6693017</v>
       </c>
       <c r="F215" s="4" t="s">
         <v>48</v>
@@ -21102,7 +21080,7 @@
         <v>108</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K215" s="4"/>
       <c r="L215" s="4" t="s">
@@ -21111,14 +21089,14 @@
       <c r="M215" s="4"/>
       <c r="N215" s="4"/>
       <c r="O215" s="4" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="P215" s="5"/>
       <c r="Q215" s="4" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="R215" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S215" s="4">
         <v>0</v>
@@ -21127,10 +21105,10 @@
         <v>0</v>
       </c>
       <c r="U215" s="4" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="V215" s="4" t="s">
-        <v>387</v>
+        <v>1090</v>
       </c>
       <c r="W215" s="4">
         <v>1</v>
@@ -21140,10 +21118,10 @@
       </c>
       <c r="Y215" s="4"/>
       <c r="Z215" s="4" t="s">
-        <v>443</v>
+        <v>243</v>
       </c>
       <c r="AA215" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB215" s="4" t="s">
         <v>46</v>
@@ -21157,13 +21135,13 @@
         <v>676</v>
       </c>
       <c r="C216" s="4">
-        <v>162831946</v>
+        <v>162831948</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E216" s="4">
-        <v>6693017</v>
+        <v>6634776</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>48</v>
@@ -21178,7 +21156,7 @@
         <v>108</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K216" s="4"/>
       <c r="L216" s="4" t="s">
@@ -21187,11 +21165,11 @@
       <c r="M216" s="4"/>
       <c r="N216" s="4"/>
       <c r="O216" s="4" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="P216" s="5"/>
       <c r="Q216" s="4" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="R216" s="4" t="s">
         <v>70</v>
@@ -21203,10 +21181,10 @@
         <v>0</v>
       </c>
       <c r="U216" s="4" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="V216" s="4" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="W216" s="4">
         <v>1</v>
@@ -21216,10 +21194,10 @@
       </c>
       <c r="Y216" s="4"/>
       <c r="Z216" s="4" t="s">
-        <v>243</v>
+        <v>405</v>
       </c>
       <c r="AA216" s="4" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="AB216" s="4" t="s">
         <v>46</v>
@@ -21230,16 +21208,16 @@
         <v>1000</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>676</v>
+        <v>1095</v>
       </c>
       <c r="C217" s="4">
-        <v>162831948</v>
+        <v>162831924</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E217" s="4">
-        <v>6634776</v>
+        <v>7667838</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>48</v>
@@ -21254,20 +21232,24 @@
         <v>108</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K217" s="4"/>
       <c r="L217" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M217" s="4"/>
-      <c r="N217" s="4"/>
+        <v>1096</v>
+      </c>
+      <c r="M217" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="N217" s="4">
+        <v>6</v>
+      </c>
       <c r="O217" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="P217" s="5"/>
       <c r="Q217" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="R217" s="4" t="s">
         <v>70</v>
@@ -21278,12 +21260,8 @@
       <c r="T217" s="4">
         <v>0</v>
       </c>
-      <c r="U217" s="4" t="s">
-        <v>1099</v>
-      </c>
-      <c r="V217" s="4" t="s">
-        <v>1100</v>
-      </c>
+      <c r="U217" s="4"/>
+      <c r="V217" s="4"/>
       <c r="W217" s="4">
         <v>1</v>
       </c>
@@ -21292,10 +21270,10 @@
       </c>
       <c r="Y217" s="4"/>
       <c r="Z217" s="4" t="s">
-        <v>405</v>
+        <v>1100</v>
       </c>
       <c r="AA217" s="4" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB217" s="4" t="s">
         <v>46</v>
@@ -21306,16 +21284,16 @@
         <v>1000</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>1101</v>
+        <v>686</v>
       </c>
       <c r="C218" s="4">
-        <v>162831924</v>
+        <v>162831943</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E218" s="4">
-        <v>7667838</v>
+        <v>6931040</v>
       </c>
       <c r="F218" s="4" t="s">
         <v>48</v>
@@ -21330,24 +21308,24 @@
         <v>108</v>
       </c>
       <c r="J218" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K218" s="4"/>
       <c r="L218" s="4" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="M218" s="4" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="N218" s="4">
         <v>6</v>
       </c>
       <c r="O218" s="4" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="P218" s="5"/>
       <c r="Q218" s="4" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="R218" s="4" t="s">
         <v>70</v>
@@ -21368,11 +21346,9 @@
       </c>
       <c r="Y218" s="4"/>
       <c r="Z218" s="4" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AA218" s="4" t="s">
-        <v>210</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA218" s="4"/>
       <c r="AB218" s="4" t="s">
         <v>46</v>
       </c>
@@ -21382,16 +21358,16 @@
         <v>1000</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>686</v>
+        <v>729</v>
       </c>
       <c r="C219" s="4">
-        <v>162831943</v>
+        <v>162831945</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E219" s="4">
-        <v>6931040</v>
+        <v>7528212</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>48</v>
@@ -21406,7 +21382,7 @@
         <v>108</v>
       </c>
       <c r="J219" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K219" s="4"/>
       <c r="L219" s="4" t="s">
@@ -21416,10 +21392,10 @@
         <v>1103</v>
       </c>
       <c r="N219" s="4">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="O219" s="4" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="P219" s="5"/>
       <c r="Q219" s="4" t="s">
@@ -21434,8 +21410,12 @@
       <c r="T219" s="4">
         <v>0</v>
       </c>
-      <c r="U219" s="4"/>
-      <c r="V219" s="4"/>
+      <c r="U219" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="V219" s="4" t="s">
+        <v>224</v>
+      </c>
       <c r="W219" s="4">
         <v>1</v>
       </c>
@@ -21456,16 +21436,16 @@
         <v>1000</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>729</v>
+        <v>1107</v>
       </c>
       <c r="C220" s="4">
-        <v>162831945</v>
+        <v>162831931</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E220" s="4">
-        <v>7528212</v>
+        <v>5863339</v>
       </c>
       <c r="F220" s="4" t="s">
         <v>48</v>
@@ -21480,27 +21460,27 @@
         <v>108</v>
       </c>
       <c r="J220" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K220" s="4"/>
       <c r="L220" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="M220" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="N220" s="4">
+        <v>23</v>
+      </c>
+      <c r="O220" s="4" t="s">
         <v>1108</v>
-      </c>
-      <c r="M220" s="4" t="s">
-        <v>1109</v>
-      </c>
-      <c r="N220" s="4">
-        <v>29</v>
-      </c>
-      <c r="O220" s="4" t="s">
-        <v>1110</v>
       </c>
       <c r="P220" s="5"/>
       <c r="Q220" s="4" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="R220" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S220" s="4">
         <v>0</v>
@@ -21509,10 +21489,10 @@
         <v>0</v>
       </c>
       <c r="U220" s="4" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="V220" s="4" t="s">
-        <v>224</v>
+        <v>294</v>
       </c>
       <c r="W220" s="4">
         <v>1</v>
@@ -21522,9 +21502,11 @@
       </c>
       <c r="Y220" s="4"/>
       <c r="Z220" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA220" s="4"/>
+        <v>243</v>
+      </c>
+      <c r="AA220" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB220" s="4" t="s">
         <v>46</v>
       </c>
@@ -21534,16 +21516,16 @@
         <v>1000</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>1113</v>
+        <v>1095</v>
       </c>
       <c r="C221" s="4">
-        <v>162831931</v>
+        <v>162831928</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E221" s="4">
-        <v>5863339</v>
+        <v>4324535</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>48</v>
@@ -21558,27 +21540,27 @@
         <v>108</v>
       </c>
       <c r="J221" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K221" s="4"/>
       <c r="L221" s="4" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="M221" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N221" s="4">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="O221" s="4" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="P221" s="5"/>
       <c r="Q221" s="4" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="R221" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S221" s="4">
         <v>0</v>
@@ -21587,10 +21569,10 @@
         <v>0</v>
       </c>
       <c r="U221" s="4" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="V221" s="4" t="s">
-        <v>294</v>
+        <v>1114</v>
       </c>
       <c r="W221" s="4">
         <v>1</v>
@@ -21614,16 +21596,16 @@
         <v>1000</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="C222" s="4">
-        <v>162831928</v>
+        <v>162831930</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E222" s="4">
-        <v>4324535</v>
+        <v>5862497</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>48</v>
@@ -21638,24 +21620,24 @@
         <v>108</v>
       </c>
       <c r="J222" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K222" s="4"/>
       <c r="L222" s="4" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="M222" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N222" s="4">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O222" s="4" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="P222" s="5"/>
       <c r="Q222" s="4" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="R222" s="4" t="s">
         <v>70</v>
@@ -21666,12 +21648,8 @@
       <c r="T222" s="4">
         <v>0</v>
       </c>
-      <c r="U222" s="4" t="s">
-        <v>1119</v>
-      </c>
-      <c r="V222" s="4" t="s">
-        <v>1120</v>
-      </c>
+      <c r="U222" s="4"/>
+      <c r="V222" s="4"/>
       <c r="W222" s="4">
         <v>1</v>
       </c>
@@ -21694,16 +21672,16 @@
         <v>1000</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="C223" s="4">
-        <v>162831930</v>
+        <v>162831936</v>
       </c>
       <c r="D223" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E223" s="4">
-        <v>5862497</v>
+        <v>6596159</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>48</v>
@@ -21718,24 +21696,24 @@
         <v>108</v>
       </c>
       <c r="J223" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K223" s="4"/>
       <c r="L223" s="4" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="M223" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N223" s="4">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="O223" s="4" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="P223" s="5"/>
       <c r="Q223" s="4" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="R223" s="4" t="s">
         <v>70</v>
@@ -21746,8 +21724,12 @@
       <c r="T223" s="4">
         <v>0</v>
       </c>
-      <c r="U223" s="4"/>
-      <c r="V223" s="4"/>
+      <c r="U223" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="V223" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="W223" s="4">
         <v>1</v>
       </c>
@@ -21756,11 +21738,9 @@
       </c>
       <c r="Y223" s="4"/>
       <c r="Z223" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA223" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA223" s="4"/>
       <c r="AB223" s="4" t="s">
         <v>46</v>
       </c>
@@ -21770,16 +21750,16 @@
         <v>1000</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>1123</v>
+        <v>729</v>
       </c>
       <c r="C224" s="4">
-        <v>162831936</v>
+        <v>162831944</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E224" s="4">
-        <v>6596159</v>
+        <v>6931805</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>48</v>
@@ -21794,24 +21774,24 @@
         <v>108</v>
       </c>
       <c r="J224" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K224" s="4"/>
       <c r="L224" s="4" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="M224" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N224" s="4">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="O224" s="4" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="P224" s="5"/>
       <c r="Q224" s="4" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="R224" s="4" t="s">
         <v>70</v>
@@ -21823,10 +21803,10 @@
         <v>0</v>
       </c>
       <c r="U224" s="4" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="V224" s="4" t="s">
-        <v>202</v>
+        <v>129</v>
       </c>
       <c r="W224" s="4">
         <v>1</v>
@@ -21836,9 +21816,11 @@
       </c>
       <c r="Y224" s="4"/>
       <c r="Z224" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA224" s="4"/>
+        <v>243</v>
+      </c>
+      <c r="AA224" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB224" s="4" t="s">
         <v>46</v>
       </c>
@@ -21848,16 +21830,16 @@
         <v>1000</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>729</v>
+        <v>686</v>
       </c>
       <c r="C225" s="4">
-        <v>162831944</v>
+        <v>162831939</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E225" s="4">
-        <v>6931805</v>
+        <v>6838437</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>48</v>
@@ -21872,27 +21854,27 @@
         <v>108</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K225" s="4"/>
       <c r="L225" s="4" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
       <c r="M225" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N225" s="4">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="O225" s="4" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="P225" s="5"/>
       <c r="Q225" s="4" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="R225" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S225" s="4">
         <v>0</v>
@@ -21901,10 +21883,10 @@
         <v>0</v>
       </c>
       <c r="U225" s="4" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="V225" s="4" t="s">
-        <v>129</v>
+        <v>1127</v>
       </c>
       <c r="W225" s="4">
         <v>1</v>
@@ -21931,13 +21913,13 @@
         <v>686</v>
       </c>
       <c r="C226" s="4">
-        <v>162831939</v>
+        <v>162831940</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E226" s="4">
-        <v>6838437</v>
+        <v>6864706</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>48</v>
@@ -21952,24 +21934,24 @@
         <v>108</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K226" s="4"/>
       <c r="L226" s="4" t="s">
         <v>1103</v>
       </c>
       <c r="M226" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N226" s="4">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="O226" s="4" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="P226" s="5"/>
       <c r="Q226" s="4" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="R226" s="4" t="s">
         <v>55</v>
@@ -21981,10 +21963,10 @@
         <v>0</v>
       </c>
       <c r="U226" s="4" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="V226" s="4" t="s">
-        <v>1133</v>
+        <v>640</v>
       </c>
       <c r="W226" s="4">
         <v>1</v>
@@ -21994,11 +21976,9 @@
       </c>
       <c r="Y226" s="4"/>
       <c r="Z226" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA226" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA226" s="4"/>
       <c r="AB226" s="4" t="s">
         <v>46</v>
       </c>
@@ -22008,16 +21988,16 @@
         <v>1000</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>686</v>
+        <v>1107</v>
       </c>
       <c r="C227" s="4">
-        <v>162831940</v>
+        <v>162831929</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E227" s="4">
-        <v>6864706</v>
+        <v>7914368</v>
       </c>
       <c r="F227" s="4" t="s">
         <v>48</v>
@@ -22032,24 +22012,24 @@
         <v>108</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K227" s="4"/>
       <c r="L227" s="4" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="M227" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N227" s="4">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="O227" s="4" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="P227" s="5"/>
       <c r="Q227" s="4" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="R227" s="4" t="s">
         <v>55</v>
@@ -22061,10 +22041,10 @@
         <v>0</v>
       </c>
       <c r="U227" s="4" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="V227" s="4" t="s">
-        <v>640</v>
+        <v>137</v>
       </c>
       <c r="W227" s="4">
         <v>1</v>
@@ -22086,16 +22066,16 @@
         <v>1000</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>1113</v>
+        <v>1095</v>
       </c>
       <c r="C228" s="4">
-        <v>162831929</v>
+        <v>162831927</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E228" s="4">
-        <v>7914368</v>
+        <v>4322184</v>
       </c>
       <c r="F228" s="4" t="s">
         <v>48</v>
@@ -22110,24 +22090,24 @@
         <v>108</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K228" s="4"/>
       <c r="L228" s="4" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="M228" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N228" s="4">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="O228" s="4" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="P228" s="5"/>
       <c r="Q228" s="4" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="R228" s="4" t="s">
         <v>55</v>
@@ -22139,7 +22119,7 @@
         <v>0</v>
       </c>
       <c r="U228" s="4" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="V228" s="4" t="s">
         <v>137</v>
@@ -22148,7 +22128,7 @@
         <v>1</v>
       </c>
       <c r="X228" s="4" t="s">
-        <v>121</v>
+        <v>483</v>
       </c>
       <c r="Y228" s="4"/>
       <c r="Z228" s="4" t="s">
@@ -22164,16 +22144,16 @@
         <v>1000</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>1101</v>
+        <v>1117</v>
       </c>
       <c r="C229" s="4">
-        <v>162831927</v>
+        <v>162831937</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E229" s="4">
-        <v>4322184</v>
+        <v>6597723</v>
       </c>
       <c r="F229" s="4" t="s">
         <v>48</v>
@@ -22188,24 +22168,24 @@
         <v>108</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K229" s="4"/>
       <c r="L229" s="4" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="M229" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="N229" s="4">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O229" s="4" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="P229" s="5"/>
       <c r="Q229" s="4" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="R229" s="4" t="s">
         <v>55</v>
@@ -22217,16 +22197,16 @@
         <v>0</v>
       </c>
       <c r="U229" s="4" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="V229" s="4" t="s">
-        <v>137</v>
+        <v>307</v>
       </c>
       <c r="W229" s="4">
         <v>1</v>
       </c>
       <c r="X229" s="4" t="s">
-        <v>483</v>
+        <v>121</v>
       </c>
       <c r="Y229" s="4"/>
       <c r="Z229" s="4" t="s">
@@ -22242,16 +22222,16 @@
         <v>1000</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>1123</v>
+        <v>1140</v>
       </c>
       <c r="C230" s="4">
-        <v>162831937</v>
+        <v>162831955</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E230" s="4">
-        <v>6597723</v>
+        <v>6891125</v>
       </c>
       <c r="F230" s="4" t="s">
         <v>48</v>
@@ -22266,39 +22246,39 @@
         <v>108</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K230" s="4"/>
       <c r="L230" s="4" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="M230" s="4" t="s">
-        <v>1108</v>
+        <v>1141</v>
       </c>
       <c r="N230" s="4">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="O230" s="4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="P230" s="5"/>
       <c r="Q230" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="R230" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S230" s="4">
+        <v>0</v>
+      </c>
+      <c r="T230" s="4">
+        <v>0</v>
+      </c>
+      <c r="U230" s="4" t="s">
         <v>1144</v>
       </c>
-      <c r="R230" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="S230" s="4">
-        <v>0</v>
-      </c>
-      <c r="T230" s="4">
-        <v>0</v>
-      </c>
-      <c r="U230" s="4" t="s">
-        <v>1145</v>
-      </c>
       <c r="V230" s="4" t="s">
-        <v>307</v>
+        <v>137</v>
       </c>
       <c r="W230" s="4">
         <v>1</v>
@@ -22308,9 +22288,11 @@
       </c>
       <c r="Y230" s="4"/>
       <c r="Z230" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA230" s="4"/>
+        <v>243</v>
+      </c>
+      <c r="AA230" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB230" s="4" t="s">
         <v>46</v>
       </c>
@@ -22320,16 +22302,16 @@
         <v>1000</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>1146</v>
+        <v>729</v>
       </c>
       <c r="C231" s="4">
-        <v>162831955</v>
+        <v>162831947</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E231" s="4">
-        <v>6891125</v>
+        <v>7640284</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>48</v>
@@ -22344,24 +22326,24 @@
         <v>108</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K231" s="4"/>
       <c r="L231" s="4" t="s">
-        <v>1109</v>
+        <v>59</v>
       </c>
       <c r="M231" s="4" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="N231" s="4">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="O231" s="4" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="P231" s="5"/>
       <c r="Q231" s="4" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="R231" s="4" t="s">
         <v>70</v>
@@ -22373,10 +22355,10 @@
         <v>0</v>
       </c>
       <c r="U231" s="4" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="V231" s="4" t="s">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="W231" s="4">
         <v>1</v>
@@ -22386,10 +22368,10 @@
       </c>
       <c r="Y231" s="4"/>
       <c r="Z231" s="4" t="s">
-        <v>243</v>
+        <v>443</v>
       </c>
       <c r="AA231" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AB231" s="4" t="s">
         <v>46</v>
@@ -22400,16 +22382,16 @@
         <v>1000</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>729</v>
+        <v>1140</v>
       </c>
       <c r="C232" s="4">
-        <v>162831947</v>
+        <v>162831951</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E232" s="4">
-        <v>7640284</v>
+        <v>6702243</v>
       </c>
       <c r="F232" s="4" t="s">
         <v>48</v>
@@ -22424,27 +22406,27 @@
         <v>108</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K232" s="4"/>
       <c r="L232" s="4" t="s">
-        <v>59</v>
+        <v>781</v>
       </c>
       <c r="M232" s="4" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="N232" s="4">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="O232" s="4" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="P232" s="5"/>
       <c r="Q232" s="4" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="R232" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S232" s="4">
         <v>0</v>
@@ -22453,10 +22435,10 @@
         <v>0</v>
       </c>
       <c r="U232" s="4" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="V232" s="4" t="s">
-        <v>281</v>
+        <v>129</v>
       </c>
       <c r="W232" s="4">
         <v>1</v>
@@ -22466,11 +22448,9 @@
       </c>
       <c r="Y232" s="4"/>
       <c r="Z232" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="AA232" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA232" s="4"/>
       <c r="AB232" s="4" t="s">
         <v>46</v>
       </c>
@@ -22480,16 +22460,16 @@
         <v>1000</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>1146</v>
+        <v>729</v>
       </c>
       <c r="C233" s="4">
-        <v>162831951</v>
+        <v>162831949</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E233" s="4">
-        <v>6702243</v>
+        <v>7739201</v>
       </c>
       <c r="F233" s="4" t="s">
         <v>48</v>
@@ -22504,27 +22484,27 @@
         <v>108</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K233" s="4"/>
       <c r="L233" s="4" t="s">
-        <v>781</v>
+        <v>1153</v>
       </c>
       <c r="M233" s="4" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="N233" s="4">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="O233" s="4" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="P233" s="5"/>
       <c r="Q233" s="4" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="R233" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S233" s="4">
         <v>0</v>
@@ -22532,12 +22512,8 @@
       <c r="T233" s="4">
         <v>0</v>
       </c>
-      <c r="U233" s="4" t="s">
-        <v>1158</v>
-      </c>
-      <c r="V233" s="4" t="s">
-        <v>129</v>
-      </c>
+      <c r="U233" s="4"/>
+      <c r="V233" s="4"/>
       <c r="W233" s="4">
         <v>1</v>
       </c>
@@ -22546,9 +22522,11 @@
       </c>
       <c r="Y233" s="4"/>
       <c r="Z233" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA233" s="4"/>
+        <v>243</v>
+      </c>
+      <c r="AA233" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB233" s="4" t="s">
         <v>46</v>
       </c>
@@ -22558,16 +22536,16 @@
         <v>1000</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>729</v>
+        <v>1140</v>
       </c>
       <c r="C234" s="4">
-        <v>162831949</v>
+        <v>162831953</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E234" s="4">
-        <v>7739201</v>
+        <v>7868098</v>
       </c>
       <c r="F234" s="4" t="s">
         <v>48</v>
@@ -22582,27 +22560,25 @@
         <v>108</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="K234" s="4"/>
       <c r="L234" s="4" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="M234" s="4" t="s">
-        <v>1155</v>
-      </c>
-      <c r="N234" s="4">
-        <v>84</v>
-      </c>
+        <v>1157</v>
+      </c>
+      <c r="N234" s="4"/>
       <c r="O234" s="4" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="P234" s="5"/>
       <c r="Q234" s="4" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="R234" s="4" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="S234" s="4">
         <v>0</v>
@@ -22634,16 +22610,16 @@
         <v>1000</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>1146</v>
+        <v>1107</v>
       </c>
       <c r="C235" s="4">
-        <v>162831953</v>
+        <v>162846797</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E235" s="4">
-        <v>7868098</v>
+        <v>8036371</v>
       </c>
       <c r="F235" s="4" t="s">
         <v>48</v>
@@ -22658,25 +22634,27 @@
         <v>108</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>1089</v>
+        <v>1160</v>
       </c>
       <c r="K235" s="4"/>
       <c r="L235" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="M235" s="4" t="s">
         <v>1162</v>
       </c>
-      <c r="M235" s="4" t="s">
+      <c r="N235" s="4">
+        <v>9</v>
+      </c>
+      <c r="O235" s="4" t="s">
         <v>1163</v>
-      </c>
-      <c r="N235" s="4"/>
-      <c r="O235" s="4" t="s">
-        <v>1164</v>
       </c>
       <c r="P235" s="5"/>
       <c r="Q235" s="4" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="R235" s="4" t="s">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="S235" s="4">
         <v>0</v>
@@ -22694,10 +22672,10 @@
       </c>
       <c r="Y235" s="4"/>
       <c r="Z235" s="4" t="s">
-        <v>243</v>
+        <v>1165</v>
       </c>
       <c r="AA235" s="4" t="s">
-        <v>66</v>
+        <v>607</v>
       </c>
       <c r="AB235" s="4" t="s">
         <v>46</v>
@@ -22708,16 +22686,16 @@
         <v>1000</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>1113</v>
+        <v>267</v>
       </c>
       <c r="C236" s="4">
-        <v>162846797</v>
+        <v>162471704</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E236" s="4">
-        <v>8036371</v>
+        <v>6688312</v>
       </c>
       <c r="F236" s="4" t="s">
         <v>48</v>
@@ -22736,44 +22714,44 @@
       </c>
       <c r="K236" s="4"/>
       <c r="L236" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M236" s="4"/>
+      <c r="N236" s="4"/>
+      <c r="O236" s="4" t="s">
         <v>1167</v>
-      </c>
-      <c r="M236" s="4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="N236" s="4">
-        <v>9</v>
-      </c>
-      <c r="O236" s="4" t="s">
-        <v>1169</v>
       </c>
       <c r="P236" s="5"/>
       <c r="Q236" s="4" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="R236" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S236" s="4">
-        <v>0</v>
+        <v>162297.36</v>
       </c>
       <c r="T236" s="4">
-        <v>0</v>
-      </c>
-      <c r="U236" s="4"/>
-      <c r="V236" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U236" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="V236" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="W236" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X236" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y236" s="4"/>
       <c r="Z236" s="4" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="AA236" s="4" t="s">
-        <v>607</v>
+        <v>66</v>
       </c>
       <c r="AB236" s="4" t="s">
         <v>46</v>
@@ -22787,13 +22765,13 @@
         <v>267</v>
       </c>
       <c r="C237" s="4">
-        <v>162471704</v>
+        <v>162444096</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>116</v>
       </c>
       <c r="E237" s="4">
-        <v>6688312</v>
+        <v>8156753</v>
       </c>
       <c r="F237" s="4" t="s">
         <v>48</v>
@@ -22808,36 +22786,36 @@
         <v>108</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="K237" s="4"/>
       <c r="L237" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M237" s="4"/>
-      <c r="N237" s="4"/>
+        <v>593</v>
+      </c>
+      <c r="M237" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="N237" s="4">
+        <v>55</v>
+      </c>
       <c r="O237" s="4" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="P237" s="5"/>
       <c r="Q237" s="4" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="R237" s="4" t="s">
         <v>55</v>
       </c>
       <c r="S237" s="4">
-        <v>162297.36</v>
+        <v>1129223.29</v>
       </c>
       <c r="T237" s="4">
-        <v>3</v>
-      </c>
-      <c r="U237" s="4" t="s">
-        <v>1175</v>
-      </c>
-      <c r="V237" s="4" t="s">
-        <v>144</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="U237" s="4"/>
+      <c r="V237" s="4"/>
       <c r="W237" s="4">
         <v>6</v>
       </c>
@@ -22846,11 +22824,9 @@
       </c>
       <c r="Y237" s="4"/>
       <c r="Z237" s="4" t="s">
-        <v>1176</v>
-      </c>
-      <c r="AA237" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>1173</v>
+      </c>
+      <c r="AA237" s="4"/>
       <c r="AB237" s="4" t="s">
         <v>46</v>
       </c>
@@ -22860,16 +22836,16 @@
         <v>1000</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>267</v>
+        <v>621</v>
       </c>
       <c r="C238" s="4">
-        <v>162444096</v>
+        <v>162690335</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E238" s="4">
-        <v>8156753</v>
+        <v>6596389</v>
       </c>
       <c r="F238" s="4" t="s">
         <v>48</v>
@@ -22884,47 +22860,51 @@
         <v>108</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="K238" s="4"/>
       <c r="L238" s="4" t="s">
-        <v>593</v>
+        <v>947</v>
       </c>
       <c r="M238" s="4" t="s">
-        <v>1167</v>
-      </c>
-      <c r="N238" s="4">
-        <v>55</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="N238" s="4"/>
       <c r="O238" s="4" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="P238" s="5"/>
       <c r="Q238" s="4" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="R238" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S238" s="4">
-        <v>1129223.29</v>
+        <v>474809.72</v>
       </c>
       <c r="T238" s="4">
-        <v>8</v>
-      </c>
-      <c r="U238" s="4"/>
-      <c r="V238" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U238" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="V238" s="4" t="s">
+        <v>318</v>
+      </c>
       <c r="W238" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X238" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y238" s="4"/>
       <c r="Z238" s="4" t="s">
-        <v>1179</v>
-      </c>
-      <c r="AA238" s="4"/>
+        <v>203</v>
+      </c>
+      <c r="AA238" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="AB238" s="4" t="s">
         <v>46</v>
       </c>
@@ -22937,13 +22917,13 @@
         <v>621</v>
       </c>
       <c r="C239" s="4">
-        <v>162690335</v>
+        <v>162690336</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E239" s="4">
-        <v>6596389</v>
+        <v>7553396</v>
       </c>
       <c r="F239" s="4" t="s">
         <v>48</v>
@@ -22958,37 +22938,39 @@
         <v>108</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="K239" s="4"/>
       <c r="L239" s="4" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="M239" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="N239" s="4"/>
+        <v>586</v>
+      </c>
+      <c r="N239" s="4">
+        <v>92</v>
+      </c>
       <c r="O239" s="4" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="P239" s="5"/>
       <c r="Q239" s="4" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="R239" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S239" s="4">
-        <v>474809.72</v>
+        <v>413067.14</v>
       </c>
       <c r="T239" s="4">
         <v>1</v>
       </c>
       <c r="U239" s="4" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="V239" s="4" t="s">
-        <v>318</v>
+        <v>224</v>
       </c>
       <c r="W239" s="4">
         <v>4</v>
@@ -22998,13 +22980,13 @@
       </c>
       <c r="Y239" s="4"/>
       <c r="Z239" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AA239" s="4" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB239" s="4" t="s">
-        <v>46</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="240" spans="1:28">
@@ -23012,16 +22994,16 @@
         <v>1000</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>621</v>
+        <v>1055</v>
       </c>
       <c r="C240" s="4">
-        <v>162690336</v>
+        <v>162329662</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E240" s="4">
-        <v>7553396</v>
+        <v>1056121</v>
       </c>
       <c r="F240" s="4" t="s">
         <v>48</v>
@@ -23033,58 +23015,52 @@
         <v>108</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>108</v>
+        <v>1181</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>1172</v>
+        <v>1181</v>
       </c>
       <c r="K240" s="4"/>
       <c r="L240" s="4" t="s">
-        <v>952</v>
+        <v>677</v>
       </c>
       <c r="M240" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="N240" s="4">
-        <v>92</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N240" s="4"/>
       <c r="O240" s="4" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="P240" s="5"/>
       <c r="Q240" s="4" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="R240" s="4" t="s">
         <v>55</v>
       </c>
       <c r="S240" s="4">
-        <v>413067.14</v>
+        <v>0</v>
       </c>
       <c r="T240" s="4">
-        <v>1</v>
-      </c>
-      <c r="U240" s="4" t="s">
-        <v>1185</v>
-      </c>
-      <c r="V240" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U240" s="4"/>
+      <c r="V240" s="4"/>
       <c r="W240" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X240" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y240" s="4"/>
       <c r="Z240" s="4" t="s">
-        <v>209</v>
+        <v>1184</v>
       </c>
       <c r="AA240" s="4" t="s">
-        <v>210</v>
+        <v>607</v>
       </c>
       <c r="AB240" s="4" t="s">
-        <v>1186</v>
+        <v>46</v>
       </c>
     </row>
     <row r="241" spans="1:28">
@@ -23092,16 +23068,16 @@
         <v>1000</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>1061</v>
+        <v>33</v>
       </c>
       <c r="C241" s="4">
-        <v>162329662</v>
+        <v>162836964</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E241" s="4">
-        <v>1056121</v>
+        <v>1031625</v>
       </c>
       <c r="F241" s="4" t="s">
         <v>48</v>
@@ -23113,52 +23089,52 @@
         <v>108</v>
       </c>
       <c r="I241" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="J241" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="K241" s="4"/>
       <c r="L241" s="4" t="s">
         <v>677</v>
       </c>
       <c r="M241" s="4" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="N241" s="4"/>
       <c r="O241" s="4" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="P241" s="5"/>
       <c r="Q241" s="4" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="R241" s="4" t="s">
         <v>55</v>
       </c>
       <c r="S241" s="4">
-        <v>0</v>
+        <v>2896300.46</v>
       </c>
       <c r="T241" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U241" s="4"/>
       <c r="V241" s="4"/>
       <c r="W241" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X241" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y241" s="4"/>
       <c r="Z241" s="4" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="AA241" s="4" t="s">
-        <v>607</v>
+        <v>190</v>
       </c>
       <c r="AB241" s="4" t="s">
-        <v>46</v>
+        <v>302</v>
       </c>
     </row>
     <row r="242" spans="1:28">
@@ -23169,13 +23145,13 @@
         <v>33</v>
       </c>
       <c r="C242" s="4">
-        <v>162836964</v>
+        <v>162857286</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="E242" s="4">
-        <v>1031625</v>
+        <v>7943318</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>48</v>
@@ -23187,37 +23163,41 @@
         <v>108</v>
       </c>
       <c r="I242" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="J242" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="K242" s="4"/>
       <c r="L242" s="4" t="s">
-        <v>677</v>
+        <v>540</v>
       </c>
       <c r="M242" s="4" t="s">
         <v>554</v>
       </c>
       <c r="N242" s="4"/>
       <c r="O242" s="4" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="P242" s="5"/>
       <c r="Q242" s="4" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="R242" s="4" t="s">
         <v>55</v>
       </c>
       <c r="S242" s="4">
-        <v>2896300.46</v>
+        <v>0</v>
       </c>
       <c r="T242" s="4">
-        <v>3</v>
-      </c>
-      <c r="U242" s="4"/>
-      <c r="V242" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U242" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="V242" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="W242" s="4">
         <v>1</v>
       </c>
@@ -23226,13 +23206,13 @@
       </c>
       <c r="Y242" s="4"/>
       <c r="Z242" s="4" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="AA242" s="4" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="AB242" s="4" t="s">
-        <v>302</v>
+        <v>46</v>
       </c>
     </row>
     <row r="243" spans="1:28">
@@ -23240,16 +23220,16 @@
         <v>1000</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>33</v>
+        <v>1055</v>
       </c>
       <c r="C243" s="4">
-        <v>162857286</v>
+        <v>162329644</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="E243" s="4">
-        <v>7943318</v>
+        <v>7956987</v>
       </c>
       <c r="F243" s="4" t="s">
         <v>48</v>
@@ -23261,17 +23241,17 @@
         <v>108</v>
       </c>
       <c r="I243" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="J243" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="K243" s="4"/>
       <c r="L243" s="4" t="s">
-        <v>540</v>
+        <v>1192</v>
       </c>
       <c r="M243" s="4" t="s">
-        <v>554</v>
+        <v>1193</v>
       </c>
       <c r="N243" s="4"/>
       <c r="O243" s="4" t="s">
@@ -23297,17 +23277,17 @@
         <v>72</v>
       </c>
       <c r="W243" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X243" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y243" s="4"/>
       <c r="Z243" s="4" t="s">
         <v>1197</v>
       </c>
       <c r="AA243" s="4" t="s">
-        <v>66</v>
+        <v>220</v>
       </c>
       <c r="AB243" s="4" t="s">
         <v>46</v>
@@ -23318,16 +23298,16 @@
         <v>1000</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="C244" s="4">
-        <v>162329644</v>
+        <v>162690429</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E244" s="4">
-        <v>7956987</v>
+        <v>8266674</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>48</v>
@@ -23339,25 +23319,27 @@
         <v>108</v>
       </c>
       <c r="I244" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="J244" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="K244" s="4"/>
       <c r="L244" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="M244" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="N244" s="4">
+        <v>84</v>
+      </c>
+      <c r="O244" s="4" t="s">
         <v>1198</v>
-      </c>
-      <c r="M244" s="4" t="s">
-        <v>1199</v>
-      </c>
-      <c r="N244" s="4"/>
-      <c r="O244" s="4" t="s">
-        <v>1200</v>
       </c>
       <c r="P244" s="5"/>
       <c r="Q244" s="4" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="R244" s="4" t="s">
         <v>55</v>
@@ -23368,25 +23350,19 @@
       <c r="T244" s="4">
         <v>0</v>
       </c>
-      <c r="U244" s="4" t="s">
-        <v>1202</v>
-      </c>
-      <c r="V244" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="U244" s="4"/>
+      <c r="V244" s="4"/>
       <c r="W244" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="X244" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y244" s="4"/>
       <c r="Z244" s="4" t="s">
-        <v>1203</v>
-      </c>
-      <c r="AA244" s="4" t="s">
-        <v>220</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="AA244" s="4"/>
       <c r="AB244" s="4" t="s">
         <v>46</v>
       </c>
@@ -23396,16 +23372,16 @@
         <v>1000</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>1061</v>
+        <v>151</v>
       </c>
       <c r="C245" s="4">
-        <v>162690429</v>
+        <v>162329649</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E245" s="4">
-        <v>8266674</v>
+        <v>6835850</v>
       </c>
       <c r="F245" s="4" t="s">
         <v>48</v>
@@ -23417,27 +23393,27 @@
         <v>108</v>
       </c>
       <c r="I245" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="J245" s="4" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="K245" s="4"/>
       <c r="L245" s="4" t="s">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="M245" s="4" t="s">
-        <v>1199</v>
+        <v>994</v>
       </c>
       <c r="N245" s="4">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="O245" s="4" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="P245" s="5"/>
       <c r="Q245" s="4" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="R245" s="4" t="s">
         <v>55</v>
@@ -23448,19 +23424,25 @@
       <c r="T245" s="4">
         <v>0</v>
       </c>
-      <c r="U245" s="4"/>
-      <c r="V245" s="4"/>
+      <c r="U245" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="V245" s="4" t="s">
+        <v>195</v>
+      </c>
       <c r="W245" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X245" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y245" s="4"/>
       <c r="Z245" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="AA245" s="4"/>
+        <v>282</v>
+      </c>
+      <c r="AA245" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB245" s="4" t="s">
         <v>46</v>
       </c>
@@ -23470,16 +23452,16 @@
         <v>1000</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>151</v>
+        <v>459</v>
       </c>
       <c r="C246" s="4">
-        <v>162329649</v>
+        <v>162583521</v>
       </c>
       <c r="D246" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E246" s="4">
-        <v>6835850</v>
+        <v>4318833</v>
       </c>
       <c r="F246" s="4" t="s">
         <v>48</v>
@@ -23491,52 +23473,52 @@
         <v>108</v>
       </c>
       <c r="I246" s="4" t="s">
-        <v>1187</v>
+        <v>108</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>1187</v>
+        <v>1204</v>
       </c>
       <c r="K246" s="4"/>
       <c r="L246" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="M246" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="N246" s="4">
+        <v>114</v>
+      </c>
+      <c r="O246" s="4" t="s">
         <v>1206</v>
-      </c>
-      <c r="M246" s="4" t="s">
-        <v>994</v>
-      </c>
-      <c r="N246" s="4">
-        <v>11</v>
-      </c>
-      <c r="O246" s="4" t="s">
-        <v>1207</v>
       </c>
       <c r="P246" s="5"/>
       <c r="Q246" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="R246" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="S246" s="4">
+        <v>0</v>
+      </c>
+      <c r="T246" s="4">
+        <v>0</v>
+      </c>
+      <c r="U246" s="4" t="s">
         <v>1208</v>
       </c>
-      <c r="R246" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="S246" s="4">
-        <v>0</v>
-      </c>
-      <c r="T246" s="4">
-        <v>0</v>
-      </c>
-      <c r="U246" s="4" t="s">
-        <v>1209</v>
-      </c>
       <c r="V246" s="4" t="s">
-        <v>195</v>
+        <v>294</v>
       </c>
       <c r="W246" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X246" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y246" s="4"/>
       <c r="Z246" s="4" t="s">
-        <v>282</v>
+        <v>692</v>
       </c>
       <c r="AA246" s="4" t="s">
         <v>66</v>
@@ -23553,13 +23535,13 @@
         <v>459</v>
       </c>
       <c r="C247" s="4">
-        <v>162583521</v>
+        <v>162583522</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E247" s="4">
-        <v>4318833</v>
+        <v>4318838</v>
       </c>
       <c r="F247" s="4" t="s">
         <v>48</v>
@@ -23574,36 +23556,36 @@
         <v>108</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="K247" s="4"/>
       <c r="L247" s="4" t="s">
         <v>715</v>
       </c>
       <c r="M247" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="N247" s="4">
         <v>114</v>
       </c>
       <c r="O247" s="4" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="P247" s="5"/>
       <c r="Q247" s="4" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="R247" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S247" s="4">
-        <v>0</v>
+        <v>117366.53</v>
       </c>
       <c r="T247" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U247" s="4" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="V247" s="4" t="s">
         <v>294</v>
@@ -23616,10 +23598,10 @@
       </c>
       <c r="Y247" s="4"/>
       <c r="Z247" s="4" t="s">
-        <v>692</v>
+        <v>1212</v>
       </c>
       <c r="AA247" s="4" t="s">
-        <v>66</v>
+        <v>1033</v>
       </c>
       <c r="AB247" s="4" t="s">
         <v>46</v>
@@ -23630,16 +23612,16 @@
         <v>1000</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>459</v>
+        <v>33</v>
       </c>
       <c r="C248" s="4">
-        <v>162583522</v>
+        <v>162855645</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E248" s="4">
-        <v>4318838</v>
+        <v>8026156</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>48</v>
@@ -23654,52 +23636,42 @@
         <v>108</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="K248" s="4"/>
-      <c r="L248" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="M248" s="4" t="s">
-        <v>1211</v>
-      </c>
-      <c r="N248" s="4">
-        <v>114</v>
-      </c>
+      <c r="L248" s="4"/>
+      <c r="M248" s="4"/>
+      <c r="N248" s="4"/>
       <c r="O248" s="4" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="P248" s="5"/>
       <c r="Q248" s="4" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="R248" s="4" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="S248" s="4">
-        <v>117366.53</v>
+        <v>0</v>
       </c>
       <c r="T248" s="4">
-        <v>2</v>
-      </c>
-      <c r="U248" s="4" t="s">
-        <v>1217</v>
-      </c>
-      <c r="V248" s="4" t="s">
-        <v>294</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U248" s="4"/>
+      <c r="V248" s="4"/>
       <c r="W248" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X248" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y248" s="4"/>
       <c r="Z248" s="4" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="AA248" s="4" t="s">
-        <v>1038</v>
+        <v>74</v>
       </c>
       <c r="AB248" s="4" t="s">
         <v>46</v>
@@ -23710,16 +23682,16 @@
         <v>1000</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>33</v>
+        <v>258</v>
       </c>
       <c r="C249" s="4">
-        <v>162855645</v>
+        <v>162675689</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E249" s="4">
-        <v>8026156</v>
+        <v>6548439</v>
       </c>
       <c r="F249" s="4" t="s">
         <v>48</v>
@@ -23734,21 +23706,23 @@
         <v>108</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="K249" s="4"/>
-      <c r="L249" s="4"/>
+      <c r="L249" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="M249" s="4"/>
       <c r="N249" s="4"/>
       <c r="O249" s="4" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="P249" s="5"/>
       <c r="Q249" s="4" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="R249" s="4" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="S249" s="4">
         <v>0</v>
@@ -23756,20 +23730,24 @@
       <c r="T249" s="4">
         <v>0</v>
       </c>
-      <c r="U249" s="4"/>
-      <c r="V249" s="4"/>
+      <c r="U249" s="4" t="s">
+        <v>1219</v>
+      </c>
+      <c r="V249" s="4" t="s">
+        <v>427</v>
+      </c>
       <c r="W249" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X249" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y249" s="4"/>
       <c r="Z249" s="4" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="AA249" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB249" s="4" t="s">
         <v>46</v>
@@ -23783,13 +23761,13 @@
         <v>258</v>
       </c>
       <c r="C250" s="4">
-        <v>162675689</v>
+        <v>162731979</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>116</v>
       </c>
       <c r="E250" s="4">
-        <v>6548439</v>
+        <v>6992089</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>48</v>
@@ -23804,7 +23782,7 @@
         <v>108</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="K250" s="4"/>
       <c r="L250" s="4" t="s">
@@ -23813,11 +23791,11 @@
       <c r="M250" s="4"/>
       <c r="N250" s="4"/>
       <c r="O250" s="4" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="P250" s="5"/>
       <c r="Q250" s="4" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="R250" s="4" t="s">
         <v>43</v>
@@ -23829,20 +23807,20 @@
         <v>0</v>
       </c>
       <c r="U250" s="4" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="V250" s="4" t="s">
-        <v>427</v>
+        <v>195</v>
       </c>
       <c r="W250" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X250" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y250" s="4"/>
       <c r="Z250" s="4" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="AA250" s="4" t="s">
         <v>66</v>
@@ -23856,16 +23834,16 @@
         <v>1000</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>258</v>
+        <v>33</v>
       </c>
       <c r="C251" s="4">
-        <v>162731979</v>
+        <v>162855641</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E251" s="4">
-        <v>6992089</v>
+        <v>7993716</v>
       </c>
       <c r="F251" s="4" t="s">
         <v>48</v>
@@ -23880,7 +23858,7 @@
         <v>108</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="K251" s="4"/>
       <c r="L251" s="4" t="s">
@@ -23889,36 +23867,32 @@
       <c r="M251" s="4"/>
       <c r="N251" s="4"/>
       <c r="O251" s="4" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="P251" s="5"/>
       <c r="Q251" s="4" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="R251" s="4" t="s">
         <v>43</v>
       </c>
       <c r="S251" s="4">
-        <v>0</v>
+        <v>85255.03</v>
       </c>
       <c r="T251" s="4">
-        <v>0</v>
-      </c>
-      <c r="U251" s="4" t="s">
-        <v>1229</v>
-      </c>
-      <c r="V251" s="4" t="s">
-        <v>195</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="U251" s="4"/>
+      <c r="V251" s="4"/>
       <c r="W251" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X251" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y251" s="4"/>
       <c r="Z251" s="4" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="AA251" s="4" t="s">
         <v>66</v>
@@ -23932,16 +23906,16 @@
         <v>1000</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>33</v>
+        <v>333</v>
       </c>
       <c r="C252" s="4">
-        <v>162855641</v>
+        <v>162867865</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E252" s="4">
-        <v>7993716</v>
+        <v>6548335</v>
       </c>
       <c r="F252" s="4" t="s">
         <v>48</v>
@@ -23956,7 +23930,7 @@
         <v>108</v>
       </c>
       <c r="J252" s="4" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="K252" s="4"/>
       <c r="L252" s="4" t="s">
@@ -23965,35 +23939,39 @@
       <c r="M252" s="4"/>
       <c r="N252" s="4"/>
       <c r="O252" s="4" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="P252" s="5"/>
       <c r="Q252" s="4" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="R252" s="4" t="s">
         <v>43</v>
       </c>
       <c r="S252" s="4">
-        <v>85255.03</v>
+        <v>0</v>
       </c>
       <c r="T252" s="4">
-        <v>4</v>
-      </c>
-      <c r="U252" s="4"/>
-      <c r="V252" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U252" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="V252" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="W252" s="4">
         <v>1</v>
       </c>
       <c r="X252" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y252" s="4"/>
       <c r="Z252" s="4" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="AA252" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AB252" s="4" t="s">
         <v>46</v>
@@ -24004,16 +23982,16 @@
         <v>1000</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>333</v>
+        <v>258</v>
       </c>
       <c r="C253" s="4">
-        <v>162867865</v>
+        <v>162697084</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E253" s="4">
-        <v>6548335</v>
+        <v>7064700</v>
       </c>
       <c r="F253" s="4" t="s">
         <v>48</v>
@@ -24028,7 +24006,7 @@
         <v>108</v>
       </c>
       <c r="J253" s="4" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="K253" s="4"/>
       <c r="L253" s="4" t="s">
@@ -24037,11 +24015,11 @@
       <c r="M253" s="4"/>
       <c r="N253" s="4"/>
       <c r="O253" s="4" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="P253" s="5"/>
       <c r="Q253" s="4" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="R253" s="4" t="s">
         <v>43</v>
@@ -24053,20 +24031,20 @@
         <v>0</v>
       </c>
       <c r="U253" s="4" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="V253" s="4" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="W253" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X253" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y253" s="4"/>
       <c r="Z253" s="4" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="AA253" s="4" t="s">
         <v>74</v>
@@ -24083,13 +24061,13 @@
         <v>258</v>
       </c>
       <c r="C254" s="4">
-        <v>162697084</v>
+        <v>162567144</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>116</v>
       </c>
       <c r="E254" s="4">
-        <v>7064700</v>
+        <v>7064671</v>
       </c>
       <c r="F254" s="4" t="s">
         <v>48</v>
@@ -24104,7 +24082,7 @@
         <v>108</v>
       </c>
       <c r="J254" s="4" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="K254" s="4"/>
       <c r="L254" s="4" t="s">
@@ -24113,11 +24091,11 @@
       <c r="M254" s="4"/>
       <c r="N254" s="4"/>
       <c r="O254" s="4" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="P254" s="5"/>
       <c r="Q254" s="4" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="R254" s="4" t="s">
         <v>43</v>
@@ -24128,21 +24106,17 @@
       <c r="T254" s="4">
         <v>0</v>
       </c>
-      <c r="U254" s="4" t="s">
-        <v>1241</v>
-      </c>
-      <c r="V254" s="4" t="s">
-        <v>173</v>
-      </c>
+      <c r="U254" s="4"/>
+      <c r="V254" s="4"/>
       <c r="W254" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X254" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y254" s="4"/>
       <c r="Z254" s="4" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="AA254" s="4" t="s">
         <v>74</v>
@@ -24156,16 +24130,16 @@
         <v>1000</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>258</v>
+        <v>33</v>
       </c>
       <c r="C255" s="4">
-        <v>162567144</v>
+        <v>162855643</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E255" s="4">
-        <v>7064671</v>
+        <v>1138288</v>
       </c>
       <c r="F255" s="4" t="s">
         <v>48</v>
@@ -24180,20 +24154,22 @@
         <v>108</v>
       </c>
       <c r="J255" s="4" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="K255" s="4"/>
       <c r="L255" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M255" s="4"/>
+        <v>761</v>
+      </c>
+      <c r="M255" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="N255" s="4"/>
       <c r="O255" s="4" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="P255" s="5"/>
       <c r="Q255" s="4" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="R255" s="4" t="s">
         <v>43</v>
@@ -24204,21 +24180,23 @@
       <c r="T255" s="4">
         <v>0</v>
       </c>
-      <c r="U255" s="4"/>
-      <c r="V255" s="4"/>
+      <c r="U255" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="V255" s="4" t="s">
+        <v>743</v>
+      </c>
       <c r="W255" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X255" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y255" s="4"/>
       <c r="Z255" s="4" t="s">
-        <v>1246</v>
-      </c>
-      <c r="AA255" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>1244</v>
+      </c>
+      <c r="AA255" s="4"/>
       <c r="AB255" s="4" t="s">
         <v>46</v>
       </c>
@@ -24228,16 +24206,16 @@
         <v>1000</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>33</v>
+        <v>258</v>
       </c>
       <c r="C256" s="4">
-        <v>162855643</v>
+        <v>162574945</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E256" s="4">
-        <v>1138288</v>
+        <v>8077892</v>
       </c>
       <c r="F256" s="4" t="s">
         <v>48</v>
@@ -24252,47 +24230,45 @@
         <v>108</v>
       </c>
       <c r="J256" s="4" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="K256" s="4"/>
       <c r="L256" s="4" t="s">
-        <v>761</v>
+        <v>1245</v>
       </c>
       <c r="M256" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="N256" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="N256" s="4">
+        <v>5</v>
+      </c>
       <c r="O256" s="4" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="P256" s="5"/>
       <c r="Q256" s="4" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="R256" s="4" t="s">
         <v>43</v>
       </c>
       <c r="S256" s="4">
-        <v>0</v>
+        <v>128004.54</v>
       </c>
       <c r="T256" s="4">
-        <v>0</v>
-      </c>
-      <c r="U256" s="4" t="s">
-        <v>1249</v>
-      </c>
-      <c r="V256" s="4" t="s">
-        <v>743</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U256" s="4"/>
+      <c r="V256" s="4"/>
       <c r="W256" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X256" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y256" s="4"/>
       <c r="Z256" s="4" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="AA256" s="4"/>
       <c r="AB256" s="4" t="s">
@@ -24304,16 +24280,16 @@
         <v>1000</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>258</v>
+        <v>33</v>
       </c>
       <c r="C257" s="4">
-        <v>162574945</v>
+        <v>162855644</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E257" s="4">
-        <v>8077892</v>
+        <v>7927850</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>48</v>
@@ -24328,45 +24304,45 @@
         <v>108</v>
       </c>
       <c r="J257" s="4" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="K257" s="4"/>
       <c r="L257" s="4" t="s">
-        <v>1251</v>
-      </c>
-      <c r="M257" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="N257" s="4">
-        <v>5</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="M257" s="4"/>
+      <c r="N257" s="4"/>
       <c r="O257" s="4" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="P257" s="5"/>
       <c r="Q257" s="4" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="R257" s="4" t="s">
         <v>43</v>
       </c>
       <c r="S257" s="4">
-        <v>128004.54</v>
+        <v>0</v>
       </c>
       <c r="T257" s="4">
-        <v>2</v>
-      </c>
-      <c r="U257" s="4"/>
-      <c r="V257" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U257" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="V257" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="W257" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X257" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y257" s="4"/>
       <c r="Z257" s="4" t="s">
-        <v>1254</v>
+        <v>184</v>
       </c>
       <c r="AA257" s="4"/>
       <c r="AB257" s="4" t="s">
@@ -24381,13 +24357,13 @@
         <v>33</v>
       </c>
       <c r="C258" s="4">
-        <v>162855644</v>
+        <v>162863709</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E258" s="4">
-        <v>7927850</v>
+        <v>5923556</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>48</v>
@@ -24402,7 +24378,7 @@
         <v>108</v>
       </c>
       <c r="J258" s="4" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="K258" s="4"/>
       <c r="L258" s="4" t="s">
@@ -24411,14 +24387,14 @@
       <c r="M258" s="4"/>
       <c r="N258" s="4"/>
       <c r="O258" s="4" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="P258" s="5"/>
       <c r="Q258" s="4" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="R258" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="S258" s="4">
         <v>0</v>
@@ -24426,12 +24402,8 @@
       <c r="T258" s="4">
         <v>0</v>
       </c>
-      <c r="U258" s="4" t="s">
-        <v>1258</v>
-      </c>
-      <c r="V258" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="U258" s="4"/>
+      <c r="V258" s="4"/>
       <c r="W258" s="4">
         <v>1</v>
       </c>
@@ -24440,9 +24412,11 @@
       </c>
       <c r="Y258" s="4"/>
       <c r="Z258" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA258" s="4"/>
+        <v>1256</v>
+      </c>
+      <c r="AA258" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="AB258" s="4" t="s">
         <v>46</v>
       </c>
@@ -24455,13 +24429,13 @@
         <v>33</v>
       </c>
       <c r="C259" s="4">
-        <v>162863709</v>
+        <v>162899177</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E259" s="4">
-        <v>5923556</v>
+        <v>7715397</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>48</v>
@@ -24476,7 +24450,7 @@
         <v>108</v>
       </c>
       <c r="J259" s="4" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="K259" s="4"/>
       <c r="L259" s="4" t="s">
@@ -24485,35 +24459,39 @@
       <c r="M259" s="4"/>
       <c r="N259" s="4"/>
       <c r="O259" s="4" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="P259" s="5"/>
       <c r="Q259" s="4" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="R259" s="4" t="s">
         <v>55</v>
       </c>
       <c r="S259" s="4">
-        <v>0</v>
+        <v>92134.10000000001</v>
       </c>
       <c r="T259" s="4">
-        <v>0</v>
-      </c>
-      <c r="U259" s="4"/>
-      <c r="V259" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U259" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="V259" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="W259" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X259" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y259" s="4"/>
       <c r="Z259" s="4" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="AA259" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB259" s="4" t="s">
         <v>46</v>
@@ -24524,16 +24502,16 @@
         <v>1000</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>33</v>
+        <v>1261</v>
       </c>
       <c r="C260" s="4">
-        <v>162899177</v>
+        <v>162831956</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E260" s="4">
-        <v>7715397</v>
+        <v>6888773</v>
       </c>
       <c r="F260" s="4" t="s">
         <v>48</v>
@@ -24548,7 +24526,7 @@
         <v>108</v>
       </c>
       <c r="J260" s="4" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="K260" s="4"/>
       <c r="L260" s="4" t="s">
@@ -24567,26 +24545,26 @@
         <v>55</v>
       </c>
       <c r="S260" s="4">
-        <v>92134.10000000001</v>
+        <v>0</v>
       </c>
       <c r="T260" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U260" s="4" t="s">
         <v>1265</v>
       </c>
       <c r="V260" s="4" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="W260" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X260" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y260" s="4"/>
       <c r="Z260" s="4" t="s">
-        <v>1266</v>
+        <v>243</v>
       </c>
       <c r="AA260" s="4" t="s">
         <v>66</v>
@@ -24600,16 +24578,16 @@
         <v>1000</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="C261" s="4">
-        <v>162831956</v>
+        <v>162831957</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E261" s="4">
-        <v>6888773</v>
+        <v>7512834</v>
       </c>
       <c r="F261" s="4" t="s">
         <v>48</v>
@@ -24624,7 +24602,7 @@
         <v>108</v>
       </c>
       <c r="J261" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K261" s="4"/>
       <c r="L261" s="4" t="s">
@@ -24633,11 +24611,11 @@
       <c r="M261" s="4"/>
       <c r="N261" s="4"/>
       <c r="O261" s="4" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="P261" s="5"/>
       <c r="Q261" s="4" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="R261" s="4" t="s">
         <v>55</v>
@@ -24648,12 +24626,8 @@
       <c r="T261" s="4">
         <v>0</v>
       </c>
-      <c r="U261" s="4" t="s">
-        <v>1271</v>
-      </c>
-      <c r="V261" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="U261" s="4"/>
+      <c r="V261" s="4"/>
       <c r="W261" s="4">
         <v>1</v>
       </c>
@@ -24676,16 +24650,16 @@
         <v>1000</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="C262" s="4">
-        <v>162831957</v>
+        <v>162831959</v>
       </c>
       <c r="D262" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E262" s="4">
-        <v>7512834</v>
+        <v>7544244</v>
       </c>
       <c r="F262" s="4" t="s">
         <v>48</v>
@@ -24700,7 +24674,7 @@
         <v>108</v>
       </c>
       <c r="J262" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K262" s="4"/>
       <c r="L262" s="4" t="s">
@@ -24709,14 +24683,14 @@
       <c r="M262" s="4"/>
       <c r="N262" s="4"/>
       <c r="O262" s="4" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="P262" s="5"/>
       <c r="Q262" s="4" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="R262" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S262" s="4">
         <v>0</v>
@@ -24724,13 +24698,17 @@
       <c r="T262" s="4">
         <v>0</v>
       </c>
-      <c r="U262" s="4"/>
-      <c r="V262" s="4"/>
+      <c r="U262" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="V262" s="4" t="s">
+        <v>1094</v>
+      </c>
       <c r="W262" s="4">
         <v>1</v>
       </c>
       <c r="X262" s="4" t="s">
-        <v>121</v>
+        <v>483</v>
       </c>
       <c r="Y262" s="4"/>
       <c r="Z262" s="4" t="s">
@@ -24748,16 +24726,16 @@
         <v>1000</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>1267</v>
+        <v>196</v>
       </c>
       <c r="C263" s="4">
-        <v>162831959</v>
+        <v>162831962</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E263" s="4">
-        <v>7544244</v>
+        <v>7530816</v>
       </c>
       <c r="F263" s="4" t="s">
         <v>48</v>
@@ -24772,7 +24750,7 @@
         <v>108</v>
       </c>
       <c r="J263" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K263" s="4"/>
       <c r="L263" s="4" t="s">
@@ -24781,11 +24759,11 @@
       <c r="M263" s="4"/>
       <c r="N263" s="4"/>
       <c r="O263" s="4" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="P263" s="5"/>
       <c r="Q263" s="4" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="R263" s="4" t="s">
         <v>70</v>
@@ -24796,25 +24774,19 @@
       <c r="T263" s="4">
         <v>0</v>
       </c>
-      <c r="U263" s="4" t="s">
-        <v>1276</v>
-      </c>
-      <c r="V263" s="4" t="s">
-        <v>1100</v>
-      </c>
+      <c r="U263" s="4"/>
+      <c r="V263" s="4"/>
       <c r="W263" s="4">
         <v>1</v>
       </c>
       <c r="X263" s="4" t="s">
-        <v>483</v>
+        <v>121</v>
       </c>
       <c r="Y263" s="4"/>
       <c r="Z263" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA263" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA263" s="4"/>
       <c r="AB263" s="4" t="s">
         <v>46</v>
       </c>
@@ -24824,16 +24796,16 @@
         <v>1000</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>196</v>
+        <v>508</v>
       </c>
       <c r="C264" s="4">
-        <v>162831962</v>
+        <v>162831964</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E264" s="4">
-        <v>7530816</v>
+        <v>7606532</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>48</v>
@@ -24848,7 +24820,7 @@
         <v>108</v>
       </c>
       <c r="J264" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K264" s="4"/>
       <c r="L264" s="4" t="s">
@@ -24857,11 +24829,11 @@
       <c r="M264" s="4"/>
       <c r="N264" s="4"/>
       <c r="O264" s="4" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="P264" s="5"/>
       <c r="Q264" s="4" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="R264" s="4" t="s">
         <v>70</v>
@@ -24897,13 +24869,13 @@
         <v>508</v>
       </c>
       <c r="C265" s="4">
-        <v>162831964</v>
+        <v>162831965</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E265" s="4">
-        <v>7606532</v>
+        <v>7783563</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>48</v>
@@ -24918,7 +24890,7 @@
         <v>108</v>
       </c>
       <c r="J265" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K265" s="4"/>
       <c r="L265" s="4" t="s">
@@ -24927,11 +24899,11 @@
       <c r="M265" s="4"/>
       <c r="N265" s="4"/>
       <c r="O265" s="4" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="P265" s="5"/>
       <c r="Q265" s="4" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="R265" s="4" t="s">
         <v>70</v>
@@ -24952,9 +24924,11 @@
       </c>
       <c r="Y265" s="4"/>
       <c r="Z265" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA265" s="4"/>
+        <v>443</v>
+      </c>
+      <c r="AA265" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="AB265" s="4" t="s">
         <v>46</v>
       </c>
@@ -24967,13 +24941,13 @@
         <v>508</v>
       </c>
       <c r="C266" s="4">
-        <v>162831965</v>
+        <v>162831969</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E266" s="4">
-        <v>7783563</v>
+        <v>7678763</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>48</v>
@@ -24988,7 +24962,7 @@
         <v>108</v>
       </c>
       <c r="J266" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K266" s="4"/>
       <c r="L266" s="4" t="s">
@@ -24997,11 +24971,11 @@
       <c r="M266" s="4"/>
       <c r="N266" s="4"/>
       <c r="O266" s="4" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="P266" s="5"/>
       <c r="Q266" s="4" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="R266" s="4" t="s">
         <v>70</v>
@@ -25018,14 +24992,14 @@
         <v>1</v>
       </c>
       <c r="X266" s="4" t="s">
-        <v>121</v>
+        <v>1279</v>
       </c>
       <c r="Y266" s="4"/>
       <c r="Z266" s="4" t="s">
-        <v>443</v>
+        <v>243</v>
       </c>
       <c r="AA266" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB266" s="4" t="s">
         <v>46</v>
@@ -25036,16 +25010,16 @@
         <v>1000</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>508</v>
+        <v>33</v>
       </c>
       <c r="C267" s="4">
-        <v>162831969</v>
+        <v>162846516</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E267" s="4">
-        <v>7678763</v>
+        <v>6915169</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>48</v>
@@ -25060,7 +25034,7 @@
         <v>108</v>
       </c>
       <c r="J267" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K267" s="4"/>
       <c r="L267" s="4" t="s">
@@ -25069,11 +25043,11 @@
       <c r="M267" s="4"/>
       <c r="N267" s="4"/>
       <c r="O267" s="4" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="P267" s="5"/>
       <c r="Q267" s="4" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="R267" s="4" t="s">
         <v>70</v>
@@ -25090,11 +25064,11 @@
         <v>1</v>
       </c>
       <c r="X267" s="4" t="s">
-        <v>1285</v>
+        <v>44</v>
       </c>
       <c r="Y267" s="4"/>
       <c r="Z267" s="4" t="s">
-        <v>243</v>
+        <v>1282</v>
       </c>
       <c r="AA267" s="4" t="s">
         <v>66</v>
@@ -25111,13 +25085,13 @@
         <v>33</v>
       </c>
       <c r="C268" s="4">
-        <v>162846516</v>
+        <v>162852287</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E268" s="4">
-        <v>6915169</v>
+        <v>7506253</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>48</v>
@@ -25132,7 +25106,7 @@
         <v>108</v>
       </c>
       <c r="J268" s="4" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="K268" s="4"/>
       <c r="L268" s="4" t="s">
@@ -25141,11 +25115,11 @@
       <c r="M268" s="4"/>
       <c r="N268" s="4"/>
       <c r="O268" s="4" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="P268" s="5"/>
       <c r="Q268" s="4" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="R268" s="4" t="s">
         <v>70</v>
@@ -25166,11 +25140,9 @@
       </c>
       <c r="Y268" s="4"/>
       <c r="Z268" s="4" t="s">
-        <v>1288</v>
-      </c>
-      <c r="AA268" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>1285</v>
+      </c>
+      <c r="AA268" s="4"/>
       <c r="AB268" s="4" t="s">
         <v>46</v>
       </c>
@@ -25183,13 +25155,13 @@
         <v>33</v>
       </c>
       <c r="C269" s="4">
-        <v>162852287</v>
+        <v>162583519</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="E269" s="4">
-        <v>7506253</v>
+        <v>4322159</v>
       </c>
       <c r="F269" s="4" t="s">
         <v>48</v>
@@ -25204,7 +25176,7 @@
         <v>108</v>
       </c>
       <c r="J269" s="4" t="s">
-        <v>1268</v>
+        <v>1286</v>
       </c>
       <c r="K269" s="4"/>
       <c r="L269" s="4" t="s">
@@ -25213,34 +25185,36 @@
       <c r="M269" s="4"/>
       <c r="N269" s="4"/>
       <c r="O269" s="4" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="P269" s="5"/>
       <c r="Q269" s="4" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="R269" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S269" s="4">
-        <v>0</v>
+        <v>195227.35</v>
       </c>
       <c r="T269" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U269" s="4"/>
       <c r="V269" s="4"/>
       <c r="W269" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X269" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y269" s="4"/>
       <c r="Z269" s="4" t="s">
-        <v>1291</v>
-      </c>
-      <c r="AA269" s="4"/>
+        <v>1289</v>
+      </c>
+      <c r="AA269" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="AB269" s="4" t="s">
         <v>46</v>
       </c>
@@ -25250,16 +25224,16 @@
         <v>1000</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>33</v>
+        <v>1290</v>
       </c>
       <c r="C270" s="4">
-        <v>162583519</v>
+        <v>162834375</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E270" s="4">
-        <v>4322159</v>
+        <v>7644399</v>
       </c>
       <c r="F270" s="4" t="s">
         <v>48</v>
@@ -25274,7 +25248,7 @@
         <v>108</v>
       </c>
       <c r="J270" s="4" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="K270" s="4"/>
       <c r="L270" s="4" t="s">
@@ -25283,35 +25257,39 @@
       <c r="M270" s="4"/>
       <c r="N270" s="4"/>
       <c r="O270" s="4" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="P270" s="5"/>
       <c r="Q270" s="4" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="R270" s="4" t="s">
         <v>55</v>
       </c>
       <c r="S270" s="4">
-        <v>195227.35</v>
+        <v>0</v>
       </c>
       <c r="T270" s="4">
+        <v>0</v>
+      </c>
+      <c r="U270" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="V270" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="W270" s="4">
         <v>1</v>
       </c>
-      <c r="U270" s="4"/>
-      <c r="V270" s="4"/>
-      <c r="W270" s="4">
-        <v>5</v>
-      </c>
       <c r="X270" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y270" s="4"/>
       <c r="Z270" s="4" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="AA270" s="4" t="s">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="AB270" s="4" t="s">
         <v>46</v>
@@ -25322,16 +25300,16 @@
         <v>1000</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="C271" s="4">
-        <v>162834375</v>
+        <v>162834376</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E271" s="4">
-        <v>7644399</v>
+        <v>6846319</v>
       </c>
       <c r="F271" s="4" t="s">
         <v>48</v>
@@ -25346,7 +25324,7 @@
         <v>108</v>
       </c>
       <c r="J271" s="4" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="K271" s="4"/>
       <c r="L271" s="4" t="s">
@@ -25355,11 +25333,11 @@
       <c r="M271" s="4"/>
       <c r="N271" s="4"/>
       <c r="O271" s="4" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="P271" s="5"/>
       <c r="Q271" s="4" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="R271" s="4" t="s">
         <v>55</v>
@@ -25370,12 +25348,8 @@
       <c r="T271" s="4">
         <v>0</v>
       </c>
-      <c r="U271" s="4" t="s">
-        <v>1299</v>
-      </c>
-      <c r="V271" s="4" t="s">
-        <v>506</v>
-      </c>
+      <c r="U271" s="4"/>
+      <c r="V271" s="4"/>
       <c r="W271" s="4">
         <v>1</v>
       </c>
@@ -25384,7 +25358,7 @@
       </c>
       <c r="Y271" s="4"/>
       <c r="Z271" s="4" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="AA271" s="4" t="s">
         <v>74</v>
@@ -25398,16 +25372,16 @@
         <v>1000</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>1296</v>
+        <v>508</v>
       </c>
       <c r="C272" s="4">
-        <v>162834376</v>
+        <v>162855636</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E272" s="4">
-        <v>6846319</v>
+        <v>7845781</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>48</v>
@@ -25422,7 +25396,7 @@
         <v>108</v>
       </c>
       <c r="J272" s="4" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="K272" s="4"/>
       <c r="L272" s="4" t="s">
@@ -25431,11 +25405,11 @@
       <c r="M272" s="4"/>
       <c r="N272" s="4"/>
       <c r="O272" s="4" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="P272" s="5"/>
       <c r="Q272" s="4" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="R272" s="4" t="s">
         <v>55</v>
@@ -25456,10 +25430,10 @@
       </c>
       <c r="Y272" s="4"/>
       <c r="Z272" s="4" t="s">
-        <v>1303</v>
+        <v>145</v>
       </c>
       <c r="AA272" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB272" s="4" t="s">
         <v>46</v>
@@ -25473,13 +25447,13 @@
         <v>508</v>
       </c>
       <c r="C273" s="4">
-        <v>162855636</v>
+        <v>162855637</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E273" s="4">
-        <v>7845781</v>
+        <v>7636517</v>
       </c>
       <c r="F273" s="4" t="s">
         <v>48</v>
@@ -25494,7 +25468,7 @@
         <v>108</v>
       </c>
       <c r="J273" s="4" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
       <c r="K273" s="4"/>
       <c r="L273" s="4" t="s">
@@ -25503,11 +25477,11 @@
       <c r="M273" s="4"/>
       <c r="N273" s="4"/>
       <c r="O273" s="4" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="P273" s="5"/>
       <c r="Q273" s="4" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="R273" s="4" t="s">
         <v>55</v>
@@ -25528,11 +25502,9 @@
       </c>
       <c r="Y273" s="4"/>
       <c r="Z273" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA273" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="AA273" s="4"/>
       <c r="AB273" s="4" t="s">
         <v>46</v>
       </c>
@@ -25542,16 +25514,16 @@
         <v>1000</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>508</v>
+        <v>33</v>
       </c>
       <c r="C274" s="4">
-        <v>162855637</v>
+        <v>162835500</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E274" s="4">
-        <v>7636517</v>
+        <v>7561877</v>
       </c>
       <c r="F274" s="4" t="s">
         <v>48</v>
@@ -25566,7 +25538,7 @@
         <v>108</v>
       </c>
       <c r="J274" s="4" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="K274" s="4"/>
       <c r="L274" s="4" t="s">
@@ -25575,14 +25547,14 @@
       <c r="M274" s="4"/>
       <c r="N274" s="4"/>
       <c r="O274" s="4" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="P274" s="5"/>
       <c r="Q274" s="4" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="R274" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S274" s="4">
         <v>0</v>
@@ -25596,13 +25568,15 @@
         <v>1</v>
       </c>
       <c r="X274" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y274" s="4"/>
       <c r="Z274" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA274" s="4"/>
+        <v>1305</v>
+      </c>
+      <c r="AA274" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB274" s="4" t="s">
         <v>46</v>
       </c>
@@ -25615,13 +25589,13 @@
         <v>33</v>
       </c>
       <c r="C275" s="4">
-        <v>162835500</v>
+        <v>162690363</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E275" s="4">
-        <v>7561877</v>
+        <v>7544051</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>48</v>
@@ -25636,7 +25610,7 @@
         <v>108</v>
       </c>
       <c r="J275" s="4" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="K275" s="4"/>
       <c r="L275" s="4" t="s">
@@ -25645,11 +25619,11 @@
       <c r="M275" s="4"/>
       <c r="N275" s="4"/>
       <c r="O275" s="4" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="P275" s="5"/>
       <c r="Q275" s="4" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="R275" s="4" t="s">
         <v>70</v>
@@ -25660,21 +25634,23 @@
       <c r="T275" s="4">
         <v>0</v>
       </c>
-      <c r="U275" s="4"/>
-      <c r="V275" s="4"/>
+      <c r="U275" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="V275" s="4" t="s">
+        <v>1094</v>
+      </c>
       <c r="W275" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X275" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y275" s="4"/>
       <c r="Z275" s="4" t="s">
-        <v>1311</v>
-      </c>
-      <c r="AA275" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="AA275" s="4"/>
       <c r="AB275" s="4" t="s">
         <v>46</v>
       </c>
@@ -25684,16 +25660,16 @@
         <v>1000</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>33</v>
+        <v>286</v>
       </c>
       <c r="C276" s="4">
-        <v>162690363</v>
+        <v>162813313</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E276" s="4">
-        <v>7544051</v>
+        <v>6312850</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>48</v>
@@ -25708,7 +25684,7 @@
         <v>108</v>
       </c>
       <c r="J276" s="4" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="K276" s="4"/>
       <c r="L276" s="4" t="s">
@@ -25717,14 +25693,14 @@
       <c r="M276" s="4"/>
       <c r="N276" s="4"/>
       <c r="O276" s="4" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="P276" s="5"/>
       <c r="Q276" s="4" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="R276" s="4" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="S276" s="4">
         <v>0</v>
@@ -25733,20 +25709,20 @@
         <v>0</v>
       </c>
       <c r="U276" s="4" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="V276" s="4" t="s">
-        <v>1100</v>
+        <v>64</v>
       </c>
       <c r="W276" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X276" s="4" t="s">
-        <v>44</v>
+        <v>483</v>
       </c>
       <c r="Y276" s="4"/>
       <c r="Z276" s="4" t="s">
-        <v>165</v>
+        <v>1314</v>
       </c>
       <c r="AA276" s="4"/>
       <c r="AB276" s="4" t="s">
@@ -25758,16 +25734,16 @@
         <v>1000</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>286</v>
+        <v>33</v>
       </c>
       <c r="C277" s="4">
-        <v>162813313</v>
+        <v>162912281</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E277" s="4">
-        <v>6312850</v>
+        <v>1328537</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>48</v>
@@ -25779,16 +25755,18 @@
         <v>108</v>
       </c>
       <c r="I277" s="4" t="s">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="J277" s="4" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="K277" s="4"/>
       <c r="L277" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M277" s="4"/>
+        <v>52</v>
+      </c>
+      <c r="M277" s="4" t="s">
+        <v>1316</v>
+      </c>
       <c r="N277" s="4"/>
       <c r="O277" s="4" t="s">
         <v>1317</v>
@@ -25801,30 +25779,28 @@
         <v>43</v>
       </c>
       <c r="S277" s="4">
-        <v>0</v>
+        <v>61986.87</v>
       </c>
       <c r="T277" s="4">
-        <v>0</v>
-      </c>
-      <c r="U277" s="4" t="s">
-        <v>1319</v>
-      </c>
-      <c r="V277" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="U277" s="4"/>
+      <c r="V277" s="4"/>
       <c r="W277" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X277" s="4" t="s">
-        <v>483</v>
+        <v>44</v>
       </c>
       <c r="Y277" s="4"/>
       <c r="Z277" s="4" t="s">
-        <v>1320</v>
-      </c>
-      <c r="AA277" s="4"/>
+        <v>1319</v>
+      </c>
+      <c r="AA277" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="AB277" s="4" t="s">
-        <v>46</v>
+        <v>302</v>
       </c>
     </row>
     <row r="278" spans="1:28">
@@ -25835,13 +25811,13 @@
         <v>33</v>
       </c>
       <c r="C278" s="4">
-        <v>162912281</v>
+        <v>162835183</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>116</v>
+        <v>1320</v>
       </c>
       <c r="E278" s="4">
-        <v>1328537</v>
+        <v>8377686</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>48</v>
@@ -25853,52 +25829,46 @@
         <v>108</v>
       </c>
       <c r="I278" s="4" t="s">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="J278" s="4" t="s">
         <v>1321</v>
       </c>
       <c r="K278" s="4"/>
-      <c r="L278" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M278" s="4" t="s">
-        <v>1322</v>
-      </c>
+      <c r="L278" s="4"/>
+      <c r="M278" s="4"/>
       <c r="N278" s="4"/>
       <c r="O278" s="4" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="P278" s="5"/>
       <c r="Q278" s="4" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="R278" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="S278" s="4">
-        <v>61986.87</v>
+        <v>0</v>
       </c>
       <c r="T278" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U278" s="4"/>
       <c r="V278" s="4"/>
       <c r="W278" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X278" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y278" s="4"/>
       <c r="Z278" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="AA278" s="4"/>
+      <c r="AB278" s="4" t="s">
         <v>1325</v>
-      </c>
-      <c r="AA278" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB278" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="279" spans="1:28">
@@ -25909,42 +25879,44 @@
         <v>33</v>
       </c>
       <c r="C279" s="4">
-        <v>162835183</v>
+        <v>162859912</v>
       </c>
       <c r="D279" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E279" s="4">
+        <v>7936821</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G279" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H279" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I279" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J279" s="4" t="s">
         <v>1326</v>
       </c>
-      <c r="E279" s="4">
-        <v>8377686</v>
-      </c>
-      <c r="F279" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G279" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H279" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I279" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J279" s="4" t="s">
-        <v>1327</v>
-      </c>
       <c r="K279" s="4"/>
-      <c r="L279" s="4"/>
+      <c r="L279" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="M279" s="4"/>
       <c r="N279" s="4"/>
       <c r="O279" s="4" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="P279" s="5"/>
       <c r="Q279" s="4" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="R279" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S279" s="4">
         <v>0</v>
@@ -25962,11 +25934,13 @@
       </c>
       <c r="Y279" s="4"/>
       <c r="Z279" s="4" t="s">
-        <v>1330</v>
-      </c>
-      <c r="AA279" s="4"/>
+        <v>1329</v>
+      </c>
+      <c r="AA279" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB279" s="4" t="s">
-        <v>1331</v>
+        <v>46</v>
       </c>
     </row>
     <row r="280" spans="1:28">
@@ -25977,13 +25951,13 @@
         <v>33</v>
       </c>
       <c r="C280" s="4">
-        <v>162859912</v>
+        <v>162832014</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="E280" s="4">
-        <v>7936821</v>
+        <v>7957698</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>48</v>
@@ -25998,23 +25972,25 @@
         <v>108</v>
       </c>
       <c r="J280" s="4" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="K280" s="4"/>
       <c r="L280" s="4" t="s">
-        <v>277</v>
+        <v>1331</v>
       </c>
       <c r="M280" s="4"/>
-      <c r="N280" s="4"/>
+      <c r="N280" s="4">
+        <v>40</v>
+      </c>
       <c r="O280" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="P280" s="5"/>
       <c r="Q280" s="4" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="R280" s="4" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="S280" s="4">
         <v>0</v>
@@ -26032,7 +26008,7 @@
       </c>
       <c r="Y280" s="4"/>
       <c r="Z280" s="4" t="s">
-        <v>1335</v>
+        <v>243</v>
       </c>
       <c r="AA280" s="4" t="s">
         <v>66</v>
@@ -26046,16 +26022,16 @@
         <v>1000</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>33</v>
+        <v>258</v>
       </c>
       <c r="C281" s="4">
-        <v>162832014</v>
+        <v>162852725</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="E281" s="4">
-        <v>7957698</v>
+        <v>7111132</v>
       </c>
       <c r="F281" s="4" t="s">
         <v>48</v>
@@ -26070,25 +26046,21 @@
         <v>108</v>
       </c>
       <c r="J281" s="4" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="K281" s="4"/>
-      <c r="L281" s="4" t="s">
-        <v>1337</v>
-      </c>
+      <c r="L281" s="4"/>
       <c r="M281" s="4"/>
-      <c r="N281" s="4">
-        <v>40</v>
-      </c>
+      <c r="N281" s="4"/>
       <c r="O281" s="4" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="P281" s="5"/>
       <c r="Q281" s="4" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="R281" s="4" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="S281" s="4">
         <v>0</v>
@@ -26102,15 +26074,13 @@
         <v>1</v>
       </c>
       <c r="X281" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y281" s="4"/>
       <c r="Z281" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA281" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>1337</v>
+      </c>
+      <c r="AA281" s="4"/>
       <c r="AB281" s="4" t="s">
         <v>46</v>
       </c>
@@ -26120,16 +26090,16 @@
         <v>1000</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>258</v>
+        <v>33</v>
       </c>
       <c r="C282" s="4">
-        <v>162852725</v>
+        <v>162466849</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="E282" s="4">
-        <v>7111132</v>
+        <v>6927785</v>
       </c>
       <c r="F282" s="4" t="s">
         <v>48</v>
@@ -26144,21 +26114,23 @@
         <v>108</v>
       </c>
       <c r="J282" s="4" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="K282" s="4"/>
-      <c r="L282" s="4"/>
+      <c r="L282" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="M282" s="4"/>
       <c r="N282" s="4"/>
       <c r="O282" s="4" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="P282" s="5"/>
       <c r="Q282" s="4" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="R282" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="S282" s="4">
         <v>0</v>
@@ -26169,16 +26141,18 @@
       <c r="U282" s="4"/>
       <c r="V282" s="4"/>
       <c r="W282" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X282" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y282" s="4"/>
       <c r="Z282" s="4" t="s">
-        <v>1343</v>
-      </c>
-      <c r="AA282" s="4"/>
+        <v>703</v>
+      </c>
+      <c r="AA282" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="AB282" s="4" t="s">
         <v>46</v>
       </c>
@@ -26188,16 +26162,16 @@
         <v>1000</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="C283" s="4">
-        <v>162466849</v>
+        <v>162835808</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E283" s="4">
-        <v>6927785</v>
+        <v>5901464</v>
       </c>
       <c r="F283" s="4" t="s">
         <v>48</v>
@@ -26212,7 +26186,7 @@
         <v>108</v>
       </c>
       <c r="J283" s="4" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="K283" s="4"/>
       <c r="L283" s="4" t="s">
@@ -26221,11 +26195,11 @@
       <c r="M283" s="4"/>
       <c r="N283" s="4"/>
       <c r="O283" s="4" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="P283" s="5"/>
       <c r="Q283" s="4" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="R283" s="4" t="s">
         <v>55</v>
@@ -26236,21 +26210,23 @@
       <c r="T283" s="4">
         <v>0</v>
       </c>
-      <c r="U283" s="4"/>
-      <c r="V283" s="4"/>
+      <c r="U283" s="4" t="s">
+        <v>1343</v>
+      </c>
+      <c r="V283" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="W283" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X283" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y283" s="4"/>
       <c r="Z283" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="AA283" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>1344</v>
+      </c>
+      <c r="AA283" s="4"/>
       <c r="AB283" s="4" t="s">
         <v>46</v>
       </c>
@@ -26260,16 +26236,16 @@
         <v>1000</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C284" s="4">
-        <v>162835808</v>
+        <v>162724334</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E284" s="4">
-        <v>5901464</v>
+        <v>6623150</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>48</v>
@@ -26284,14 +26260,18 @@
         <v>108</v>
       </c>
       <c r="J284" s="4" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="K284" s="4"/>
       <c r="L284" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M284" s="4"/>
-      <c r="N284" s="4"/>
+        <v>1346</v>
+      </c>
+      <c r="M284" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N284" s="4">
+        <v>19</v>
+      </c>
       <c r="O284" s="4" t="s">
         <v>1347</v>
       </c>
@@ -26300,7 +26280,7 @@
         <v>1348</v>
       </c>
       <c r="R284" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S284" s="4">
         <v>0</v>
@@ -26308,23 +26288,21 @@
       <c r="T284" s="4">
         <v>0</v>
       </c>
-      <c r="U284" s="4" t="s">
-        <v>1349</v>
-      </c>
-      <c r="V284" s="4" t="s">
-        <v>144</v>
-      </c>
+      <c r="U284" s="4"/>
+      <c r="V284" s="4"/>
       <c r="W284" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X284" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y284" s="4"/>
       <c r="Z284" s="4" t="s">
-        <v>1350</v>
-      </c>
-      <c r="AA284" s="4"/>
+        <v>1349</v>
+      </c>
+      <c r="AA284" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="AB284" s="4" t="s">
         <v>46</v>
       </c>
@@ -26334,16 +26312,16 @@
         <v>1000</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>115</v>
+        <v>33</v>
       </c>
       <c r="C285" s="4">
-        <v>162724334</v>
+        <v>162855617</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E285" s="4">
-        <v>6623150</v>
+        <v>6690107</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>48</v>
@@ -26358,24 +26336,20 @@
         <v>108</v>
       </c>
       <c r="J285" s="4" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="K285" s="4"/>
       <c r="L285" s="4" t="s">
-        <v>1352</v>
-      </c>
-      <c r="M285" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N285" s="4">
-        <v>19</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="M285" s="4"/>
+      <c r="N285" s="4"/>
       <c r="O285" s="4" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="P285" s="5"/>
       <c r="Q285" s="4" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="R285" s="4" t="s">
         <v>70</v>
@@ -26389,17 +26363,17 @@
       <c r="U285" s="4"/>
       <c r="V285" s="4"/>
       <c r="W285" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X285" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y285" s="4"/>
       <c r="Z285" s="4" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="AA285" s="4" t="s">
-        <v>74</v>
+        <v>220</v>
       </c>
       <c r="AB285" s="4" t="s">
         <v>46</v>
@@ -26410,16 +26384,16 @@
         <v>1000</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>33</v>
+        <v>267</v>
       </c>
       <c r="C286" s="4">
-        <v>162855617</v>
+        <v>162451007</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E286" s="4">
-        <v>6690107</v>
+        <v>5903236</v>
       </c>
       <c r="F286" s="4" t="s">
         <v>48</v>
@@ -26434,7 +26408,7 @@
         <v>108</v>
       </c>
       <c r="J286" s="4" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="K286" s="4"/>
       <c r="L286" s="4" t="s">
@@ -26443,35 +26417,35 @@
       <c r="M286" s="4"/>
       <c r="N286" s="4"/>
       <c r="O286" s="4" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="P286" s="5"/>
       <c r="Q286" s="4" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="R286" s="4" t="s">
-        <v>70</v>
+        <v>597</v>
       </c>
       <c r="S286" s="4">
-        <v>0</v>
+        <v>53994.21</v>
       </c>
       <c r="T286" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U286" s="4"/>
       <c r="V286" s="4"/>
       <c r="W286" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X286" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y286" s="4"/>
       <c r="Z286" s="4" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="AA286" s="4" t="s">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="AB286" s="4" t="s">
         <v>46</v>
@@ -26482,16 +26456,16 @@
         <v>1000</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>267</v>
+        <v>1117</v>
       </c>
       <c r="C287" s="4">
-        <v>162451007</v>
+        <v>162466854</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E287" s="4">
-        <v>5903236</v>
+        <v>7548563</v>
       </c>
       <c r="F287" s="4" t="s">
         <v>48</v>
@@ -26506,7 +26480,7 @@
         <v>108</v>
       </c>
       <c r="J287" s="4" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="K287" s="4"/>
       <c r="L287" s="4" t="s">
@@ -26515,36 +26489,38 @@
       <c r="M287" s="4"/>
       <c r="N287" s="4"/>
       <c r="O287" s="4" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="P287" s="5"/>
       <c r="Q287" s="4" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="R287" s="4" t="s">
-        <v>597</v>
+        <v>70</v>
       </c>
       <c r="S287" s="4">
-        <v>53994.21</v>
+        <v>0</v>
       </c>
       <c r="T287" s="4">
-        <v>1</v>
-      </c>
-      <c r="U287" s="4"/>
-      <c r="V287" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U287" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="V287" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="W287" s="4">
         <v>6</v>
       </c>
       <c r="X287" s="4" t="s">
-        <v>121</v>
+        <v>483</v>
       </c>
       <c r="Y287" s="4"/>
       <c r="Z287" s="4" t="s">
-        <v>1363</v>
-      </c>
-      <c r="AA287" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>1362</v>
+      </c>
+      <c r="AA287" s="4"/>
       <c r="AB287" s="4" t="s">
         <v>46</v>
       </c>
@@ -26554,16 +26530,16 @@
         <v>1000</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>1123</v>
+        <v>676</v>
       </c>
       <c r="C288" s="4">
-        <v>162466854</v>
+        <v>162583541</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E288" s="4">
-        <v>7548563</v>
+        <v>7624653</v>
       </c>
       <c r="F288" s="4" t="s">
         <v>48</v>
@@ -26578,7 +26554,7 @@
         <v>108</v>
       </c>
       <c r="J288" s="4" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="K288" s="4"/>
       <c r="L288" s="4" t="s">
@@ -26587,14 +26563,14 @@
       <c r="M288" s="4"/>
       <c r="N288" s="4"/>
       <c r="O288" s="4" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="P288" s="5"/>
       <c r="Q288" s="4" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="R288" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S288" s="4">
         <v>0</v>
@@ -26602,23 +26578,21 @@
       <c r="T288" s="4">
         <v>0</v>
       </c>
-      <c r="U288" s="4" t="s">
-        <v>1367</v>
-      </c>
-      <c r="V288" s="4" t="s">
-        <v>144</v>
-      </c>
+      <c r="U288" s="4"/>
+      <c r="V288" s="4"/>
       <c r="W288" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X288" s="4" t="s">
-        <v>483</v>
+        <v>121</v>
       </c>
       <c r="Y288" s="4"/>
       <c r="Z288" s="4" t="s">
-        <v>1368</v>
-      </c>
-      <c r="AA288" s="4"/>
+        <v>1365</v>
+      </c>
+      <c r="AA288" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB288" s="4" t="s">
         <v>46</v>
       </c>
@@ -26628,16 +26602,16 @@
         <v>1000</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>676</v>
+        <v>33</v>
       </c>
       <c r="C289" s="4">
-        <v>162583541</v>
+        <v>162867011</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E289" s="4">
-        <v>7624653</v>
+        <v>1119534</v>
       </c>
       <c r="F289" s="4" t="s">
         <v>48</v>
@@ -26652,20 +26626,22 @@
         <v>108</v>
       </c>
       <c r="J289" s="4" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="K289" s="4"/>
       <c r="L289" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M289" s="4"/>
+        <v>1367</v>
+      </c>
+      <c r="M289" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="N289" s="4"/>
       <c r="O289" s="4" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="P289" s="5"/>
       <c r="Q289" s="4" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="R289" s="4" t="s">
         <v>55</v>
@@ -26679,14 +26655,14 @@
       <c r="U289" s="4"/>
       <c r="V289" s="4"/>
       <c r="W289" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X289" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y289" s="4"/>
       <c r="Z289" s="4" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="AA289" s="4" t="s">
         <v>66</v>
@@ -26703,13 +26679,13 @@
         <v>33</v>
       </c>
       <c r="C290" s="4">
-        <v>162867011</v>
+        <v>162864408</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E290" s="4">
-        <v>1119534</v>
+        <v>7551212</v>
       </c>
       <c r="F290" s="4" t="s">
         <v>48</v>
@@ -26724,22 +26700,24 @@
         <v>108</v>
       </c>
       <c r="J290" s="4" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="K290" s="4"/>
       <c r="L290" s="4" t="s">
-        <v>1373</v>
+        <v>1161</v>
       </c>
       <c r="M290" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N290" s="4"/>
+        <v>812</v>
+      </c>
+      <c r="N290" s="4">
+        <v>56</v>
+      </c>
       <c r="O290" s="4" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="P290" s="5"/>
       <c r="Q290" s="4" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="R290" s="4" t="s">
         <v>55</v>
@@ -26750,8 +26728,12 @@
       <c r="T290" s="4">
         <v>0</v>
       </c>
-      <c r="U290" s="4"/>
-      <c r="V290" s="4"/>
+      <c r="U290" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="V290" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="W290" s="4">
         <v>1</v>
       </c>
@@ -26760,7 +26742,7 @@
       </c>
       <c r="Y290" s="4"/>
       <c r="Z290" s="4" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="AA290" s="4" t="s">
         <v>66</v>
@@ -26777,13 +26759,13 @@
         <v>33</v>
       </c>
       <c r="C291" s="4">
-        <v>162864408</v>
+        <v>162860854</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>116</v>
       </c>
       <c r="E291" s="4">
-        <v>7551212</v>
+        <v>7694404</v>
       </c>
       <c r="F291" s="4" t="s">
         <v>48</v>
@@ -26798,27 +26780,21 @@
         <v>108</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="K291" s="4"/>
-      <c r="L291" s="4" t="s">
-        <v>1167</v>
-      </c>
-      <c r="M291" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="N291" s="4">
-        <v>56</v>
-      </c>
+      <c r="L291" s="4"/>
+      <c r="M291" s="4"/>
+      <c r="N291" s="4"/>
       <c r="O291" s="4" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="P291" s="5"/>
       <c r="Q291" s="4" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="R291" s="4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="S291" s="4">
         <v>0</v>
@@ -26826,12 +26802,8 @@
       <c r="T291" s="4">
         <v>0</v>
       </c>
-      <c r="U291" s="4" t="s">
-        <v>1379</v>
-      </c>
-      <c r="V291" s="4" t="s">
-        <v>144</v>
-      </c>
+      <c r="U291" s="4"/>
+      <c r="V291" s="4"/>
       <c r="W291" s="4">
         <v>1</v>
       </c>
@@ -26840,10 +26812,10 @@
       </c>
       <c r="Y291" s="4"/>
       <c r="Z291" s="4" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="AA291" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AB291" s="4" t="s">
         <v>46</v>
@@ -26857,13 +26829,13 @@
         <v>33</v>
       </c>
       <c r="C292" s="4">
-        <v>162860854</v>
+        <v>162858857</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="E292" s="4">
-        <v>7694404</v>
+        <v>8275483</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>48</v>
@@ -26878,21 +26850,21 @@
         <v>108</v>
       </c>
       <c r="J292" s="4" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="K292" s="4"/>
       <c r="L292" s="4"/>
       <c r="M292" s="4"/>
       <c r="N292" s="4"/>
       <c r="O292" s="4" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="P292" s="5"/>
       <c r="Q292" s="4" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="R292" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="S292" s="4">
         <v>0</v>
@@ -26910,10 +26882,10 @@
       </c>
       <c r="Y292" s="4"/>
       <c r="Z292" s="4" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="AA292" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB292" s="4" t="s">
         <v>46</v>
@@ -26927,13 +26899,13 @@
         <v>33</v>
       </c>
       <c r="C293" s="4">
-        <v>162858857</v>
+        <v>162899829</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>47</v>
       </c>
       <c r="E293" s="4">
-        <v>8275483</v>
+        <v>7613100</v>
       </c>
       <c r="F293" s="4" t="s">
         <v>48</v>
@@ -26948,21 +26920,23 @@
         <v>108</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="K293" s="4"/>
-      <c r="L293" s="4"/>
+      <c r="L293" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="M293" s="4"/>
       <c r="N293" s="4"/>
       <c r="O293" s="4" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="P293" s="5"/>
       <c r="Q293" s="4" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="R293" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S293" s="4">
         <v>0</v>
@@ -26970,17 +26944,21 @@
       <c r="T293" s="4">
         <v>0</v>
       </c>
-      <c r="U293" s="4"/>
-      <c r="V293" s="4"/>
+      <c r="U293" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="V293" s="4" t="s">
+        <v>224</v>
+      </c>
       <c r="W293" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X293" s="4" t="s">
         <v>44</v>
       </c>
       <c r="Y293" s="4"/>
       <c r="Z293" s="4" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="AA293" s="4" t="s">
         <v>66</v>
@@ -26994,16 +26972,16 @@
         <v>1000</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>33</v>
+        <v>799</v>
       </c>
       <c r="C294" s="4">
-        <v>162899829</v>
+        <v>162460151</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="E294" s="4">
-        <v>7613100</v>
+        <v>8029419</v>
       </c>
       <c r="F294" s="4" t="s">
         <v>48</v>
@@ -27018,23 +26996,21 @@
         <v>108</v>
       </c>
       <c r="J294" s="4" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="K294" s="4"/>
-      <c r="L294" s="4" t="s">
-        <v>277</v>
-      </c>
+      <c r="L294" s="4"/>
       <c r="M294" s="4"/>
       <c r="N294" s="4"/>
       <c r="O294" s="4" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="P294" s="5"/>
       <c r="Q294" s="4" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="R294" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S294" s="4">
         <v>0</v>
@@ -27042,24 +27018,20 @@
       <c r="T294" s="4">
         <v>0</v>
       </c>
-      <c r="U294" s="4" t="s">
-        <v>1392</v>
-      </c>
-      <c r="V294" s="4" t="s">
-        <v>224</v>
-      </c>
+      <c r="U294" s="4"/>
+      <c r="V294" s="4"/>
       <c r="W294" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X294" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y294" s="4"/>
       <c r="Z294" s="4" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="AA294" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AB294" s="4" t="s">
         <v>46</v>
@@ -27070,16 +27042,16 @@
         <v>1000</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>799</v>
+        <v>33</v>
       </c>
       <c r="C295" s="4">
-        <v>162460151</v>
+        <v>162836578</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>116</v>
       </c>
       <c r="E295" s="4">
-        <v>8029419</v>
+        <v>8330879</v>
       </c>
       <c r="F295" s="4" t="s">
         <v>48</v>
@@ -27094,42 +27066,42 @@
         <v>108</v>
       </c>
       <c r="J295" s="4" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="K295" s="4"/>
       <c r="L295" s="4"/>
       <c r="M295" s="4"/>
       <c r="N295" s="4"/>
       <c r="O295" s="4" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P295" s="5"/>
       <c r="Q295" s="4" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="R295" s="4" t="s">
         <v>55</v>
       </c>
       <c r="S295" s="4">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="T295" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U295" s="4"/>
       <c r="V295" s="4"/>
       <c r="W295" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X295" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y295" s="4"/>
       <c r="Z295" s="4" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="AA295" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB295" s="4" t="s">
         <v>46</v>
@@ -27140,16 +27112,16 @@
         <v>1000</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>33</v>
+        <v>676</v>
       </c>
       <c r="C296" s="4">
-        <v>162836578</v>
+        <v>162466864</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E296" s="4">
-        <v>8330879</v>
+        <v>7678758</v>
       </c>
       <c r="F296" s="4" t="s">
         <v>48</v>
@@ -27164,12 +27136,18 @@
         <v>108</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="K296" s="4"/>
-      <c r="L296" s="4"/>
-      <c r="M296" s="4"/>
-      <c r="N296" s="4"/>
+      <c r="L296" s="4" t="s">
+        <v>1396</v>
+      </c>
+      <c r="M296" s="4" t="s">
+        <v>1397</v>
+      </c>
+      <c r="N296" s="4">
+        <v>17</v>
+      </c>
       <c r="O296" s="4" t="s">
         <v>1398</v>
       </c>
@@ -27181,25 +27159,29 @@
         <v>55</v>
       </c>
       <c r="S296" s="4">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="T296" s="4">
-        <v>1</v>
-      </c>
-      <c r="U296" s="4"/>
-      <c r="V296" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U296" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="V296" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="W296" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X296" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y296" s="4"/>
       <c r="Z296" s="4" t="s">
-        <v>1400</v>
+        <v>728</v>
       </c>
       <c r="AA296" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AB296" s="4" t="s">
         <v>46</v>
@@ -27213,13 +27195,13 @@
         <v>676</v>
       </c>
       <c r="C297" s="4">
-        <v>162466864</v>
+        <v>162466863</v>
       </c>
       <c r="D297" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E297" s="4">
-        <v>7678758</v>
+        <v>7801157</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>48</v>
@@ -27234,24 +27216,24 @@
         <v>108</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
       <c r="K297" s="4"/>
       <c r="L297" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="M297" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="N297" s="4">
+        <v>73</v>
+      </c>
+      <c r="O297" s="4" t="s">
         <v>1402</v>
-      </c>
-      <c r="M297" s="4" t="s">
-        <v>1403</v>
-      </c>
-      <c r="N297" s="4">
-        <v>17</v>
-      </c>
-      <c r="O297" s="4" t="s">
-        <v>1404</v>
       </c>
       <c r="P297" s="5"/>
       <c r="Q297" s="4" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="R297" s="4" t="s">
         <v>55</v>
@@ -27263,7 +27245,7 @@
         <v>0</v>
       </c>
       <c r="U297" s="4" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="V297" s="4" t="s">
         <v>144</v>
@@ -27276,10 +27258,10 @@
       </c>
       <c r="Y297" s="4"/>
       <c r="Z297" s="4" t="s">
-        <v>728</v>
+        <v>489</v>
       </c>
       <c r="AA297" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="AB297" s="4" t="s">
         <v>46</v>
@@ -27290,16 +27272,16 @@
         <v>1000</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>676</v>
+        <v>33</v>
       </c>
       <c r="C298" s="4">
-        <v>162466863</v>
+        <v>162845470</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E298" s="4">
-        <v>7801157</v>
+        <v>7963750</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>48</v>
@@ -27314,52 +27296,44 @@
         <v>108</v>
       </c>
       <c r="J298" s="4" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="K298" s="4"/>
       <c r="L298" s="4" t="s">
-        <v>1407</v>
-      </c>
-      <c r="M298" s="4" t="s">
-        <v>1108</v>
-      </c>
-      <c r="N298" s="4">
-        <v>73</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="M298" s="4"/>
+      <c r="N298" s="4"/>
       <c r="O298" s="4" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="P298" s="5"/>
       <c r="Q298" s="4" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="R298" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S298" s="4">
-        <v>0</v>
+        <v>68473.99000000001</v>
       </c>
       <c r="T298" s="4">
-        <v>0</v>
-      </c>
-      <c r="U298" s="4" t="s">
-        <v>1410</v>
-      </c>
-      <c r="V298" s="4" t="s">
-        <v>144</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U298" s="4"/>
+      <c r="V298" s="4"/>
       <c r="W298" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X298" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y298" s="4"/>
       <c r="Z298" s="4" t="s">
-        <v>489</v>
+        <v>1408</v>
       </c>
       <c r="AA298" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AB298" s="4" t="s">
         <v>46</v>
@@ -27370,16 +27344,16 @@
         <v>1000</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>33</v>
+        <v>1261</v>
       </c>
       <c r="C299" s="4">
-        <v>162845470</v>
+        <v>162466871</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E299" s="4">
-        <v>7963750</v>
+        <v>7954906</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>48</v>
@@ -27394,41 +27368,47 @@
         <v>108</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="K299" s="4"/>
       <c r="L299" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M299" s="4"/>
+        <v>1409</v>
+      </c>
+      <c r="M299" s="4" t="s">
+        <v>1410</v>
+      </c>
       <c r="N299" s="4"/>
       <c r="O299" s="4" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="P299" s="5"/>
       <c r="Q299" s="4" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="R299" s="4" t="s">
         <v>70</v>
       </c>
       <c r="S299" s="4">
-        <v>68473.99000000001</v>
+        <v>0</v>
       </c>
       <c r="T299" s="4">
-        <v>1</v>
-      </c>
-      <c r="U299" s="4"/>
-      <c r="V299" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U299" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="V299" s="4" t="s">
+        <v>723</v>
+      </c>
       <c r="W299" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X299" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y299" s="4"/>
       <c r="Z299" s="4" t="s">
-        <v>1414</v>
+        <v>319</v>
       </c>
       <c r="AA299" s="4" t="s">
         <v>74</v>
@@ -27442,16 +27422,16 @@
         <v>1000</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>1267</v>
+        <v>1414</v>
       </c>
       <c r="C300" s="4">
-        <v>162466871</v>
+        <v>162835253</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>139</v>
+        <v>1320</v>
       </c>
       <c r="E300" s="4">
-        <v>7954906</v>
+        <v>8384210</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>48</v>
@@ -27463,28 +27443,24 @@
         <v>108</v>
       </c>
       <c r="I300" s="4" t="s">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="K300" s="4"/>
-      <c r="L300" s="4" t="s">
-        <v>1415</v>
-      </c>
-      <c r="M300" s="4" t="s">
-        <v>1416</v>
-      </c>
+      <c r="L300" s="4"/>
+      <c r="M300" s="4"/>
       <c r="N300" s="4"/>
       <c r="O300" s="4" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="P300" s="5"/>
       <c r="Q300" s="4" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="R300" s="4" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="S300" s="4">
         <v>0</v>
@@ -27492,27 +27468,21 @@
       <c r="T300" s="4">
         <v>0</v>
       </c>
-      <c r="U300" s="4" t="s">
-        <v>1419</v>
-      </c>
-      <c r="V300" s="4" t="s">
-        <v>723</v>
-      </c>
+      <c r="U300" s="4"/>
+      <c r="V300" s="4"/>
       <c r="W300" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X300" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y300" s="4"/>
       <c r="Z300" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="AA300" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>1418</v>
+      </c>
+      <c r="AA300" s="4"/>
       <c r="AB300" s="4" t="s">
-        <v>46</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="301" spans="1:28">
@@ -27520,16 +27490,16 @@
         <v>1000</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="C301" s="4">
-        <v>162835253</v>
+        <v>162835429</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="E301" s="4">
-        <v>8384210</v>
+        <v>8384211</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>48</v>
@@ -27544,18 +27514,18 @@
         <v>288</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="K301" s="4"/>
       <c r="L301" s="4"/>
       <c r="M301" s="4"/>
       <c r="N301" s="4"/>
       <c r="O301" s="4" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="P301" s="5"/>
       <c r="Q301" s="4" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="R301" s="4" t="s">
         <v>43</v>
@@ -27576,11 +27546,11 @@
       </c>
       <c r="Y301" s="4"/>
       <c r="Z301" s="4" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="AA301" s="4"/>
       <c r="AB301" s="4" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="302" spans="1:28">
@@ -27588,16 +27558,16 @@
         <v>1000</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>1420</v>
+        <v>33</v>
       </c>
       <c r="C302" s="4">
-        <v>162835429</v>
+        <v>162856454</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>1326</v>
+        <v>139</v>
       </c>
       <c r="E302" s="4">
-        <v>8384211</v>
+        <v>7059939</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>48</v>
@@ -27612,18 +27582,18 @@
         <v>288</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="K302" s="4"/>
       <c r="L302" s="4"/>
       <c r="M302" s="4"/>
       <c r="N302" s="4"/>
       <c r="O302" s="4" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="P302" s="5"/>
       <c r="Q302" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="R302" s="4" t="s">
         <v>43</v>
@@ -27634,21 +27604,27 @@
       <c r="T302" s="4">
         <v>0</v>
       </c>
-      <c r="U302" s="4"/>
-      <c r="V302" s="4"/>
+      <c r="U302" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="V302" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="W302" s="4">
         <v>1</v>
       </c>
       <c r="X302" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y302" s="4"/>
       <c r="Z302" s="4" t="s">
-        <v>1426</v>
-      </c>
-      <c r="AA302" s="4"/>
+        <v>877</v>
+      </c>
+      <c r="AA302" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="AB302" s="4" t="s">
-        <v>1331</v>
+        <v>46</v>
       </c>
     </row>
     <row r="303" spans="1:28">
@@ -27656,16 +27632,16 @@
         <v>1000</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>33</v>
+        <v>626</v>
       </c>
       <c r="C303" s="4">
-        <v>162856454</v>
+        <v>162831981</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E303" s="4">
-        <v>7059939</v>
+        <v>5907108</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>48</v>
@@ -27677,49 +27653,51 @@
         <v>108</v>
       </c>
       <c r="I303" s="4" t="s">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="K303" s="4"/>
-      <c r="L303" s="4"/>
+      <c r="L303" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="M303" s="4"/>
       <c r="N303" s="4"/>
       <c r="O303" s="4" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="P303" s="5"/>
       <c r="Q303" s="4" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="R303" s="4" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="S303" s="4">
-        <v>0</v>
+        <v>145787.85</v>
       </c>
       <c r="T303" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U303" s="4" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="V303" s="4" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="W303" s="4">
         <v>1</v>
       </c>
       <c r="X303" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y303" s="4"/>
       <c r="Z303" s="4" t="s">
-        <v>877</v>
+        <v>243</v>
       </c>
       <c r="AA303" s="4" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="AB303" s="4" t="s">
         <v>46</v>
@@ -27733,13 +27711,13 @@
         <v>626</v>
       </c>
       <c r="C304" s="4">
-        <v>162831981</v>
+        <v>162831982</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E304" s="4">
-        <v>5907108</v>
+        <v>5927513</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>48</v>
@@ -27754,7 +27732,7 @@
         <v>108</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K304" s="4"/>
       <c r="L304" s="4" t="s">
@@ -27763,27 +27741,23 @@
       <c r="M304" s="4"/>
       <c r="N304" s="4"/>
       <c r="O304" s="4" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="P304" s="5"/>
       <c r="Q304" s="4" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="R304" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S304" s="4">
-        <v>145787.85</v>
+        <v>0</v>
       </c>
       <c r="T304" s="4">
-        <v>1</v>
-      </c>
-      <c r="U304" s="4" t="s">
-        <v>1433</v>
-      </c>
-      <c r="V304" s="4" t="s">
-        <v>195</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U304" s="4"/>
+      <c r="V304" s="4"/>
       <c r="W304" s="4">
         <v>1</v>
       </c>
@@ -27809,13 +27783,13 @@
         <v>626</v>
       </c>
       <c r="C305" s="4">
-        <v>162831982</v>
+        <v>162831986</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E305" s="4">
-        <v>5927513</v>
+        <v>5891688</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>48</v>
@@ -27830,7 +27804,7 @@
         <v>108</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K305" s="4"/>
       <c r="L305" s="4" t="s">
@@ -27839,11 +27813,11 @@
       <c r="M305" s="4"/>
       <c r="N305" s="4"/>
       <c r="O305" s="4" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="P305" s="5"/>
       <c r="Q305" s="4" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="R305" s="4" t="s">
         <v>157</v>
@@ -27878,16 +27852,16 @@
         <v>1000</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>626</v>
+        <v>161</v>
       </c>
       <c r="C306" s="4">
-        <v>162831986</v>
+        <v>162855600</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E306" s="4">
-        <v>5891688</v>
+        <v>5877340</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>48</v>
@@ -27902,7 +27876,7 @@
         <v>108</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K306" s="4"/>
       <c r="L306" s="4" t="s">
@@ -27911,20 +27885,20 @@
       <c r="M306" s="4"/>
       <c r="N306" s="4"/>
       <c r="O306" s="4" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="P306" s="5"/>
       <c r="Q306" s="4" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="R306" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S306" s="4">
-        <v>0</v>
+        <v>119301.34</v>
       </c>
       <c r="T306" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U306" s="4"/>
       <c r="V306" s="4"/>
@@ -27950,16 +27924,16 @@
         <v>1000</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="C307" s="4">
-        <v>162855600</v>
+        <v>162855601</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E307" s="4">
-        <v>5877340</v>
+        <v>4327543</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>48</v>
@@ -27974,7 +27948,7 @@
         <v>108</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K307" s="4"/>
       <c r="L307" s="4" t="s">
@@ -27983,20 +27957,20 @@
       <c r="M307" s="4"/>
       <c r="N307" s="4"/>
       <c r="O307" s="4" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="4" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S307" s="4">
-        <v>119301.34</v>
+        <v>0</v>
       </c>
       <c r="T307" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U307" s="4"/>
       <c r="V307" s="4"/>
@@ -28004,15 +27978,13 @@
         <v>1</v>
       </c>
       <c r="X307" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y307" s="4"/>
       <c r="Z307" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA307" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA307" s="4"/>
       <c r="AB307" s="4" t="s">
         <v>46</v>
       </c>
@@ -28022,16 +27994,16 @@
         <v>1000</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="C308" s="4">
-        <v>162855601</v>
+        <v>162855602</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E308" s="4">
-        <v>4327543</v>
+        <v>5899631</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>48</v>
@@ -28046,7 +28018,7 @@
         <v>108</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K308" s="4"/>
       <c r="L308" s="4" t="s">
@@ -28055,14 +28027,14 @@
       <c r="M308" s="4"/>
       <c r="N308" s="4"/>
       <c r="O308" s="4" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="4" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="R308" s="4" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="S308" s="4">
         <v>0</v>
@@ -28070,19 +28042,25 @@
       <c r="T308" s="4">
         <v>0</v>
       </c>
-      <c r="U308" s="4"/>
-      <c r="V308" s="4"/>
+      <c r="U308" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="V308" s="4" t="s">
+        <v>195</v>
+      </c>
       <c r="W308" s="4">
         <v>1</v>
       </c>
       <c r="X308" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y308" s="4"/>
       <c r="Z308" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA308" s="4"/>
+        <v>1439</v>
+      </c>
+      <c r="AA308" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB308" s="4" t="s">
         <v>46</v>
       </c>
@@ -28092,16 +28070,16 @@
         <v>1000</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="C309" s="4">
-        <v>162855602</v>
+        <v>162855603</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E309" s="4">
-        <v>5899631</v>
+        <v>5933325</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>48</v>
@@ -28116,7 +28094,7 @@
         <v>108</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K309" s="4"/>
       <c r="L309" s="4" t="s">
@@ -28125,36 +28103,36 @@
       <c r="M309" s="4"/>
       <c r="N309" s="4"/>
       <c r="O309" s="4" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="P309" s="5"/>
       <c r="Q309" s="4" t="s">
+        <v>1441</v>
+      </c>
+      <c r="R309" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="S309" s="4">
+        <v>0</v>
+      </c>
+      <c r="T309" s="4">
+        <v>0</v>
+      </c>
+      <c r="U309" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="V309" s="4" t="s">
         <v>1443</v>
-      </c>
-      <c r="R309" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S309" s="4">
-        <v>0</v>
-      </c>
-      <c r="T309" s="4">
-        <v>0</v>
-      </c>
-      <c r="U309" s="4" t="s">
-        <v>1444</v>
-      </c>
-      <c r="V309" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="W309" s="4">
         <v>1</v>
       </c>
       <c r="X309" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y309" s="4"/>
       <c r="Z309" s="4" t="s">
-        <v>1445</v>
+        <v>243</v>
       </c>
       <c r="AA309" s="4" t="s">
         <v>66</v>
@@ -28168,16 +28146,16 @@
         <v>1000</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="C310" s="4">
-        <v>162855603</v>
+        <v>162855604</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E310" s="4">
-        <v>5933325</v>
+        <v>5933018</v>
       </c>
       <c r="F310" s="4" t="s">
         <v>48</v>
@@ -28192,7 +28170,7 @@
         <v>108</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K310" s="4"/>
       <c r="L310" s="4" t="s">
@@ -28201,11 +28179,11 @@
       <c r="M310" s="4"/>
       <c r="N310" s="4"/>
       <c r="O310" s="4" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="4" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="R310" s="4" t="s">
         <v>157</v>
@@ -28217,24 +28195,22 @@
         <v>0</v>
       </c>
       <c r="U310" s="4" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="V310" s="4" t="s">
-        <v>1449</v>
+        <v>195</v>
       </c>
       <c r="W310" s="4">
         <v>1</v>
       </c>
       <c r="X310" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y310" s="4"/>
       <c r="Z310" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA310" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA310" s="4"/>
       <c r="AB310" s="4" t="s">
         <v>46</v>
       </c>
@@ -28244,16 +28220,16 @@
         <v>1000</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="C311" s="4">
-        <v>162855604</v>
+        <v>162855605</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E311" s="4">
-        <v>5933018</v>
+        <v>5363929</v>
       </c>
       <c r="F311" s="4" t="s">
         <v>48</v>
@@ -28268,7 +28244,7 @@
         <v>108</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K311" s="4"/>
       <c r="L311" s="4" t="s">
@@ -28277,32 +28253,32 @@
       <c r="M311" s="4"/>
       <c r="N311" s="4"/>
       <c r="O311" s="4" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="P311" s="5"/>
       <c r="Q311" s="4" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="R311" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S311" s="4">
-        <v>0</v>
+        <v>147950.55</v>
       </c>
       <c r="T311" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U311" s="4" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="V311" s="4" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="W311" s="4">
         <v>1</v>
       </c>
       <c r="X311" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y311" s="4"/>
       <c r="Z311" s="4" t="s">
@@ -28321,13 +28297,13 @@
         <v>33</v>
       </c>
       <c r="C312" s="4">
-        <v>162855605</v>
+        <v>162855607</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E312" s="4">
-        <v>5363929</v>
+        <v>6513947</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>48</v>
@@ -28342,7 +28318,7 @@
         <v>108</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K312" s="4"/>
       <c r="L312" s="4" t="s">
@@ -28351,26 +28327,26 @@
       <c r="M312" s="4"/>
       <c r="N312" s="4"/>
       <c r="O312" s="4" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="4" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="R312" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S312" s="4">
-        <v>147950.55</v>
+        <v>0</v>
       </c>
       <c r="T312" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U312" s="4" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="V312" s="4" t="s">
-        <v>144</v>
+        <v>1443</v>
       </c>
       <c r="W312" s="4">
         <v>1</v>
@@ -28380,9 +28356,11 @@
       </c>
       <c r="Y312" s="4"/>
       <c r="Z312" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA312" s="4"/>
+        <v>243</v>
+      </c>
+      <c r="AA312" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB312" s="4" t="s">
         <v>46</v>
       </c>
@@ -28392,16 +28370,16 @@
         <v>1000</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="C313" s="4">
-        <v>162855607</v>
+        <v>162855608</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E313" s="4">
-        <v>6513947</v>
+        <v>6518662</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>48</v>
@@ -28416,7 +28394,7 @@
         <v>108</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K313" s="4"/>
       <c r="L313" s="4" t="s">
@@ -28425,11 +28403,11 @@
       <c r="M313" s="4"/>
       <c r="N313" s="4"/>
       <c r="O313" s="4" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="P313" s="5"/>
       <c r="Q313" s="4" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="R313" s="4" t="s">
         <v>157</v>
@@ -28441,16 +28419,16 @@
         <v>0</v>
       </c>
       <c r="U313" s="4" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="V313" s="4" t="s">
-        <v>1449</v>
+        <v>72</v>
       </c>
       <c r="W313" s="4">
         <v>1</v>
       </c>
       <c r="X313" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y313" s="4"/>
       <c r="Z313" s="4" t="s">
@@ -28468,16 +28446,16 @@
         <v>1000</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="C314" s="4">
-        <v>162855608</v>
+        <v>162855609</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E314" s="4">
-        <v>6518662</v>
+        <v>6531264</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>48</v>
@@ -28492,7 +28470,7 @@
         <v>108</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K314" s="4"/>
       <c r="L314" s="4" t="s">
@@ -28501,11 +28479,11 @@
       <c r="M314" s="4"/>
       <c r="N314" s="4"/>
       <c r="O314" s="4" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="4" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="R314" s="4" t="s">
         <v>157</v>
@@ -28516,24 +28494,20 @@
       <c r="T314" s="4">
         <v>0</v>
       </c>
-      <c r="U314" s="4" t="s">
-        <v>1461</v>
-      </c>
-      <c r="V314" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="U314" s="4"/>
+      <c r="V314" s="4"/>
       <c r="W314" s="4">
         <v>1</v>
       </c>
       <c r="X314" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y314" s="4"/>
       <c r="Z314" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AA314" s="4" t="s">
-        <v>66</v>
+        <v>247</v>
       </c>
       <c r="AB314" s="4" t="s">
         <v>46</v>
@@ -28547,13 +28521,13 @@
         <v>33</v>
       </c>
       <c r="C315" s="4">
-        <v>162855609</v>
+        <v>162855610</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E315" s="4">
-        <v>6531264</v>
+        <v>6532302</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>48</v>
@@ -28568,7 +28542,7 @@
         <v>108</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K315" s="4"/>
       <c r="L315" s="4" t="s">
@@ -28577,20 +28551,20 @@
       <c r="M315" s="4"/>
       <c r="N315" s="4"/>
       <c r="O315" s="4" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="P315" s="5"/>
       <c r="Q315" s="4" t="s">
-        <v>1460</v>
+        <v>1451</v>
       </c>
       <c r="R315" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S315" s="4">
-        <v>0</v>
+        <v>419845.11</v>
       </c>
       <c r="T315" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U315" s="4"/>
       <c r="V315" s="4"/>
@@ -28616,16 +28590,16 @@
         <v>1000</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="C316" s="4">
-        <v>162855610</v>
+        <v>162855616</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E316" s="4">
-        <v>6532302</v>
+        <v>5880437</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>48</v>
@@ -28640,7 +28614,7 @@
         <v>108</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K316" s="4"/>
       <c r="L316" s="4" t="s">
@@ -28649,35 +28623,39 @@
       <c r="M316" s="4"/>
       <c r="N316" s="4"/>
       <c r="O316" s="4" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="P316" s="5"/>
       <c r="Q316" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="R316" s="4" t="s">
         <v>157</v>
       </c>
       <c r="S316" s="4">
-        <v>419845.11</v>
+        <v>67625.84</v>
       </c>
       <c r="T316" s="4">
         <v>1</v>
       </c>
-      <c r="U316" s="4"/>
-      <c r="V316" s="4"/>
+      <c r="U316" s="4" t="s">
+        <v>1460</v>
+      </c>
+      <c r="V316" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="W316" s="4">
         <v>1</v>
       </c>
       <c r="X316" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y316" s="4"/>
       <c r="Z316" s="4" t="s">
-        <v>246</v>
+        <v>443</v>
       </c>
       <c r="AA316" s="4" t="s">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="AB316" s="4" t="s">
         <v>46</v>
@@ -28688,16 +28666,16 @@
         <v>1000</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="C317" s="4">
-        <v>162855616</v>
+        <v>162855614</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E317" s="4">
-        <v>5880437</v>
+        <v>6530732</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>48</v>
@@ -28712,41 +28690,45 @@
         <v>108</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K317" s="4"/>
       <c r="L317" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M317" s="4"/>
-      <c r="N317" s="4"/>
+        <v>1461</v>
+      </c>
+      <c r="M317" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="N317" s="4">
+        <v>11</v>
+      </c>
       <c r="O317" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="P317" s="5"/>
       <c r="Q317" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="R317" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S317" s="4">
+        <v>0</v>
+      </c>
+      <c r="T317" s="4">
+        <v>0</v>
+      </c>
+      <c r="U317" s="4" t="s">
         <v>1465</v>
       </c>
-      <c r="R317" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="S317" s="4">
-        <v>67625.84</v>
-      </c>
-      <c r="T317" s="4">
-        <v>1</v>
-      </c>
-      <c r="U317" s="4" t="s">
-        <v>1466</v>
-      </c>
       <c r="V317" s="4" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="W317" s="4">
         <v>1</v>
       </c>
       <c r="X317" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y317" s="4"/>
       <c r="Z317" s="4" t="s">
@@ -28767,13 +28749,13 @@
         <v>33</v>
       </c>
       <c r="C318" s="4">
-        <v>162855614</v>
+        <v>162855613</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E318" s="4">
-        <v>6530732</v>
+        <v>6513277</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>48</v>
@@ -28788,36 +28770,36 @@
         <v>108</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K318" s="4"/>
       <c r="L318" s="4" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="M318" s="4" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="N318" s="4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O318" s="4" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="P318" s="5"/>
       <c r="Q318" s="4" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="R318" s="4" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="S318" s="4">
-        <v>0</v>
+        <v>79562.11</v>
       </c>
       <c r="T318" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U318" s="4" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="V318" s="4" t="s">
         <v>72</v>
@@ -28830,10 +28812,10 @@
       </c>
       <c r="Y318" s="4"/>
       <c r="Z318" s="4" t="s">
-        <v>443</v>
+        <v>405</v>
       </c>
       <c r="AA318" s="4" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="AB318" s="4" t="s">
         <v>46</v>
@@ -28847,13 +28829,13 @@
         <v>33</v>
       </c>
       <c r="C319" s="4">
-        <v>162855613</v>
+        <v>162855611</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E319" s="4">
-        <v>6513277</v>
+        <v>6539798</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>48</v>
@@ -28868,39 +28850,39 @@
         <v>108</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K319" s="4"/>
       <c r="L319" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="M319" s="4" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="N319" s="4">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O319" s="4" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="4" t="s">
+        <v>1472</v>
+      </c>
+      <c r="R319" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S319" s="4">
+        <v>0</v>
+      </c>
+      <c r="T319" s="4">
+        <v>0</v>
+      </c>
+      <c r="U319" s="4" t="s">
         <v>1473</v>
       </c>
-      <c r="R319" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="S319" s="4">
-        <v>79562.11</v>
-      </c>
-      <c r="T319" s="4">
-        <v>1</v>
-      </c>
-      <c r="U319" s="4" t="s">
-        <v>1474</v>
-      </c>
       <c r="V319" s="4" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="W319" s="4">
         <v>1</v>
@@ -28910,11 +28892,9 @@
       </c>
       <c r="Y319" s="4"/>
       <c r="Z319" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="AA319" s="4" t="s">
-        <v>190</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AA319" s="4"/>
       <c r="AB319" s="4" t="s">
         <v>46</v>
       </c>
@@ -28927,13 +28907,13 @@
         <v>33</v>
       </c>
       <c r="C320" s="4">
-        <v>162855611</v>
+        <v>162855606</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E320" s="4">
-        <v>6539798</v>
+        <v>5934164</v>
       </c>
       <c r="F320" s="4" t="s">
         <v>48</v>
@@ -28948,24 +28928,24 @@
         <v>108</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K320" s="4"/>
       <c r="L320" s="4" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="M320" s="4" t="s">
-        <v>1476</v>
+        <v>1461</v>
       </c>
       <c r="N320" s="4">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="O320" s="4" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="P320" s="5"/>
       <c r="Q320" s="4" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="R320" s="4" t="s">
         <v>70</v>
@@ -28976,12 +28956,8 @@
       <c r="T320" s="4">
         <v>0</v>
       </c>
-      <c r="U320" s="4" t="s">
-        <v>1479</v>
-      </c>
-      <c r="V320" s="4" t="s">
-        <v>173</v>
-      </c>
+      <c r="U320" s="4"/>
+      <c r="V320" s="4"/>
       <c r="W320" s="4">
         <v>1</v>
       </c>
@@ -28990,9 +28966,11 @@
       </c>
       <c r="Y320" s="4"/>
       <c r="Z320" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="AA320" s="4"/>
+        <v>405</v>
+      </c>
+      <c r="AA320" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="AB320" s="4" t="s">
         <v>46</v>
       </c>
@@ -29005,13 +28983,13 @@
         <v>33</v>
       </c>
       <c r="C321" s="4">
-        <v>162855606</v>
+        <v>162855612</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E321" s="4">
-        <v>5934164</v>
+        <v>6954940</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>48</v>
@@ -29026,24 +29004,24 @@
         <v>108</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K321" s="4"/>
       <c r="L321" s="4" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="M321" s="4" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="N321" s="4">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O321" s="4" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="P321" s="5"/>
       <c r="Q321" s="4" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="R321" s="4" t="s">
         <v>70</v>
@@ -29054,8 +29032,12 @@
       <c r="T321" s="4">
         <v>0</v>
       </c>
-      <c r="U321" s="4"/>
-      <c r="V321" s="4"/>
+      <c r="U321" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="V321" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="W321" s="4">
         <v>1</v>
       </c>
@@ -29064,10 +29046,10 @@
       </c>
       <c r="Y321" s="4"/>
       <c r="Z321" s="4" t="s">
-        <v>405</v>
+        <v>243</v>
       </c>
       <c r="AA321" s="4" t="s">
-        <v>190</v>
+        <v>66</v>
       </c>
       <c r="AB321" s="4" t="s">
         <v>46</v>
@@ -29081,13 +29063,13 @@
         <v>33</v>
       </c>
       <c r="C322" s="4">
-        <v>162855612</v>
+        <v>162855615</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E322" s="4">
-        <v>6954940</v>
+        <v>5886001</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>48</v>
@@ -29102,24 +29084,24 @@
         <v>108</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="K322" s="4"/>
       <c r="L322" s="4" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="M322" s="4" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="N322" s="4">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="O322" s="4" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="P322" s="5"/>
       <c r="Q322" s="4" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="R322" s="4" t="s">
         <v>70</v>
@@ -29130,12 +29112,8 @@
       <c r="T322" s="4">
         <v>0</v>
       </c>
-      <c r="U322" s="4" t="s">
-        <v>1485</v>
-      </c>
-      <c r="V322" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="U322" s="4"/>
+      <c r="V322" s="4"/>
       <c r="W322" s="4">
         <v>1</v>
       </c>
@@ -29161,13 +29139,13 @@
         <v>33</v>
       </c>
       <c r="C323" s="4">
-        <v>162855615</v>
+        <v>162833497</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>139</v>
+        <v>564</v>
       </c>
       <c r="E323" s="4">
-        <v>5886001</v>
+        <v>1012585</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>48</v>
@@ -29182,36 +29160,40 @@
         <v>108</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1430</v>
+        <v>1483</v>
       </c>
       <c r="K323" s="4"/>
       <c r="L323" s="4" t="s">
-        <v>1482</v>
+        <v>518</v>
       </c>
       <c r="M323" s="4" t="s">
-        <v>1486</v>
+        <v>169</v>
       </c>
       <c r="N323" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O323" s="4" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="4" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="R323" s="4" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="S323" s="4">
-        <v>0</v>
+        <v>22335447.38</v>
       </c>
       <c r="T323" s="4">
-        <v>0</v>
-      </c>
-      <c r="U323" s="4"/>
-      <c r="V323" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="U323" s="4" t="s">
+        <v>1486</v>
+      </c>
+      <c r="V323" s="4" t="s">
+        <v>1443</v>
+      </c>
       <c r="W323" s="4">
         <v>1</v>
       </c>
@@ -29220,13 +29202,13 @@
       </c>
       <c r="Y323" s="4"/>
       <c r="Z323" s="4" t="s">
-        <v>243</v>
+        <v>1487</v>
       </c>
       <c r="AA323" s="4" t="s">
-        <v>66</v>
+        <v>220</v>
       </c>
       <c r="AB323" s="4" t="s">
-        <v>46</v>
+        <v>302</v>
       </c>
     </row>
     <row r="324" spans="1:28">
@@ -29237,13 +29219,13 @@
         <v>33</v>
       </c>
       <c r="C324" s="4">
-        <v>162833497</v>
+        <v>162855647</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>564</v>
+        <v>139</v>
       </c>
       <c r="E324" s="4">
-        <v>1012585</v>
+        <v>8288781</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>48</v>
@@ -29255,43 +29237,33 @@
         <v>108</v>
       </c>
       <c r="I324" s="4" t="s">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="J324" s="4" t="s">
+        <v>1488</v>
+      </c>
+      <c r="K324" s="4"/>
+      <c r="L324" s="4"/>
+      <c r="M324" s="4"/>
+      <c r="N324" s="4"/>
+      <c r="O324" s="4" t="s">
         <v>1489</v>
-      </c>
-      <c r="K324" s="4"/>
-      <c r="L324" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="M324" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="N324" s="4">
-        <v>18</v>
-      </c>
-      <c r="O324" s="4" t="s">
-        <v>1490</v>
       </c>
       <c r="P324" s="5"/>
       <c r="Q324" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="R324" s="4" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="S324" s="4">
-        <v>22335447.38</v>
+        <v>0</v>
       </c>
       <c r="T324" s="4">
-        <v>17</v>
-      </c>
-      <c r="U324" s="4" t="s">
-        <v>1492</v>
-      </c>
-      <c r="V324" s="4" t="s">
-        <v>1449</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U324" s="4"/>
+      <c r="V324" s="4"/>
       <c r="W324" s="4">
         <v>1</v>
       </c>
@@ -29300,13 +29272,11 @@
       </c>
       <c r="Y324" s="4"/>
       <c r="Z324" s="4" t="s">
-        <v>1493</v>
-      </c>
-      <c r="AA324" s="4" t="s">
-        <v>220</v>
-      </c>
+        <v>1362</v>
+      </c>
+      <c r="AA324" s="4"/>
       <c r="AB324" s="4" t="s">
-        <v>302</v>
+        <v>46</v>
       </c>
     </row>
     <row r="325" spans="1:28">
@@ -29317,13 +29287,13 @@
         <v>33</v>
       </c>
       <c r="C325" s="4">
-        <v>162855647</v>
+        <v>162855646</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E325" s="4">
-        <v>8288781</v>
+        <v>1108684</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>48</v>
@@ -29338,21 +29308,23 @@
         <v>288</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="K325" s="4"/>
-      <c r="L325" s="4"/>
+      <c r="L325" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="M325" s="4"/>
       <c r="N325" s="4"/>
       <c r="O325" s="4" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="4" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="R325" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S325" s="4">
         <v>0</v>
@@ -29360,8 +29332,12 @@
       <c r="T325" s="4">
         <v>0</v>
       </c>
-      <c r="U325" s="4"/>
-      <c r="V325" s="4"/>
+      <c r="U325" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="V325" s="4" t="s">
+        <v>195</v>
+      </c>
       <c r="W325" s="4">
         <v>1</v>
       </c>
@@ -29370,9 +29346,11 @@
       </c>
       <c r="Y325" s="4"/>
       <c r="Z325" s="4" t="s">
-        <v>1368</v>
-      </c>
-      <c r="AA325" s="4"/>
+        <v>675</v>
+      </c>
+      <c r="AA325" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB325" s="4" t="s">
         <v>46</v>
       </c>
@@ -29382,16 +29360,16 @@
         <v>1000</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>33</v>
+        <v>1140</v>
       </c>
       <c r="C326" s="4">
-        <v>162855646</v>
+        <v>162461734</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E326" s="4">
-        <v>1108684</v>
+        <v>7080342</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>48</v>
@@ -29403,26 +29381,30 @@
         <v>108</v>
       </c>
       <c r="I326" s="4" t="s">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="K326" s="4"/>
       <c r="L326" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M326" s="4"/>
-      <c r="N326" s="4"/>
+        <v>849</v>
+      </c>
+      <c r="M326" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N326" s="4">
+        <v>26</v>
+      </c>
       <c r="O326" s="4" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="P326" s="5"/>
       <c r="Q326" s="4" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="R326" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="S326" s="4">
         <v>0</v>
@@ -29431,20 +29413,20 @@
         <v>0</v>
       </c>
       <c r="U326" s="4" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="V326" s="4" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="W326" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X326" s="4" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="Y326" s="4"/>
       <c r="Z326" s="4" t="s">
-        <v>675</v>
+        <v>1499</v>
       </c>
       <c r="AA326" s="4" t="s">
         <v>66</v>
@@ -29458,16 +29440,16 @@
         <v>1000</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1146</v>
+        <v>258</v>
       </c>
       <c r="C327" s="4">
-        <v>162461734</v>
+        <v>162615258</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="E327" s="4">
-        <v>7080342</v>
+        <v>6540862</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>48</v>
@@ -29482,17 +29464,17 @@
         <v>108</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="K327" s="4"/>
       <c r="L327" s="4" t="s">
-        <v>849</v>
+        <v>760</v>
       </c>
       <c r="M327" s="4" t="s">
-        <v>239</v>
+        <v>1501</v>
       </c>
       <c r="N327" s="4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O327" s="4" t="s">
         <v>1502</v>
@@ -29502,7 +29484,7 @@
         <v>1503</v>
       </c>
       <c r="R327" s="4" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="S327" s="4">
         <v>0</v>
@@ -29514,10 +29496,10 @@
         <v>1504</v>
       </c>
       <c r="V327" s="4" t="s">
-        <v>173</v>
+        <v>1090</v>
       </c>
       <c r="W327" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X327" s="4" t="s">
         <v>121</v>
@@ -29527,7 +29509,7 @@
         <v>1505</v>
       </c>
       <c r="AA327" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AB327" s="4" t="s">
         <v>46</v>
@@ -29538,16 +29520,16 @@
         <v>1000</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>258</v>
+        <v>790</v>
       </c>
       <c r="C328" s="4">
-        <v>162615258</v>
+        <v>162851323</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="E328" s="4">
-        <v>6540862</v>
+        <v>1016479</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>48</v>
@@ -29562,24 +29544,24 @@
         <v>108</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="K328" s="4"/>
       <c r="L328" s="4" t="s">
         <v>760</v>
       </c>
       <c r="M328" s="4" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="N328" s="4">
         <v>19</v>
       </c>
       <c r="O328" s="4" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="P328" s="5"/>
       <c r="Q328" s="4" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="R328" s="4" t="s">
         <v>157</v>
@@ -29591,23 +29573,23 @@
         <v>0</v>
       </c>
       <c r="U328" s="4" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="V328" s="4" t="s">
-        <v>1096</v>
+        <v>57</v>
       </c>
       <c r="W328" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X328" s="4" t="s">
         <v>121</v>
       </c>
       <c r="Y328" s="4"/>
       <c r="Z328" s="4" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="AA328" s="4" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="AB328" s="4" t="s">
         <v>46</v>
@@ -29618,16 +29600,16 @@
         <v>1000</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>790</v>
+        <v>33</v>
       </c>
       <c r="C329" s="4">
-        <v>162851323</v>
+        <v>162835119</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E329" s="4">
-        <v>1016479</v>
+        <v>1024172</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>48</v>
@@ -29642,130 +29624,50 @@
         <v>108</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="K329" s="4"/>
       <c r="L329" s="4" t="s">
-        <v>760</v>
+        <v>920</v>
       </c>
       <c r="M329" s="4" t="s">
-        <v>1507</v>
+        <v>90</v>
       </c>
       <c r="N329" s="4">
-        <v>19</v>
+        <v>380</v>
       </c>
       <c r="O329" s="4" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="P329" s="5"/>
       <c r="Q329" s="4" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="R329" s="4" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="S329" s="4">
-        <v>0</v>
+        <v>4917216.08</v>
       </c>
       <c r="T329" s="4">
-        <v>0</v>
-      </c>
-      <c r="U329" s="4" t="s">
-        <v>1513</v>
-      </c>
-      <c r="V329" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="U329" s="4"/>
+      <c r="V329" s="4"/>
       <c r="W329" s="4">
         <v>1</v>
       </c>
       <c r="X329" s="4" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="Y329" s="4"/>
       <c r="Z329" s="4" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="AA329" s="4" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AB329" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="330" spans="1:28">
-      <c r="A330" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C330" s="4">
-        <v>162835119</v>
-      </c>
-      <c r="D330" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E330" s="4">
-        <v>1024172</v>
-      </c>
-      <c r="F330" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G330" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H330" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I330" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J330" s="4" t="s">
-        <v>1506</v>
-      </c>
-      <c r="K330" s="4"/>
-      <c r="L330" s="4" t="s">
-        <v>920</v>
-      </c>
-      <c r="M330" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="N330" s="4">
-        <v>380</v>
-      </c>
-      <c r="O330" s="4" t="s">
-        <v>1515</v>
-      </c>
-      <c r="P330" s="5"/>
-      <c r="Q330" s="4" t="s">
-        <v>1516</v>
-      </c>
-      <c r="R330" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="S330" s="4">
-        <v>4917216.08</v>
-      </c>
-      <c r="T330" s="4">
-        <v>8</v>
-      </c>
-      <c r="U330" s="4"/>
-      <c r="V330" s="4"/>
-      <c r="W330" s="4">
-        <v>1</v>
-      </c>
-      <c r="X330" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y330" s="4"/>
-      <c r="Z330" s="4" t="s">
-        <v>1517</v>
-      </c>
-      <c r="AA330" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="AB330" s="4" t="s">
         <v>302</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>28/07/2026 a las 11:01:02</t>
+    <t>28/07/2026 a las 11:02:27</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1778">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 17:01:25</t>
+    <t>09/08/2026 a las 18:00:53</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -3953,6 +3953,15 @@
     <t>AGUILAR MESA  ISMAEL ANTONIO</t>
   </si>
   <si>
+    <t>CL 15 CR 14A - 57</t>
+  </si>
+  <si>
+    <t>PEREZ  ARMANDO</t>
+  </si>
+  <si>
+    <t>Inspeccion PQR Peticion SUSPENSION DE BORNERA. Sr ARTURO GAMARRA SENIOR tel. 3054314955 verificar medidor instalado cargas si pertenece al suministro direccion</t>
+  </si>
+  <si>
     <t>CL 15A</t>
   </si>
   <si>
@@ -3963,6 +3972,9 @@
   </si>
   <si>
     <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Senor Arturo Gamarra Senior, cedula 85451625, telefono 3104145858, no aporta correo, en calidad de usuario, no esta de acuerdo con el cobro de materiales emitido en julio 2026, indica que el medidor instalado y la acometida pertenecen al nic 8120774,</t>
+  </si>
+  <si>
+    <t>Inspeccion PQR Reclamo SUSPENSION EN TENDIDO. Senor Arturo Gamarra Senior, cedula 85451625, telefono 3104145858, no aporta correo, en calidad de usuario, no esta de acuerdo con el cobro de materiales emitido en julio 2026, indica que el medidor instalado y la acometida pertenecen al nic 8120774,</t>
   </si>
   <si>
     <t>CL 16A</t>
@@ -5730,7 +5742,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB420"/>
+  <dimension ref="A1:AB422"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -28057,13 +28069,13 @@
         <v>33</v>
       </c>
       <c r="C296" s="4">
-        <v>163589423</v>
+        <v>163664164</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="E296" s="4">
-        <v>1047924</v>
+        <v>8120774</v>
       </c>
       <c r="F296" s="4" t="s">
         <v>51</v>
@@ -28082,42 +28094,44 @@
       </c>
       <c r="K296" s="4"/>
       <c r="L296" s="4" t="s">
-        <v>1312</v>
+        <v>359</v>
       </c>
       <c r="M296" s="4" t="s">
         <v>1307</v>
       </c>
-      <c r="N296" s="4"/>
+      <c r="N296" s="4">
+        <v>57</v>
+      </c>
       <c r="O296" s="4" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="P296" s="5"/>
       <c r="Q296" s="4" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="R296" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S296" s="4">
-        <v>0</v>
+        <v>248038.74</v>
       </c>
       <c r="T296" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U296" s="4"/>
       <c r="V296" s="4"/>
       <c r="W296" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X296" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y296" s="4"/>
       <c r="Z296" s="4" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="AA296" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB296" s="4" t="s">
         <v>49</v>
@@ -28131,13 +28145,13 @@
         <v>33</v>
       </c>
       <c r="C297" s="4">
-        <v>163577122</v>
+        <v>163589423</v>
       </c>
       <c r="D297" s="4" t="s">
         <v>216</v>
       </c>
       <c r="E297" s="4">
-        <v>1048017</v>
+        <v>1047924</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>51</v>
@@ -28156,21 +28170,21 @@
       </c>
       <c r="K297" s="4"/>
       <c r="L297" s="4" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="M297" s="4" t="s">
-        <v>182</v>
+        <v>1307</v>
       </c>
       <c r="N297" s="4"/>
       <c r="O297" s="4" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="P297" s="5"/>
       <c r="Q297" s="4" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="R297" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S297" s="4">
         <v>0</v>
@@ -28181,17 +28195,17 @@
       <c r="U297" s="4"/>
       <c r="V297" s="4"/>
       <c r="W297" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X297" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y297" s="4"/>
       <c r="Z297" s="4" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="AA297" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB297" s="4" t="s">
         <v>49</v>
@@ -28205,13 +28219,13 @@
         <v>33</v>
       </c>
       <c r="C298" s="4">
-        <v>163575858</v>
+        <v>163664193</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="E298" s="4">
-        <v>6915140</v>
+        <v>1047924</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>51</v>
@@ -28230,23 +28244,21 @@
       </c>
       <c r="K298" s="4"/>
       <c r="L298" s="4" t="s">
-        <v>74</v>
+        <v>1315</v>
       </c>
       <c r="M298" s="4" t="s">
-        <v>1320</v>
-      </c>
-      <c r="N298" s="4">
-        <v>15</v>
-      </c>
+        <v>1307</v>
+      </c>
+      <c r="N298" s="4"/>
       <c r="O298" s="4" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="P298" s="5"/>
       <c r="Q298" s="4" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="R298" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S298" s="4">
         <v>0</v>
@@ -28254,21 +28266,17 @@
       <c r="T298" s="4">
         <v>0</v>
       </c>
-      <c r="U298" s="4" t="s">
-        <v>1323</v>
-      </c>
-      <c r="V298" s="4" t="s">
-        <v>402</v>
-      </c>
+      <c r="U298" s="4"/>
+      <c r="V298" s="4"/>
       <c r="W298" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X298" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y298" s="4"/>
       <c r="Z298" s="4" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="AA298" s="4" t="s">
         <v>48</v>
@@ -28285,13 +28293,13 @@
         <v>33</v>
       </c>
       <c r="C299" s="4">
-        <v>163587384</v>
+        <v>163577122</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>216</v>
       </c>
       <c r="E299" s="4">
-        <v>7370282</v>
+        <v>1048017</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>51</v>
@@ -28306,27 +28314,25 @@
         <v>133</v>
       </c>
       <c r="J299" s="4" t="s">
-        <v>1325</v>
+        <v>93</v>
       </c>
       <c r="K299" s="4"/>
       <c r="L299" s="4" t="s">
-        <v>150</v>
+        <v>1320</v>
       </c>
       <c r="M299" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="N299" s="4">
-        <v>60</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N299" s="4"/>
       <c r="O299" s="4" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="P299" s="5"/>
       <c r="Q299" s="4" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="R299" s="4" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="S299" s="4">
         <v>0</v>
@@ -28337,17 +28343,17 @@
       <c r="U299" s="4"/>
       <c r="V299" s="4"/>
       <c r="W299" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X299" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y299" s="4"/>
       <c r="Z299" s="4" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="AA299" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB299" s="4" t="s">
         <v>49</v>
@@ -28361,13 +28367,13 @@
         <v>33</v>
       </c>
       <c r="C300" s="4">
-        <v>163339888</v>
+        <v>163575858</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>233</v>
+        <v>34</v>
       </c>
       <c r="E300" s="4">
-        <v>8013470</v>
+        <v>6915140</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>51</v>
@@ -28382,27 +28388,27 @@
         <v>133</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>1325</v>
+        <v>93</v>
       </c>
       <c r="K300" s="4"/>
       <c r="L300" s="4" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="M300" s="4" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="N300" s="4">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="O300" s="4" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="P300" s="5"/>
       <c r="Q300" s="4" t="s">
-        <v>129</v>
+        <v>1326</v>
       </c>
       <c r="R300" s="4" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="S300" s="4">
         <v>0</v>
@@ -28410,20 +28416,24 @@
       <c r="T300" s="4">
         <v>0</v>
       </c>
-      <c r="U300" s="4"/>
-      <c r="V300" s="4"/>
+      <c r="U300" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="V300" s="4" t="s">
+        <v>402</v>
+      </c>
       <c r="W300" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X300" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y300" s="4"/>
       <c r="Z300" s="4" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="AA300" s="4" t="s">
-        <v>642</v>
+        <v>48</v>
       </c>
       <c r="AB300" s="4" t="s">
         <v>49</v>
@@ -28437,13 +28447,13 @@
         <v>33</v>
       </c>
       <c r="C301" s="4">
-        <v>163598305</v>
+        <v>163587384</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="E301" s="4">
-        <v>7956976</v>
+        <v>7370282</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>51</v>
@@ -28458,27 +28468,27 @@
         <v>133</v>
       </c>
       <c r="J301" s="4" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="K301" s="4"/>
       <c r="L301" s="4" t="s">
-        <v>539</v>
+        <v>150</v>
       </c>
       <c r="M301" s="4" t="s">
-        <v>538</v>
+        <v>109</v>
       </c>
       <c r="N301" s="4">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O301" s="4" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="P301" s="5"/>
       <c r="Q301" s="4" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="R301" s="4" t="s">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="S301" s="4">
         <v>0</v>
@@ -28489,17 +28499,17 @@
       <c r="U301" s="4"/>
       <c r="V301" s="4"/>
       <c r="W301" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X301" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y301" s="4"/>
       <c r="Z301" s="4" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="AA301" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB301" s="4" t="s">
         <v>49</v>
@@ -28510,16 +28520,16 @@
         <v>1000</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>1136</v>
+        <v>33</v>
       </c>
       <c r="C302" s="4">
-        <v>163548983</v>
+        <v>163339888</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="E302" s="4">
-        <v>5366036</v>
+        <v>8013470</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>51</v>
@@ -28534,48 +28544,48 @@
         <v>133</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
       <c r="K302" s="4"/>
       <c r="L302" s="4" t="s">
-        <v>1098</v>
+        <v>109</v>
       </c>
       <c r="M302" s="4" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="N302" s="4">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="O302" s="4" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="P302" s="5"/>
       <c r="Q302" s="4" t="s">
-        <v>1339</v>
+        <v>129</v>
       </c>
       <c r="R302" s="4" t="s">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="S302" s="4">
-        <v>117145.62</v>
+        <v>0</v>
       </c>
       <c r="T302" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U302" s="4"/>
       <c r="V302" s="4"/>
       <c r="W302" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X302" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y302" s="4"/>
       <c r="Z302" s="4" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="AA302" s="4" t="s">
-        <v>142</v>
+        <v>642</v>
       </c>
       <c r="AB302" s="4" t="s">
         <v>49</v>
@@ -28589,13 +28599,13 @@
         <v>33</v>
       </c>
       <c r="C303" s="4">
-        <v>163591755</v>
+        <v>163598305</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>216</v>
+        <v>34</v>
       </c>
       <c r="E303" s="4">
-        <v>1033458</v>
+        <v>7956976</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>51</v>
@@ -28610,31 +28620,33 @@
         <v>133</v>
       </c>
       <c r="J303" s="4" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="K303" s="4"/>
       <c r="L303" s="4" t="s">
-        <v>296</v>
+        <v>539</v>
       </c>
       <c r="M303" s="4" t="s">
-        <v>1342</v>
-      </c>
-      <c r="N303" s="4"/>
+        <v>538</v>
+      </c>
+      <c r="N303" s="4">
+        <v>27</v>
+      </c>
       <c r="O303" s="4" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="P303" s="5"/>
       <c r="Q303" s="4" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
       <c r="R303" s="4" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="S303" s="4">
-        <v>126020.34</v>
+        <v>0</v>
       </c>
       <c r="T303" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U303" s="4"/>
       <c r="V303" s="4"/>
@@ -28646,13 +28658,13 @@
       </c>
       <c r="Y303" s="4"/>
       <c r="Z303" s="4" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="AA303" s="4" t="s">
         <v>66</v>
       </c>
       <c r="AB303" s="4" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
     </row>
     <row r="304" spans="1:28">
@@ -28660,16 +28672,16 @@
         <v>1000</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>1346</v>
+        <v>1136</v>
       </c>
       <c r="C304" s="4">
-        <v>163048919</v>
+        <v>163548983</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E304" s="4">
-        <v>1032436</v>
+        <v>5366036</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>51</v>
@@ -28684,48 +28696,48 @@
         <v>133</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>1347</v>
+        <v>1340</v>
       </c>
       <c r="K304" s="4"/>
       <c r="L304" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M304" s="4"/>
-      <c r="N304" s="4"/>
+        <v>1098</v>
+      </c>
+      <c r="M304" s="4" t="s">
+        <v>1341</v>
+      </c>
+      <c r="N304" s="4">
+        <v>12</v>
+      </c>
       <c r="O304" s="4" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="P304" s="5"/>
       <c r="Q304" s="4" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="R304" s="4" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="S304" s="4">
-        <v>0</v>
+        <v>117145.62</v>
       </c>
       <c r="T304" s="4">
-        <v>0</v>
-      </c>
-      <c r="U304" s="4" t="s">
-        <v>1350</v>
-      </c>
-      <c r="V304" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U304" s="4"/>
+      <c r="V304" s="4"/>
       <c r="W304" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X304" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y304" s="4"/>
       <c r="Z304" s="4" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
       <c r="AA304" s="4" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AB304" s="4" t="s">
         <v>49</v>
@@ -28736,16 +28748,16 @@
         <v>1000</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>351</v>
+        <v>33</v>
       </c>
       <c r="C305" s="4">
-        <v>163048963</v>
+        <v>163591755</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E305" s="4">
-        <v>1329834</v>
+        <v>1033458</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>51</v>
@@ -28760,51 +28772,49 @@
         <v>133</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="K305" s="4"/>
       <c r="L305" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="M305" s="4"/>
+      <c r="M305" s="4" t="s">
+        <v>1346</v>
+      </c>
       <c r="N305" s="4"/>
       <c r="O305" s="4" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="P305" s="5"/>
       <c r="Q305" s="4" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="R305" s="4" t="s">
         <v>92</v>
       </c>
       <c r="S305" s="4">
-        <v>0</v>
+        <v>126020.34</v>
       </c>
       <c r="T305" s="4">
-        <v>0</v>
-      </c>
-      <c r="U305" s="4" t="s">
-        <v>1354</v>
-      </c>
-      <c r="V305" s="4" t="s">
-        <v>333</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U305" s="4"/>
+      <c r="V305" s="4"/>
       <c r="W305" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="X305" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y305" s="4"/>
       <c r="Z305" s="4" t="s">
-        <v>516</v>
+        <v>1349</v>
       </c>
       <c r="AA305" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB305" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="306" spans="1:28">
@@ -28812,16 +28822,16 @@
         <v>1000</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="C306" s="4">
-        <v>163528715</v>
+        <v>163048919</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E306" s="4">
-        <v>7713775</v>
+        <v>1032436</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>51</v>
@@ -28836,7 +28846,7 @@
         <v>133</v>
       </c>
       <c r="J306" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K306" s="4"/>
       <c r="L306" s="4" t="s">
@@ -28845,11 +28855,11 @@
       <c r="M306" s="4"/>
       <c r="N306" s="4"/>
       <c r="O306" s="4" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="P306" s="5"/>
       <c r="Q306" s="4" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="R306" s="4" t="s">
         <v>92</v>
@@ -28861,23 +28871,23 @@
         <v>0</v>
       </c>
       <c r="U306" s="4" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="V306" s="4" t="s">
-        <v>266</v>
+        <v>131</v>
       </c>
       <c r="W306" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="X306" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y306" s="4"/>
       <c r="Z306" s="4" t="s">
-        <v>516</v>
+        <v>1355</v>
       </c>
       <c r="AA306" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB306" s="4" t="s">
         <v>49</v>
@@ -28888,16 +28898,16 @@
         <v>1000</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>521</v>
+        <v>351</v>
       </c>
       <c r="C307" s="4">
-        <v>163568451</v>
+        <v>163048963</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E307" s="4">
-        <v>7691954</v>
+        <v>1329834</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>51</v>
@@ -28912,7 +28922,7 @@
         <v>133</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K307" s="4"/>
       <c r="L307" s="4" t="s">
@@ -28921,35 +28931,39 @@
       <c r="M307" s="4"/>
       <c r="N307" s="4"/>
       <c r="O307" s="4" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="P307" s="5"/>
       <c r="Q307" s="4" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="R307" s="4" t="s">
         <v>92</v>
       </c>
       <c r="S307" s="4">
-        <v>55712.94</v>
+        <v>0</v>
       </c>
       <c r="T307" s="4">
-        <v>1</v>
-      </c>
-      <c r="U307" s="4"/>
-      <c r="V307" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U307" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="V307" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W307" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X307" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y307" s="4"/>
       <c r="Z307" s="4" t="s">
-        <v>1361</v>
+        <v>516</v>
       </c>
       <c r="AA307" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB307" s="4" t="s">
         <v>49</v>
@@ -28960,16 +28974,16 @@
         <v>1000</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>192</v>
+        <v>1359</v>
       </c>
       <c r="C308" s="4">
-        <v>163528668</v>
+        <v>163528715</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E308" s="4">
-        <v>1034070</v>
+        <v>7713775</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>51</v>
@@ -28984,22 +28998,20 @@
         <v>133</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K308" s="4"/>
       <c r="L308" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="M308" s="4" t="s">
-        <v>1362</v>
-      </c>
+      <c r="M308" s="4"/>
       <c r="N308" s="4"/>
       <c r="O308" s="4" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="P308" s="5"/>
       <c r="Q308" s="4" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="R308" s="4" t="s">
         <v>92</v>
@@ -29011,10 +29023,10 @@
         <v>0</v>
       </c>
       <c r="U308" s="4" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="V308" s="4" t="s">
-        <v>581</v>
+        <v>266</v>
       </c>
       <c r="W308" s="4">
         <v>4</v>
@@ -29024,9 +29036,11 @@
       </c>
       <c r="Y308" s="4"/>
       <c r="Z308" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA308" s="4"/>
+        <v>516</v>
+      </c>
+      <c r="AA308" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB308" s="4" t="s">
         <v>49</v>
       </c>
@@ -29036,16 +29050,16 @@
         <v>1000</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>1355</v>
+        <v>521</v>
       </c>
       <c r="C309" s="4">
-        <v>163528713</v>
+        <v>163568451</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E309" s="4">
-        <v>4324140</v>
+        <v>7691954</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>51</v>
@@ -29060,48 +29074,44 @@
         <v>133</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K309" s="4"/>
       <c r="L309" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="M309" s="4" t="s">
-        <v>1366</v>
-      </c>
-      <c r="N309" s="4">
-        <v>33</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M309" s="4"/>
+      <c r="N309" s="4"/>
       <c r="O309" s="4" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="P309" s="5"/>
       <c r="Q309" s="4" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="R309" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S309" s="4">
-        <v>0</v>
+        <v>55712.94</v>
       </c>
       <c r="T309" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U309" s="4"/>
       <c r="V309" s="4"/>
       <c r="W309" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X309" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y309" s="4"/>
       <c r="Z309" s="4" t="s">
-        <v>516</v>
+        <v>1365</v>
       </c>
       <c r="AA309" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB309" s="4" t="s">
         <v>49</v>
@@ -29112,16 +29122,16 @@
         <v>1000</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="C310" s="4">
-        <v>163583084</v>
+        <v>163528668</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E310" s="4">
-        <v>8121618</v>
+        <v>1034070</v>
       </c>
       <c r="F310" s="4" t="s">
         <v>51</v>
@@ -29136,27 +29146,25 @@
         <v>133</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K310" s="4"/>
       <c r="L310" s="4" t="s">
-        <v>552</v>
+        <v>296</v>
       </c>
       <c r="M310" s="4" t="s">
-        <v>1369</v>
-      </c>
-      <c r="N310" s="4">
-        <v>48</v>
-      </c>
+        <v>1366</v>
+      </c>
+      <c r="N310" s="4"/>
       <c r="O310" s="4" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="4" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="R310" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S310" s="4">
         <v>0</v>
@@ -29164,17 +29172,21 @@
       <c r="T310" s="4">
         <v>0</v>
       </c>
-      <c r="U310" s="4"/>
-      <c r="V310" s="4"/>
+      <c r="U310" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="V310" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="W310" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X310" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y310" s="4"/>
       <c r="Z310" s="4" t="s">
-        <v>1372</v>
+        <v>229</v>
       </c>
       <c r="AA310" s="4"/>
       <c r="AB310" s="4" t="s">
@@ -29186,16 +29198,16 @@
         <v>1000</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>33</v>
+        <v>1359</v>
       </c>
       <c r="C311" s="4">
-        <v>163592891</v>
+        <v>163528713</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E311" s="4">
-        <v>7676206</v>
+        <v>4324140</v>
       </c>
       <c r="F311" s="4" t="s">
         <v>51</v>
@@ -29210,24 +29222,24 @@
         <v>133</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K311" s="4"/>
       <c r="L311" s="4" t="s">
-        <v>1373</v>
+        <v>552</v>
       </c>
       <c r="M311" s="4" t="s">
-        <v>1054</v>
+        <v>1370</v>
       </c>
       <c r="N311" s="4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O311" s="4" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="P311" s="5"/>
       <c r="Q311" s="4" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="R311" s="4" t="s">
         <v>185</v>
@@ -29241,17 +29253,17 @@
       <c r="U311" s="4"/>
       <c r="V311" s="4"/>
       <c r="W311" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X311" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y311" s="4"/>
       <c r="Z311" s="4" t="s">
-        <v>1376</v>
+        <v>516</v>
       </c>
       <c r="AA311" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB311" s="4" t="s">
         <v>49</v>
@@ -29262,16 +29274,16 @@
         <v>1000</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>1346</v>
+        <v>33</v>
       </c>
       <c r="C312" s="4">
-        <v>163528706</v>
+        <v>163583084</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E312" s="4">
-        <v>5895750</v>
+        <v>8121618</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>51</v>
@@ -29286,24 +29298,24 @@
         <v>133</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K312" s="4"/>
       <c r="L312" s="4" t="s">
-        <v>1377</v>
+        <v>552</v>
       </c>
       <c r="M312" s="4" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="N312" s="4">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="O312" s="4" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="P312" s="5"/>
       <c r="Q312" s="4" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="R312" s="4" t="s">
         <v>185</v>
@@ -29314,25 +29326,19 @@
       <c r="T312" s="4">
         <v>0</v>
       </c>
-      <c r="U312" s="4" t="s">
-        <v>1381</v>
-      </c>
-      <c r="V312" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="U312" s="4"/>
+      <c r="V312" s="4"/>
       <c r="W312" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X312" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y312" s="4"/>
       <c r="Z312" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA312" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1376</v>
+      </c>
+      <c r="AA312" s="4"/>
       <c r="AB312" s="4" t="s">
         <v>49</v>
       </c>
@@ -29342,16 +29348,16 @@
         <v>1000</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>1355</v>
+        <v>33</v>
       </c>
       <c r="C313" s="4">
-        <v>163528710</v>
+        <v>163592891</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E313" s="4">
-        <v>6804758</v>
+        <v>7676206</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>51</v>
@@ -29366,27 +29372,27 @@
         <v>133</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K313" s="4"/>
       <c r="L313" s="4" t="s">
-        <v>1366</v>
+        <v>1377</v>
       </c>
       <c r="M313" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="N313" s="4">
+        <v>30</v>
+      </c>
+      <c r="O313" s="4" t="s">
         <v>1378</v>
-      </c>
-      <c r="N313" s="4">
-        <v>60</v>
-      </c>
-      <c r="O313" s="4" t="s">
-        <v>1382</v>
       </c>
       <c r="P313" s="5"/>
       <c r="Q313" s="4" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="R313" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S313" s="4">
         <v>0</v>
@@ -29397,17 +29403,17 @@
       <c r="U313" s="4"/>
       <c r="V313" s="4"/>
       <c r="W313" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X313" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y313" s="4"/>
       <c r="Z313" s="4" t="s">
-        <v>516</v>
+        <v>1380</v>
       </c>
       <c r="AA313" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB313" s="4" t="s">
         <v>49</v>
@@ -29418,16 +29424,16 @@
         <v>1000</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="C314" s="4">
-        <v>163528699</v>
+        <v>163528706</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E314" s="4">
-        <v>6585280</v>
+        <v>5895750</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>51</v>
@@ -29442,27 +29448,27 @@
         <v>133</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="K314" s="4"/>
       <c r="L314" s="4" t="s">
-        <v>904</v>
+        <v>1381</v>
       </c>
       <c r="M314" s="4" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="N314" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O314" s="4" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="P314" s="5"/>
       <c r="Q314" s="4" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="R314" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S314" s="4">
         <v>0</v>
@@ -29471,10 +29477,10 @@
         <v>0</v>
       </c>
       <c r="U314" s="4" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="V314" s="4" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="W314" s="4">
         <v>4</v>
@@ -29484,9 +29490,11 @@
       </c>
       <c r="Y314" s="4"/>
       <c r="Z314" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA314" s="4"/>
+        <v>516</v>
+      </c>
+      <c r="AA314" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB314" s="4" t="s">
         <v>49</v>
       </c>
@@ -29496,16 +29504,16 @@
         <v>1000</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>33</v>
+        <v>1359</v>
       </c>
       <c r="C315" s="4">
-        <v>163572236</v>
+        <v>163528710</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E315" s="4">
-        <v>7996679</v>
+        <v>6804758</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>51</v>
@@ -29520,27 +29528,27 @@
         <v>133</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1388</v>
+        <v>1351</v>
       </c>
       <c r="K315" s="4"/>
       <c r="L315" s="4" t="s">
-        <v>539</v>
+        <v>1370</v>
       </c>
       <c r="M315" s="4" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="N315" s="4">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="O315" s="4" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="P315" s="5"/>
       <c r="Q315" s="4" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="R315" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S315" s="4">
         <v>0</v>
@@ -29551,17 +29559,17 @@
       <c r="U315" s="4"/>
       <c r="V315" s="4"/>
       <c r="W315" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X315" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y315" s="4"/>
       <c r="Z315" s="4" t="s">
-        <v>1392</v>
+        <v>516</v>
       </c>
       <c r="AA315" s="4" t="s">
-        <v>797</v>
+        <v>48</v>
       </c>
       <c r="AB315" s="4" t="s">
         <v>49</v>
@@ -29572,16 +29580,16 @@
         <v>1000</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>1162</v>
+        <v>1350</v>
       </c>
       <c r="C316" s="4">
-        <v>163048959</v>
+        <v>163528699</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E316" s="4">
-        <v>7524753</v>
+        <v>6585280</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>51</v>
@@ -29596,20 +29604,24 @@
         <v>133</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1393</v>
+        <v>1351</v>
       </c>
       <c r="K316" s="4"/>
       <c r="L316" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M316" s="4"/>
-      <c r="N316" s="4"/>
+        <v>904</v>
+      </c>
+      <c r="M316" s="4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="N316" s="4">
+        <v>21</v>
+      </c>
       <c r="O316" s="4" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="P316" s="5"/>
       <c r="Q316" s="4" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="R316" s="4" t="s">
         <v>92</v>
@@ -29621,24 +29633,22 @@
         <v>0</v>
       </c>
       <c r="U316" s="4" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="V316" s="4" t="s">
-        <v>581</v>
+        <v>266</v>
       </c>
       <c r="W316" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X316" s="4" t="s">
-        <v>943</v>
+        <v>178</v>
       </c>
       <c r="Y316" s="4"/>
       <c r="Z316" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA316" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="AA316" s="4"/>
       <c r="AB316" s="4" t="s">
         <v>49</v>
       </c>
@@ -29648,16 +29658,16 @@
         <v>1000</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="C317" s="4">
-        <v>163048960</v>
+        <v>163572236</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E317" s="4">
-        <v>7648761</v>
+        <v>7996679</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>51</v>
@@ -29672,51 +29682,51 @@
         <v>133</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="K317" s="4"/>
       <c r="L317" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M317" s="4"/>
-      <c r="N317" s="4"/>
+        <v>539</v>
+      </c>
+      <c r="M317" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="N317" s="4">
+        <v>9</v>
+      </c>
       <c r="O317" s="4" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="P317" s="5"/>
       <c r="Q317" s="4" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="R317" s="4" t="s">
         <v>43</v>
       </c>
       <c r="S317" s="4">
-        <v>23957058.77</v>
+        <v>0</v>
       </c>
       <c r="T317" s="4">
-        <v>72</v>
-      </c>
-      <c r="U317" s="4" t="s">
-        <v>1399</v>
-      </c>
-      <c r="V317" s="4" t="s">
-        <v>581</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U317" s="4"/>
+      <c r="V317" s="4"/>
       <c r="W317" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X317" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y317" s="4"/>
       <c r="Z317" s="4" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="AA317" s="4" t="s">
-        <v>280</v>
+        <v>797</v>
       </c>
       <c r="AB317" s="4" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
     </row>
     <row r="318" spans="1:28">
@@ -29724,16 +29734,16 @@
         <v>1000</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>169</v>
+        <v>1162</v>
       </c>
       <c r="C318" s="4">
-        <v>163048993</v>
+        <v>163048959</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E318" s="4">
-        <v>6537549</v>
+        <v>7524753</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>51</v>
@@ -29748,7 +29758,7 @@
         <v>133</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="K318" s="4"/>
       <c r="L318" s="4" t="s">
@@ -29757,11 +29767,11 @@
       <c r="M318" s="4"/>
       <c r="N318" s="4"/>
       <c r="O318" s="4" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="P318" s="5"/>
       <c r="Q318" s="4" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="R318" s="4" t="s">
         <v>92</v>
@@ -29772,20 +29782,24 @@
       <c r="T318" s="4">
         <v>0</v>
       </c>
-      <c r="U318" s="4"/>
-      <c r="V318" s="4"/>
+      <c r="U318" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="V318" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="W318" s="4">
         <v>10</v>
       </c>
       <c r="X318" s="4" t="s">
-        <v>178</v>
+        <v>943</v>
       </c>
       <c r="Y318" s="4"/>
       <c r="Z318" s="4" t="s">
-        <v>1351</v>
+        <v>516</v>
       </c>
       <c r="AA318" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB318" s="4" t="s">
         <v>49</v>
@@ -29796,16 +29810,16 @@
         <v>1000</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>169</v>
+        <v>536</v>
       </c>
       <c r="C319" s="4">
-        <v>163568460</v>
+        <v>163048960</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E319" s="4">
-        <v>6918208</v>
+        <v>7648761</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>51</v>
@@ -29820,7 +29834,7 @@
         <v>133</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="K319" s="4"/>
       <c r="L319" s="4" t="s">
@@ -29829,42 +29843,42 @@
       <c r="M319" s="4"/>
       <c r="N319" s="4"/>
       <c r="O319" s="4" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="P319" s="5"/>
       <c r="Q319" s="4" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="R319" s="4" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="S319" s="4">
-        <v>0</v>
+        <v>23957058.77</v>
       </c>
       <c r="T319" s="4">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U319" s="4" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="V319" s="4" t="s">
         <v>581</v>
       </c>
       <c r="W319" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X319" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y319" s="4"/>
       <c r="Z319" s="4" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AA319" s="4" t="s">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="AB319" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="320" spans="1:28">
@@ -29872,16 +29886,16 @@
         <v>1000</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>351</v>
+        <v>169</v>
       </c>
       <c r="C320" s="4">
-        <v>163328752</v>
+        <v>163048993</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E320" s="4">
-        <v>7361712</v>
+        <v>6537549</v>
       </c>
       <c r="F320" s="4" t="s">
         <v>51</v>
@@ -29893,25 +29907,23 @@
         <v>133</v>
       </c>
       <c r="I320" s="4" t="s">
-        <v>1407</v>
+        <v>133</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1407</v>
+        <v>1397</v>
       </c>
       <c r="K320" s="4"/>
       <c r="L320" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="M320" s="4" t="s">
-        <v>1408</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M320" s="4"/>
       <c r="N320" s="4"/>
       <c r="O320" s="4" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="P320" s="5"/>
       <c r="Q320" s="4" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="R320" s="4" t="s">
         <v>92</v>
@@ -29922,23 +29934,21 @@
       <c r="T320" s="4">
         <v>0</v>
       </c>
-      <c r="U320" s="4" t="s">
-        <v>1411</v>
-      </c>
-      <c r="V320" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="U320" s="4"/>
+      <c r="V320" s="4"/>
       <c r="W320" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X320" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y320" s="4"/>
       <c r="Z320" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA320" s="4"/>
+        <v>1355</v>
+      </c>
+      <c r="AA320" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="AB320" s="4" t="s">
         <v>49</v>
       </c>
@@ -29948,16 +29958,16 @@
         <v>1000</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="C321" s="4">
-        <v>163456332</v>
+        <v>163568460</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E321" s="4">
-        <v>1056109</v>
+        <v>6918208</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>51</v>
@@ -29969,25 +29979,23 @@
         <v>133</v>
       </c>
       <c r="I321" s="4" t="s">
-        <v>1407</v>
+        <v>133</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1407</v>
+        <v>1397</v>
       </c>
       <c r="K321" s="4"/>
       <c r="L321" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="M321" s="4" t="s">
-        <v>1412</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M321" s="4"/>
       <c r="N321" s="4"/>
       <c r="O321" s="4" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="P321" s="5"/>
       <c r="Q321" s="4" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="R321" s="4" t="s">
         <v>92</v>
@@ -29999,23 +30007,23 @@
         <v>0</v>
       </c>
       <c r="U321" s="4" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="V321" s="4" t="s">
-        <v>45</v>
+        <v>581</v>
       </c>
       <c r="W321" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X321" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y321" s="4"/>
       <c r="Z321" s="4" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="AA321" s="4" t="s">
-        <v>527</v>
+        <v>48</v>
       </c>
       <c r="AB321" s="4" t="s">
         <v>49</v>
@@ -30026,16 +30034,16 @@
         <v>1000</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>1162</v>
+        <v>351</v>
       </c>
       <c r="C322" s="4">
-        <v>163328776</v>
+        <v>163328752</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E322" s="4">
-        <v>1056047</v>
+        <v>7361712</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>51</v>
@@ -30047,25 +30055,25 @@
         <v>133</v>
       </c>
       <c r="I322" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="K322" s="4"/>
       <c r="L322" s="4" t="s">
-        <v>359</v>
+        <v>589</v>
       </c>
       <c r="M322" s="4" t="s">
-        <v>1138</v>
+        <v>1412</v>
       </c>
       <c r="N322" s="4"/>
       <c r="O322" s="4" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="P322" s="5"/>
       <c r="Q322" s="4" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="R322" s="4" t="s">
         <v>92</v>
@@ -30076,8 +30084,12 @@
       <c r="T322" s="4">
         <v>0</v>
       </c>
-      <c r="U322" s="4"/>
-      <c r="V322" s="4"/>
+      <c r="U322" s="4" t="s">
+        <v>1415</v>
+      </c>
+      <c r="V322" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="W322" s="4">
         <v>6</v>
       </c>
@@ -30086,11 +30098,9 @@
       </c>
       <c r="Y322" s="4"/>
       <c r="Z322" s="4" t="s">
-        <v>1351</v>
-      </c>
-      <c r="AA322" s="4" t="s">
-        <v>101</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="AA322" s="4"/>
       <c r="AB322" s="4" t="s">
         <v>49</v>
       </c>
@@ -30100,16 +30110,16 @@
         <v>1000</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>1162</v>
+        <v>33</v>
       </c>
       <c r="C323" s="4">
-        <v>163328778</v>
+        <v>163456332</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E323" s="4">
-        <v>1056058</v>
+        <v>1056109</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>51</v>
@@ -30121,25 +30131,25 @@
         <v>133</v>
       </c>
       <c r="I323" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="K323" s="4"/>
       <c r="L323" s="4" t="s">
-        <v>359</v>
+        <v>630</v>
       </c>
       <c r="M323" s="4" t="s">
-        <v>1042</v>
+        <v>1416</v>
       </c>
       <c r="N323" s="4"/>
       <c r="O323" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="P323" s="5"/>
       <c r="Q323" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="R323" s="4" t="s">
         <v>92</v>
@@ -30150,20 +30160,24 @@
       <c r="T323" s="4">
         <v>0</v>
       </c>
-      <c r="U323" s="4"/>
-      <c r="V323" s="4"/>
+      <c r="U323" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="V323" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="W323" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X323" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y323" s="4"/>
       <c r="Z323" s="4" t="s">
-        <v>505</v>
+        <v>1420</v>
       </c>
       <c r="AA323" s="4" t="s">
-        <v>66</v>
+        <v>527</v>
       </c>
       <c r="AB323" s="4" t="s">
         <v>49</v>
@@ -30174,16 +30188,16 @@
         <v>1000</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>33</v>
+        <v>1162</v>
       </c>
       <c r="C324" s="4">
-        <v>163550126</v>
+        <v>163328776</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>1421</v>
+        <v>170</v>
       </c>
       <c r="E324" s="4">
-        <v>6946045</v>
+        <v>1056047</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>51</v>
@@ -30195,27 +30209,25 @@
         <v>133</v>
       </c>
       <c r="I324" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="K324" s="4"/>
       <c r="L324" s="4" t="s">
         <v>359</v>
       </c>
       <c r="M324" s="4" t="s">
-        <v>1042</v>
-      </c>
-      <c r="N324" s="4">
-        <v>93</v>
-      </c>
+        <v>1138</v>
+      </c>
+      <c r="N324" s="4"/>
       <c r="O324" s="4" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="P324" s="5"/>
       <c r="Q324" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="R324" s="4" t="s">
         <v>92</v>
@@ -30229,17 +30241,17 @@
       <c r="U324" s="4"/>
       <c r="V324" s="4"/>
       <c r="W324" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X324" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y324" s="4"/>
       <c r="Z324" s="4" t="s">
-        <v>1424</v>
+        <v>1355</v>
       </c>
       <c r="AA324" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB324" s="4" t="s">
         <v>49</v>
@@ -30253,13 +30265,13 @@
         <v>1162</v>
       </c>
       <c r="C325" s="4">
-        <v>163328787</v>
+        <v>163328778</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E325" s="4">
-        <v>7667718</v>
+        <v>1056058</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>51</v>
@@ -30271,30 +30283,28 @@
         <v>133</v>
       </c>
       <c r="I325" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="K325" s="4"/>
       <c r="L325" s="4" t="s">
-        <v>709</v>
+        <v>359</v>
       </c>
       <c r="M325" s="4" t="s">
         <v>1042</v>
       </c>
-      <c r="N325" s="4">
-        <v>20</v>
-      </c>
+      <c r="N325" s="4"/>
       <c r="O325" s="4" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="P325" s="5"/>
       <c r="Q325" s="4" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="R325" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S325" s="4">
         <v>0</v>
@@ -30302,12 +30312,8 @@
       <c r="T325" s="4">
         <v>0</v>
       </c>
-      <c r="U325" s="4" t="s">
-        <v>1427</v>
-      </c>
-      <c r="V325" s="4" t="s">
-        <v>469</v>
-      </c>
+      <c r="U325" s="4"/>
+      <c r="V325" s="4"/>
       <c r="W325" s="4">
         <v>6</v>
       </c>
@@ -30333,13 +30339,13 @@
         <v>33</v>
       </c>
       <c r="C326" s="4">
-        <v>163328786</v>
+        <v>163550126</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>170</v>
+        <v>1425</v>
       </c>
       <c r="E326" s="4">
-        <v>1055957</v>
+        <v>6946045</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>51</v>
@@ -30351,25 +30357,27 @@
         <v>133</v>
       </c>
       <c r="I326" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="K326" s="4"/>
       <c r="L326" s="4" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="M326" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="N326" s="4"/>
+        <v>1042</v>
+      </c>
+      <c r="N326" s="4">
+        <v>93</v>
+      </c>
       <c r="O326" s="4" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="P326" s="5"/>
       <c r="Q326" s="4" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="R326" s="4" t="s">
         <v>92</v>
@@ -30383,16 +30391,18 @@
       <c r="U326" s="4"/>
       <c r="V326" s="4"/>
       <c r="W326" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X326" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y326" s="4"/>
       <c r="Z326" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA326" s="4"/>
+        <v>1428</v>
+      </c>
+      <c r="AA326" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB326" s="4" t="s">
         <v>49</v>
       </c>
@@ -30402,16 +30412,16 @@
         <v>1000</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>192</v>
+        <v>1162</v>
       </c>
       <c r="C327" s="4">
-        <v>163429968</v>
+        <v>163328787</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E327" s="4">
-        <v>5875396</v>
+        <v>7667718</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>51</v>
@@ -30423,26 +30433,30 @@
         <v>133</v>
       </c>
       <c r="I327" s="4" t="s">
-        <v>133</v>
+        <v>1411</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1430</v>
+        <v>1411</v>
       </c>
       <c r="K327" s="4"/>
       <c r="L327" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M327" s="4"/>
-      <c r="N327" s="4"/>
+        <v>709</v>
+      </c>
+      <c r="M327" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="N327" s="4">
+        <v>20</v>
+      </c>
       <c r="O327" s="4" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="P327" s="5"/>
       <c r="Q327" s="4" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="R327" s="4" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="S327" s="4">
         <v>0</v>
@@ -30450,20 +30464,24 @@
       <c r="T327" s="4">
         <v>0</v>
       </c>
-      <c r="U327" s="4"/>
-      <c r="V327" s="4"/>
+      <c r="U327" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="V327" s="4" t="s">
+        <v>469</v>
+      </c>
       <c r="W327" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X327" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y327" s="4"/>
       <c r="Z327" s="4" t="s">
-        <v>1433</v>
+        <v>505</v>
       </c>
       <c r="AA327" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB327" s="4" t="s">
         <v>49</v>
@@ -30477,13 +30495,13 @@
         <v>33</v>
       </c>
       <c r="C328" s="4">
-        <v>163425677</v>
+        <v>163328786</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="E328" s="4">
-        <v>7678784</v>
+        <v>1055957</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>51</v>
@@ -30495,26 +30513,28 @@
         <v>133</v>
       </c>
       <c r="I328" s="4" t="s">
-        <v>133</v>
+        <v>1411</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1434</v>
+        <v>1411</v>
       </c>
       <c r="K328" s="4"/>
       <c r="L328" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M328" s="4"/>
+        <v>368</v>
+      </c>
+      <c r="M328" s="4" t="s">
+        <v>709</v>
+      </c>
       <c r="N328" s="4"/>
       <c r="O328" s="4" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="P328" s="5"/>
       <c r="Q328" s="4" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="R328" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S328" s="4">
         <v>0</v>
@@ -30525,18 +30545,16 @@
       <c r="U328" s="4"/>
       <c r="V328" s="4"/>
       <c r="W328" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X328" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y328" s="4"/>
       <c r="Z328" s="4" t="s">
-        <v>880</v>
-      </c>
-      <c r="AA328" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="AA328" s="4"/>
       <c r="AB328" s="4" t="s">
         <v>49</v>
       </c>
@@ -30546,16 +30564,16 @@
         <v>1000</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1346</v>
+        <v>192</v>
       </c>
       <c r="C329" s="4">
-        <v>163568412</v>
+        <v>163429968</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E329" s="4">
-        <v>7673602</v>
+        <v>5875396</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>51</v>
@@ -30579,11 +30597,11 @@
       <c r="M329" s="4"/>
       <c r="N329" s="4"/>
       <c r="O329" s="4" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="P329" s="5"/>
       <c r="Q329" s="4" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="R329" s="4" t="s">
         <v>185</v>
@@ -30597,17 +30615,17 @@
       <c r="U329" s="4"/>
       <c r="V329" s="4"/>
       <c r="W329" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X329" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y329" s="4"/>
       <c r="Z329" s="4" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="AA329" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB329" s="4" t="s">
         <v>49</v>
@@ -30618,16 +30636,16 @@
         <v>1000</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>1346</v>
+        <v>33</v>
       </c>
       <c r="C330" s="4">
-        <v>163568414</v>
+        <v>163425677</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="E330" s="4">
-        <v>7679002</v>
+        <v>7678784</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>51</v>
@@ -30642,7 +30660,7 @@
         <v>133</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="K330" s="4"/>
       <c r="L330" s="4" t="s">
@@ -30651,11 +30669,11 @@
       <c r="M330" s="4"/>
       <c r="N330" s="4"/>
       <c r="O330" s="4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="P330" s="5"/>
       <c r="Q330" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="R330" s="4" t="s">
         <v>185</v>
@@ -30669,14 +30687,14 @@
       <c r="U330" s="4"/>
       <c r="V330" s="4"/>
       <c r="W330" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X330" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y330" s="4"/>
       <c r="Z330" s="4" t="s">
-        <v>1442</v>
+        <v>880</v>
       </c>
       <c r="AA330" s="4" t="s">
         <v>48</v>
@@ -30690,16 +30708,16 @@
         <v>1000</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>33</v>
+        <v>1350</v>
       </c>
       <c r="C331" s="4">
-        <v>163574967</v>
+        <v>163568412</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E331" s="4">
-        <v>7678784</v>
+        <v>7673602</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>51</v>
@@ -30714,7 +30732,7 @@
         <v>133</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
@@ -30723,11 +30741,11 @@
       <c r="M331" s="4"/>
       <c r="N331" s="4"/>
       <c r="O331" s="4" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="4" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="R331" s="4" t="s">
         <v>185</v>
@@ -30744,14 +30762,14 @@
         <v>3</v>
       </c>
       <c r="X331" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y331" s="4"/>
       <c r="Z331" s="4" t="s">
         <v>1443</v>
       </c>
       <c r="AA331" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB331" s="4" t="s">
         <v>49</v>
@@ -30762,16 +30780,16 @@
         <v>1000</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>33</v>
+        <v>1350</v>
       </c>
       <c r="C332" s="4">
-        <v>163583525</v>
+        <v>163568414</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E332" s="4">
-        <v>7584651</v>
+        <v>7679002</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>51</v>
@@ -30786,7 +30804,7 @@
         <v>133</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="K332" s="4"/>
       <c r="L332" s="4" t="s">
@@ -30802,7 +30820,7 @@
         <v>1445</v>
       </c>
       <c r="R332" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S332" s="4">
         <v>0</v>
@@ -30810,24 +30828,20 @@
       <c r="T332" s="4">
         <v>0</v>
       </c>
-      <c r="U332" s="4" t="s">
-        <v>1446</v>
-      </c>
-      <c r="V332" s="4" t="s">
-        <v>266</v>
-      </c>
+      <c r="U332" s="4"/>
+      <c r="V332" s="4"/>
       <c r="W332" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X332" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y332" s="4"/>
       <c r="Z332" s="4" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="AA332" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB332" s="4" t="s">
         <v>49</v>
@@ -30838,16 +30852,16 @@
         <v>1000</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>1355</v>
+        <v>33</v>
       </c>
       <c r="C333" s="4">
-        <v>163568418</v>
+        <v>163574967</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E333" s="4">
-        <v>6571789</v>
+        <v>7678784</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>51</v>
@@ -30862,7 +30876,7 @@
         <v>133</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
       <c r="K333" s="4"/>
       <c r="L333" s="4" t="s">
@@ -30871,14 +30885,14 @@
       <c r="M333" s="4"/>
       <c r="N333" s="4"/>
       <c r="O333" s="4" t="s">
-        <v>1449</v>
+        <v>1439</v>
       </c>
       <c r="P333" s="5"/>
       <c r="Q333" s="4" t="s">
-        <v>1450</v>
+        <v>1440</v>
       </c>
       <c r="R333" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S333" s="4">
         <v>0</v>
@@ -30892,11 +30906,11 @@
         <v>3</v>
       </c>
       <c r="X333" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y333" s="4"/>
       <c r="Z333" s="4" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="AA333" s="4" t="s">
         <v>48</v>
@@ -30910,16 +30924,16 @@
         <v>1000</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1355</v>
+        <v>33</v>
       </c>
       <c r="C334" s="4">
-        <v>163568419</v>
+        <v>163583525</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E334" s="4">
-        <v>7089749</v>
+        <v>7584651</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>51</v>
@@ -30934,7 +30948,7 @@
         <v>133</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
       <c r="K334" s="4"/>
       <c r="L334" s="4" t="s">
@@ -30943,35 +30957,39 @@
       <c r="M334" s="4"/>
       <c r="N334" s="4"/>
       <c r="O334" s="4" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="4" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="R334" s="4" t="s">
         <v>92</v>
       </c>
       <c r="S334" s="4">
-        <v>191660.62</v>
+        <v>0</v>
       </c>
       <c r="T334" s="4">
-        <v>1</v>
-      </c>
-      <c r="U334" s="4"/>
-      <c r="V334" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U334" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="V334" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="W334" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X334" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y334" s="4"/>
       <c r="Z334" s="4" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="AA334" s="4" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="AB334" s="4" t="s">
         <v>49</v>
@@ -30982,16 +31000,16 @@
         <v>1000</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="C335" s="4">
-        <v>163568420</v>
+        <v>163568418</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E335" s="4">
-        <v>4325969</v>
+        <v>6571789</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>51</v>
@@ -31006,7 +31024,7 @@
         <v>133</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="K335" s="4"/>
       <c r="L335" s="4" t="s">
@@ -31015,11 +31033,11 @@
       <c r="M335" s="4"/>
       <c r="N335" s="4"/>
       <c r="O335" s="4" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="P335" s="5"/>
       <c r="Q335" s="4" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="R335" s="4" t="s">
         <v>92</v>
@@ -31030,12 +31048,8 @@
       <c r="T335" s="4">
         <v>0</v>
       </c>
-      <c r="U335" s="4" t="s">
-        <v>1457</v>
-      </c>
-      <c r="V335" s="4" t="s">
-        <v>581</v>
-      </c>
+      <c r="U335" s="4"/>
+      <c r="V335" s="4"/>
       <c r="W335" s="4">
         <v>3</v>
       </c>
@@ -31044,10 +31058,10 @@
       </c>
       <c r="Y335" s="4"/>
       <c r="Z335" s="4" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="AA335" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB335" s="4" t="s">
         <v>49</v>
@@ -31058,16 +31072,16 @@
         <v>1000</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="C336" s="4">
-        <v>163568422</v>
+        <v>163568419</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E336" s="4">
-        <v>7033295</v>
+        <v>7089749</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>51</v>
@@ -31082,7 +31096,7 @@
         <v>133</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="K336" s="4"/>
       <c r="L336" s="4" t="s">
@@ -31091,20 +31105,20 @@
       <c r="M336" s="4"/>
       <c r="N336" s="4"/>
       <c r="O336" s="4" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="P336" s="5"/>
       <c r="Q336" s="4" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="R336" s="4" t="s">
         <v>92</v>
       </c>
       <c r="S336" s="4">
-        <v>0</v>
+        <v>191660.62</v>
       </c>
       <c r="T336" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U336" s="4"/>
       <c r="V336" s="4"/>
@@ -31116,10 +31130,10 @@
       </c>
       <c r="Y336" s="4"/>
       <c r="Z336" s="4" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="AA336" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB336" s="4" t="s">
         <v>49</v>
@@ -31130,16 +31144,16 @@
         <v>1000</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>824</v>
+        <v>1359</v>
       </c>
       <c r="C337" s="4">
-        <v>163568454</v>
+        <v>163568420</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E337" s="4">
-        <v>6914875</v>
+        <v>4325969</v>
       </c>
       <c r="F337" s="4" t="s">
         <v>51</v>
@@ -31154,7 +31168,7 @@
         <v>133</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1462</v>
+        <v>1452</v>
       </c>
       <c r="K337" s="4"/>
       <c r="L337" s="4" t="s">
@@ -31163,14 +31177,14 @@
       <c r="M337" s="4"/>
       <c r="N337" s="4"/>
       <c r="O337" s="4" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="P337" s="5"/>
       <c r="Q337" s="4" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="R337" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S337" s="4">
         <v>0</v>
@@ -31179,10 +31193,10 @@
         <v>0</v>
       </c>
       <c r="U337" s="4" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="V337" s="4" t="s">
-        <v>333</v>
+        <v>581</v>
       </c>
       <c r="W337" s="4">
         <v>3</v>
@@ -31192,7 +31206,7 @@
       </c>
       <c r="Y337" s="4"/>
       <c r="Z337" s="4" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="AA337" s="4" t="s">
         <v>66</v>
@@ -31206,16 +31220,16 @@
         <v>1000</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>33</v>
+        <v>1359</v>
       </c>
       <c r="C338" s="4">
-        <v>163529327</v>
+        <v>163568422</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>248</v>
+        <v>170</v>
       </c>
       <c r="E338" s="4">
-        <v>8377686</v>
+        <v>7033295</v>
       </c>
       <c r="F338" s="4" t="s">
         <v>51</v>
@@ -31230,18 +31244,20 @@
         <v>133</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1467</v>
+        <v>1452</v>
       </c>
       <c r="K338" s="4"/>
-      <c r="L338" s="4"/>
+      <c r="L338" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M338" s="4"/>
       <c r="N338" s="4"/>
       <c r="O338" s="4" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="P338" s="5"/>
       <c r="Q338" s="4" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="R338" s="4" t="s">
         <v>92</v>
@@ -31255,18 +31271,20 @@
       <c r="U338" s="4"/>
       <c r="V338" s="4"/>
       <c r="W338" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X338" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y338" s="4"/>
       <c r="Z338" s="4" t="s">
-        <v>1470</v>
-      </c>
-      <c r="AA338" s="4"/>
+        <v>1465</v>
+      </c>
+      <c r="AA338" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB338" s="4" t="s">
-        <v>253</v>
+        <v>49</v>
       </c>
     </row>
     <row r="339" spans="1:28">
@@ -31277,13 +31295,13 @@
         <v>824</v>
       </c>
       <c r="C339" s="4">
-        <v>163568469</v>
+        <v>163568454</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E339" s="4">
-        <v>4322512</v>
+        <v>6914875</v>
       </c>
       <c r="F339" s="4" t="s">
         <v>51</v>
@@ -31298,7 +31316,7 @@
         <v>133</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="K339" s="4"/>
       <c r="L339" s="4" t="s">
@@ -31307,11 +31325,11 @@
       <c r="M339" s="4"/>
       <c r="N339" s="4"/>
       <c r="O339" s="4" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="4" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="R339" s="4" t="s">
         <v>185</v>
@@ -31322,8 +31340,12 @@
       <c r="T339" s="4">
         <v>0</v>
       </c>
-      <c r="U339" s="4"/>
-      <c r="V339" s="4"/>
+      <c r="U339" s="4" t="s">
+        <v>1469</v>
+      </c>
+      <c r="V339" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W339" s="4">
         <v>3</v>
       </c>
@@ -31332,9 +31354,11 @@
       </c>
       <c r="Y339" s="4"/>
       <c r="Z339" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="AA339" s="4"/>
+        <v>1470</v>
+      </c>
+      <c r="AA339" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB339" s="4" t="s">
         <v>49</v>
       </c>
@@ -31347,13 +31371,13 @@
         <v>33</v>
       </c>
       <c r="C340" s="4">
-        <v>163034344</v>
+        <v>163529327</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>50</v>
+        <v>248</v>
       </c>
       <c r="E340" s="4">
-        <v>8376943</v>
+        <v>8377686</v>
       </c>
       <c r="F340" s="4" t="s">
         <v>51</v>
@@ -31368,18 +31392,18 @@
         <v>133</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="K340" s="4"/>
       <c r="L340" s="4"/>
       <c r="M340" s="4"/>
       <c r="N340" s="4"/>
       <c r="O340" s="4" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="P340" s="5"/>
       <c r="Q340" s="4" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="R340" s="4" t="s">
         <v>92</v>
@@ -31393,18 +31417,18 @@
       <c r="U340" s="4"/>
       <c r="V340" s="4"/>
       <c r="W340" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="X340" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y340" s="4"/>
       <c r="Z340" s="4" t="s">
-        <v>77</v>
+        <v>1474</v>
       </c>
       <c r="AA340" s="4"/>
       <c r="AB340" s="4" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
     </row>
     <row r="341" spans="1:28">
@@ -31412,16 +31436,16 @@
         <v>1000</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>33</v>
+        <v>824</v>
       </c>
       <c r="C341" s="4">
-        <v>163585695</v>
+        <v>163568469</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E341" s="4">
-        <v>7216255</v>
+        <v>4322512</v>
       </c>
       <c r="F341" s="4" t="s">
         <v>51</v>
@@ -31436,7 +31460,7 @@
         <v>133</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="K341" s="4"/>
       <c r="L341" s="4" t="s">
@@ -31445,14 +31469,14 @@
       <c r="M341" s="4"/>
       <c r="N341" s="4"/>
       <c r="O341" s="4" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="P341" s="5"/>
       <c r="Q341" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="R341" s="4" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="S341" s="4">
         <v>0</v>
@@ -31463,18 +31487,16 @@
       <c r="U341" s="4"/>
       <c r="V341" s="4"/>
       <c r="W341" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X341" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y341" s="4"/>
       <c r="Z341" s="4" t="s">
-        <v>1479</v>
-      </c>
-      <c r="AA341" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>953</v>
+      </c>
+      <c r="AA341" s="4"/>
       <c r="AB341" s="4" t="s">
         <v>49</v>
       </c>
@@ -31487,13 +31509,13 @@
         <v>33</v>
       </c>
       <c r="C342" s="4">
-        <v>163595690</v>
+        <v>163034344</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>216</v>
+        <v>50</v>
       </c>
       <c r="E342" s="4">
-        <v>7111159</v>
+        <v>8376943</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>51</v>
@@ -31508,23 +31530,21 @@
         <v>133</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="K342" s="4"/>
-      <c r="L342" s="4" t="s">
-        <v>296</v>
-      </c>
+      <c r="L342" s="4"/>
       <c r="M342" s="4"/>
       <c r="N342" s="4"/>
       <c r="O342" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="R342" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S342" s="4">
         <v>0</v>
@@ -31532,25 +31552,19 @@
       <c r="T342" s="4">
         <v>0</v>
       </c>
-      <c r="U342" s="4" t="s">
-        <v>1482</v>
-      </c>
-      <c r="V342" s="4" t="s">
-        <v>581</v>
-      </c>
+      <c r="U342" s="4"/>
+      <c r="V342" s="4"/>
       <c r="W342" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X342" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y342" s="4"/>
       <c r="Z342" s="4" t="s">
-        <v>1483</v>
-      </c>
-      <c r="AA342" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="AA342" s="4"/>
       <c r="AB342" s="4" t="s">
         <v>49</v>
       </c>
@@ -31563,13 +31577,13 @@
         <v>33</v>
       </c>
       <c r="C343" s="4">
-        <v>163594532</v>
+        <v>163585695</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E343" s="4">
-        <v>8382163</v>
+        <v>7216255</v>
       </c>
       <c r="F343" s="4" t="s">
         <v>51</v>
@@ -31584,21 +31598,23 @@
         <v>133</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="K343" s="4"/>
-      <c r="L343" s="4"/>
+      <c r="L343" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M343" s="4"/>
       <c r="N343" s="4"/>
       <c r="O343" s="4" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="4" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="R343" s="4" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="S343" s="4">
         <v>0</v>
@@ -31609,16 +31625,18 @@
       <c r="U343" s="4"/>
       <c r="V343" s="4"/>
       <c r="W343" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X343" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y343" s="4"/>
       <c r="Z343" s="4" t="s">
-        <v>1487</v>
-      </c>
-      <c r="AA343" s="4"/>
+        <v>1483</v>
+      </c>
+      <c r="AA343" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB343" s="4" t="s">
         <v>49</v>
       </c>
@@ -31631,13 +31649,13 @@
         <v>33</v>
       </c>
       <c r="C344" s="4">
-        <v>163588829</v>
+        <v>163595690</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="E344" s="4">
-        <v>1053551</v>
+        <v>7111159</v>
       </c>
       <c r="F344" s="4" t="s">
         <v>51</v>
@@ -31652,27 +31670,23 @@
         <v>133</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1488</v>
+        <v>1478</v>
       </c>
       <c r="K344" s="4"/>
       <c r="L344" s="4" t="s">
-        <v>1489</v>
-      </c>
-      <c r="M344" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="N344" s="4">
-        <v>7</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M344" s="4"/>
+      <c r="N344" s="4"/>
       <c r="O344" s="4" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="P344" s="5"/>
       <c r="Q344" s="4" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
       <c r="R344" s="4" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="S344" s="4">
         <v>0</v>
@@ -31680,17 +31694,21 @@
       <c r="T344" s="4">
         <v>0</v>
       </c>
-      <c r="U344" s="4"/>
-      <c r="V344" s="4"/>
+      <c r="U344" s="4" t="s">
+        <v>1486</v>
+      </c>
+      <c r="V344" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="W344" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X344" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y344" s="4"/>
       <c r="Z344" s="4" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="AA344" s="4" t="s">
         <v>48</v>
@@ -31707,13 +31725,13 @@
         <v>33</v>
       </c>
       <c r="C345" s="4">
-        <v>163592289</v>
+        <v>163594532</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E345" s="4">
-        <v>7412708</v>
+        <v>8382163</v>
       </c>
       <c r="F345" s="4" t="s">
         <v>51</v>
@@ -31728,20 +31746,18 @@
         <v>133</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="K345" s="4"/>
-      <c r="L345" s="4" t="s">
-        <v>296</v>
-      </c>
+      <c r="L345" s="4"/>
       <c r="M345" s="4"/>
       <c r="N345" s="4"/>
       <c r="O345" s="4" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="P345" s="5"/>
       <c r="Q345" s="4" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="R345" s="4" t="s">
         <v>92</v>
@@ -31752,12 +31768,8 @@
       <c r="T345" s="4">
         <v>0</v>
       </c>
-      <c r="U345" s="4" t="s">
-        <v>1496</v>
-      </c>
-      <c r="V345" s="4" t="s">
-        <v>416</v>
-      </c>
+      <c r="U345" s="4"/>
+      <c r="V345" s="4"/>
       <c r="W345" s="4">
         <v>1</v>
       </c>
@@ -31766,7 +31778,7 @@
       </c>
       <c r="Y345" s="4"/>
       <c r="Z345" s="4" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="AA345" s="4"/>
       <c r="AB345" s="4" t="s">
@@ -31778,16 +31790,16 @@
         <v>1000</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="C346" s="4">
-        <v>163568424</v>
+        <v>163588829</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E346" s="4">
-        <v>1140986</v>
+        <v>1053551</v>
       </c>
       <c r="F346" s="4" t="s">
         <v>51</v>
@@ -31802,25 +31814,27 @@
         <v>133</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="K346" s="4"/>
       <c r="L346" s="4" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="M346" s="4" t="s">
-        <v>1499</v>
-      </c>
-      <c r="N346" s="4"/>
+        <v>476</v>
+      </c>
+      <c r="N346" s="4">
+        <v>7</v>
+      </c>
       <c r="O346" s="4" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="P346" s="5"/>
       <c r="Q346" s="4" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="R346" s="4" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="S346" s="4">
         <v>0</v>
@@ -31831,17 +31845,17 @@
       <c r="U346" s="4"/>
       <c r="V346" s="4"/>
       <c r="W346" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X346" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y346" s="4"/>
       <c r="Z346" s="4" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="AA346" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB346" s="4" t="s">
         <v>49</v>
@@ -31855,13 +31869,13 @@
         <v>33</v>
       </c>
       <c r="C347" s="4">
-        <v>163529361</v>
+        <v>163592289</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>216</v>
+        <v>34</v>
       </c>
       <c r="E347" s="4">
-        <v>6840249</v>
+        <v>7412708</v>
       </c>
       <c r="F347" s="4" t="s">
         <v>51</v>
@@ -31876,53 +31890,47 @@
         <v>133</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="K347" s="4"/>
       <c r="L347" s="4" t="s">
-        <v>1504</v>
-      </c>
-      <c r="M347" s="4" t="s">
-        <v>1505</v>
-      </c>
-      <c r="N347" s="4">
-        <v>4</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M347" s="4"/>
+      <c r="N347" s="4"/>
       <c r="O347" s="4" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
       <c r="P347" s="5"/>
       <c r="Q347" s="4" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="R347" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S347" s="4">
-        <v>76308.22</v>
+        <v>0</v>
       </c>
       <c r="T347" s="4">
+        <v>0</v>
+      </c>
+      <c r="U347" s="4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="V347" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="W347" s="4">
         <v>1</v>
-      </c>
-      <c r="U347" s="4" t="s">
-        <v>1508</v>
-      </c>
-      <c r="V347" s="4" t="s">
-        <v>1509</v>
-      </c>
-      <c r="W347" s="4">
-        <v>4</v>
       </c>
       <c r="X347" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y347" s="4"/>
       <c r="Z347" s="4" t="s">
-        <v>1510</v>
-      </c>
-      <c r="AA347" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>1501</v>
+      </c>
+      <c r="AA347" s="4"/>
       <c r="AB347" s="4" t="s">
         <v>49</v>
       </c>
@@ -31932,16 +31940,16 @@
         <v>1000</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>33</v>
+        <v>536</v>
       </c>
       <c r="C348" s="4">
-        <v>163584051</v>
+        <v>163568424</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E348" s="4">
-        <v>6630607</v>
+        <v>1140986</v>
       </c>
       <c r="F348" s="4" t="s">
         <v>51</v>
@@ -31956,27 +31964,25 @@
         <v>133</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="K348" s="4"/>
       <c r="L348" s="4" t="s">
-        <v>1511</v>
+        <v>1502</v>
       </c>
       <c r="M348" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="N348" s="4">
-        <v>18</v>
-      </c>
+        <v>1503</v>
+      </c>
+      <c r="N348" s="4"/>
       <c r="O348" s="4" t="s">
-        <v>1513</v>
+        <v>1504</v>
       </c>
       <c r="P348" s="5"/>
       <c r="Q348" s="4" t="s">
-        <v>1514</v>
+        <v>1505</v>
       </c>
       <c r="R348" s="4" t="s">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="S348" s="4">
         <v>0</v>
@@ -31987,17 +31993,17 @@
       <c r="U348" s="4"/>
       <c r="V348" s="4"/>
       <c r="W348" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X348" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y348" s="4"/>
       <c r="Z348" s="4" t="s">
-        <v>1515</v>
+        <v>1506</v>
       </c>
       <c r="AA348" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB348" s="4" t="s">
         <v>49</v>
@@ -32008,16 +32014,16 @@
         <v>1000</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="C349" s="4">
-        <v>163568416</v>
+        <v>163529361</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E349" s="4">
-        <v>7753862</v>
+        <v>6840249</v>
       </c>
       <c r="F349" s="4" t="s">
         <v>51</v>
@@ -32032,49 +32038,49 @@
         <v>133</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1516</v>
+        <v>1507</v>
       </c>
       <c r="K349" s="4"/>
       <c r="L349" s="4" t="s">
-        <v>1517</v>
+        <v>1508</v>
       </c>
       <c r="M349" s="4" t="s">
-        <v>1518</v>
+        <v>1509</v>
       </c>
       <c r="N349" s="4">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O349" s="4" t="s">
-        <v>1519</v>
+        <v>1510</v>
       </c>
       <c r="P349" s="5"/>
       <c r="Q349" s="4" t="s">
-        <v>1520</v>
+        <v>1511</v>
       </c>
       <c r="R349" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S349" s="4">
-        <v>0</v>
+        <v>76308.22</v>
       </c>
       <c r="T349" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U349" s="4" t="s">
-        <v>1521</v>
+        <v>1512</v>
       </c>
       <c r="V349" s="4" t="s">
-        <v>131</v>
+        <v>1513</v>
       </c>
       <c r="W349" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X349" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y349" s="4"/>
       <c r="Z349" s="4" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="AA349" s="4" t="s">
         <v>66</v>
@@ -32091,13 +32097,13 @@
         <v>33</v>
       </c>
       <c r="C350" s="4">
-        <v>163594016</v>
+        <v>163584051</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>216</v>
       </c>
       <c r="E350" s="4">
-        <v>7753863</v>
+        <v>6630607</v>
       </c>
       <c r="F350" s="4" t="s">
         <v>51</v>
@@ -32112,24 +32118,24 @@
         <v>133</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1516</v>
+        <v>1507</v>
       </c>
       <c r="K350" s="4"/>
       <c r="L350" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="M350" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="N350" s="4">
+        <v>18</v>
+      </c>
+      <c r="O350" s="4" t="s">
         <v>1517</v>
-      </c>
-      <c r="M350" s="4" t="s">
-        <v>1518</v>
-      </c>
-      <c r="N350" s="4">
-        <v>21</v>
-      </c>
-      <c r="O350" s="4" t="s">
-        <v>1523</v>
       </c>
       <c r="P350" s="5"/>
       <c r="Q350" s="4" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="R350" s="4" t="s">
         <v>185</v>
@@ -32140,21 +32146,17 @@
       <c r="T350" s="4">
         <v>0</v>
       </c>
-      <c r="U350" s="4" t="s">
-        <v>1525</v>
-      </c>
-      <c r="V350" s="4" t="s">
-        <v>333</v>
-      </c>
+      <c r="U350" s="4"/>
+      <c r="V350" s="4"/>
       <c r="W350" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X350" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y350" s="4"/>
       <c r="Z350" s="4" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
       <c r="AA350" s="4" t="s">
         <v>48</v>
@@ -32168,16 +32170,16 @@
         <v>1000</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>33</v>
+        <v>536</v>
       </c>
       <c r="C351" s="4">
-        <v>163584015</v>
+        <v>163568416</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E351" s="4">
-        <v>5903236</v>
+        <v>7753862</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>51</v>
@@ -32192,44 +32194,52 @@
         <v>133</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
       <c r="K351" s="4"/>
       <c r="L351" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M351" s="4"/>
-      <c r="N351" s="4"/>
+        <v>1521</v>
+      </c>
+      <c r="M351" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="N351" s="4">
+        <v>15</v>
+      </c>
       <c r="O351" s="4" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="P351" s="5"/>
       <c r="Q351" s="4" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="R351" s="4" t="s">
-        <v>396</v>
+        <v>185</v>
       </c>
       <c r="S351" s="4">
-        <v>53994.21</v>
+        <v>0</v>
       </c>
       <c r="T351" s="4">
-        <v>1</v>
-      </c>
-      <c r="U351" s="4"/>
-      <c r="V351" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U351" s="4" t="s">
+        <v>1525</v>
+      </c>
+      <c r="V351" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="W351" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X351" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y351" s="4"/>
       <c r="Z351" s="4" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="AA351" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB351" s="4" t="s">
         <v>49</v>
@@ -32243,13 +32253,13 @@
         <v>33</v>
       </c>
       <c r="C352" s="4">
-        <v>163592352</v>
+        <v>163594016</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>216</v>
       </c>
       <c r="E352" s="4">
-        <v>7313578</v>
+        <v>7753863</v>
       </c>
       <c r="F352" s="4" t="s">
         <v>51</v>
@@ -32264,24 +32274,24 @@
         <v>133</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1531</v>
+        <v>1520</v>
       </c>
       <c r="K352" s="4"/>
       <c r="L352" s="4" t="s">
-        <v>1532</v>
+        <v>1521</v>
       </c>
       <c r="M352" s="4" t="s">
-        <v>1533</v>
+        <v>1522</v>
       </c>
       <c r="N352" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O352" s="4" t="s">
-        <v>1534</v>
+        <v>1527</v>
       </c>
       <c r="P352" s="5"/>
       <c r="Q352" s="4" t="s">
-        <v>1535</v>
+        <v>1528</v>
       </c>
       <c r="R352" s="4" t="s">
         <v>185</v>
@@ -32293,10 +32303,10 @@
         <v>0</v>
       </c>
       <c r="U352" s="4" t="s">
-        <v>1536</v>
+        <v>1529</v>
       </c>
       <c r="V352" s="4" t="s">
-        <v>1537</v>
+        <v>333</v>
       </c>
       <c r="W352" s="4">
         <v>1</v>
@@ -32306,9 +32316,11 @@
       </c>
       <c r="Y352" s="4"/>
       <c r="Z352" s="4" t="s">
-        <v>1538</v>
-      </c>
-      <c r="AA352" s="4"/>
+        <v>1530</v>
+      </c>
+      <c r="AA352" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB352" s="4" t="s">
         <v>49</v>
       </c>
@@ -32318,16 +32330,16 @@
         <v>1000</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="C353" s="4">
-        <v>163568467</v>
+        <v>163584015</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E353" s="4">
-        <v>6571089</v>
+        <v>5903236</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>51</v>
@@ -32342,7 +32354,7 @@
         <v>133</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
       <c r="K353" s="4"/>
       <c r="L353" s="4" t="s">
@@ -32351,39 +32363,35 @@
       <c r="M353" s="4"/>
       <c r="N353" s="4"/>
       <c r="O353" s="4" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
       <c r="P353" s="5"/>
       <c r="Q353" s="4" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
       <c r="R353" s="4" t="s">
-        <v>92</v>
+        <v>396</v>
       </c>
       <c r="S353" s="4">
-        <v>0</v>
+        <v>53994.21</v>
       </c>
       <c r="T353" s="4">
-        <v>0</v>
-      </c>
-      <c r="U353" s="4" t="s">
-        <v>1542</v>
-      </c>
-      <c r="V353" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U353" s="4"/>
+      <c r="V353" s="4"/>
       <c r="W353" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X353" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y353" s="4"/>
       <c r="Z353" s="4" t="s">
-        <v>1543</v>
+        <v>1534</v>
       </c>
       <c r="AA353" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB353" s="4" t="s">
         <v>49</v>
@@ -32397,13 +32405,13 @@
         <v>33</v>
       </c>
       <c r="C354" s="4">
-        <v>163433658</v>
+        <v>163592352</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="E354" s="4">
-        <v>1124725</v>
+        <v>7313578</v>
       </c>
       <c r="F354" s="4" t="s">
         <v>51</v>
@@ -32418,49 +32426,51 @@
         <v>133</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1544</v>
+        <v>1535</v>
       </c>
       <c r="K354" s="4"/>
       <c r="L354" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M354" s="4"/>
-      <c r="N354" s="4"/>
+        <v>1536</v>
+      </c>
+      <c r="M354" s="4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="N354" s="4">
+        <v>14</v>
+      </c>
       <c r="O354" s="4" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
       <c r="P354" s="5"/>
       <c r="Q354" s="4" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="R354" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S354" s="4">
-        <v>362404.38</v>
+        <v>0</v>
       </c>
       <c r="T354" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U354" s="4" t="s">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="V354" s="4" t="s">
-        <v>333</v>
+        <v>1541</v>
       </c>
       <c r="W354" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X354" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y354" s="4"/>
       <c r="Z354" s="4" t="s">
-        <v>880</v>
-      </c>
-      <c r="AA354" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1542</v>
+      </c>
+      <c r="AA354" s="4"/>
       <c r="AB354" s="4" t="s">
         <v>49</v>
       </c>
@@ -32470,16 +32480,16 @@
         <v>1000</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1548</v>
+        <v>536</v>
       </c>
       <c r="C355" s="4">
-        <v>163568476</v>
+        <v>163568467</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E355" s="4">
-        <v>7911951</v>
+        <v>6571089</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>51</v>
@@ -32494,7 +32504,7 @@
         <v>133</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="K355" s="4"/>
       <c r="L355" s="4" t="s">
@@ -32503,11 +32513,11 @@
       <c r="M355" s="4"/>
       <c r="N355" s="4"/>
       <c r="O355" s="4" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="P355" s="5"/>
       <c r="Q355" s="4" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="R355" s="4" t="s">
         <v>92</v>
@@ -32518,8 +32528,12 @@
       <c r="T355" s="4">
         <v>0</v>
       </c>
-      <c r="U355" s="4"/>
-      <c r="V355" s="4"/>
+      <c r="U355" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="V355" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="W355" s="4">
         <v>3</v>
       </c>
@@ -32528,10 +32542,10 @@
       </c>
       <c r="Y355" s="4"/>
       <c r="Z355" s="4" t="s">
-        <v>1406</v>
+        <v>1547</v>
       </c>
       <c r="AA355" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB355" s="4" t="s">
         <v>49</v>
@@ -32542,31 +32556,31 @@
         <v>1000</v>
       </c>
       <c r="B356" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C356" s="4">
+        <v>163433658</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E356" s="4">
+        <v>1124725</v>
+      </c>
+      <c r="F356" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G356" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H356" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I356" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J356" s="4" t="s">
         <v>1548</v>
-      </c>
-      <c r="C356" s="4">
-        <v>163568477</v>
-      </c>
-      <c r="D356" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E356" s="4">
-        <v>6831349</v>
-      </c>
-      <c r="F356" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G356" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H356" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I356" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J356" s="4" t="s">
-        <v>1549</v>
       </c>
       <c r="K356" s="4"/>
       <c r="L356" s="4" t="s">
@@ -32575,34 +32589,40 @@
       <c r="M356" s="4"/>
       <c r="N356" s="4"/>
       <c r="O356" s="4" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="P356" s="5"/>
       <c r="Q356" s="4" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="R356" s="4" t="s">
         <v>92</v>
       </c>
       <c r="S356" s="4">
-        <v>0</v>
+        <v>362404.38</v>
       </c>
       <c r="T356" s="4">
-        <v>0</v>
-      </c>
-      <c r="U356" s="4"/>
-      <c r="V356" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U356" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="V356" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W356" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X356" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y356" s="4"/>
       <c r="Z356" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="AA356" s="4"/>
+        <v>880</v>
+      </c>
+      <c r="AA356" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB356" s="4" t="s">
         <v>49</v>
       </c>
@@ -32612,16 +32632,16 @@
         <v>1000</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="C357" s="4">
-        <v>163568478</v>
+        <v>163568476</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E357" s="4">
-        <v>7716168</v>
+        <v>7911951</v>
       </c>
       <c r="F357" s="4" t="s">
         <v>51</v>
@@ -32636,7 +32656,7 @@
         <v>133</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="K357" s="4"/>
       <c r="L357" s="4" t="s">
@@ -32670,10 +32690,10 @@
       </c>
       <c r="Y357" s="4"/>
       <c r="Z357" s="4" t="s">
-        <v>1543</v>
+        <v>1410</v>
       </c>
       <c r="AA357" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB357" s="4" t="s">
         <v>49</v>
@@ -32684,16 +32704,16 @@
         <v>1000</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="C358" s="4">
-        <v>163568479</v>
+        <v>163568477</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E358" s="4">
-        <v>6656976</v>
+        <v>6831349</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>51</v>
@@ -32708,7 +32728,7 @@
         <v>133</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="K358" s="4"/>
       <c r="L358" s="4" t="s">
@@ -32742,11 +32762,9 @@
       </c>
       <c r="Y358" s="4"/>
       <c r="Z358" s="4" t="s">
-        <v>1406</v>
-      </c>
-      <c r="AA358" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>953</v>
+      </c>
+      <c r="AA358" s="4"/>
       <c r="AB358" s="4" t="s">
         <v>49</v>
       </c>
@@ -32756,16 +32774,16 @@
         <v>1000</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="C359" s="4">
-        <v>163568437</v>
+        <v>163568478</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E359" s="4">
-        <v>7868219</v>
+        <v>7716168</v>
       </c>
       <c r="F359" s="4" t="s">
         <v>51</v>
@@ -32780,7 +32798,7 @@
         <v>133</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="K359" s="4"/>
       <c r="L359" s="4" t="s">
@@ -32789,14 +32807,14 @@
       <c r="M359" s="4"/>
       <c r="N359" s="4"/>
       <c r="O359" s="4" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="P359" s="5"/>
       <c r="Q359" s="4" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="R359" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S359" s="4">
         <v>0</v>
@@ -32814,7 +32832,7 @@
       </c>
       <c r="Y359" s="4"/>
       <c r="Z359" s="4" t="s">
-        <v>1562</v>
+        <v>1547</v>
       </c>
       <c r="AA359" s="4" t="s">
         <v>66</v>
@@ -32828,16 +32846,16 @@
         <v>1000</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="C360" s="4">
-        <v>163568473</v>
+        <v>163568479</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E360" s="4">
-        <v>7746659</v>
+        <v>6656976</v>
       </c>
       <c r="F360" s="4" t="s">
         <v>51</v>
@@ -32852,7 +32870,7 @@
         <v>133</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="K360" s="4"/>
       <c r="L360" s="4" t="s">
@@ -32861,14 +32879,14 @@
       <c r="M360" s="4"/>
       <c r="N360" s="4"/>
       <c r="O360" s="4" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="P360" s="5"/>
       <c r="Q360" s="4" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="R360" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S360" s="4">
         <v>0</v>
@@ -32886,10 +32904,10 @@
       </c>
       <c r="Y360" s="4"/>
       <c r="Z360" s="4" t="s">
-        <v>1565</v>
+        <v>1410</v>
       </c>
       <c r="AA360" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB360" s="4" t="s">
         <v>49</v>
@@ -32900,16 +32918,16 @@
         <v>1000</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="C361" s="4">
-        <v>163568439</v>
+        <v>163568437</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E361" s="4">
-        <v>7649853</v>
+        <v>7868219</v>
       </c>
       <c r="F361" s="4" t="s">
         <v>51</v>
@@ -32924,27 +32942,23 @@
         <v>133</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="K361" s="4"/>
       <c r="L361" s="4" t="s">
-        <v>1566</v>
-      </c>
-      <c r="M361" s="4" t="s">
-        <v>1567</v>
-      </c>
-      <c r="N361" s="4">
-        <v>17</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M361" s="4"/>
+      <c r="N361" s="4"/>
       <c r="O361" s="4" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="P361" s="5"/>
       <c r="Q361" s="4" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="R361" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S361" s="4">
         <v>0</v>
@@ -32962,9 +32976,11 @@
       </c>
       <c r="Y361" s="4"/>
       <c r="Z361" s="4" t="s">
-        <v>919</v>
-      </c>
-      <c r="AA361" s="4"/>
+        <v>1566</v>
+      </c>
+      <c r="AA361" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB361" s="4" t="s">
         <v>49</v>
       </c>
@@ -32974,16 +32990,16 @@
         <v>1000</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="C362" s="4">
-        <v>163568474</v>
+        <v>163568473</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E362" s="4">
-        <v>7938906</v>
+        <v>7746659</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>51</v>
@@ -32998,22 +33014,20 @@
         <v>133</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="K362" s="4"/>
       <c r="L362" s="4" t="s">
-        <v>1566</v>
-      </c>
-      <c r="M362" s="4" t="s">
-        <v>1570</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M362" s="4"/>
       <c r="N362" s="4"/>
       <c r="O362" s="4" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="P362" s="5"/>
       <c r="Q362" s="4" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="R362" s="4" t="s">
         <v>185</v>
@@ -33024,12 +33038,8 @@
       <c r="T362" s="4">
         <v>0</v>
       </c>
-      <c r="U362" s="4" t="s">
-        <v>1573</v>
-      </c>
-      <c r="V362" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="U362" s="4"/>
+      <c r="V362" s="4"/>
       <c r="W362" s="4">
         <v>3</v>
       </c>
@@ -33038,10 +33048,10 @@
       </c>
       <c r="Y362" s="4"/>
       <c r="Z362" s="4" t="s">
-        <v>531</v>
+        <v>1569</v>
       </c>
       <c r="AA362" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB362" s="4" t="s">
         <v>49</v>
@@ -33052,16 +33062,16 @@
         <v>1000</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="C363" s="4">
-        <v>163568475</v>
+        <v>163568439</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E363" s="4">
-        <v>7938920</v>
+        <v>7649853</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>51</v>
@@ -33076,25 +33086,27 @@
         <v>133</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="K363" s="4"/>
       <c r="L363" s="4" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="M363" s="4" t="s">
-        <v>1570</v>
-      </c>
-      <c r="N363" s="4"/>
+        <v>1571</v>
+      </c>
+      <c r="N363" s="4">
+        <v>17</v>
+      </c>
       <c r="O363" s="4" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="P363" s="5"/>
       <c r="Q363" s="4" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="R363" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S363" s="4">
         <v>0</v>
@@ -33102,12 +33114,8 @@
       <c r="T363" s="4">
         <v>0</v>
       </c>
-      <c r="U363" s="4" t="s">
-        <v>1576</v>
-      </c>
-      <c r="V363" s="4" t="s">
-        <v>1577</v>
-      </c>
+      <c r="U363" s="4"/>
+      <c r="V363" s="4"/>
       <c r="W363" s="4">
         <v>3</v>
       </c>
@@ -33116,7 +33124,7 @@
       </c>
       <c r="Y363" s="4"/>
       <c r="Z363" s="4" t="s">
-        <v>953</v>
+        <v>919</v>
       </c>
       <c r="AA363" s="4"/>
       <c r="AB363" s="4" t="s">
@@ -33128,16 +33136,16 @@
         <v>1000</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1136</v>
+        <v>1562</v>
       </c>
       <c r="C364" s="4">
-        <v>163549539</v>
+        <v>163568474</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E364" s="4">
-        <v>4316661</v>
+        <v>7938906</v>
       </c>
       <c r="F364" s="4" t="s">
         <v>51</v>
@@ -33152,23 +33160,25 @@
         <v>133</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1578</v>
+        <v>1563</v>
       </c>
       <c r="K364" s="4"/>
       <c r="L364" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M364" s="4"/>
+        <v>1570</v>
+      </c>
+      <c r="M364" s="4" t="s">
+        <v>1574</v>
+      </c>
       <c r="N364" s="4"/>
       <c r="O364" s="4" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="P364" s="5"/>
       <c r="Q364" s="4" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="R364" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S364" s="4">
         <v>0</v>
@@ -33176,17 +33186,21 @@
       <c r="T364" s="4">
         <v>0</v>
       </c>
-      <c r="U364" s="4"/>
-      <c r="V364" s="4"/>
+      <c r="U364" s="4" t="s">
+        <v>1577</v>
+      </c>
+      <c r="V364" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="W364" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X364" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y364" s="4"/>
       <c r="Z364" s="4" t="s">
-        <v>1581</v>
+        <v>531</v>
       </c>
       <c r="AA364" s="4" t="s">
         <v>48</v>
@@ -33200,16 +33214,16 @@
         <v>1000</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>425</v>
+        <v>1562</v>
       </c>
       <c r="C365" s="4">
-        <v>163568504</v>
+        <v>163568475</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E365" s="4">
-        <v>5880389</v>
+        <v>7938920</v>
       </c>
       <c r="F365" s="4" t="s">
         <v>51</v>
@@ -33224,20 +33238,22 @@
         <v>133</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1582</v>
+        <v>1563</v>
       </c>
       <c r="K365" s="4"/>
       <c r="L365" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M365" s="4"/>
+        <v>1570</v>
+      </c>
+      <c r="M365" s="4" t="s">
+        <v>1574</v>
+      </c>
       <c r="N365" s="4"/>
       <c r="O365" s="4" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="P365" s="5"/>
       <c r="Q365" s="4" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="R365" s="4" t="s">
         <v>185</v>
@@ -33248,8 +33264,12 @@
       <c r="T365" s="4">
         <v>0</v>
       </c>
-      <c r="U365" s="4"/>
-      <c r="V365" s="4"/>
+      <c r="U365" s="4" t="s">
+        <v>1580</v>
+      </c>
+      <c r="V365" s="4" t="s">
+        <v>1581</v>
+      </c>
       <c r="W365" s="4">
         <v>3</v>
       </c>
@@ -33258,7 +33278,7 @@
       </c>
       <c r="Y365" s="4"/>
       <c r="Z365" s="4" t="s">
-        <v>457</v>
+        <v>953</v>
       </c>
       <c r="AA365" s="4"/>
       <c r="AB365" s="4" t="s">
@@ -33270,16 +33290,16 @@
         <v>1000</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1585</v>
+        <v>1136</v>
       </c>
       <c r="C366" s="4">
-        <v>163568522</v>
+        <v>163549539</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E366" s="4">
-        <v>5867262</v>
+        <v>4316661</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>51</v>
@@ -33303,14 +33323,14 @@
       <c r="M366" s="4"/>
       <c r="N366" s="4"/>
       <c r="O366" s="4" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="P366" s="5"/>
       <c r="Q366" s="4" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="R366" s="4" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="S366" s="4">
         <v>0</v>
@@ -33318,23 +33338,21 @@
       <c r="T366" s="4">
         <v>0</v>
       </c>
-      <c r="U366" s="4" t="s">
-        <v>1588</v>
-      </c>
-      <c r="V366" s="4" t="s">
-        <v>604</v>
-      </c>
+      <c r="U366" s="4"/>
+      <c r="V366" s="4"/>
       <c r="W366" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X366" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y366" s="4"/>
       <c r="Z366" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA366" s="4"/>
+        <v>1585</v>
+      </c>
+      <c r="AA366" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB366" s="4" t="s">
         <v>49</v>
       </c>
@@ -33344,16 +33362,16 @@
         <v>1000</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1585</v>
+        <v>425</v>
       </c>
       <c r="C367" s="4">
-        <v>163568524</v>
+        <v>163568504</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E367" s="4">
-        <v>7948448</v>
+        <v>5880389</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>51</v>
@@ -33368,7 +33386,7 @@
         <v>133</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K367" s="4"/>
       <c r="L367" s="4" t="s">
@@ -33377,11 +33395,11 @@
       <c r="M367" s="4"/>
       <c r="N367" s="4"/>
       <c r="O367" s="4" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="P367" s="5"/>
       <c r="Q367" s="4" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="R367" s="4" t="s">
         <v>185</v>
@@ -33392,12 +33410,8 @@
       <c r="T367" s="4">
         <v>0</v>
       </c>
-      <c r="U367" s="4" t="s">
-        <v>1591</v>
-      </c>
-      <c r="V367" s="4" t="s">
-        <v>266</v>
-      </c>
+      <c r="U367" s="4"/>
+      <c r="V367" s="4"/>
       <c r="W367" s="4">
         <v>3</v>
       </c>
@@ -33406,11 +33420,9 @@
       </c>
       <c r="Y367" s="4"/>
       <c r="Z367" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA367" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AA367" s="4"/>
       <c r="AB367" s="4" t="s">
         <v>49</v>
       </c>
@@ -33420,16 +33432,16 @@
         <v>1000</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="C368" s="4">
-        <v>163568535</v>
+        <v>163568522</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E368" s="4">
-        <v>4326685</v>
+        <v>5867262</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>51</v>
@@ -33444,7 +33456,7 @@
         <v>133</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K368" s="4"/>
       <c r="L368" s="4" t="s">
@@ -33453,11 +33465,11 @@
       <c r="M368" s="4"/>
       <c r="N368" s="4"/>
       <c r="O368" s="4" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="P368" s="5"/>
       <c r="Q368" s="4" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="R368" s="4" t="s">
         <v>167</v>
@@ -33469,10 +33481,10 @@
         <v>0</v>
       </c>
       <c r="U368" s="4" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="V368" s="4" t="s">
-        <v>333</v>
+        <v>604</v>
       </c>
       <c r="W368" s="4">
         <v>3</v>
@@ -33482,11 +33494,9 @@
       </c>
       <c r="Y368" s="4"/>
       <c r="Z368" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA368" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AA368" s="4"/>
       <c r="AB368" s="4" t="s">
         <v>49</v>
       </c>
@@ -33496,16 +33506,16 @@
         <v>1000</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="C369" s="4">
-        <v>163568536</v>
+        <v>163568524</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E369" s="4">
-        <v>5891609</v>
+        <v>7948448</v>
       </c>
       <c r="F369" s="4" t="s">
         <v>51</v>
@@ -33520,7 +33530,7 @@
         <v>133</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K369" s="4"/>
       <c r="L369" s="4" t="s">
@@ -33529,14 +33539,14 @@
       <c r="M369" s="4"/>
       <c r="N369" s="4"/>
       <c r="O369" s="4" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="R369" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S369" s="4">
         <v>0</v>
@@ -33545,10 +33555,10 @@
         <v>0</v>
       </c>
       <c r="U369" s="4" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="V369" s="4" t="s">
-        <v>402</v>
+        <v>266</v>
       </c>
       <c r="W369" s="4">
         <v>3</v>
@@ -33572,16 +33582,16 @@
         <v>1000</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="C370" s="4">
-        <v>163568541</v>
+        <v>163568535</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E370" s="4">
-        <v>5366500</v>
+        <v>4326685</v>
       </c>
       <c r="F370" s="4" t="s">
         <v>51</v>
@@ -33596,7 +33606,7 @@
         <v>133</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K370" s="4"/>
       <c r="L370" s="4" t="s">
@@ -33605,11 +33615,11 @@
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
       <c r="O370" s="4" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="R370" s="4" t="s">
         <v>167</v>
@@ -33620,8 +33630,12 @@
       <c r="T370" s="4">
         <v>0</v>
       </c>
-      <c r="U370" s="4"/>
-      <c r="V370" s="4"/>
+      <c r="U370" s="4" t="s">
+        <v>1598</v>
+      </c>
+      <c r="V370" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W370" s="4">
         <v>3</v>
       </c>
@@ -33630,10 +33644,10 @@
       </c>
       <c r="Y370" s="4"/>
       <c r="Z370" s="4" t="s">
-        <v>1600</v>
+        <v>334</v>
       </c>
       <c r="AA370" s="4" t="s">
-        <v>903</v>
+        <v>48</v>
       </c>
       <c r="AB370" s="4" t="s">
         <v>49</v>
@@ -33644,16 +33658,16 @@
         <v>1000</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1288</v>
+        <v>1589</v>
       </c>
       <c r="C371" s="4">
-        <v>163568542</v>
+        <v>163568536</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E371" s="4">
-        <v>6530876</v>
+        <v>5891609</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>51</v>
@@ -33668,7 +33682,7 @@
         <v>133</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K371" s="4"/>
       <c r="L371" s="4" t="s">
@@ -33677,23 +33691,27 @@
       <c r="M371" s="4"/>
       <c r="N371" s="4"/>
       <c r="O371" s="4" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="P371" s="5"/>
       <c r="Q371" s="4" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="R371" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S371" s="4">
-        <v>3957267.07</v>
+        <v>0</v>
       </c>
       <c r="T371" s="4">
-        <v>1</v>
-      </c>
-      <c r="U371" s="4"/>
-      <c r="V371" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U371" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="V371" s="4" t="s">
+        <v>402</v>
+      </c>
       <c r="W371" s="4">
         <v>3</v>
       </c>
@@ -33702,13 +33720,13 @@
       </c>
       <c r="Y371" s="4"/>
       <c r="Z371" s="4" t="s">
-        <v>1603</v>
+        <v>424</v>
       </c>
       <c r="AA371" s="4" t="s">
-        <v>903</v>
+        <v>48</v>
       </c>
       <c r="AB371" s="4" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
     </row>
     <row r="372" spans="1:28">
@@ -33716,16 +33734,16 @@
         <v>1000</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1288</v>
+        <v>1589</v>
       </c>
       <c r="C372" s="4">
-        <v>163568543</v>
+        <v>163568541</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E372" s="4">
-        <v>5885728</v>
+        <v>5366500</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>51</v>
@@ -33740,7 +33758,7 @@
         <v>133</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K372" s="4"/>
       <c r="L372" s="4" t="s">
@@ -33749,11 +33767,11 @@
       <c r="M372" s="4"/>
       <c r="N372" s="4"/>
       <c r="O372" s="4" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="P372" s="5"/>
       <c r="Q372" s="4" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="R372" s="4" t="s">
         <v>167</v>
@@ -33764,12 +33782,8 @@
       <c r="T372" s="4">
         <v>0</v>
       </c>
-      <c r="U372" s="4" t="s">
-        <v>1606</v>
-      </c>
-      <c r="V372" s="4" t="s">
-        <v>266</v>
-      </c>
+      <c r="U372" s="4"/>
+      <c r="V372" s="4"/>
       <c r="W372" s="4">
         <v>3</v>
       </c>
@@ -33778,10 +33792,10 @@
       </c>
       <c r="Y372" s="4"/>
       <c r="Z372" s="4" t="s">
-        <v>461</v>
+        <v>1604</v>
       </c>
       <c r="AA372" s="4" t="s">
-        <v>66</v>
+        <v>903</v>
       </c>
       <c r="AB372" s="4" t="s">
         <v>49</v>
@@ -33792,16 +33806,16 @@
         <v>1000</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>33</v>
+        <v>1288</v>
       </c>
       <c r="C373" s="4">
-        <v>163568568</v>
+        <v>163568542</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E373" s="4">
-        <v>5927513</v>
+        <v>6530876</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>51</v>
@@ -33816,7 +33830,7 @@
         <v>133</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K373" s="4"/>
       <c r="L373" s="4" t="s">
@@ -33825,20 +33839,20 @@
       <c r="M373" s="4"/>
       <c r="N373" s="4"/>
       <c r="O373" s="4" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="P373" s="5"/>
       <c r="Q373" s="4" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="R373" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S373" s="4">
-        <v>0</v>
+        <v>3957267.07</v>
       </c>
       <c r="T373" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U373" s="4"/>
       <c r="V373" s="4"/>
@@ -33846,17 +33860,17 @@
         <v>3</v>
       </c>
       <c r="X373" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y373" s="4"/>
       <c r="Z373" s="4" t="s">
-        <v>424</v>
+        <v>1607</v>
       </c>
       <c r="AA373" s="4" t="s">
-        <v>48</v>
+        <v>903</v>
       </c>
       <c r="AB373" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="374" spans="1:28">
@@ -33864,16 +33878,16 @@
         <v>1000</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>33</v>
+        <v>1288</v>
       </c>
       <c r="C374" s="4">
-        <v>163569194</v>
+        <v>163568543</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E374" s="4">
-        <v>5867636</v>
+        <v>5885728</v>
       </c>
       <c r="F374" s="4" t="s">
         <v>51</v>
@@ -33888,7 +33902,7 @@
         <v>133</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K374" s="4"/>
       <c r="L374" s="4" t="s">
@@ -33897,11 +33911,11 @@
       <c r="M374" s="4"/>
       <c r="N374" s="4"/>
       <c r="O374" s="4" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="P374" s="5"/>
       <c r="Q374" s="4" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="R374" s="4" t="s">
         <v>167</v>
@@ -33912,19 +33926,25 @@
       <c r="T374" s="4">
         <v>0</v>
       </c>
-      <c r="U374" s="4"/>
-      <c r="V374" s="4"/>
+      <c r="U374" s="4" t="s">
+        <v>1610</v>
+      </c>
+      <c r="V374" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="W374" s="4">
         <v>3</v>
       </c>
       <c r="X374" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y374" s="4"/>
       <c r="Z374" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA374" s="4"/>
+        <v>461</v>
+      </c>
+      <c r="AA374" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB374" s="4" t="s">
         <v>49</v>
       </c>
@@ -33937,13 +33957,13 @@
         <v>33</v>
       </c>
       <c r="C375" s="4">
-        <v>163568517</v>
+        <v>163568568</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E375" s="4">
-        <v>5877224</v>
+        <v>5927513</v>
       </c>
       <c r="F375" s="4" t="s">
         <v>51</v>
@@ -33958,40 +33978,32 @@
         <v>133</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K375" s="4"/>
       <c r="L375" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="M375" s="4"/>
+      <c r="N375" s="4"/>
+      <c r="O375" s="4" t="s">
         <v>1611</v>
-      </c>
-      <c r="M375" s="4" t="s">
-        <v>1612</v>
-      </c>
-      <c r="N375" s="4">
-        <v>48</v>
-      </c>
-      <c r="O375" s="4" t="s">
-        <v>1613</v>
       </c>
       <c r="P375" s="5"/>
       <c r="Q375" s="4" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="R375" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S375" s="4">
-        <v>443605.59</v>
+        <v>0</v>
       </c>
       <c r="T375" s="4">
-        <v>1</v>
-      </c>
-      <c r="U375" s="4" t="s">
-        <v>1615</v>
-      </c>
-      <c r="V375" s="4" t="s">
-        <v>430</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U375" s="4"/>
+      <c r="V375" s="4"/>
       <c r="W375" s="4">
         <v>3</v>
       </c>
@@ -34000,10 +34012,10 @@
       </c>
       <c r="Y375" s="4"/>
       <c r="Z375" s="4" t="s">
-        <v>1616</v>
+        <v>424</v>
       </c>
       <c r="AA375" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB375" s="4" t="s">
         <v>49</v>
@@ -34017,13 +34029,13 @@
         <v>33</v>
       </c>
       <c r="C376" s="4">
-        <v>163568544</v>
+        <v>163569194</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E376" s="4">
-        <v>5916137</v>
+        <v>5867636</v>
       </c>
       <c r="F376" s="4" t="s">
         <v>51</v>
@@ -34038,27 +34050,23 @@
         <v>133</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K376" s="4"/>
       <c r="L376" s="4" t="s">
-        <v>1617</v>
-      </c>
-      <c r="M376" s="4" t="s">
-        <v>1618</v>
-      </c>
-      <c r="N376" s="4">
-        <v>22</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M376" s="4"/>
+      <c r="N376" s="4"/>
       <c r="O376" s="4" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="P376" s="5"/>
       <c r="Q376" s="4" t="s">
-        <v>1620</v>
+        <v>1614</v>
       </c>
       <c r="R376" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S376" s="4">
         <v>0</v>
@@ -34076,7 +34084,7 @@
       </c>
       <c r="Y376" s="4"/>
       <c r="Z376" s="4" t="s">
-        <v>1621</v>
+        <v>457</v>
       </c>
       <c r="AA376" s="4"/>
       <c r="AB376" s="4" t="s">
@@ -34091,13 +34099,13 @@
         <v>33</v>
       </c>
       <c r="C377" s="4">
-        <v>163568533</v>
+        <v>163568517</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E377" s="4">
-        <v>5915736</v>
+        <v>5877224</v>
       </c>
       <c r="F377" s="4" t="s">
         <v>51</v>
@@ -34112,36 +34120,40 @@
         <v>133</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K377" s="4"/>
       <c r="L377" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="M377" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="N377" s="4">
+        <v>48</v>
+      </c>
+      <c r="O377" s="4" t="s">
         <v>1617</v>
-      </c>
-      <c r="M377" s="4" t="s">
-        <v>1618</v>
-      </c>
-      <c r="N377" s="4">
-        <v>34</v>
-      </c>
-      <c r="O377" s="4" t="s">
-        <v>1622</v>
       </c>
       <c r="P377" s="5"/>
       <c r="Q377" s="4" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="R377" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S377" s="4">
-        <v>0</v>
+        <v>443605.59</v>
       </c>
       <c r="T377" s="4">
-        <v>0</v>
-      </c>
-      <c r="U377" s="4"/>
-      <c r="V377" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U377" s="4" t="s">
+        <v>1619</v>
+      </c>
+      <c r="V377" s="4" t="s">
+        <v>430</v>
+      </c>
       <c r="W377" s="4">
         <v>3</v>
       </c>
@@ -34150,10 +34162,10 @@
       </c>
       <c r="Y377" s="4"/>
       <c r="Z377" s="4" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="AA377" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB377" s="4" t="s">
         <v>49</v>
@@ -34164,16 +34176,16 @@
         <v>1000</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1355</v>
+        <v>33</v>
       </c>
       <c r="C378" s="4">
-        <v>163568520</v>
+        <v>163568544</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E378" s="4">
-        <v>5364215</v>
+        <v>5916137</v>
       </c>
       <c r="F378" s="4" t="s">
         <v>51</v>
@@ -34188,24 +34200,24 @@
         <v>133</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K378" s="4"/>
       <c r="L378" s="4" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="M378" s="4" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="N378" s="4">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="O378" s="4" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="P378" s="5"/>
       <c r="Q378" s="4" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="R378" s="4" t="s">
         <v>185</v>
@@ -34216,25 +34228,19 @@
       <c r="T378" s="4">
         <v>0</v>
       </c>
-      <c r="U378" s="4" t="s">
-        <v>1627</v>
-      </c>
-      <c r="V378" s="4" t="s">
-        <v>430</v>
-      </c>
+      <c r="U378" s="4"/>
+      <c r="V378" s="4"/>
       <c r="W378" s="4">
         <v>3</v>
       </c>
       <c r="X378" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y378" s="4"/>
       <c r="Z378" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA378" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1625</v>
+      </c>
+      <c r="AA378" s="4"/>
       <c r="AB378" s="4" t="s">
         <v>49</v>
       </c>
@@ -34244,16 +34250,16 @@
         <v>1000</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
       <c r="C379" s="4">
-        <v>163568516</v>
+        <v>163568533</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E379" s="4">
-        <v>7725669</v>
+        <v>5915736</v>
       </c>
       <c r="F379" s="4" t="s">
         <v>51</v>
@@ -34268,24 +34274,24 @@
         <v>133</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K379" s="4"/>
       <c r="L379" s="4" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="M379" s="4" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="N379" s="4">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="O379" s="4" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="P379" s="5"/>
       <c r="Q379" s="4" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="R379" s="4" t="s">
         <v>185</v>
@@ -34296,21 +34302,17 @@
       <c r="T379" s="4">
         <v>0</v>
       </c>
-      <c r="U379" s="4" t="s">
-        <v>1630</v>
-      </c>
-      <c r="V379" s="4" t="s">
-        <v>333</v>
-      </c>
+      <c r="U379" s="4"/>
+      <c r="V379" s="4"/>
       <c r="W379" s="4">
         <v>3</v>
       </c>
       <c r="X379" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y379" s="4"/>
       <c r="Z379" s="4" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="AA379" s="4" t="s">
         <v>48</v>
@@ -34324,16 +34326,16 @@
         <v>1000</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="C380" s="4">
-        <v>163568519</v>
+        <v>163568520</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E380" s="4">
-        <v>5899639</v>
+        <v>5364215</v>
       </c>
       <c r="F380" s="4" t="s">
         <v>51</v>
@@ -34348,24 +34350,24 @@
         <v>133</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K380" s="4"/>
       <c r="L380" s="4" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="M380" s="4" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="N380" s="4">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="O380" s="4" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="P380" s="5"/>
       <c r="Q380" s="4" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="R380" s="4" t="s">
         <v>185</v>
@@ -34377,10 +34379,10 @@
         <v>0</v>
       </c>
       <c r="U380" s="4" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="V380" s="4" t="s">
-        <v>525</v>
+        <v>430</v>
       </c>
       <c r="W380" s="4">
         <v>3</v>
@@ -34404,16 +34406,16 @@
         <v>1000</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>824</v>
+        <v>211</v>
       </c>
       <c r="C381" s="4">
-        <v>163568518</v>
+        <v>163568516</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E381" s="4">
-        <v>5902466</v>
+        <v>7725669</v>
       </c>
       <c r="F381" s="4" t="s">
         <v>51</v>
@@ -34428,24 +34430,24 @@
         <v>133</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K381" s="4"/>
       <c r="L381" s="4" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="M381" s="4" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="N381" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O381" s="4" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="P381" s="5"/>
       <c r="Q381" s="4" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="R381" s="4" t="s">
         <v>185</v>
@@ -34457,10 +34459,10 @@
         <v>0</v>
       </c>
       <c r="U381" s="4" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="V381" s="4" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="W381" s="4">
         <v>3</v>
@@ -34470,9 +34472,11 @@
       </c>
       <c r="Y381" s="4"/>
       <c r="Z381" s="4" t="s">
-        <v>1636</v>
-      </c>
-      <c r="AA381" s="4"/>
+        <v>1628</v>
+      </c>
+      <c r="AA381" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB381" s="4" t="s">
         <v>49</v>
       </c>
@@ -34482,16 +34486,16 @@
         <v>1000</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>824</v>
+        <v>1359</v>
       </c>
       <c r="C382" s="4">
-        <v>163568532</v>
+        <v>163568519</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E382" s="4">
-        <v>4326681</v>
+        <v>5899639</v>
       </c>
       <c r="F382" s="4" t="s">
         <v>51</v>
@@ -34506,24 +34510,24 @@
         <v>133</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K382" s="4"/>
       <c r="L382" s="4" t="s">
-        <v>1637</v>
+        <v>1621</v>
       </c>
       <c r="M382" s="4" t="s">
-        <v>1638</v>
+        <v>1616</v>
       </c>
       <c r="N382" s="4">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="O382" s="4" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="P382" s="5"/>
       <c r="Q382" s="4" t="s">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="R382" s="4" t="s">
         <v>185</v>
@@ -34535,10 +34539,10 @@
         <v>0</v>
       </c>
       <c r="U382" s="4" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="V382" s="4" t="s">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="W382" s="4">
         <v>3</v>
@@ -34548,7 +34552,7 @@
       </c>
       <c r="Y382" s="4"/>
       <c r="Z382" s="4" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="AA382" s="4" t="s">
         <v>48</v>
@@ -34565,13 +34569,13 @@
         <v>824</v>
       </c>
       <c r="C383" s="4">
-        <v>163568534</v>
+        <v>163568518</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E383" s="4">
-        <v>4326782</v>
+        <v>5902466</v>
       </c>
       <c r="F383" s="4" t="s">
         <v>51</v>
@@ -34586,24 +34590,24 @@
         <v>133</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K383" s="4"/>
       <c r="L383" s="4" t="s">
+        <v>1621</v>
+      </c>
+      <c r="M383" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="N383" s="4">
+        <v>42</v>
+      </c>
+      <c r="O383" s="4" t="s">
         <v>1637</v>
-      </c>
-      <c r="M383" s="4" t="s">
-        <v>1638</v>
-      </c>
-      <c r="N383" s="4">
-        <v>16</v>
-      </c>
-      <c r="O383" s="4" t="s">
-        <v>1642</v>
       </c>
       <c r="P383" s="5"/>
       <c r="Q383" s="4" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="R383" s="4" t="s">
         <v>185</v>
@@ -34615,10 +34619,10 @@
         <v>0</v>
       </c>
       <c r="U383" s="4" t="s">
-        <v>1644</v>
+        <v>1639</v>
       </c>
       <c r="V383" s="4" t="s">
-        <v>45</v>
+        <v>349</v>
       </c>
       <c r="W383" s="4">
         <v>3</v>
@@ -34628,11 +34632,9 @@
       </c>
       <c r="Y383" s="4"/>
       <c r="Z383" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA383" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1640</v>
+      </c>
+      <c r="AA383" s="4"/>
       <c r="AB383" s="4" t="s">
         <v>49</v>
       </c>
@@ -34645,13 +34647,13 @@
         <v>824</v>
       </c>
       <c r="C384" s="4">
-        <v>163568525</v>
+        <v>163568532</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E384" s="4">
-        <v>7752848</v>
+        <v>4326681</v>
       </c>
       <c r="F384" s="4" t="s">
         <v>51</v>
@@ -34666,24 +34668,24 @@
         <v>133</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K384" s="4"/>
       <c r="L384" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M384" s="4" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="N384" s="4">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="O384" s="4" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="P384" s="5"/>
       <c r="Q384" s="4" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="R384" s="4" t="s">
         <v>185</v>
@@ -34695,10 +34697,10 @@
         <v>0</v>
       </c>
       <c r="U384" s="4" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="V384" s="4" t="s">
-        <v>131</v>
+        <v>581</v>
       </c>
       <c r="W384" s="4">
         <v>3</v>
@@ -34708,7 +34710,7 @@
       </c>
       <c r="Y384" s="4"/>
       <c r="Z384" s="4" t="s">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="AA384" s="4" t="s">
         <v>48</v>
@@ -34722,16 +34724,16 @@
         <v>1000</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>33</v>
+        <v>824</v>
       </c>
       <c r="C385" s="4">
-        <v>163568527</v>
+        <v>163568534</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E385" s="4">
-        <v>4326678</v>
+        <v>4326782</v>
       </c>
       <c r="F385" s="4" t="s">
         <v>51</v>
@@ -34746,24 +34748,24 @@
         <v>133</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K385" s="4"/>
       <c r="L385" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M385" s="4" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="N385" s="4">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="O385" s="4" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="P385" s="5"/>
       <c r="Q385" s="4" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="R385" s="4" t="s">
         <v>185</v>
@@ -34775,20 +34777,20 @@
         <v>0</v>
       </c>
       <c r="U385" s="4" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="V385" s="4" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="W385" s="4">
         <v>3</v>
       </c>
       <c r="X385" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y385" s="4"/>
       <c r="Z385" s="4" t="s">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="AA385" s="4" t="s">
         <v>48</v>
@@ -34802,16 +34804,16 @@
         <v>1000</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>33</v>
+        <v>824</v>
       </c>
       <c r="C386" s="4">
-        <v>163568530</v>
+        <v>163568525</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E386" s="4">
-        <v>4323381</v>
+        <v>7752848</v>
       </c>
       <c r="F386" s="4" t="s">
         <v>51</v>
@@ -34826,24 +34828,24 @@
         <v>133</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K386" s="4"/>
       <c r="L386" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M386" s="4" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="N386" s="4">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="O386" s="4" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="P386" s="5"/>
       <c r="Q386" s="4" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="R386" s="4" t="s">
         <v>185</v>
@@ -34855,22 +34857,24 @@
         <v>0</v>
       </c>
       <c r="U386" s="4" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="V386" s="4" t="s">
-        <v>349</v>
+        <v>131</v>
       </c>
       <c r="W386" s="4">
         <v>3</v>
       </c>
       <c r="X386" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y386" s="4"/>
       <c r="Z386" s="4" t="s">
-        <v>1636</v>
-      </c>
-      <c r="AA386" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="AA386" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB386" s="4" t="s">
         <v>49</v>
       </c>
@@ -34883,13 +34887,13 @@
         <v>33</v>
       </c>
       <c r="C387" s="4">
-        <v>163568531</v>
+        <v>163568527</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E387" s="4">
-        <v>5867265</v>
+        <v>4326678</v>
       </c>
       <c r="F387" s="4" t="s">
         <v>51</v>
@@ -34904,24 +34908,24 @@
         <v>133</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K387" s="4"/>
       <c r="L387" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M387" s="4" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="N387" s="4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="O387" s="4" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="P387" s="5"/>
       <c r="Q387" s="4" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="R387" s="4" t="s">
         <v>185</v>
@@ -34933,10 +34937,10 @@
         <v>0</v>
       </c>
       <c r="U387" s="4" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="V387" s="4" t="s">
-        <v>487</v>
+        <v>131</v>
       </c>
       <c r="W387" s="4">
         <v>3</v>
@@ -34963,13 +34967,13 @@
         <v>33</v>
       </c>
       <c r="C388" s="4">
-        <v>163568529</v>
+        <v>163568530</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E388" s="4">
-        <v>6528085</v>
+        <v>4323381</v>
       </c>
       <c r="F388" s="4" t="s">
         <v>51</v>
@@ -34984,36 +34988,36 @@
         <v>133</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K388" s="4"/>
       <c r="L388" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M388" s="4" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="N388" s="4">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O388" s="4" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="P388" s="5"/>
       <c r="Q388" s="4" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="R388" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S388" s="4">
-        <v>62003.21</v>
+        <v>0</v>
       </c>
       <c r="T388" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U388" s="4" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="V388" s="4" t="s">
         <v>349</v>
@@ -35026,11 +35030,9 @@
       </c>
       <c r="Y388" s="4"/>
       <c r="Z388" s="4" t="s">
-        <v>1616</v>
-      </c>
-      <c r="AA388" s="4" t="s">
-        <v>101</v>
-      </c>
+        <v>1640</v>
+      </c>
+      <c r="AA388" s="4"/>
       <c r="AB388" s="4" t="s">
         <v>49</v>
       </c>
@@ -35040,16 +35042,16 @@
         <v>1000</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
       <c r="C389" s="4">
-        <v>163568513</v>
+        <v>163568531</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E389" s="4">
-        <v>4323378</v>
+        <v>5867265</v>
       </c>
       <c r="F389" s="4" t="s">
         <v>51</v>
@@ -35064,24 +35066,24 @@
         <v>133</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K389" s="4"/>
       <c r="L389" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M389" s="4" t="s">
-        <v>1612</v>
+        <v>1642</v>
       </c>
       <c r="N389" s="4">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O389" s="4" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="P389" s="5"/>
       <c r="Q389" s="4" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="R389" s="4" t="s">
         <v>185</v>
@@ -35092,19 +35094,25 @@
       <c r="T389" s="4">
         <v>0</v>
       </c>
-      <c r="U389" s="4"/>
-      <c r="V389" s="4"/>
+      <c r="U389" s="4" t="s">
+        <v>1660</v>
+      </c>
+      <c r="V389" s="4" t="s">
+        <v>487</v>
+      </c>
       <c r="W389" s="4">
         <v>3</v>
       </c>
       <c r="X389" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y389" s="4"/>
       <c r="Z389" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA389" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="AA389" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB389" s="4" t="s">
         <v>49</v>
       </c>
@@ -35114,16 +35122,16 @@
         <v>1000</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
       <c r="C390" s="4">
-        <v>163568514</v>
+        <v>163568529</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E390" s="4">
-        <v>5867630</v>
+        <v>6528085</v>
       </c>
       <c r="F390" s="4" t="s">
         <v>51</v>
@@ -35138,36 +35146,36 @@
         <v>133</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K390" s="4"/>
       <c r="L390" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M390" s="4" t="s">
-        <v>1612</v>
+        <v>1642</v>
       </c>
       <c r="N390" s="4">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="O390" s="4" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="P390" s="5"/>
       <c r="Q390" s="4" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="R390" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S390" s="4">
-        <v>0</v>
+        <v>62003.21</v>
       </c>
       <c r="T390" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U390" s="4" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="V390" s="4" t="s">
         <v>349</v>
@@ -35176,14 +35184,14 @@
         <v>3</v>
       </c>
       <c r="X390" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y390" s="4"/>
       <c r="Z390" s="4" t="s">
-        <v>334</v>
+        <v>1620</v>
       </c>
       <c r="AA390" s="4" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="AB390" s="4" t="s">
         <v>49</v>
@@ -35194,16 +35202,16 @@
         <v>1000</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="C391" s="4">
-        <v>163569195</v>
+        <v>163568513</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E391" s="4">
-        <v>5364204</v>
+        <v>4323378</v>
       </c>
       <c r="F391" s="4" t="s">
         <v>51</v>
@@ -35218,24 +35226,24 @@
         <v>133</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K391" s="4"/>
       <c r="L391" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M391" s="4" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="N391" s="4">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O391" s="4" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="P391" s="5"/>
       <c r="Q391" s="4" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="R391" s="4" t="s">
         <v>185</v>
@@ -35252,15 +35260,13 @@
         <v>3</v>
       </c>
       <c r="X391" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y391" s="4"/>
       <c r="Z391" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA391" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AA391" s="4"/>
       <c r="AB391" s="4" t="s">
         <v>49</v>
       </c>
@@ -35273,13 +35279,13 @@
         <v>211</v>
       </c>
       <c r="C392" s="4">
-        <v>163568511</v>
+        <v>163568514</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E392" s="4">
-        <v>4326661</v>
+        <v>5867630</v>
       </c>
       <c r="F392" s="4" t="s">
         <v>51</v>
@@ -35294,24 +35300,24 @@
         <v>133</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K392" s="4"/>
       <c r="L392" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M392" s="4" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="N392" s="4">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="O392" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="P392" s="5"/>
       <c r="Q392" s="4" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="R392" s="4" t="s">
         <v>185</v>
@@ -35323,10 +35329,10 @@
         <v>0</v>
       </c>
       <c r="U392" s="4" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="V392" s="4" t="s">
-        <v>581</v>
+        <v>349</v>
       </c>
       <c r="W392" s="4">
         <v>3</v>
@@ -35353,13 +35359,13 @@
         <v>33</v>
       </c>
       <c r="C393" s="4">
-        <v>163568523</v>
+        <v>163569195</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E393" s="4">
-        <v>4327238</v>
+        <v>5364204</v>
       </c>
       <c r="F393" s="4" t="s">
         <v>51</v>
@@ -35374,24 +35380,24 @@
         <v>133</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K393" s="4"/>
       <c r="L393" s="4" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="M393" s="4" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="N393" s="4">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="O393" s="4" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="P393" s="5"/>
       <c r="Q393" s="4" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="R393" s="4" t="s">
         <v>185</v>
@@ -35412,9 +35418,11 @@
       </c>
       <c r="Y393" s="4"/>
       <c r="Z393" s="4" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AA393" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="AA393" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB393" s="4" t="s">
         <v>49</v>
       </c>
@@ -35424,16 +35432,16 @@
         <v>1000</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="C394" s="4">
-        <v>163568558</v>
+        <v>163568511</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E394" s="4">
-        <v>7209364</v>
+        <v>4326661</v>
       </c>
       <c r="F394" s="4" t="s">
         <v>51</v>
@@ -35448,27 +35456,27 @@
         <v>133</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1672</v>
+        <v>1586</v>
       </c>
       <c r="K394" s="4"/>
       <c r="L394" s="4" t="s">
-        <v>1673</v>
+        <v>1641</v>
       </c>
       <c r="M394" s="4" t="s">
-        <v>1674</v>
+        <v>1616</v>
       </c>
       <c r="N394" s="4">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="O394" s="4" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="P394" s="5"/>
       <c r="Q394" s="4" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="R394" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S394" s="4">
         <v>0</v>
@@ -35477,16 +35485,16 @@
         <v>0</v>
       </c>
       <c r="U394" s="4" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="V394" s="4" t="s">
-        <v>45</v>
+        <v>581</v>
       </c>
       <c r="W394" s="4">
         <v>3</v>
       </c>
       <c r="X394" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y394" s="4"/>
       <c r="Z394" s="4" t="s">
@@ -35507,13 +35515,13 @@
         <v>33</v>
       </c>
       <c r="C395" s="4">
-        <v>163568551</v>
+        <v>163568523</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E395" s="4">
-        <v>7949838</v>
+        <v>4327238</v>
       </c>
       <c r="F395" s="4" t="s">
         <v>51</v>
@@ -35528,27 +35536,27 @@
         <v>133</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1672</v>
+        <v>1586</v>
       </c>
       <c r="K395" s="4"/>
       <c r="L395" s="4" t="s">
-        <v>1673</v>
+        <v>1641</v>
       </c>
       <c r="M395" s="4" t="s">
-        <v>1678</v>
+        <v>1616</v>
       </c>
       <c r="N395" s="4">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O395" s="4" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="P395" s="5"/>
       <c r="Q395" s="4" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="R395" s="4" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="S395" s="4">
         <v>0</v>
@@ -35556,12 +35564,8 @@
       <c r="T395" s="4">
         <v>0</v>
       </c>
-      <c r="U395" s="4" t="s">
-        <v>1681</v>
-      </c>
-      <c r="V395" s="4" t="s">
-        <v>266</v>
-      </c>
+      <c r="U395" s="4"/>
+      <c r="V395" s="4"/>
       <c r="W395" s="4">
         <v>3</v>
       </c>
@@ -35570,11 +35574,9 @@
       </c>
       <c r="Y395" s="4"/>
       <c r="Z395" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA395" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1625</v>
+      </c>
+      <c r="AA395" s="4"/>
       <c r="AB395" s="4" t="s">
         <v>49</v>
       </c>
@@ -35587,13 +35589,13 @@
         <v>33</v>
       </c>
       <c r="C396" s="4">
-        <v>163568548</v>
+        <v>163568558</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E396" s="4">
-        <v>7742088</v>
+        <v>7209364</v>
       </c>
       <c r="F396" s="4" t="s">
         <v>51</v>
@@ -35608,27 +35610,27 @@
         <v>133</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="K396" s="4"/>
       <c r="L396" s="4" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="M396" s="4" t="s">
         <v>1678</v>
       </c>
       <c r="N396" s="4">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="O396" s="4" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="P396" s="5"/>
       <c r="Q396" s="4" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="R396" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S396" s="4">
         <v>0</v>
@@ -35637,10 +35639,10 @@
         <v>0</v>
       </c>
       <c r="U396" s="4" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="V396" s="4" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="W396" s="4">
         <v>3</v>
@@ -35650,7 +35652,7 @@
       </c>
       <c r="Y396" s="4"/>
       <c r="Z396" s="4" t="s">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="AA396" s="4" t="s">
         <v>48</v>
@@ -35667,13 +35669,13 @@
         <v>33</v>
       </c>
       <c r="C397" s="4">
-        <v>163568549</v>
+        <v>163568551</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E397" s="4">
-        <v>7730020</v>
+        <v>7949838</v>
       </c>
       <c r="F397" s="4" t="s">
         <v>51</v>
@@ -35688,24 +35690,24 @@
         <v>133</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="K397" s="4"/>
       <c r="L397" s="4" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="M397" s="4" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="N397" s="4">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="O397" s="4" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="P397" s="5"/>
       <c r="Q397" s="4" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="R397" s="4" t="s">
         <v>43</v>
@@ -35717,10 +35719,10 @@
         <v>0</v>
       </c>
       <c r="U397" s="4" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="V397" s="4" t="s">
-        <v>131</v>
+        <v>266</v>
       </c>
       <c r="W397" s="4">
         <v>3</v>
@@ -35747,13 +35749,13 @@
         <v>33</v>
       </c>
       <c r="C398" s="4">
-        <v>163568552</v>
+        <v>163568548</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E398" s="4">
-        <v>7258875</v>
+        <v>7742088</v>
       </c>
       <c r="F398" s="4" t="s">
         <v>51</v>
@@ -35768,24 +35770,24 @@
         <v>133</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="K398" s="4"/>
       <c r="L398" s="4" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="M398" s="4" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="N398" s="4">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="O398" s="4" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="P398" s="5"/>
       <c r="Q398" s="4" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="R398" s="4" t="s">
         <v>43</v>
@@ -35797,10 +35799,10 @@
         <v>0</v>
       </c>
       <c r="U398" s="4" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="V398" s="4" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="W398" s="4">
         <v>3</v>
@@ -35810,9 +35812,11 @@
       </c>
       <c r="Y398" s="4"/>
       <c r="Z398" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="AA398" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="AA398" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB398" s="4" t="s">
         <v>49</v>
       </c>
@@ -35825,13 +35829,13 @@
         <v>33</v>
       </c>
       <c r="C399" s="4">
-        <v>163568560</v>
+        <v>163568549</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E399" s="4">
-        <v>7949883</v>
+        <v>7730020</v>
       </c>
       <c r="F399" s="4" t="s">
         <v>51</v>
@@ -35846,24 +35850,24 @@
         <v>133</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="K399" s="4"/>
       <c r="L399" s="4" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="M399" s="4" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="N399" s="4">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="O399" s="4" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="P399" s="5"/>
       <c r="Q399" s="4" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="R399" s="4" t="s">
         <v>43</v>
@@ -35875,10 +35879,10 @@
         <v>0</v>
       </c>
       <c r="U399" s="4" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="V399" s="4" t="s">
-        <v>266</v>
+        <v>131</v>
       </c>
       <c r="W399" s="4">
         <v>3</v>
@@ -35888,9 +35892,11 @@
       </c>
       <c r="Y399" s="4"/>
       <c r="Z399" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="AA399" s="4"/>
+        <v>334</v>
+      </c>
+      <c r="AA399" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB399" s="4" t="s">
         <v>49</v>
       </c>
@@ -35903,13 +35909,13 @@
         <v>33</v>
       </c>
       <c r="C400" s="4">
-        <v>163342542</v>
+        <v>163568552</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E400" s="4">
-        <v>1108684</v>
+        <v>7258875</v>
       </c>
       <c r="F400" s="4" t="s">
         <v>51</v>
@@ -35921,26 +35927,30 @@
         <v>133</v>
       </c>
       <c r="I400" s="4" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1694</v>
+        <v>1676</v>
       </c>
       <c r="K400" s="4"/>
       <c r="L400" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M400" s="4"/>
-      <c r="N400" s="4"/>
+        <v>1677</v>
+      </c>
+      <c r="M400" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="N400" s="4">
+        <v>51</v>
+      </c>
       <c r="O400" s="4" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="P400" s="5"/>
       <c r="Q400" s="4" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="R400" s="4" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="S400" s="4">
         <v>0</v>
@@ -35949,24 +35959,22 @@
         <v>0</v>
       </c>
       <c r="U400" s="4" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="V400" s="4" t="s">
-        <v>333</v>
+        <v>45</v>
       </c>
       <c r="W400" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X400" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y400" s="4"/>
       <c r="Z400" s="4" t="s">
-        <v>1698</v>
-      </c>
-      <c r="AA400" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AA400" s="4"/>
       <c r="AB400" s="4" t="s">
         <v>49</v>
       </c>
@@ -35976,16 +35984,16 @@
         <v>1000</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1136</v>
+        <v>33</v>
       </c>
       <c r="C401" s="4">
-        <v>163569111</v>
+        <v>163568560</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E401" s="4">
-        <v>8161103</v>
+        <v>7949883</v>
       </c>
       <c r="F401" s="4" t="s">
         <v>51</v>
@@ -36000,21 +36008,27 @@
         <v>133</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1699</v>
+        <v>1676</v>
       </c>
       <c r="K401" s="4"/>
-      <c r="L401" s="4"/>
-      <c r="M401" s="4"/>
-      <c r="N401" s="4"/>
+      <c r="L401" s="4" t="s">
+        <v>1677</v>
+      </c>
+      <c r="M401" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="N401" s="4">
+        <v>51</v>
+      </c>
       <c r="O401" s="4" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="P401" s="5"/>
       <c r="Q401" s="4" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="R401" s="4" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="S401" s="4">
         <v>0</v>
@@ -36022,21 +36036,23 @@
       <c r="T401" s="4">
         <v>0</v>
       </c>
-      <c r="U401" s="4"/>
-      <c r="V401" s="4"/>
+      <c r="U401" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="V401" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="W401" s="4">
         <v>3</v>
       </c>
       <c r="X401" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y401" s="4"/>
       <c r="Z401" s="4" t="s">
-        <v>1702</v>
-      </c>
-      <c r="AA401" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AA401" s="4"/>
       <c r="AB401" s="4" t="s">
         <v>49</v>
       </c>
@@ -36049,13 +36065,13 @@
         <v>33</v>
       </c>
       <c r="C402" s="4">
-        <v>163529880</v>
+        <v>163342542</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="E402" s="4">
-        <v>1052016</v>
+        <v>1108684</v>
       </c>
       <c r="F402" s="4" t="s">
         <v>51</v>
@@ -36067,28 +36083,26 @@
         <v>133</v>
       </c>
       <c r="I402" s="4" t="s">
-        <v>133</v>
+        <v>287</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="K402" s="4"/>
       <c r="L402" s="4" t="s">
-        <v>982</v>
-      </c>
-      <c r="M402" s="4" t="s">
-        <v>1703</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M402" s="4"/>
       <c r="N402" s="4"/>
       <c r="O402" s="4" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="P402" s="5"/>
       <c r="Q402" s="4" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
       <c r="R402" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S402" s="4">
         <v>0</v>
@@ -36096,20 +36110,24 @@
       <c r="T402" s="4">
         <v>0</v>
       </c>
-      <c r="U402" s="4"/>
-      <c r="V402" s="4"/>
+      <c r="U402" s="4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="V402" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W402" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X402" s="4" t="s">
-        <v>1706</v>
+        <v>46</v>
       </c>
       <c r="Y402" s="4"/>
       <c r="Z402" s="4" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="AA402" s="4" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="AB402" s="4" t="s">
         <v>49</v>
@@ -36120,16 +36138,16 @@
         <v>1000</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>33</v>
+        <v>1136</v>
       </c>
       <c r="C403" s="4">
-        <v>163585693</v>
+        <v>163569111</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E403" s="4">
-        <v>6765644</v>
+        <v>8161103</v>
       </c>
       <c r="F403" s="4" t="s">
         <v>51</v>
@@ -36144,23 +36162,21 @@
         <v>133</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="K403" s="4"/>
-      <c r="L403" s="4" t="s">
-        <v>296</v>
-      </c>
+      <c r="L403" s="4"/>
       <c r="M403" s="4"/>
       <c r="N403" s="4"/>
       <c r="O403" s="4" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="P403" s="5"/>
       <c r="Q403" s="4" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
       <c r="R403" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S403" s="4">
         <v>0</v>
@@ -36171,14 +36187,14 @@
       <c r="U403" s="4"/>
       <c r="V403" s="4"/>
       <c r="W403" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X403" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y403" s="4"/>
       <c r="Z403" s="4" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
       <c r="AA403" s="4" t="s">
         <v>66</v>
@@ -36195,13 +36211,13 @@
         <v>33</v>
       </c>
       <c r="C404" s="4">
-        <v>163568562</v>
+        <v>163529880</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E404" s="4">
-        <v>1030230</v>
+        <v>1052016</v>
       </c>
       <c r="F404" s="4" t="s">
         <v>51</v>
@@ -36216,28 +36232,28 @@
         <v>133</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1712</v>
+        <v>1703</v>
       </c>
       <c r="K404" s="4"/>
       <c r="L404" s="4" t="s">
-        <v>296</v>
+        <v>982</v>
       </c>
       <c r="M404" s="4" t="s">
-        <v>1713</v>
+        <v>1707</v>
       </c>
       <c r="N404" s="4"/>
       <c r="O404" s="4" t="s">
-        <v>1714</v>
+        <v>1708</v>
       </c>
       <c r="P404" s="5"/>
       <c r="Q404" s="4" t="s">
-        <v>1715</v>
+        <v>1709</v>
       </c>
       <c r="R404" s="4" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="S404" s="4">
-        <v>2968256.09</v>
+        <v>0</v>
       </c>
       <c r="T404" s="4">
         <v>0</v>
@@ -36245,17 +36261,17 @@
       <c r="U404" s="4"/>
       <c r="V404" s="4"/>
       <c r="W404" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X404" s="4" t="s">
-        <v>46</v>
+        <v>1710</v>
       </c>
       <c r="Y404" s="4"/>
       <c r="Z404" s="4" t="s">
-        <v>1624</v>
+        <v>1711</v>
       </c>
       <c r="AA404" s="4" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="AB404" s="4" t="s">
         <v>49</v>
@@ -36269,13 +36285,13 @@
         <v>33</v>
       </c>
       <c r="C405" s="4">
-        <v>163568564</v>
+        <v>163585693</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E405" s="4">
-        <v>1024682</v>
+        <v>6765644</v>
       </c>
       <c r="F405" s="4" t="s">
         <v>51</v>
@@ -36296,19 +36312,17 @@
       <c r="L405" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="M405" s="4" t="s">
-        <v>1713</v>
-      </c>
+      <c r="M405" s="4"/>
       <c r="N405" s="4"/>
       <c r="O405" s="4" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="P405" s="5"/>
       <c r="Q405" s="4" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
       <c r="R405" s="4" t="s">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="S405" s="4">
         <v>0</v>
@@ -36319,14 +36333,14 @@
       <c r="U405" s="4"/>
       <c r="V405" s="4"/>
       <c r="W405" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X405" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y405" s="4"/>
       <c r="Z405" s="4" t="s">
-        <v>461</v>
+        <v>1715</v>
       </c>
       <c r="AA405" s="4" t="s">
         <v>66</v>
@@ -36343,13 +36357,13 @@
         <v>33</v>
       </c>
       <c r="C406" s="4">
-        <v>163568569</v>
+        <v>163568562</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E406" s="4">
-        <v>1024675</v>
+        <v>1030230</v>
       </c>
       <c r="F406" s="4" t="s">
         <v>51</v>
@@ -36364,14 +36378,14 @@
         <v>133</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K406" s="4"/>
       <c r="L406" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M406" s="4" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="N406" s="4"/>
       <c r="O406" s="4" t="s">
@@ -36385,10 +36399,10 @@
         <v>167</v>
       </c>
       <c r="S406" s="4">
-        <v>806727.6800000001</v>
+        <v>2968256.09</v>
       </c>
       <c r="T406" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U406" s="4"/>
       <c r="V406" s="4"/>
@@ -36400,13 +36414,13 @@
       </c>
       <c r="Y406" s="4"/>
       <c r="Z406" s="4" t="s">
-        <v>436</v>
+        <v>1628</v>
       </c>
       <c r="AA406" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB406" s="4" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
     </row>
     <row r="407" spans="1:28">
@@ -36417,13 +36431,13 @@
         <v>33</v>
       </c>
       <c r="C407" s="4">
-        <v>163568570</v>
+        <v>163568564</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E407" s="4">
-        <v>1024679</v>
+        <v>1024682</v>
       </c>
       <c r="F407" s="4" t="s">
         <v>51</v>
@@ -36438,14 +36452,14 @@
         <v>133</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K407" s="4"/>
       <c r="L407" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M407" s="4" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="N407" s="4"/>
       <c r="O407" s="4" t="s">
@@ -36459,17 +36473,13 @@
         <v>167</v>
       </c>
       <c r="S407" s="4">
-        <v>255459.04</v>
+        <v>0</v>
       </c>
       <c r="T407" s="4">
-        <v>1</v>
-      </c>
-      <c r="U407" s="4" t="s">
-        <v>1722</v>
-      </c>
-      <c r="V407" s="4" t="s">
-        <v>610</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U407" s="4"/>
+      <c r="V407" s="4"/>
       <c r="W407" s="4">
         <v>3</v>
       </c>
@@ -36478,10 +36488,10 @@
       </c>
       <c r="Y407" s="4"/>
       <c r="Z407" s="4" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="AA407" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB407" s="4" t="s">
         <v>49</v>
@@ -36495,13 +36505,13 @@
         <v>33</v>
       </c>
       <c r="C408" s="4">
-        <v>163568574</v>
+        <v>163568569</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E408" s="4">
-        <v>1024684</v>
+        <v>1024675</v>
       </c>
       <c r="F408" s="4" t="s">
         <v>51</v>
@@ -36516,38 +36526,34 @@
         <v>133</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K408" s="4"/>
       <c r="L408" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M408" s="4" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="N408" s="4"/>
       <c r="O408" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="P408" s="5"/>
       <c r="Q408" s="4" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="R408" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S408" s="4">
-        <v>6432996.49</v>
+        <v>806727.6800000001</v>
       </c>
       <c r="T408" s="4">
-        <v>30</v>
-      </c>
-      <c r="U408" s="4" t="s">
-        <v>1725</v>
-      </c>
-      <c r="V408" s="4" t="s">
-        <v>610</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="U408" s="4"/>
+      <c r="V408" s="4"/>
       <c r="W408" s="4">
         <v>3</v>
       </c>
@@ -36556,10 +36562,10 @@
       </c>
       <c r="Y408" s="4"/>
       <c r="Z408" s="4" t="s">
-        <v>1726</v>
+        <v>436</v>
       </c>
       <c r="AA408" s="4" t="s">
-        <v>280</v>
+        <v>66</v>
       </c>
       <c r="AB408" s="4" t="s">
         <v>223</v>
@@ -36573,13 +36579,13 @@
         <v>33</v>
       </c>
       <c r="C409" s="4">
-        <v>163568546</v>
+        <v>163568570</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E409" s="4">
-        <v>1024712</v>
+        <v>1024679</v>
       </c>
       <c r="F409" s="4" t="s">
         <v>51</v>
@@ -36594,34 +36600,38 @@
         <v>133</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K409" s="4"/>
       <c r="L409" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M409" s="4" t="s">
-        <v>1727</v>
+        <v>1717</v>
       </c>
       <c r="N409" s="4"/>
       <c r="O409" s="4" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="P409" s="5"/>
       <c r="Q409" s="4" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
       <c r="R409" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S409" s="4">
-        <v>0</v>
+        <v>255459.04</v>
       </c>
       <c r="T409" s="4">
-        <v>0</v>
-      </c>
-      <c r="U409" s="4"/>
-      <c r="V409" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U409" s="4" t="s">
+        <v>1726</v>
+      </c>
+      <c r="V409" s="4" t="s">
+        <v>610</v>
+      </c>
       <c r="W409" s="4">
         <v>3</v>
       </c>
@@ -36630,10 +36640,10 @@
       </c>
       <c r="Y409" s="4"/>
       <c r="Z409" s="4" t="s">
-        <v>1730</v>
+        <v>424</v>
       </c>
       <c r="AA409" s="4" t="s">
-        <v>642</v>
+        <v>48</v>
       </c>
       <c r="AB409" s="4" t="s">
         <v>49</v>
@@ -36644,16 +36654,16 @@
         <v>1000</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>418</v>
+        <v>33</v>
       </c>
       <c r="C410" s="4">
-        <v>163568554</v>
+        <v>163568574</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E410" s="4">
-        <v>1024719</v>
+        <v>1024684</v>
       </c>
       <c r="F410" s="4" t="s">
         <v>51</v>
@@ -36668,51 +36678,53 @@
         <v>133</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K410" s="4"/>
       <c r="L410" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M410" s="4" t="s">
-        <v>1727</v>
+        <v>1717</v>
       </c>
       <c r="N410" s="4"/>
       <c r="O410" s="4" t="s">
-        <v>1731</v>
+        <v>1727</v>
       </c>
       <c r="P410" s="5"/>
       <c r="Q410" s="4" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
       <c r="R410" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S410" s="4">
-        <v>0</v>
+        <v>6432996.49</v>
       </c>
       <c r="T410" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="U410" s="4" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
       <c r="V410" s="4" t="s">
-        <v>1734</v>
+        <v>610</v>
       </c>
       <c r="W410" s="4">
         <v>3</v>
       </c>
       <c r="X410" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y410" s="4"/>
       <c r="Z410" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="AA410" s="4"/>
+        <v>1730</v>
+      </c>
+      <c r="AA410" s="4" t="s">
+        <v>280</v>
+      </c>
       <c r="AB410" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="411" spans="1:28">
@@ -36720,16 +36732,16 @@
         <v>1000</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>418</v>
+        <v>33</v>
       </c>
       <c r="C411" s="4">
-        <v>163568555</v>
+        <v>163568546</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E411" s="4">
-        <v>1024710</v>
+        <v>1024712</v>
       </c>
       <c r="F411" s="4" t="s">
         <v>51</v>
@@ -36744,31 +36756,31 @@
         <v>133</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K411" s="4"/>
       <c r="L411" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M411" s="4" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="N411" s="4"/>
       <c r="O411" s="4" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
       <c r="P411" s="5"/>
       <c r="Q411" s="4" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="R411" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S411" s="4">
-        <v>208021.49</v>
+        <v>0</v>
       </c>
       <c r="T411" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U411" s="4"/>
       <c r="V411" s="4"/>
@@ -36776,14 +36788,14 @@
         <v>3</v>
       </c>
       <c r="X411" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y411" s="4"/>
       <c r="Z411" s="4" t="s">
-        <v>1624</v>
+        <v>1734</v>
       </c>
       <c r="AA411" s="4" t="s">
-        <v>48</v>
+        <v>642</v>
       </c>
       <c r="AB411" s="4" t="s">
         <v>49</v>
@@ -36794,16 +36806,16 @@
         <v>1000</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1136</v>
+        <v>418</v>
       </c>
       <c r="C412" s="4">
-        <v>163568559</v>
+        <v>163568554</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E412" s="4">
-        <v>1024718</v>
+        <v>1024719</v>
       </c>
       <c r="F412" s="4" t="s">
         <v>51</v>
@@ -36818,22 +36830,22 @@
         <v>133</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K412" s="4"/>
       <c r="L412" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M412" s="4" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="N412" s="4"/>
       <c r="O412" s="4" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="P412" s="5"/>
       <c r="Q412" s="4" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="R412" s="4" t="s">
         <v>167</v>
@@ -36845,10 +36857,10 @@
         <v>0</v>
       </c>
       <c r="U412" s="4" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="V412" s="4" t="s">
-        <v>581</v>
+        <v>1738</v>
       </c>
       <c r="W412" s="4">
         <v>3</v>
@@ -36858,11 +36870,9 @@
       </c>
       <c r="Y412" s="4"/>
       <c r="Z412" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="AA412" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AA412" s="4"/>
       <c r="AB412" s="4" t="s">
         <v>49</v>
       </c>
@@ -36872,16 +36882,16 @@
         <v>1000</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1136</v>
+        <v>418</v>
       </c>
       <c r="C413" s="4">
-        <v>163568561</v>
+        <v>163568555</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E413" s="4">
-        <v>1024748</v>
+        <v>1024710</v>
       </c>
       <c r="F413" s="4" t="s">
         <v>51</v>
@@ -36896,38 +36906,34 @@
         <v>133</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K413" s="4"/>
       <c r="L413" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M413" s="4" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="N413" s="4"/>
       <c r="O413" s="4" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="P413" s="5"/>
       <c r="Q413" s="4" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="R413" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S413" s="4">
-        <v>0</v>
+        <v>208021.49</v>
       </c>
       <c r="T413" s="4">
-        <v>0</v>
-      </c>
-      <c r="U413" s="4" t="s">
-        <v>1742</v>
-      </c>
-      <c r="V413" s="4" t="s">
-        <v>604</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U413" s="4"/>
+      <c r="V413" s="4"/>
       <c r="W413" s="4">
         <v>3</v>
       </c>
@@ -36936,7 +36942,7 @@
       </c>
       <c r="Y413" s="4"/>
       <c r="Z413" s="4" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="AA413" s="4" t="s">
         <v>48</v>
@@ -36953,13 +36959,13 @@
         <v>1136</v>
       </c>
       <c r="C414" s="4">
-        <v>163568571</v>
+        <v>163568559</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E414" s="4">
-        <v>1024704</v>
+        <v>1024718</v>
       </c>
       <c r="F414" s="4" t="s">
         <v>51</v>
@@ -36974,37 +36980,37 @@
         <v>133</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K414" s="4"/>
       <c r="L414" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M414" s="4" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="N414" s="4"/>
       <c r="O414" s="4" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="P414" s="5"/>
       <c r="Q414" s="4" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="R414" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S414" s="4">
-        <v>178233.87</v>
+        <v>0</v>
       </c>
       <c r="T414" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U414" s="4" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="V414" s="4" t="s">
-        <v>610</v>
+        <v>581</v>
       </c>
       <c r="W414" s="4">
         <v>3</v>
@@ -37014,10 +37020,10 @@
       </c>
       <c r="Y414" s="4"/>
       <c r="Z414" s="4" t="s">
-        <v>424</v>
+        <v>494</v>
       </c>
       <c r="AA414" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB414" s="4" t="s">
         <v>49</v>
@@ -37031,13 +37037,13 @@
         <v>1136</v>
       </c>
       <c r="C415" s="4">
-        <v>163568589</v>
+        <v>163568561</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E415" s="4">
-        <v>1024701</v>
+        <v>1024748</v>
       </c>
       <c r="F415" s="4" t="s">
         <v>51</v>
@@ -37052,22 +37058,22 @@
         <v>133</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="K415" s="4"/>
       <c r="L415" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M415" s="4" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="N415" s="4"/>
       <c r="O415" s="4" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="P415" s="5"/>
       <c r="Q415" s="4" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="R415" s="4" t="s">
         <v>167</v>
@@ -37079,10 +37085,10 @@
         <v>0</v>
       </c>
       <c r="U415" s="4" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="V415" s="4" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="W415" s="4">
         <v>3</v>
@@ -37092,10 +37098,10 @@
       </c>
       <c r="Y415" s="4"/>
       <c r="Z415" s="4" t="s">
-        <v>490</v>
+        <v>1628</v>
       </c>
       <c r="AA415" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB415" s="4" t="s">
         <v>49</v>
@@ -37106,16 +37112,16 @@
         <v>1000</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>536</v>
+        <v>1136</v>
       </c>
       <c r="C416" s="4">
-        <v>163568435</v>
+        <v>163568571</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E416" s="4">
-        <v>7870323</v>
+        <v>1024704</v>
       </c>
       <c r="F416" s="4" t="s">
         <v>51</v>
@@ -37130,34 +37136,38 @@
         <v>133</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1749</v>
+        <v>1716</v>
       </c>
       <c r="K416" s="4"/>
       <c r="L416" s="4" t="s">
-        <v>1750</v>
+        <v>296</v>
       </c>
       <c r="M416" s="4" t="s">
-        <v>1751</v>
+        <v>1731</v>
       </c>
       <c r="N416" s="4"/>
       <c r="O416" s="4" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="P416" s="5"/>
       <c r="Q416" s="4" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="R416" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S416" s="4">
-        <v>0</v>
+        <v>178233.87</v>
       </c>
       <c r="T416" s="4">
-        <v>0</v>
-      </c>
-      <c r="U416" s="4"/>
-      <c r="V416" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U416" s="4" t="s">
+        <v>1749</v>
+      </c>
+      <c r="V416" s="4" t="s">
+        <v>610</v>
+      </c>
       <c r="W416" s="4">
         <v>3</v>
       </c>
@@ -37166,10 +37176,10 @@
       </c>
       <c r="Y416" s="4"/>
       <c r="Z416" s="4" t="s">
-        <v>1754</v>
+        <v>424</v>
       </c>
       <c r="AA416" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB416" s="4" t="s">
         <v>49</v>
@@ -37180,16 +37190,16 @@
         <v>1000</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>33</v>
+        <v>1136</v>
       </c>
       <c r="C417" s="4">
-        <v>163586934</v>
+        <v>163568589</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E417" s="4">
-        <v>7788272</v>
+        <v>1024701</v>
       </c>
       <c r="F417" s="4" t="s">
         <v>51</v>
@@ -37204,23 +37214,25 @@
         <v>133</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1755</v>
+        <v>1716</v>
       </c>
       <c r="K417" s="4"/>
       <c r="L417" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="M417" s="4"/>
+      <c r="M417" s="4" t="s">
+        <v>1731</v>
+      </c>
       <c r="N417" s="4"/>
       <c r="O417" s="4" t="s">
-        <v>1756</v>
+        <v>1750</v>
       </c>
       <c r="P417" s="5"/>
       <c r="Q417" s="4" t="s">
-        <v>1757</v>
+        <v>1751</v>
       </c>
       <c r="R417" s="4" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="S417" s="4">
         <v>0</v>
@@ -37228,20 +37240,24 @@
       <c r="T417" s="4">
         <v>0</v>
       </c>
-      <c r="U417" s="4"/>
-      <c r="V417" s="4"/>
+      <c r="U417" s="4" t="s">
+        <v>1752</v>
+      </c>
+      <c r="V417" s="4" t="s">
+        <v>610</v>
+      </c>
       <c r="W417" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X417" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y417" s="4"/>
       <c r="Z417" s="4" t="s">
-        <v>1758</v>
+        <v>490</v>
       </c>
       <c r="AA417" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB417" s="4" t="s">
         <v>49</v>
@@ -37252,16 +37268,16 @@
         <v>1000</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>192</v>
+        <v>536</v>
       </c>
       <c r="C418" s="4">
-        <v>163568415</v>
+        <v>163568435</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E418" s="4">
-        <v>8370323</v>
+        <v>7870323</v>
       </c>
       <c r="F418" s="4" t="s">
         <v>51</v>
@@ -37273,24 +37289,28 @@
         <v>133</v>
       </c>
       <c r="I418" s="4" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1759</v>
+        <v>1753</v>
       </c>
       <c r="K418" s="4"/>
-      <c r="L418" s="4"/>
-      <c r="M418" s="4"/>
+      <c r="L418" s="4" t="s">
+        <v>1754</v>
+      </c>
+      <c r="M418" s="4" t="s">
+        <v>1755</v>
+      </c>
       <c r="N418" s="4"/>
       <c r="O418" s="4" t="s">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="P418" s="5"/>
       <c r="Q418" s="4" t="s">
-        <v>1761</v>
+        <v>1757</v>
       </c>
       <c r="R418" s="4" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="S418" s="4">
         <v>0</v>
@@ -37308,9 +37328,11 @@
       </c>
       <c r="Y418" s="4"/>
       <c r="Z418" s="4" t="s">
-        <v>1762</v>
-      </c>
-      <c r="AA418" s="4"/>
+        <v>1758</v>
+      </c>
+      <c r="AA418" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB418" s="4" t="s">
         <v>49</v>
       </c>
@@ -37323,13 +37345,13 @@
         <v>33</v>
       </c>
       <c r="C419" s="4">
-        <v>163581320</v>
+        <v>163586934</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E419" s="4">
-        <v>8074238</v>
+        <v>7788272</v>
       </c>
       <c r="F419" s="4" t="s">
         <v>51</v>
@@ -37338,27 +37360,29 @@
         <v>36</v>
       </c>
       <c r="H419" s="4" t="s">
-        <v>1763</v>
+        <v>133</v>
       </c>
       <c r="I419" s="4" t="s">
-        <v>1764</v>
+        <v>133</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1765</v>
+        <v>1759</v>
       </c>
       <c r="K419" s="4"/>
-      <c r="L419" s="4"/>
+      <c r="L419" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M419" s="4"/>
       <c r="N419" s="4"/>
       <c r="O419" s="4" t="s">
-        <v>1766</v>
+        <v>1760</v>
       </c>
       <c r="P419" s="5"/>
       <c r="Q419" s="4" t="s">
-        <v>1767</v>
+        <v>1761</v>
       </c>
       <c r="R419" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S419" s="4">
         <v>0</v>
@@ -37369,17 +37393,17 @@
       <c r="U419" s="4"/>
       <c r="V419" s="4"/>
       <c r="W419" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X419" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y419" s="4"/>
       <c r="Z419" s="4" t="s">
-        <v>1768</v>
+        <v>1762</v>
       </c>
       <c r="AA419" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB419" s="4" t="s">
         <v>49</v>
@@ -37390,16 +37414,16 @@
         <v>1000</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="C420" s="4">
-        <v>163584981</v>
+        <v>163568415</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="E420" s="4">
-        <v>7362058</v>
+        <v>8370323</v>
       </c>
       <c r="F420" s="4" t="s">
         <v>51</v>
@@ -37408,24 +37432,24 @@
         <v>36</v>
       </c>
       <c r="H420" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I420" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J420" s="4" t="s">
         <v>1763</v>
-      </c>
-      <c r="I420" s="4" t="s">
-        <v>1769</v>
-      </c>
-      <c r="J420" s="4" t="s">
-        <v>1770</v>
       </c>
       <c r="K420" s="4"/>
       <c r="L420" s="4"/>
       <c r="M420" s="4"/>
       <c r="N420" s="4"/>
       <c r="O420" s="4" t="s">
-        <v>1771</v>
+        <v>1764</v>
       </c>
       <c r="P420" s="5"/>
       <c r="Q420" s="4" t="s">
-        <v>1772</v>
+        <v>1765</v>
       </c>
       <c r="R420" s="4" t="s">
         <v>43</v>
@@ -37439,17 +37463,155 @@
       <c r="U420" s="4"/>
       <c r="V420" s="4"/>
       <c r="W420" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X420" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y420" s="4"/>
       <c r="Z420" s="4" t="s">
-        <v>1773</v>
+        <v>1766</v>
       </c>
       <c r="AA420" s="4"/>
       <c r="AB420" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="421" spans="1:28">
+      <c r="A421" s="4">
+        <v>1000</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C421" s="4">
+        <v>163581320</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E421" s="4">
+        <v>8074238</v>
+      </c>
+      <c r="F421" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G421" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H421" s="4" t="s">
+        <v>1767</v>
+      </c>
+      <c r="I421" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="J421" s="4" t="s">
+        <v>1769</v>
+      </c>
+      <c r="K421" s="4"/>
+      <c r="L421" s="4"/>
+      <c r="M421" s="4"/>
+      <c r="N421" s="4"/>
+      <c r="O421" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="P421" s="5"/>
+      <c r="Q421" s="4" t="s">
+        <v>1771</v>
+      </c>
+      <c r="R421" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S421" s="4">
+        <v>0</v>
+      </c>
+      <c r="T421" s="4">
+        <v>0</v>
+      </c>
+      <c r="U421" s="4"/>
+      <c r="V421" s="4"/>
+      <c r="W421" s="4">
+        <v>3</v>
+      </c>
+      <c r="X421" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y421" s="4"/>
+      <c r="Z421" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="AA421" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB421" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="422" spans="1:28">
+      <c r="A422" s="4">
+        <v>1000</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C422" s="4">
+        <v>163584981</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E422" s="4">
+        <v>7362058</v>
+      </c>
+      <c r="F422" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G422" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H422" s="4" t="s">
+        <v>1767</v>
+      </c>
+      <c r="I422" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="J422" s="4" t="s">
+        <v>1774</v>
+      </c>
+      <c r="K422" s="4"/>
+      <c r="L422" s="4"/>
+      <c r="M422" s="4"/>
+      <c r="N422" s="4"/>
+      <c r="O422" s="4" t="s">
+        <v>1775</v>
+      </c>
+      <c r="P422" s="5"/>
+      <c r="Q422" s="4" t="s">
+        <v>1776</v>
+      </c>
+      <c r="R422" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S422" s="4">
+        <v>0</v>
+      </c>
+      <c r="T422" s="4">
+        <v>0</v>
+      </c>
+      <c r="U422" s="4"/>
+      <c r="V422" s="4"/>
+      <c r="W422" s="4">
+        <v>2</v>
+      </c>
+      <c r="X422" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y422" s="4"/>
+      <c r="Z422" s="4" t="s">
+        <v>1777</v>
+      </c>
+      <c r="AA422" s="4"/>
+      <c r="AB422" s="4" t="s">
         <v>49</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1783">
   <si>
     <t>DELTEC - MAGDALENA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 18:00:53</t>
+    <t>09/08/2026 a las 19:00:52</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -4317,6 +4317,21 @@
   </si>
   <si>
     <t>RUIZ FERNANDEZ  CRISTINA ISABEL</t>
+  </si>
+  <si>
+    <t>TIMAYUI 2 LOS ALPES</t>
+  </si>
+  <si>
+    <t>CR 78A</t>
+  </si>
+  <si>
+    <t>CR 78A CL 16 - 4</t>
+  </si>
+  <si>
+    <t>BERNAL BERMUDEZ  YADIRIS</t>
+  </si>
+  <si>
+    <t>Revision Suministromedidor MD PQR se comunica la yadiris  Bernal tel 3104511247 nic 8241107  cc 57442911 correo yadirisbernal415gmail.com propi  reporta contador quemado se le indica que es para una revision se le indica costo  acepta</t>
   </si>
   <si>
     <t>URB ALEXANDRAS</t>
@@ -5742,7 +5757,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB422"/>
+  <dimension ref="A1:AB423"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -30564,16 +30579,16 @@
         <v>1000</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="C329" s="4">
-        <v>163429968</v>
+        <v>163664259</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E329" s="4">
-        <v>5875396</v>
+        <v>8241107</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>51</v>
@@ -30592,19 +30607,23 @@
       </c>
       <c r="K329" s="4"/>
       <c r="L329" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M329" s="4"/>
-      <c r="N329" s="4"/>
+        <v>1435</v>
+      </c>
+      <c r="M329" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N329" s="4">
+        <v>4</v>
+      </c>
       <c r="O329" s="4" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="P329" s="5"/>
       <c r="Q329" s="4" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="R329" s="4" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="S329" s="4">
         <v>0</v>
@@ -30615,18 +30634,16 @@
       <c r="U329" s="4"/>
       <c r="V329" s="4"/>
       <c r="W329" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X329" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y329" s="4"/>
       <c r="Z329" s="4" t="s">
-        <v>1437</v>
-      </c>
-      <c r="AA329" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1438</v>
+      </c>
+      <c r="AA329" s="4"/>
       <c r="AB329" s="4" t="s">
         <v>49</v>
       </c>
@@ -30636,16 +30653,16 @@
         <v>1000</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="C330" s="4">
-        <v>163425677</v>
+        <v>163429968</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="E330" s="4">
-        <v>7678784</v>
+        <v>5875396</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>51</v>
@@ -30660,7 +30677,7 @@
         <v>133</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="K330" s="4"/>
       <c r="L330" s="4" t="s">
@@ -30669,11 +30686,11 @@
       <c r="M330" s="4"/>
       <c r="N330" s="4"/>
       <c r="O330" s="4" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="P330" s="5"/>
       <c r="Q330" s="4" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="R330" s="4" t="s">
         <v>185</v>
@@ -30690,11 +30707,11 @@
         <v>5</v>
       </c>
       <c r="X330" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y330" s="4"/>
       <c r="Z330" s="4" t="s">
-        <v>880</v>
+        <v>1442</v>
       </c>
       <c r="AA330" s="4" t="s">
         <v>48</v>
@@ -30708,16 +30725,16 @@
         <v>1000</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1350</v>
+        <v>33</v>
       </c>
       <c r="C331" s="4">
-        <v>163568412</v>
+        <v>163425677</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="E331" s="4">
-        <v>7673602</v>
+        <v>7678784</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>51</v>
@@ -30732,7 +30749,7 @@
         <v>133</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="K331" s="4"/>
       <c r="L331" s="4" t="s">
@@ -30741,11 +30758,11 @@
       <c r="M331" s="4"/>
       <c r="N331" s="4"/>
       <c r="O331" s="4" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="P331" s="5"/>
       <c r="Q331" s="4" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="R331" s="4" t="s">
         <v>185</v>
@@ -30759,17 +30776,17 @@
       <c r="U331" s="4"/>
       <c r="V331" s="4"/>
       <c r="W331" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X331" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y331" s="4"/>
       <c r="Z331" s="4" t="s">
-        <v>1443</v>
+        <v>880</v>
       </c>
       <c r="AA331" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB331" s="4" t="s">
         <v>49</v>
@@ -30783,13 +30800,13 @@
         <v>1350</v>
       </c>
       <c r="C332" s="4">
-        <v>163568414</v>
+        <v>163568412</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E332" s="4">
-        <v>7679002</v>
+        <v>7673602</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>51</v>
@@ -30804,7 +30821,7 @@
         <v>133</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="K332" s="4"/>
       <c r="L332" s="4" t="s">
@@ -30813,11 +30830,11 @@
       <c r="M332" s="4"/>
       <c r="N332" s="4"/>
       <c r="O332" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="P332" s="5"/>
       <c r="Q332" s="4" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="R332" s="4" t="s">
         <v>185</v>
@@ -30838,10 +30855,10 @@
       </c>
       <c r="Y332" s="4"/>
       <c r="Z332" s="4" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="AA332" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB332" s="4" t="s">
         <v>49</v>
@@ -30852,16 +30869,16 @@
         <v>1000</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>33</v>
+        <v>1350</v>
       </c>
       <c r="C333" s="4">
-        <v>163574967</v>
+        <v>163568414</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E333" s="4">
-        <v>7678784</v>
+        <v>7679002</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>51</v>
@@ -30876,7 +30893,7 @@
         <v>133</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="K333" s="4"/>
       <c r="L333" s="4" t="s">
@@ -30885,11 +30902,11 @@
       <c r="M333" s="4"/>
       <c r="N333" s="4"/>
       <c r="O333" s="4" t="s">
-        <v>1439</v>
+        <v>1449</v>
       </c>
       <c r="P333" s="5"/>
       <c r="Q333" s="4" t="s">
-        <v>1440</v>
+        <v>1450</v>
       </c>
       <c r="R333" s="4" t="s">
         <v>185</v>
@@ -30906,11 +30923,11 @@
         <v>3</v>
       </c>
       <c r="X333" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y333" s="4"/>
       <c r="Z333" s="4" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="AA333" s="4" t="s">
         <v>48</v>
@@ -30927,13 +30944,13 @@
         <v>33</v>
       </c>
       <c r="C334" s="4">
-        <v>163583525</v>
+        <v>163574967</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="E334" s="4">
-        <v>7584651</v>
+        <v>7678784</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>51</v>
@@ -30948,7 +30965,7 @@
         <v>133</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="K334" s="4"/>
       <c r="L334" s="4" t="s">
@@ -30957,14 +30974,14 @@
       <c r="M334" s="4"/>
       <c r="N334" s="4"/>
       <c r="O334" s="4" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="P334" s="5"/>
       <c r="Q334" s="4" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="R334" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S334" s="4">
         <v>0</v>
@@ -30972,24 +30989,20 @@
       <c r="T334" s="4">
         <v>0</v>
       </c>
-      <c r="U334" s="4" t="s">
-        <v>1450</v>
-      </c>
-      <c r="V334" s="4" t="s">
-        <v>266</v>
-      </c>
+      <c r="U334" s="4"/>
+      <c r="V334" s="4"/>
       <c r="W334" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X334" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y334" s="4"/>
       <c r="Z334" s="4" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="AA334" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB334" s="4" t="s">
         <v>49</v>
@@ -31000,16 +31013,16 @@
         <v>1000</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1359</v>
+        <v>33</v>
       </c>
       <c r="C335" s="4">
-        <v>163568418</v>
+        <v>163583525</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E335" s="4">
-        <v>6571789</v>
+        <v>7584651</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>51</v>
@@ -31024,7 +31037,7 @@
         <v>133</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1452</v>
+        <v>1443</v>
       </c>
       <c r="K335" s="4"/>
       <c r="L335" s="4" t="s">
@@ -31048,20 +31061,24 @@
       <c r="T335" s="4">
         <v>0</v>
       </c>
-      <c r="U335" s="4"/>
-      <c r="V335" s="4"/>
+      <c r="U335" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="V335" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="W335" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X335" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y335" s="4"/>
       <c r="Z335" s="4" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="AA335" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB335" s="4" t="s">
         <v>49</v>
@@ -31075,13 +31092,13 @@
         <v>1359</v>
       </c>
       <c r="C336" s="4">
-        <v>163568419</v>
+        <v>163568418</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E336" s="4">
-        <v>7089749</v>
+        <v>6571789</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>51</v>
@@ -31096,7 +31113,7 @@
         <v>133</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="K336" s="4"/>
       <c r="L336" s="4" t="s">
@@ -31105,20 +31122,20 @@
       <c r="M336" s="4"/>
       <c r="N336" s="4"/>
       <c r="O336" s="4" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="P336" s="5"/>
       <c r="Q336" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="R336" s="4" t="s">
         <v>92</v>
       </c>
       <c r="S336" s="4">
-        <v>191660.62</v>
+        <v>0</v>
       </c>
       <c r="T336" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U336" s="4"/>
       <c r="V336" s="4"/>
@@ -31130,10 +31147,10 @@
       </c>
       <c r="Y336" s="4"/>
       <c r="Z336" s="4" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="AA336" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB336" s="4" t="s">
         <v>49</v>
@@ -31147,13 +31164,13 @@
         <v>1359</v>
       </c>
       <c r="C337" s="4">
-        <v>163568420</v>
+        <v>163568419</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E337" s="4">
-        <v>4325969</v>
+        <v>7089749</v>
       </c>
       <c r="F337" s="4" t="s">
         <v>51</v>
@@ -31168,7 +31185,7 @@
         <v>133</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="K337" s="4"/>
       <c r="L337" s="4" t="s">
@@ -31177,27 +31194,23 @@
       <c r="M337" s="4"/>
       <c r="N337" s="4"/>
       <c r="O337" s="4" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="P337" s="5"/>
       <c r="Q337" s="4" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="R337" s="4" t="s">
         <v>92</v>
       </c>
       <c r="S337" s="4">
-        <v>0</v>
+        <v>191660.62</v>
       </c>
       <c r="T337" s="4">
-        <v>0</v>
-      </c>
-      <c r="U337" s="4" t="s">
-        <v>1461</v>
-      </c>
-      <c r="V337" s="4" t="s">
-        <v>581</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U337" s="4"/>
+      <c r="V337" s="4"/>
       <c r="W337" s="4">
         <v>3</v>
       </c>
@@ -31206,10 +31219,10 @@
       </c>
       <c r="Y337" s="4"/>
       <c r="Z337" s="4" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="AA337" s="4" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="AB337" s="4" t="s">
         <v>49</v>
@@ -31223,13 +31236,13 @@
         <v>1359</v>
       </c>
       <c r="C338" s="4">
-        <v>163568422</v>
+        <v>163568420</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E338" s="4">
-        <v>7033295</v>
+        <v>4325969</v>
       </c>
       <c r="F338" s="4" t="s">
         <v>51</v>
@@ -31244,7 +31257,7 @@
         <v>133</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="K338" s="4"/>
       <c r="L338" s="4" t="s">
@@ -31253,11 +31266,11 @@
       <c r="M338" s="4"/>
       <c r="N338" s="4"/>
       <c r="O338" s="4" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="P338" s="5"/>
       <c r="Q338" s="4" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="R338" s="4" t="s">
         <v>92</v>
@@ -31268,8 +31281,12 @@
       <c r="T338" s="4">
         <v>0</v>
       </c>
-      <c r="U338" s="4"/>
-      <c r="V338" s="4"/>
+      <c r="U338" s="4" t="s">
+        <v>1466</v>
+      </c>
+      <c r="V338" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="W338" s="4">
         <v>3</v>
       </c>
@@ -31278,10 +31295,10 @@
       </c>
       <c r="Y338" s="4"/>
       <c r="Z338" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="AA338" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB338" s="4" t="s">
         <v>49</v>
@@ -31292,16 +31309,16 @@
         <v>1000</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>824</v>
+        <v>1359</v>
       </c>
       <c r="C339" s="4">
-        <v>163568454</v>
+        <v>163568422</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E339" s="4">
-        <v>6914875</v>
+        <v>7033295</v>
       </c>
       <c r="F339" s="4" t="s">
         <v>51</v>
@@ -31316,7 +31333,7 @@
         <v>133</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1466</v>
+        <v>1457</v>
       </c>
       <c r="K339" s="4"/>
       <c r="L339" s="4" t="s">
@@ -31325,14 +31342,14 @@
       <c r="M339" s="4"/>
       <c r="N339" s="4"/>
       <c r="O339" s="4" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="P339" s="5"/>
       <c r="Q339" s="4" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="R339" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S339" s="4">
         <v>0</v>
@@ -31340,12 +31357,8 @@
       <c r="T339" s="4">
         <v>0</v>
       </c>
-      <c r="U339" s="4" t="s">
-        <v>1469</v>
-      </c>
-      <c r="V339" s="4" t="s">
-        <v>333</v>
-      </c>
+      <c r="U339" s="4"/>
+      <c r="V339" s="4"/>
       <c r="W339" s="4">
         <v>3</v>
       </c>
@@ -31357,7 +31370,7 @@
         <v>1470</v>
       </c>
       <c r="AA339" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB339" s="4" t="s">
         <v>49</v>
@@ -31368,16 +31381,16 @@
         <v>1000</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>33</v>
+        <v>824</v>
       </c>
       <c r="C340" s="4">
-        <v>163529327</v>
+        <v>163568454</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>248</v>
+        <v>170</v>
       </c>
       <c r="E340" s="4">
-        <v>8377686</v>
+        <v>6914875</v>
       </c>
       <c r="F340" s="4" t="s">
         <v>51</v>
@@ -31395,7 +31408,9 @@
         <v>1471</v>
       </c>
       <c r="K340" s="4"/>
-      <c r="L340" s="4"/>
+      <c r="L340" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M340" s="4"/>
       <c r="N340" s="4"/>
       <c r="O340" s="4" t="s">
@@ -31406,7 +31421,7 @@
         <v>1473</v>
       </c>
       <c r="R340" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S340" s="4">
         <v>0</v>
@@ -31414,21 +31429,27 @@
       <c r="T340" s="4">
         <v>0</v>
       </c>
-      <c r="U340" s="4"/>
-      <c r="V340" s="4"/>
+      <c r="U340" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="V340" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W340" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X340" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y340" s="4"/>
       <c r="Z340" s="4" t="s">
-        <v>1474</v>
-      </c>
-      <c r="AA340" s="4"/>
+        <v>1475</v>
+      </c>
+      <c r="AA340" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB340" s="4" t="s">
-        <v>253</v>
+        <v>49</v>
       </c>
     </row>
     <row r="341" spans="1:28">
@@ -31436,16 +31457,16 @@
         <v>1000</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>824</v>
+        <v>33</v>
       </c>
       <c r="C341" s="4">
-        <v>163568469</v>
+        <v>163529327</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="E341" s="4">
-        <v>4322512</v>
+        <v>8377686</v>
       </c>
       <c r="F341" s="4" t="s">
         <v>51</v>
@@ -31460,23 +31481,21 @@
         <v>133</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="K341" s="4"/>
-      <c r="L341" s="4" t="s">
-        <v>296</v>
-      </c>
+      <c r="L341" s="4"/>
       <c r="M341" s="4"/>
       <c r="N341" s="4"/>
       <c r="O341" s="4" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="P341" s="5"/>
       <c r="Q341" s="4" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="R341" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S341" s="4">
         <v>0</v>
@@ -31487,18 +31506,18 @@
       <c r="U341" s="4"/>
       <c r="V341" s="4"/>
       <c r="W341" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X341" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y341" s="4"/>
       <c r="Z341" s="4" t="s">
-        <v>953</v>
+        <v>1479</v>
       </c>
       <c r="AA341" s="4"/>
       <c r="AB341" s="4" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
     </row>
     <row r="342" spans="1:28">
@@ -31506,16 +31525,16 @@
         <v>1000</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>33</v>
+        <v>824</v>
       </c>
       <c r="C342" s="4">
-        <v>163034344</v>
+        <v>163568469</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="E342" s="4">
-        <v>8376943</v>
+        <v>4322512</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>51</v>
@@ -31530,21 +31549,23 @@
         <v>133</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="K342" s="4"/>
-      <c r="L342" s="4"/>
+      <c r="L342" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M342" s="4"/>
       <c r="N342" s="4"/>
       <c r="O342" s="4" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="P342" s="5"/>
       <c r="Q342" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="R342" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S342" s="4">
         <v>0</v>
@@ -31555,14 +31576,14 @@
       <c r="U342" s="4"/>
       <c r="V342" s="4"/>
       <c r="W342" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X342" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y342" s="4"/>
       <c r="Z342" s="4" t="s">
-        <v>77</v>
+        <v>953</v>
       </c>
       <c r="AA342" s="4"/>
       <c r="AB342" s="4" t="s">
@@ -31577,13 +31598,13 @@
         <v>33</v>
       </c>
       <c r="C343" s="4">
-        <v>163585695</v>
+        <v>163034344</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E343" s="4">
-        <v>7216255</v>
+        <v>8376943</v>
       </c>
       <c r="F343" s="4" t="s">
         <v>51</v>
@@ -31598,23 +31619,21 @@
         <v>133</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1478</v>
+        <v>1483</v>
       </c>
       <c r="K343" s="4"/>
-      <c r="L343" s="4" t="s">
-        <v>296</v>
-      </c>
+      <c r="L343" s="4"/>
       <c r="M343" s="4"/>
       <c r="N343" s="4"/>
       <c r="O343" s="4" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="P343" s="5"/>
       <c r="Q343" s="4" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="R343" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S343" s="4">
         <v>0</v>
@@ -31625,18 +31644,16 @@
       <c r="U343" s="4"/>
       <c r="V343" s="4"/>
       <c r="W343" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="X343" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y343" s="4"/>
       <c r="Z343" s="4" t="s">
-        <v>1483</v>
-      </c>
-      <c r="AA343" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="AA343" s="4"/>
       <c r="AB343" s="4" t="s">
         <v>49</v>
       </c>
@@ -31649,13 +31666,13 @@
         <v>33</v>
       </c>
       <c r="C344" s="4">
-        <v>163595690</v>
+        <v>163585695</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>216</v>
+        <v>34</v>
       </c>
       <c r="E344" s="4">
-        <v>7111159</v>
+        <v>7216255</v>
       </c>
       <c r="F344" s="4" t="s">
         <v>51</v>
@@ -31670,7 +31687,7 @@
         <v>133</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1478</v>
+        <v>1483</v>
       </c>
       <c r="K344" s="4"/>
       <c r="L344" s="4" t="s">
@@ -31679,11 +31696,11 @@
       <c r="M344" s="4"/>
       <c r="N344" s="4"/>
       <c r="O344" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="P344" s="5"/>
       <c r="Q344" s="4" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="R344" s="4" t="s">
         <v>43</v>
@@ -31694,24 +31711,20 @@
       <c r="T344" s="4">
         <v>0</v>
       </c>
-      <c r="U344" s="4" t="s">
-        <v>1486</v>
-      </c>
-      <c r="V344" s="4" t="s">
-        <v>581</v>
-      </c>
+      <c r="U344" s="4"/>
+      <c r="V344" s="4"/>
       <c r="W344" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X344" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y344" s="4"/>
       <c r="Z344" s="4" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="AA344" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB344" s="4" t="s">
         <v>49</v>
@@ -31725,13 +31738,13 @@
         <v>33</v>
       </c>
       <c r="C345" s="4">
-        <v>163594532</v>
+        <v>163595690</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>50</v>
+        <v>216</v>
       </c>
       <c r="E345" s="4">
-        <v>8382163</v>
+        <v>7111159</v>
       </c>
       <c r="F345" s="4" t="s">
         <v>51</v>
@@ -31746,10 +31759,12 @@
         <v>133</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="K345" s="4"/>
-      <c r="L345" s="4"/>
+      <c r="L345" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M345" s="4"/>
       <c r="N345" s="4"/>
       <c r="O345" s="4" t="s">
@@ -31760,7 +31775,7 @@
         <v>1490</v>
       </c>
       <c r="R345" s="4" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="S345" s="4">
         <v>0</v>
@@ -31768,8 +31783,12 @@
       <c r="T345" s="4">
         <v>0</v>
       </c>
-      <c r="U345" s="4"/>
-      <c r="V345" s="4"/>
+      <c r="U345" s="4" t="s">
+        <v>1491</v>
+      </c>
+      <c r="V345" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="W345" s="4">
         <v>1</v>
       </c>
@@ -31778,9 +31797,11 @@
       </c>
       <c r="Y345" s="4"/>
       <c r="Z345" s="4" t="s">
-        <v>1491</v>
-      </c>
-      <c r="AA345" s="4"/>
+        <v>1492</v>
+      </c>
+      <c r="AA345" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB345" s="4" t="s">
         <v>49</v>
       </c>
@@ -31793,13 +31814,13 @@
         <v>33</v>
       </c>
       <c r="C346" s="4">
-        <v>163588829</v>
+        <v>163594532</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E346" s="4">
-        <v>1053551</v>
+        <v>8382163</v>
       </c>
       <c r="F346" s="4" t="s">
         <v>51</v>
@@ -31814,18 +31835,12 @@
         <v>133</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="K346" s="4"/>
-      <c r="L346" s="4" t="s">
-        <v>1493</v>
-      </c>
-      <c r="M346" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="N346" s="4">
-        <v>7</v>
-      </c>
+      <c r="L346" s="4"/>
+      <c r="M346" s="4"/>
+      <c r="N346" s="4"/>
       <c r="O346" s="4" t="s">
         <v>1494</v>
       </c>
@@ -31834,7 +31849,7 @@
         <v>1495</v>
       </c>
       <c r="R346" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S346" s="4">
         <v>0</v>
@@ -31845,7 +31860,7 @@
       <c r="U346" s="4"/>
       <c r="V346" s="4"/>
       <c r="W346" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X346" s="4" t="s">
         <v>46</v>
@@ -31854,9 +31869,7 @@
       <c r="Z346" s="4" t="s">
         <v>1496</v>
       </c>
-      <c r="AA346" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="AA346" s="4"/>
       <c r="AB346" s="4" t="s">
         <v>49</v>
       </c>
@@ -31869,13 +31882,13 @@
         <v>33</v>
       </c>
       <c r="C347" s="4">
-        <v>163592289</v>
+        <v>163588829</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E347" s="4">
-        <v>7412708</v>
+        <v>1053551</v>
       </c>
       <c r="F347" s="4" t="s">
         <v>51</v>
@@ -31894,19 +31907,23 @@
       </c>
       <c r="K347" s="4"/>
       <c r="L347" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M347" s="4"/>
-      <c r="N347" s="4"/>
+        <v>1498</v>
+      </c>
+      <c r="M347" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="N347" s="4">
+        <v>7</v>
+      </c>
       <c r="O347" s="4" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="P347" s="5"/>
       <c r="Q347" s="4" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="R347" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S347" s="4">
         <v>0</v>
@@ -31914,14 +31931,10 @@
       <c r="T347" s="4">
         <v>0</v>
       </c>
-      <c r="U347" s="4" t="s">
-        <v>1500</v>
-      </c>
-      <c r="V347" s="4" t="s">
-        <v>416</v>
-      </c>
+      <c r="U347" s="4"/>
+      <c r="V347" s="4"/>
       <c r="W347" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X347" s="4" t="s">
         <v>46</v>
@@ -31930,7 +31943,9 @@
       <c r="Z347" s="4" t="s">
         <v>1501</v>
       </c>
-      <c r="AA347" s="4"/>
+      <c r="AA347" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB347" s="4" t="s">
         <v>49</v>
       </c>
@@ -31940,16 +31955,16 @@
         <v>1000</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="C348" s="4">
-        <v>163568424</v>
+        <v>163592289</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E348" s="4">
-        <v>1140986</v>
+        <v>7412708</v>
       </c>
       <c r="F348" s="4" t="s">
         <v>51</v>
@@ -31964,47 +31979,47 @@
         <v>133</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1497</v>
+        <v>1502</v>
       </c>
       <c r="K348" s="4"/>
       <c r="L348" s="4" t="s">
-        <v>1502</v>
-      </c>
-      <c r="M348" s="4" t="s">
-        <v>1503</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M348" s="4"/>
       <c r="N348" s="4"/>
       <c r="O348" s="4" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="P348" s="5"/>
       <c r="Q348" s="4" t="s">
+        <v>1504</v>
+      </c>
+      <c r="R348" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="S348" s="4">
+        <v>0</v>
+      </c>
+      <c r="T348" s="4">
+        <v>0</v>
+      </c>
+      <c r="U348" s="4" t="s">
         <v>1505</v>
       </c>
-      <c r="R348" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="S348" s="4">
-        <v>0</v>
-      </c>
-      <c r="T348" s="4">
-        <v>0</v>
-      </c>
-      <c r="U348" s="4"/>
-      <c r="V348" s="4"/>
+      <c r="V348" s="4" t="s">
+        <v>416</v>
+      </c>
       <c r="W348" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X348" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y348" s="4"/>
       <c r="Z348" s="4" t="s">
         <v>1506</v>
       </c>
-      <c r="AA348" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="AA348" s="4"/>
       <c r="AB348" s="4" t="s">
         <v>49</v>
       </c>
@@ -32014,16 +32029,16 @@
         <v>1000</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>33</v>
+        <v>536</v>
       </c>
       <c r="C349" s="4">
-        <v>163529361</v>
+        <v>163568424</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E349" s="4">
-        <v>6840249</v>
+        <v>1140986</v>
       </c>
       <c r="F349" s="4" t="s">
         <v>51</v>
@@ -32038,52 +32053,46 @@
         <v>133</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="K349" s="4"/>
       <c r="L349" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="M349" s="4" t="s">
         <v>1508</v>
       </c>
-      <c r="M349" s="4" t="s">
+      <c r="N349" s="4"/>
+      <c r="O349" s="4" t="s">
         <v>1509</v>
-      </c>
-      <c r="N349" s="4">
-        <v>4</v>
-      </c>
-      <c r="O349" s="4" t="s">
-        <v>1510</v>
       </c>
       <c r="P349" s="5"/>
       <c r="Q349" s="4" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="R349" s="4" t="s">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="S349" s="4">
-        <v>76308.22</v>
+        <v>0</v>
       </c>
       <c r="T349" s="4">
-        <v>1</v>
-      </c>
-      <c r="U349" s="4" t="s">
-        <v>1512</v>
-      </c>
-      <c r="V349" s="4" t="s">
-        <v>1513</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U349" s="4"/>
+      <c r="V349" s="4"/>
       <c r="W349" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X349" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y349" s="4"/>
       <c r="Z349" s="4" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="AA349" s="4" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="AB349" s="4" t="s">
         <v>49</v>
@@ -32097,13 +32106,13 @@
         <v>33</v>
       </c>
       <c r="C350" s="4">
-        <v>163584051</v>
+        <v>163529361</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>216</v>
       </c>
       <c r="E350" s="4">
-        <v>6630607</v>
+        <v>6840249</v>
       </c>
       <c r="F350" s="4" t="s">
         <v>51</v>
@@ -32118,38 +32127,42 @@
         <v>133</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="K350" s="4"/>
       <c r="L350" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="M350" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="N350" s="4">
+        <v>4</v>
+      </c>
+      <c r="O350" s="4" t="s">
         <v>1515</v>
-      </c>
-      <c r="M350" s="4" t="s">
-        <v>1516</v>
-      </c>
-      <c r="N350" s="4">
-        <v>18</v>
-      </c>
-      <c r="O350" s="4" t="s">
-        <v>1517</v>
       </c>
       <c r="P350" s="5"/>
       <c r="Q350" s="4" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="R350" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S350" s="4">
-        <v>0</v>
+        <v>76308.22</v>
       </c>
       <c r="T350" s="4">
-        <v>0</v>
-      </c>
-      <c r="U350" s="4"/>
-      <c r="V350" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U350" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="V350" s="4" t="s">
+        <v>1518</v>
+      </c>
       <c r="W350" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X350" s="4" t="s">
         <v>46</v>
@@ -32159,7 +32172,7 @@
         <v>1519</v>
       </c>
       <c r="AA350" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB350" s="4" t="s">
         <v>49</v>
@@ -32170,16 +32183,16 @@
         <v>1000</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="C351" s="4">
-        <v>163568416</v>
+        <v>163584051</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E351" s="4">
-        <v>7753862</v>
+        <v>6630607</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>51</v>
@@ -32194,24 +32207,24 @@
         <v>133</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
       <c r="K351" s="4"/>
       <c r="L351" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="M351" s="4" t="s">
         <v>1521</v>
       </c>
-      <c r="M351" s="4" t="s">
+      <c r="N351" s="4">
+        <v>18</v>
+      </c>
+      <c r="O351" s="4" t="s">
         <v>1522</v>
-      </c>
-      <c r="N351" s="4">
-        <v>15</v>
-      </c>
-      <c r="O351" s="4" t="s">
-        <v>1523</v>
       </c>
       <c r="P351" s="5"/>
       <c r="Q351" s="4" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="R351" s="4" t="s">
         <v>185</v>
@@ -32222,24 +32235,20 @@
       <c r="T351" s="4">
         <v>0</v>
       </c>
-      <c r="U351" s="4" t="s">
-        <v>1525</v>
-      </c>
-      <c r="V351" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="U351" s="4"/>
+      <c r="V351" s="4"/>
       <c r="W351" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X351" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y351" s="4"/>
       <c r="Z351" s="4" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="AA351" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB351" s="4" t="s">
         <v>49</v>
@@ -32250,16 +32259,16 @@
         <v>1000</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>33</v>
+        <v>536</v>
       </c>
       <c r="C352" s="4">
-        <v>163594016</v>
+        <v>163568416</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E352" s="4">
-        <v>7753863</v>
+        <v>7753862</v>
       </c>
       <c r="F352" s="4" t="s">
         <v>51</v>
@@ -32274,24 +32283,24 @@
         <v>133</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="K352" s="4"/>
       <c r="L352" s="4" t="s">
-        <v>1521</v>
+        <v>1526</v>
       </c>
       <c r="M352" s="4" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="N352" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O352" s="4" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="P352" s="5"/>
       <c r="Q352" s="4" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="R352" s="4" t="s">
         <v>185</v>
@@ -32303,23 +32312,23 @@
         <v>0</v>
       </c>
       <c r="U352" s="4" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="V352" s="4" t="s">
-        <v>333</v>
+        <v>131</v>
       </c>
       <c r="W352" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X352" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y352" s="4"/>
       <c r="Z352" s="4" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="AA352" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB352" s="4" t="s">
         <v>49</v>
@@ -32333,13 +32342,13 @@
         <v>33</v>
       </c>
       <c r="C353" s="4">
-        <v>163584015</v>
+        <v>163594016</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>216</v>
       </c>
       <c r="E353" s="4">
-        <v>5903236</v>
+        <v>7753863</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>51</v>
@@ -32354,14 +32363,18 @@
         <v>133</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="K353" s="4"/>
       <c r="L353" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M353" s="4"/>
-      <c r="N353" s="4"/>
+        <v>1526</v>
+      </c>
+      <c r="M353" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="N353" s="4">
+        <v>21</v>
+      </c>
       <c r="O353" s="4" t="s">
         <v>1532</v>
       </c>
@@ -32370,25 +32383,29 @@
         <v>1533</v>
       </c>
       <c r="R353" s="4" t="s">
-        <v>396</v>
+        <v>185</v>
       </c>
       <c r="S353" s="4">
-        <v>53994.21</v>
+        <v>0</v>
       </c>
       <c r="T353" s="4">
+        <v>0</v>
+      </c>
+      <c r="U353" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="V353" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="W353" s="4">
         <v>1</v>
-      </c>
-      <c r="U353" s="4"/>
-      <c r="V353" s="4"/>
-      <c r="W353" s="4">
-        <v>2</v>
       </c>
       <c r="X353" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y353" s="4"/>
       <c r="Z353" s="4" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="AA353" s="4" t="s">
         <v>48</v>
@@ -32405,13 +32422,13 @@
         <v>33</v>
       </c>
       <c r="C354" s="4">
-        <v>163592352</v>
+        <v>163584015</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>216</v>
       </c>
       <c r="E354" s="4">
-        <v>7313578</v>
+        <v>5903236</v>
       </c>
       <c r="F354" s="4" t="s">
         <v>51</v>
@@ -32426,51 +32443,45 @@
         <v>133</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="K354" s="4"/>
       <c r="L354" s="4" t="s">
-        <v>1536</v>
-      </c>
-      <c r="M354" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="M354" s="4"/>
+      <c r="N354" s="4"/>
+      <c r="O354" s="4" t="s">
         <v>1537</v>
-      </c>
-      <c r="N354" s="4">
-        <v>14</v>
-      </c>
-      <c r="O354" s="4" t="s">
-        <v>1538</v>
       </c>
       <c r="P354" s="5"/>
       <c r="Q354" s="4" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="R354" s="4" t="s">
-        <v>185</v>
+        <v>396</v>
       </c>
       <c r="S354" s="4">
-        <v>0</v>
+        <v>53994.21</v>
       </c>
       <c r="T354" s="4">
-        <v>0</v>
-      </c>
-      <c r="U354" s="4" t="s">
-        <v>1540</v>
-      </c>
-      <c r="V354" s="4" t="s">
-        <v>1541</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U354" s="4"/>
+      <c r="V354" s="4"/>
       <c r="W354" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X354" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y354" s="4"/>
       <c r="Z354" s="4" t="s">
-        <v>1542</v>
-      </c>
-      <c r="AA354" s="4"/>
+        <v>1539</v>
+      </c>
+      <c r="AA354" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB354" s="4" t="s">
         <v>49</v>
       </c>
@@ -32480,16 +32491,16 @@
         <v>1000</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>536</v>
+        <v>33</v>
       </c>
       <c r="C355" s="4">
-        <v>163568467</v>
+        <v>163592352</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="E355" s="4">
-        <v>6571089</v>
+        <v>7313578</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>51</v>
@@ -32504,49 +32515,51 @@
         <v>133</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="K355" s="4"/>
       <c r="L355" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M355" s="4"/>
-      <c r="N355" s="4"/>
+        <v>1541</v>
+      </c>
+      <c r="M355" s="4" t="s">
+        <v>1542</v>
+      </c>
+      <c r="N355" s="4">
+        <v>14</v>
+      </c>
       <c r="O355" s="4" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="P355" s="5"/>
       <c r="Q355" s="4" t="s">
+        <v>1544</v>
+      </c>
+      <c r="R355" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="S355" s="4">
+        <v>0</v>
+      </c>
+      <c r="T355" s="4">
+        <v>0</v>
+      </c>
+      <c r="U355" s="4" t="s">
         <v>1545</v>
       </c>
-      <c r="R355" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="S355" s="4">
-        <v>0</v>
-      </c>
-      <c r="T355" s="4">
-        <v>0</v>
-      </c>
-      <c r="U355" s="4" t="s">
+      <c r="V355" s="4" t="s">
         <v>1546</v>
       </c>
-      <c r="V355" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="W355" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X355" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y355" s="4"/>
       <c r="Z355" s="4" t="s">
         <v>1547</v>
       </c>
-      <c r="AA355" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="AA355" s="4"/>
       <c r="AB355" s="4" t="s">
         <v>49</v>
       </c>
@@ -32556,16 +32569,16 @@
         <v>1000</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>33</v>
+        <v>536</v>
       </c>
       <c r="C356" s="4">
-        <v>163433658</v>
+        <v>163568467</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="E356" s="4">
-        <v>1124725</v>
+        <v>6571089</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>51</v>
@@ -32599,29 +32612,29 @@
         <v>92</v>
       </c>
       <c r="S356" s="4">
-        <v>362404.38</v>
+        <v>0</v>
       </c>
       <c r="T356" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U356" s="4" t="s">
         <v>1551</v>
       </c>
       <c r="V356" s="4" t="s">
-        <v>333</v>
+        <v>131</v>
       </c>
       <c r="W356" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X356" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y356" s="4"/>
       <c r="Z356" s="4" t="s">
-        <v>880</v>
+        <v>1552</v>
       </c>
       <c r="AA356" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB356" s="4" t="s">
         <v>49</v>
@@ -32632,16 +32645,16 @@
         <v>1000</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1552</v>
+        <v>33</v>
       </c>
       <c r="C357" s="4">
-        <v>163568476</v>
+        <v>163433658</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="E357" s="4">
-        <v>7911951</v>
+        <v>1124725</v>
       </c>
       <c r="F357" s="4" t="s">
         <v>51</v>
@@ -32675,22 +32688,26 @@
         <v>92</v>
       </c>
       <c r="S357" s="4">
-        <v>0</v>
+        <v>362404.38</v>
       </c>
       <c r="T357" s="4">
-        <v>0</v>
-      </c>
-      <c r="U357" s="4"/>
-      <c r="V357" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U357" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="V357" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W357" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X357" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y357" s="4"/>
       <c r="Z357" s="4" t="s">
-        <v>1410</v>
+        <v>880</v>
       </c>
       <c r="AA357" s="4" t="s">
         <v>48</v>
@@ -32704,16 +32721,16 @@
         <v>1000</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="C358" s="4">
-        <v>163568477</v>
+        <v>163568476</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E358" s="4">
-        <v>6831349</v>
+        <v>7911951</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>51</v>
@@ -32728,7 +32745,7 @@
         <v>133</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="K358" s="4"/>
       <c r="L358" s="4" t="s">
@@ -32737,11 +32754,11 @@
       <c r="M358" s="4"/>
       <c r="N358" s="4"/>
       <c r="O358" s="4" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="P358" s="5"/>
       <c r="Q358" s="4" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="R358" s="4" t="s">
         <v>92</v>
@@ -32762,9 +32779,11 @@
       </c>
       <c r="Y358" s="4"/>
       <c r="Z358" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="AA358" s="4"/>
+        <v>1410</v>
+      </c>
+      <c r="AA358" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB358" s="4" t="s">
         <v>49</v>
       </c>
@@ -32774,16 +32793,16 @@
         <v>1000</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="C359" s="4">
-        <v>163568478</v>
+        <v>163568477</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E359" s="4">
-        <v>7716168</v>
+        <v>6831349</v>
       </c>
       <c r="F359" s="4" t="s">
         <v>51</v>
@@ -32798,7 +32817,7 @@
         <v>133</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="K359" s="4"/>
       <c r="L359" s="4" t="s">
@@ -32807,11 +32826,11 @@
       <c r="M359" s="4"/>
       <c r="N359" s="4"/>
       <c r="O359" s="4" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="P359" s="5"/>
       <c r="Q359" s="4" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="R359" s="4" t="s">
         <v>92</v>
@@ -32832,11 +32851,9 @@
       </c>
       <c r="Y359" s="4"/>
       <c r="Z359" s="4" t="s">
-        <v>1547</v>
-      </c>
-      <c r="AA359" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>953</v>
+      </c>
+      <c r="AA359" s="4"/>
       <c r="AB359" s="4" t="s">
         <v>49</v>
       </c>
@@ -32846,16 +32863,16 @@
         <v>1000</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1552</v>
+        <v>1557</v>
       </c>
       <c r="C360" s="4">
-        <v>163568479</v>
+        <v>163568478</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E360" s="4">
-        <v>6656976</v>
+        <v>7716168</v>
       </c>
       <c r="F360" s="4" t="s">
         <v>51</v>
@@ -32870,7 +32887,7 @@
         <v>133</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="K360" s="4"/>
       <c r="L360" s="4" t="s">
@@ -32879,11 +32896,11 @@
       <c r="M360" s="4"/>
       <c r="N360" s="4"/>
       <c r="O360" s="4" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
       <c r="P360" s="5"/>
       <c r="Q360" s="4" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="R360" s="4" t="s">
         <v>92</v>
@@ -32904,10 +32921,10 @@
       </c>
       <c r="Y360" s="4"/>
       <c r="Z360" s="4" t="s">
-        <v>1410</v>
+        <v>1552</v>
       </c>
       <c r="AA360" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB360" s="4" t="s">
         <v>49</v>
@@ -32918,16 +32935,16 @@
         <v>1000</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="C361" s="4">
-        <v>163568437</v>
+        <v>163568479</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E361" s="4">
-        <v>7868219</v>
+        <v>6656976</v>
       </c>
       <c r="F361" s="4" t="s">
         <v>51</v>
@@ -32942,7 +32959,7 @@
         <v>133</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="K361" s="4"/>
       <c r="L361" s="4" t="s">
@@ -32951,14 +32968,14 @@
       <c r="M361" s="4"/>
       <c r="N361" s="4"/>
       <c r="O361" s="4" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="P361" s="5"/>
       <c r="Q361" s="4" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="R361" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S361" s="4">
         <v>0</v>
@@ -32976,10 +32993,10 @@
       </c>
       <c r="Y361" s="4"/>
       <c r="Z361" s="4" t="s">
-        <v>1566</v>
+        <v>1410</v>
       </c>
       <c r="AA361" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB361" s="4" t="s">
         <v>49</v>
@@ -32990,16 +33007,16 @@
         <v>1000</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="C362" s="4">
-        <v>163568473</v>
+        <v>163568437</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E362" s="4">
-        <v>7746659</v>
+        <v>7868219</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>51</v>
@@ -33014,7 +33031,7 @@
         <v>133</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="K362" s="4"/>
       <c r="L362" s="4" t="s">
@@ -33023,11 +33040,11 @@
       <c r="M362" s="4"/>
       <c r="N362" s="4"/>
       <c r="O362" s="4" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="P362" s="5"/>
       <c r="Q362" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="R362" s="4" t="s">
         <v>185</v>
@@ -33048,10 +33065,10 @@
       </c>
       <c r="Y362" s="4"/>
       <c r="Z362" s="4" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="AA362" s="4" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="AB362" s="4" t="s">
         <v>49</v>
@@ -33062,16 +33079,16 @@
         <v>1000</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="C363" s="4">
-        <v>163568439</v>
+        <v>163568473</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E363" s="4">
-        <v>7649853</v>
+        <v>7746659</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>51</v>
@@ -33086,18 +33103,14 @@
         <v>133</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="K363" s="4"/>
       <c r="L363" s="4" t="s">
-        <v>1570</v>
-      </c>
-      <c r="M363" s="4" t="s">
-        <v>1571</v>
-      </c>
-      <c r="N363" s="4">
-        <v>17</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M363" s="4"/>
+      <c r="N363" s="4"/>
       <c r="O363" s="4" t="s">
         <v>1572</v>
       </c>
@@ -33106,7 +33119,7 @@
         <v>1573</v>
       </c>
       <c r="R363" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S363" s="4">
         <v>0</v>
@@ -33124,9 +33137,11 @@
       </c>
       <c r="Y363" s="4"/>
       <c r="Z363" s="4" t="s">
-        <v>919</v>
-      </c>
-      <c r="AA363" s="4"/>
+        <v>1574</v>
+      </c>
+      <c r="AA363" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="AB363" s="4" t="s">
         <v>49</v>
       </c>
@@ -33136,16 +33151,16 @@
         <v>1000</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="C364" s="4">
-        <v>163568474</v>
+        <v>163568439</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E364" s="4">
-        <v>7938906</v>
+        <v>7649853</v>
       </c>
       <c r="F364" s="4" t="s">
         <v>51</v>
@@ -33160,25 +33175,27 @@
         <v>133</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="K364" s="4"/>
       <c r="L364" s="4" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="M364" s="4" t="s">
-        <v>1574</v>
-      </c>
-      <c r="N364" s="4"/>
+        <v>1576</v>
+      </c>
+      <c r="N364" s="4">
+        <v>17</v>
+      </c>
       <c r="O364" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="P364" s="5"/>
       <c r="Q364" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="R364" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S364" s="4">
         <v>0</v>
@@ -33186,12 +33203,8 @@
       <c r="T364" s="4">
         <v>0</v>
       </c>
-      <c r="U364" s="4" t="s">
-        <v>1577</v>
-      </c>
-      <c r="V364" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="U364" s="4"/>
+      <c r="V364" s="4"/>
       <c r="W364" s="4">
         <v>3</v>
       </c>
@@ -33200,11 +33213,9 @@
       </c>
       <c r="Y364" s="4"/>
       <c r="Z364" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="AA364" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>919</v>
+      </c>
+      <c r="AA364" s="4"/>
       <c r="AB364" s="4" t="s">
         <v>49</v>
       </c>
@@ -33214,16 +33225,16 @@
         <v>1000</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="C365" s="4">
-        <v>163568475</v>
+        <v>163568474</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E365" s="4">
-        <v>7938920</v>
+        <v>7938906</v>
       </c>
       <c r="F365" s="4" t="s">
         <v>51</v>
@@ -33238,22 +33249,22 @@
         <v>133</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="K365" s="4"/>
       <c r="L365" s="4" t="s">
-        <v>1570</v>
+        <v>1575</v>
       </c>
       <c r="M365" s="4" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="N365" s="4"/>
       <c r="O365" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="P365" s="5"/>
       <c r="Q365" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="R365" s="4" t="s">
         <v>185</v>
@@ -33265,10 +33276,10 @@
         <v>0</v>
       </c>
       <c r="U365" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="V365" s="4" t="s">
-        <v>1581</v>
+        <v>131</v>
       </c>
       <c r="W365" s="4">
         <v>3</v>
@@ -33278,9 +33289,11 @@
       </c>
       <c r="Y365" s="4"/>
       <c r="Z365" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="AA365" s="4"/>
+        <v>531</v>
+      </c>
+      <c r="AA365" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB365" s="4" t="s">
         <v>49</v>
       </c>
@@ -33290,16 +33303,16 @@
         <v>1000</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1136</v>
+        <v>1567</v>
       </c>
       <c r="C366" s="4">
-        <v>163549539</v>
+        <v>163568475</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E366" s="4">
-        <v>4316661</v>
+        <v>7938920</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>51</v>
@@ -33314,13 +33327,15 @@
         <v>133</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="K366" s="4"/>
       <c r="L366" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M366" s="4"/>
+        <v>1575</v>
+      </c>
+      <c r="M366" s="4" t="s">
+        <v>1579</v>
+      </c>
       <c r="N366" s="4"/>
       <c r="O366" s="4" t="s">
         <v>1583</v>
@@ -33330,7 +33345,7 @@
         <v>1584</v>
       </c>
       <c r="R366" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S366" s="4">
         <v>0</v>
@@ -33338,21 +33353,23 @@
       <c r="T366" s="4">
         <v>0</v>
       </c>
-      <c r="U366" s="4"/>
-      <c r="V366" s="4"/>
+      <c r="U366" s="4" t="s">
+        <v>1585</v>
+      </c>
+      <c r="V366" s="4" t="s">
+        <v>1586</v>
+      </c>
       <c r="W366" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X366" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y366" s="4"/>
       <c r="Z366" s="4" t="s">
-        <v>1585</v>
-      </c>
-      <c r="AA366" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>953</v>
+      </c>
+      <c r="AA366" s="4"/>
       <c r="AB366" s="4" t="s">
         <v>49</v>
       </c>
@@ -33362,16 +33379,16 @@
         <v>1000</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>425</v>
+        <v>1136</v>
       </c>
       <c r="C367" s="4">
-        <v>163568504</v>
+        <v>163549539</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E367" s="4">
-        <v>5880389</v>
+        <v>4316661</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>51</v>
@@ -33386,7 +33403,7 @@
         <v>133</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="K367" s="4"/>
       <c r="L367" s="4" t="s">
@@ -33395,14 +33412,14 @@
       <c r="M367" s="4"/>
       <c r="N367" s="4"/>
       <c r="O367" s="4" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="P367" s="5"/>
       <c r="Q367" s="4" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="R367" s="4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="S367" s="4">
         <v>0</v>
@@ -33413,16 +33430,18 @@
       <c r="U367" s="4"/>
       <c r="V367" s="4"/>
       <c r="W367" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X367" s="4" t="s">
         <v>178</v>
       </c>
       <c r="Y367" s="4"/>
       <c r="Z367" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA367" s="4"/>
+        <v>1590</v>
+      </c>
+      <c r="AA367" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB367" s="4" t="s">
         <v>49</v>
       </c>
@@ -33432,16 +33451,16 @@
         <v>1000</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1589</v>
+        <v>425</v>
       </c>
       <c r="C368" s="4">
-        <v>163568522</v>
+        <v>163568504</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E368" s="4">
-        <v>5867262</v>
+        <v>5880389</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>51</v>
@@ -33456,7 +33475,7 @@
         <v>133</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K368" s="4"/>
       <c r="L368" s="4" t="s">
@@ -33465,14 +33484,14 @@
       <c r="M368" s="4"/>
       <c r="N368" s="4"/>
       <c r="O368" s="4" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="P368" s="5"/>
       <c r="Q368" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="R368" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S368" s="4">
         <v>0</v>
@@ -33480,12 +33499,8 @@
       <c r="T368" s="4">
         <v>0</v>
       </c>
-      <c r="U368" s="4" t="s">
-        <v>1592</v>
-      </c>
-      <c r="V368" s="4" t="s">
-        <v>604</v>
-      </c>
+      <c r="U368" s="4"/>
+      <c r="V368" s="4"/>
       <c r="W368" s="4">
         <v>3</v>
       </c>
@@ -33506,16 +33521,16 @@
         <v>1000</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="C369" s="4">
-        <v>163568524</v>
+        <v>163568522</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E369" s="4">
-        <v>7948448</v>
+        <v>5867262</v>
       </c>
       <c r="F369" s="4" t="s">
         <v>51</v>
@@ -33530,7 +33545,7 @@
         <v>133</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K369" s="4"/>
       <c r="L369" s="4" t="s">
@@ -33539,14 +33554,14 @@
       <c r="M369" s="4"/>
       <c r="N369" s="4"/>
       <c r="O369" s="4" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="R369" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S369" s="4">
         <v>0</v>
@@ -33555,10 +33570,10 @@
         <v>0</v>
       </c>
       <c r="U369" s="4" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="V369" s="4" t="s">
-        <v>266</v>
+        <v>604</v>
       </c>
       <c r="W369" s="4">
         <v>3</v>
@@ -33568,11 +33583,9 @@
       </c>
       <c r="Y369" s="4"/>
       <c r="Z369" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA369" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AA369" s="4"/>
       <c r="AB369" s="4" t="s">
         <v>49</v>
       </c>
@@ -33582,16 +33595,16 @@
         <v>1000</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="C370" s="4">
-        <v>163568535</v>
+        <v>163568524</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E370" s="4">
-        <v>4326685</v>
+        <v>7948448</v>
       </c>
       <c r="F370" s="4" t="s">
         <v>51</v>
@@ -33606,7 +33619,7 @@
         <v>133</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K370" s="4"/>
       <c r="L370" s="4" t="s">
@@ -33615,14 +33628,14 @@
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
       <c r="O370" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="R370" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S370" s="4">
         <v>0</v>
@@ -33631,10 +33644,10 @@
         <v>0</v>
       </c>
       <c r="U370" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="V370" s="4" t="s">
-        <v>333</v>
+        <v>266</v>
       </c>
       <c r="W370" s="4">
         <v>3</v>
@@ -33644,7 +33657,7 @@
       </c>
       <c r="Y370" s="4"/>
       <c r="Z370" s="4" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="AA370" s="4" t="s">
         <v>48</v>
@@ -33658,16 +33671,16 @@
         <v>1000</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="C371" s="4">
-        <v>163568536</v>
+        <v>163568535</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E371" s="4">
-        <v>5891609</v>
+        <v>4326685</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>51</v>
@@ -33682,7 +33695,7 @@
         <v>133</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K371" s="4"/>
       <c r="L371" s="4" t="s">
@@ -33691,11 +33704,11 @@
       <c r="M371" s="4"/>
       <c r="N371" s="4"/>
       <c r="O371" s="4" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="P371" s="5"/>
       <c r="Q371" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="R371" s="4" t="s">
         <v>167</v>
@@ -33707,10 +33720,10 @@
         <v>0</v>
       </c>
       <c r="U371" s="4" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="V371" s="4" t="s">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="W371" s="4">
         <v>3</v>
@@ -33720,7 +33733,7 @@
       </c>
       <c r="Y371" s="4"/>
       <c r="Z371" s="4" t="s">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="AA371" s="4" t="s">
         <v>48</v>
@@ -33734,16 +33747,16 @@
         <v>1000</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="C372" s="4">
-        <v>163568541</v>
+        <v>163568536</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E372" s="4">
-        <v>5366500</v>
+        <v>5891609</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>51</v>
@@ -33758,7 +33771,7 @@
         <v>133</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K372" s="4"/>
       <c r="L372" s="4" t="s">
@@ -33767,11 +33780,11 @@
       <c r="M372" s="4"/>
       <c r="N372" s="4"/>
       <c r="O372" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="P372" s="5"/>
       <c r="Q372" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="R372" s="4" t="s">
         <v>167</v>
@@ -33782,8 +33795,12 @@
       <c r="T372" s="4">
         <v>0</v>
       </c>
-      <c r="U372" s="4"/>
-      <c r="V372" s="4"/>
+      <c r="U372" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="V372" s="4" t="s">
+        <v>402</v>
+      </c>
       <c r="W372" s="4">
         <v>3</v>
       </c>
@@ -33792,10 +33809,10 @@
       </c>
       <c r="Y372" s="4"/>
       <c r="Z372" s="4" t="s">
-        <v>1604</v>
+        <v>424</v>
       </c>
       <c r="AA372" s="4" t="s">
-        <v>903</v>
+        <v>48</v>
       </c>
       <c r="AB372" s="4" t="s">
         <v>49</v>
@@ -33806,16 +33823,16 @@
         <v>1000</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1288</v>
+        <v>1594</v>
       </c>
       <c r="C373" s="4">
-        <v>163568542</v>
+        <v>163568541</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E373" s="4">
-        <v>6530876</v>
+        <v>5366500</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>51</v>
@@ -33830,7 +33847,7 @@
         <v>133</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K373" s="4"/>
       <c r="L373" s="4" t="s">
@@ -33839,20 +33856,20 @@
       <c r="M373" s="4"/>
       <c r="N373" s="4"/>
       <c r="O373" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="P373" s="5"/>
       <c r="Q373" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="R373" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S373" s="4">
-        <v>3957267.07</v>
+        <v>0</v>
       </c>
       <c r="T373" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U373" s="4"/>
       <c r="V373" s="4"/>
@@ -33864,13 +33881,13 @@
       </c>
       <c r="Y373" s="4"/>
       <c r="Z373" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="AA373" s="4" t="s">
         <v>903</v>
       </c>
       <c r="AB373" s="4" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
     </row>
     <row r="374" spans="1:28">
@@ -33881,13 +33898,13 @@
         <v>1288</v>
       </c>
       <c r="C374" s="4">
-        <v>163568543</v>
+        <v>163568542</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E374" s="4">
-        <v>5885728</v>
+        <v>6530876</v>
       </c>
       <c r="F374" s="4" t="s">
         <v>51</v>
@@ -33902,7 +33919,7 @@
         <v>133</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K374" s="4"/>
       <c r="L374" s="4" t="s">
@@ -33911,27 +33928,23 @@
       <c r="M374" s="4"/>
       <c r="N374" s="4"/>
       <c r="O374" s="4" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="P374" s="5"/>
       <c r="Q374" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="R374" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="S374" s="4">
-        <v>0</v>
+        <v>3957267.07</v>
       </c>
       <c r="T374" s="4">
-        <v>0</v>
-      </c>
-      <c r="U374" s="4" t="s">
-        <v>1610</v>
-      </c>
-      <c r="V374" s="4" t="s">
-        <v>266</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U374" s="4"/>
+      <c r="V374" s="4"/>
       <c r="W374" s="4">
         <v>3</v>
       </c>
@@ -33940,13 +33953,13 @@
       </c>
       <c r="Y374" s="4"/>
       <c r="Z374" s="4" t="s">
-        <v>461</v>
+        <v>1612</v>
       </c>
       <c r="AA374" s="4" t="s">
-        <v>66</v>
+        <v>903</v>
       </c>
       <c r="AB374" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="375" spans="1:28">
@@ -33954,16 +33967,16 @@
         <v>1000</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>33</v>
+        <v>1288</v>
       </c>
       <c r="C375" s="4">
-        <v>163568568</v>
+        <v>163568543</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E375" s="4">
-        <v>5927513</v>
+        <v>5885728</v>
       </c>
       <c r="F375" s="4" t="s">
         <v>51</v>
@@ -33978,7 +33991,7 @@
         <v>133</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K375" s="4"/>
       <c r="L375" s="4" t="s">
@@ -33987,11 +34000,11 @@
       <c r="M375" s="4"/>
       <c r="N375" s="4"/>
       <c r="O375" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="P375" s="5"/>
       <c r="Q375" s="4" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="R375" s="4" t="s">
         <v>167</v>
@@ -34002,20 +34015,24 @@
       <c r="T375" s="4">
         <v>0</v>
       </c>
-      <c r="U375" s="4"/>
-      <c r="V375" s="4"/>
+      <c r="U375" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="V375" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="W375" s="4">
         <v>3</v>
       </c>
       <c r="X375" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y375" s="4"/>
       <c r="Z375" s="4" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="AA375" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB375" s="4" t="s">
         <v>49</v>
@@ -34029,13 +34046,13 @@
         <v>33</v>
       </c>
       <c r="C376" s="4">
-        <v>163569194</v>
+        <v>163568568</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E376" s="4">
-        <v>5867636</v>
+        <v>5927513</v>
       </c>
       <c r="F376" s="4" t="s">
         <v>51</v>
@@ -34050,7 +34067,7 @@
         <v>133</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K376" s="4"/>
       <c r="L376" s="4" t="s">
@@ -34059,11 +34076,11 @@
       <c r="M376" s="4"/>
       <c r="N376" s="4"/>
       <c r="O376" s="4" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="P376" s="5"/>
       <c r="Q376" s="4" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="R376" s="4" t="s">
         <v>167</v>
@@ -34084,9 +34101,11 @@
       </c>
       <c r="Y376" s="4"/>
       <c r="Z376" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA376" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="AA376" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB376" s="4" t="s">
         <v>49</v>
       </c>
@@ -34099,13 +34118,13 @@
         <v>33</v>
       </c>
       <c r="C377" s="4">
-        <v>163568517</v>
+        <v>163569194</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E377" s="4">
-        <v>5877224</v>
+        <v>5867636</v>
       </c>
       <c r="F377" s="4" t="s">
         <v>51</v>
@@ -34120,40 +34139,32 @@
         <v>133</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K377" s="4"/>
       <c r="L377" s="4" t="s">
-        <v>1615</v>
-      </c>
-      <c r="M377" s="4" t="s">
-        <v>1616</v>
-      </c>
-      <c r="N377" s="4">
-        <v>48</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="M377" s="4"/>
+      <c r="N377" s="4"/>
       <c r="O377" s="4" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="P377" s="5"/>
       <c r="Q377" s="4" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="R377" s="4" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="S377" s="4">
-        <v>443605.59</v>
+        <v>0</v>
       </c>
       <c r="T377" s="4">
-        <v>1</v>
-      </c>
-      <c r="U377" s="4" t="s">
-        <v>1619</v>
-      </c>
-      <c r="V377" s="4" t="s">
-        <v>430</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U377" s="4"/>
+      <c r="V377" s="4"/>
       <c r="W377" s="4">
         <v>3</v>
       </c>
@@ -34162,11 +34173,9 @@
       </c>
       <c r="Y377" s="4"/>
       <c r="Z377" s="4" t="s">
-        <v>1620</v>
-      </c>
-      <c r="AA377" s="4" t="s">
-        <v>101</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AA377" s="4"/>
       <c r="AB377" s="4" t="s">
         <v>49</v>
       </c>
@@ -34179,13 +34188,13 @@
         <v>33</v>
       </c>
       <c r="C378" s="4">
-        <v>163568544</v>
+        <v>163568517</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E378" s="4">
-        <v>5916137</v>
+        <v>5877224</v>
       </c>
       <c r="F378" s="4" t="s">
         <v>51</v>
@@ -34200,36 +34209,40 @@
         <v>133</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K378" s="4"/>
       <c r="L378" s="4" t="s">
+        <v>1620</v>
+      </c>
+      <c r="M378" s="4" t="s">
         <v>1621</v>
       </c>
-      <c r="M378" s="4" t="s">
+      <c r="N378" s="4">
+        <v>48</v>
+      </c>
+      <c r="O378" s="4" t="s">
         <v>1622</v>
-      </c>
-      <c r="N378" s="4">
-        <v>22</v>
-      </c>
-      <c r="O378" s="4" t="s">
-        <v>1623</v>
       </c>
       <c r="P378" s="5"/>
       <c r="Q378" s="4" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="R378" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S378" s="4">
-        <v>0</v>
+        <v>443605.59</v>
       </c>
       <c r="T378" s="4">
-        <v>0</v>
-      </c>
-      <c r="U378" s="4"/>
-      <c r="V378" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U378" s="4" t="s">
+        <v>1624</v>
+      </c>
+      <c r="V378" s="4" t="s">
+        <v>430</v>
+      </c>
       <c r="W378" s="4">
         <v>3</v>
       </c>
@@ -34240,7 +34253,9 @@
       <c r="Z378" s="4" t="s">
         <v>1625</v>
       </c>
-      <c r="AA378" s="4"/>
+      <c r="AA378" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="AB378" s="4" t="s">
         <v>49</v>
       </c>
@@ -34253,13 +34268,13 @@
         <v>33</v>
       </c>
       <c r="C379" s="4">
-        <v>163568533</v>
+        <v>163568544</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E379" s="4">
-        <v>5915736</v>
+        <v>5916137</v>
       </c>
       <c r="F379" s="4" t="s">
         <v>51</v>
@@ -34274,24 +34289,24 @@
         <v>133</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K379" s="4"/>
       <c r="L379" s="4" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="M379" s="4" t="s">
-        <v>1622</v>
+        <v>1627</v>
       </c>
       <c r="N379" s="4">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="O379" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="P379" s="5"/>
       <c r="Q379" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="R379" s="4" t="s">
         <v>185</v>
@@ -34312,11 +34327,9 @@
       </c>
       <c r="Y379" s="4"/>
       <c r="Z379" s="4" t="s">
-        <v>1628</v>
-      </c>
-      <c r="AA379" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1630</v>
+      </c>
+      <c r="AA379" s="4"/>
       <c r="AB379" s="4" t="s">
         <v>49</v>
       </c>
@@ -34326,16 +34339,16 @@
         <v>1000</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1359</v>
+        <v>33</v>
       </c>
       <c r="C380" s="4">
-        <v>163568520</v>
+        <v>163568533</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E380" s="4">
-        <v>5364215</v>
+        <v>5915736</v>
       </c>
       <c r="F380" s="4" t="s">
         <v>51</v>
@@ -34350,24 +34363,24 @@
         <v>133</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K380" s="4"/>
       <c r="L380" s="4" t="s">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="M380" s="4" t="s">
-        <v>1616</v>
+        <v>1627</v>
       </c>
       <c r="N380" s="4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O380" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="P380" s="5"/>
       <c r="Q380" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="R380" s="4" t="s">
         <v>185</v>
@@ -34378,21 +34391,17 @@
       <c r="T380" s="4">
         <v>0</v>
       </c>
-      <c r="U380" s="4" t="s">
-        <v>1631</v>
-      </c>
-      <c r="V380" s="4" t="s">
-        <v>430</v>
-      </c>
+      <c r="U380" s="4"/>
+      <c r="V380" s="4"/>
       <c r="W380" s="4">
         <v>3</v>
       </c>
       <c r="X380" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y380" s="4"/>
       <c r="Z380" s="4" t="s">
-        <v>424</v>
+        <v>1633</v>
       </c>
       <c r="AA380" s="4" t="s">
         <v>48</v>
@@ -34406,16 +34415,16 @@
         <v>1000</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>211</v>
+        <v>1359</v>
       </c>
       <c r="C381" s="4">
-        <v>163568516</v>
+        <v>163568520</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E381" s="4">
-        <v>7725669</v>
+        <v>5364215</v>
       </c>
       <c r="F381" s="4" t="s">
         <v>51</v>
@@ -34430,24 +34439,24 @@
         <v>133</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K381" s="4"/>
       <c r="L381" s="4" t="s">
+        <v>1626</v>
+      </c>
+      <c r="M381" s="4" t="s">
         <v>1621</v>
       </c>
-      <c r="M381" s="4" t="s">
-        <v>1616</v>
-      </c>
       <c r="N381" s="4">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="O381" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="P381" s="5"/>
       <c r="Q381" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="R381" s="4" t="s">
         <v>185</v>
@@ -34459,10 +34468,10 @@
         <v>0</v>
       </c>
       <c r="U381" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="V381" s="4" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
       <c r="W381" s="4">
         <v>3</v>
@@ -34472,7 +34481,7 @@
       </c>
       <c r="Y381" s="4"/>
       <c r="Z381" s="4" t="s">
-        <v>1628</v>
+        <v>424</v>
       </c>
       <c r="AA381" s="4" t="s">
         <v>48</v>
@@ -34486,16 +34495,16 @@
         <v>1000</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1359</v>
+        <v>211</v>
       </c>
       <c r="C382" s="4">
-        <v>163568519</v>
+        <v>163568516</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E382" s="4">
-        <v>5899639</v>
+        <v>7725669</v>
       </c>
       <c r="F382" s="4" t="s">
         <v>51</v>
@@ -34510,24 +34519,24 @@
         <v>133</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K382" s="4"/>
       <c r="L382" s="4" t="s">
+        <v>1626</v>
+      </c>
+      <c r="M382" s="4" t="s">
         <v>1621</v>
-      </c>
-      <c r="M382" s="4" t="s">
-        <v>1616</v>
       </c>
       <c r="N382" s="4">
         <v>41</v>
       </c>
       <c r="O382" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="P382" s="5"/>
       <c r="Q382" s="4" t="s">
-        <v>1633</v>
+        <v>1638</v>
       </c>
       <c r="R382" s="4" t="s">
         <v>185</v>
@@ -34539,10 +34548,10 @@
         <v>0</v>
       </c>
       <c r="U382" s="4" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="V382" s="4" t="s">
-        <v>525</v>
+        <v>333</v>
       </c>
       <c r="W382" s="4">
         <v>3</v>
@@ -34552,7 +34561,7 @@
       </c>
       <c r="Y382" s="4"/>
       <c r="Z382" s="4" t="s">
-        <v>424</v>
+        <v>1633</v>
       </c>
       <c r="AA382" s="4" t="s">
         <v>48</v>
@@ -34566,16 +34575,16 @@
         <v>1000</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>824</v>
+        <v>1359</v>
       </c>
       <c r="C383" s="4">
-        <v>163568518</v>
+        <v>163568519</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E383" s="4">
-        <v>5902466</v>
+        <v>5899639</v>
       </c>
       <c r="F383" s="4" t="s">
         <v>51</v>
@@ -34590,20 +34599,20 @@
         <v>133</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K383" s="4"/>
       <c r="L383" s="4" t="s">
+        <v>1626</v>
+      </c>
+      <c r="M383" s="4" t="s">
         <v>1621</v>
       </c>
-      <c r="M383" s="4" t="s">
-        <v>1616</v>
-      </c>
       <c r="N383" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O383" s="4" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="P383" s="5"/>
       <c r="Q383" s="4" t="s">
@@ -34619,10 +34628,10 @@
         <v>0</v>
       </c>
       <c r="U383" s="4" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="V383" s="4" t="s">
-        <v>349</v>
+        <v>525</v>
       </c>
       <c r="W383" s="4">
         <v>3</v>
@@ -34632,9 +34641,11 @@
       </c>
       <c r="Y383" s="4"/>
       <c r="Z383" s="4" t="s">
-        <v>1640</v>
-      </c>
-      <c r="AA383" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="AA383" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB383" s="4" t="s">
         <v>49</v>
       </c>
@@ -34647,13 +34658,13 @@
         <v>824</v>
       </c>
       <c r="C384" s="4">
-        <v>163568532</v>
+        <v>163568518</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E384" s="4">
-        <v>4326681</v>
+        <v>5902466</v>
       </c>
       <c r="F384" s="4" t="s">
         <v>51</v>
@@ -34668,24 +34679,24 @@
         <v>133</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K384" s="4"/>
       <c r="L384" s="4" t="s">
-        <v>1641</v>
+        <v>1626</v>
       </c>
       <c r="M384" s="4" t="s">
+        <v>1621</v>
+      </c>
+      <c r="N384" s="4">
+        <v>42</v>
+      </c>
+      <c r="O384" s="4" t="s">
         <v>1642</v>
-      </c>
-      <c r="N384" s="4">
-        <v>15</v>
-      </c>
-      <c r="O384" s="4" t="s">
-        <v>1643</v>
       </c>
       <c r="P384" s="5"/>
       <c r="Q384" s="4" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="R384" s="4" t="s">
         <v>185</v>
@@ -34697,10 +34708,10 @@
         <v>0</v>
       </c>
       <c r="U384" s="4" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="V384" s="4" t="s">
-        <v>581</v>
+        <v>349</v>
       </c>
       <c r="W384" s="4">
         <v>3</v>
@@ -34710,11 +34721,9 @@
       </c>
       <c r="Y384" s="4"/>
       <c r="Z384" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA384" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1645</v>
+      </c>
+      <c r="AA384" s="4"/>
       <c r="AB384" s="4" t="s">
         <v>49</v>
       </c>
@@ -34727,13 +34736,13 @@
         <v>824</v>
       </c>
       <c r="C385" s="4">
-        <v>163568534</v>
+        <v>163568532</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E385" s="4">
-        <v>4326782</v>
+        <v>4326681</v>
       </c>
       <c r="F385" s="4" t="s">
         <v>51</v>
@@ -34748,24 +34757,24 @@
         <v>133</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K385" s="4"/>
       <c r="L385" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M385" s="4" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="N385" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O385" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="P385" s="5"/>
       <c r="Q385" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="R385" s="4" t="s">
         <v>185</v>
@@ -34777,10 +34786,10 @@
         <v>0</v>
       </c>
       <c r="U385" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="V385" s="4" t="s">
-        <v>45</v>
+        <v>581</v>
       </c>
       <c r="W385" s="4">
         <v>3</v>
@@ -34807,13 +34816,13 @@
         <v>824</v>
       </c>
       <c r="C386" s="4">
-        <v>163568525</v>
+        <v>163568534</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E386" s="4">
-        <v>7752848</v>
+        <v>4326782</v>
       </c>
       <c r="F386" s="4" t="s">
         <v>51</v>
@@ -34828,24 +34837,24 @@
         <v>133</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K386" s="4"/>
       <c r="L386" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M386" s="4" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="N386" s="4">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="O386" s="4" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="P386" s="5"/>
       <c r="Q386" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="R386" s="4" t="s">
         <v>185</v>
@@ -34857,10 +34866,10 @@
         <v>0</v>
       </c>
       <c r="U386" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="V386" s="4" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="W386" s="4">
         <v>3</v>
@@ -34870,7 +34879,7 @@
       </c>
       <c r="Y386" s="4"/>
       <c r="Z386" s="4" t="s">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="AA386" s="4" t="s">
         <v>48</v>
@@ -34884,16 +34893,16 @@
         <v>1000</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>33</v>
+        <v>824</v>
       </c>
       <c r="C387" s="4">
-        <v>163568527</v>
+        <v>163568525</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E387" s="4">
-        <v>4326678</v>
+        <v>7752848</v>
       </c>
       <c r="F387" s="4" t="s">
         <v>51</v>
@@ -34908,24 +34917,24 @@
         <v>133</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K387" s="4"/>
       <c r="L387" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M387" s="4" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="N387" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O387" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="P387" s="5"/>
       <c r="Q387" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="R387" s="4" t="s">
         <v>185</v>
@@ -34937,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="U387" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="V387" s="4" t="s">
         <v>131</v>
@@ -34946,7 +34955,7 @@
         <v>3</v>
       </c>
       <c r="X387" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y387" s="4"/>
       <c r="Z387" s="4" t="s">
@@ -34967,13 +34976,13 @@
         <v>33</v>
       </c>
       <c r="C388" s="4">
-        <v>163568530</v>
+        <v>163568527</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E388" s="4">
-        <v>4323381</v>
+        <v>4326678</v>
       </c>
       <c r="F388" s="4" t="s">
         <v>51</v>
@@ -34988,24 +34997,24 @@
         <v>133</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K388" s="4"/>
       <c r="L388" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M388" s="4" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="N388" s="4">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O388" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="P388" s="5"/>
       <c r="Q388" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="R388" s="4" t="s">
         <v>185</v>
@@ -35017,10 +35026,10 @@
         <v>0</v>
       </c>
       <c r="U388" s="4" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="V388" s="4" t="s">
-        <v>349</v>
+        <v>131</v>
       </c>
       <c r="W388" s="4">
         <v>3</v>
@@ -35030,9 +35039,11 @@
       </c>
       <c r="Y388" s="4"/>
       <c r="Z388" s="4" t="s">
-        <v>1640</v>
-      </c>
-      <c r="AA388" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="AA388" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB388" s="4" t="s">
         <v>49</v>
       </c>
@@ -35045,13 +35056,13 @@
         <v>33</v>
       </c>
       <c r="C389" s="4">
-        <v>163568531</v>
+        <v>163568530</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E389" s="4">
-        <v>5867265</v>
+        <v>4323381</v>
       </c>
       <c r="F389" s="4" t="s">
         <v>51</v>
@@ -35066,24 +35077,24 @@
         <v>133</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K389" s="4"/>
       <c r="L389" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M389" s="4" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="N389" s="4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O389" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="P389" s="5"/>
       <c r="Q389" s="4" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="R389" s="4" t="s">
         <v>185</v>
@@ -35095,10 +35106,10 @@
         <v>0</v>
       </c>
       <c r="U389" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="V389" s="4" t="s">
-        <v>487</v>
+        <v>349</v>
       </c>
       <c r="W389" s="4">
         <v>3</v>
@@ -35108,11 +35119,9 @@
       </c>
       <c r="Y389" s="4"/>
       <c r="Z389" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA389" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1645</v>
+      </c>
+      <c r="AA389" s="4"/>
       <c r="AB389" s="4" t="s">
         <v>49</v>
       </c>
@@ -35125,13 +35134,13 @@
         <v>33</v>
       </c>
       <c r="C390" s="4">
-        <v>163568529</v>
+        <v>163568531</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E390" s="4">
-        <v>6528085</v>
+        <v>5867265</v>
       </c>
       <c r="F390" s="4" t="s">
         <v>51</v>
@@ -35146,39 +35155,39 @@
         <v>133</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K390" s="4"/>
       <c r="L390" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M390" s="4" t="s">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="N390" s="4">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O390" s="4" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="P390" s="5"/>
       <c r="Q390" s="4" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="R390" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S390" s="4">
-        <v>62003.21</v>
+        <v>0</v>
       </c>
       <c r="T390" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U390" s="4" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="V390" s="4" t="s">
-        <v>349</v>
+        <v>487</v>
       </c>
       <c r="W390" s="4">
         <v>3</v>
@@ -35188,10 +35197,10 @@
       </c>
       <c r="Y390" s="4"/>
       <c r="Z390" s="4" t="s">
-        <v>1620</v>
+        <v>424</v>
       </c>
       <c r="AA390" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="AB390" s="4" t="s">
         <v>49</v>
@@ -35202,16 +35211,16 @@
         <v>1000</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
       <c r="C391" s="4">
-        <v>163568513</v>
+        <v>163568529</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E391" s="4">
-        <v>4323378</v>
+        <v>6528085</v>
       </c>
       <c r="F391" s="4" t="s">
         <v>51</v>
@@ -35226,47 +35235,53 @@
         <v>133</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K391" s="4"/>
       <c r="L391" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M391" s="4" t="s">
-        <v>1616</v>
+        <v>1647</v>
       </c>
       <c r="N391" s="4">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="O391" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="P391" s="5"/>
       <c r="Q391" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="R391" s="4" t="s">
         <v>185</v>
       </c>
       <c r="S391" s="4">
-        <v>0</v>
+        <v>62003.21</v>
       </c>
       <c r="T391" s="4">
-        <v>0</v>
-      </c>
-      <c r="U391" s="4"/>
-      <c r="V391" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U391" s="4" t="s">
+        <v>1668</v>
+      </c>
+      <c r="V391" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="W391" s="4">
         <v>3</v>
       </c>
       <c r="X391" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y391" s="4"/>
       <c r="Z391" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="AA391" s="4"/>
+        <v>1625</v>
+      </c>
+      <c r="AA391" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="AB391" s="4" t="s">
         <v>49</v>
       </c>
@@ -35279,13 +35294,13 @@
         <v>211</v>
       </c>
       <c r="C392" s="4">
-        <v>163568514</v>
+        <v>163568513</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E392" s="4">
-        <v>5867630</v>
+        <v>4323378</v>
       </c>
       <c r="F392" s="4" t="s">
         <v>51</v>
@@ -35300,24 +35315,24 @@
         <v>133</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K392" s="4"/>
       <c r="L392" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M392" s="4" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="N392" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O392" s="4" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="P392" s="5"/>
       <c r="Q392" s="4" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="R392" s="4" t="s">
         <v>185</v>
@@ -35328,12 +35343,8 @@
       <c r="T392" s="4">
         <v>0</v>
       </c>
-      <c r="U392" s="4" t="s">
-        <v>1668</v>
-      </c>
-      <c r="V392" s="4" t="s">
-        <v>349</v>
-      </c>
+      <c r="U392" s="4"/>
+      <c r="V392" s="4"/>
       <c r="W392" s="4">
         <v>3</v>
       </c>
@@ -35342,11 +35353,9 @@
       </c>
       <c r="Y392" s="4"/>
       <c r="Z392" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA392" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="AA392" s="4"/>
       <c r="AB392" s="4" t="s">
         <v>49</v>
       </c>
@@ -35356,16 +35365,16 @@
         <v>1000</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="C393" s="4">
-        <v>163569195</v>
+        <v>163568514</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E393" s="4">
-        <v>5364204</v>
+        <v>5867630</v>
       </c>
       <c r="F393" s="4" t="s">
         <v>51</v>
@@ -35380,24 +35389,24 @@
         <v>133</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K393" s="4"/>
       <c r="L393" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M393" s="4" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="N393" s="4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="O393" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="P393" s="5"/>
       <c r="Q393" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="R393" s="4" t="s">
         <v>185</v>
@@ -35408,17 +35417,21 @@
       <c r="T393" s="4">
         <v>0</v>
       </c>
-      <c r="U393" s="4"/>
-      <c r="V393" s="4"/>
+      <c r="U393" s="4" t="s">
+        <v>1673</v>
+      </c>
+      <c r="V393" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="W393" s="4">
         <v>3</v>
       </c>
       <c r="X393" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y393" s="4"/>
       <c r="Z393" s="4" t="s">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="AA393" s="4" t="s">
         <v>48</v>
@@ -35432,16 +35445,16 @@
         <v>1000</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
       <c r="C394" s="4">
-        <v>163568511</v>
+        <v>163569195</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E394" s="4">
-        <v>4326661</v>
+        <v>5364204</v>
       </c>
       <c r="F394" s="4" t="s">
         <v>51</v>
@@ -35456,24 +35469,24 @@
         <v>133</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K394" s="4"/>
       <c r="L394" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M394" s="4" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="N394" s="4">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="O394" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="P394" s="5"/>
       <c r="Q394" s="4" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="R394" s="4" t="s">
         <v>185</v>
@@ -35484,21 +35497,17 @@
       <c r="T394" s="4">
         <v>0</v>
       </c>
-      <c r="U394" s="4" t="s">
-        <v>1673</v>
-      </c>
-      <c r="V394" s="4" t="s">
-        <v>581</v>
-      </c>
+      <c r="U394" s="4"/>
+      <c r="V394" s="4"/>
       <c r="W394" s="4">
         <v>3</v>
       </c>
       <c r="X394" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y394" s="4"/>
       <c r="Z394" s="4" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="AA394" s="4" t="s">
         <v>48</v>
@@ -35512,16 +35521,16 @@
         <v>1000</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>33</v>
+        <v>211</v>
       </c>
       <c r="C395" s="4">
-        <v>163568523</v>
+        <v>163568511</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E395" s="4">
-        <v>4327238</v>
+        <v>4326661</v>
       </c>
       <c r="F395" s="4" t="s">
         <v>51</v>
@@ -35536,24 +35545,24 @@
         <v>133</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="K395" s="4"/>
       <c r="L395" s="4" t="s">
-        <v>1641</v>
+        <v>1646</v>
       </c>
       <c r="M395" s="4" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="N395" s="4">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O395" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="P395" s="5"/>
       <c r="Q395" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="R395" s="4" t="s">
         <v>185</v>
@@ -35564,19 +35573,25 @@
       <c r="T395" s="4">
         <v>0</v>
       </c>
-      <c r="U395" s="4"/>
-      <c r="V395" s="4"/>
+      <c r="U395" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="V395" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="W395" s="4">
         <v>3</v>
       </c>
       <c r="X395" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y395" s="4"/>
       <c r="Z395" s="4" t="s">
-        <v>1625</v>
-      </c>
-      <c r="AA395" s="4"/>
+        <v>334</v>
+      </c>
+      <c r="AA395" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB395" s="4" t="s">
         <v>49</v>
       </c>
@@ -35589,13 +35604,13 @@
         <v>33</v>
       </c>
       <c r="C396" s="4">
-        <v>163568558</v>
+        <v>163568523</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E396" s="4">
-        <v>7209364</v>
+        <v>4327238</v>
       </c>
       <c r="F396" s="4" t="s">
         <v>51</v>
@@ -35610,17 +35625,17 @@
         <v>133</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1676</v>
+        <v>1591</v>
       </c>
       <c r="K396" s="4"/>
       <c r="L396" s="4" t="s">
-        <v>1677</v>
+        <v>1646</v>
       </c>
       <c r="M396" s="4" t="s">
-        <v>1678</v>
+        <v>1621</v>
       </c>
       <c r="N396" s="4">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="O396" s="4" t="s">
         <v>1679</v>
@@ -35630,7 +35645,7 @@
         <v>1680</v>
       </c>
       <c r="R396" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S396" s="4">
         <v>0</v>
@@ -35638,12 +35653,8 @@
       <c r="T396" s="4">
         <v>0</v>
       </c>
-      <c r="U396" s="4" t="s">
-        <v>1681</v>
-      </c>
-      <c r="V396" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="U396" s="4"/>
+      <c r="V396" s="4"/>
       <c r="W396" s="4">
         <v>3</v>
       </c>
@@ -35652,11 +35663,9 @@
       </c>
       <c r="Y396" s="4"/>
       <c r="Z396" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA396" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>1630</v>
+      </c>
+      <c r="AA396" s="4"/>
       <c r="AB396" s="4" t="s">
         <v>49</v>
       </c>
@@ -35669,13 +35678,13 @@
         <v>33</v>
       </c>
       <c r="C397" s="4">
-        <v>163568551</v>
+        <v>163568558</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E397" s="4">
-        <v>7949838</v>
+        <v>7209364</v>
       </c>
       <c r="F397" s="4" t="s">
         <v>51</v>
@@ -35690,27 +35699,27 @@
         <v>133</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="K397" s="4"/>
       <c r="L397" s="4" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="M397" s="4" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="N397" s="4">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="O397" s="4" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="P397" s="5"/>
       <c r="Q397" s="4" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="R397" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S397" s="4">
         <v>0</v>
@@ -35719,10 +35728,10 @@
         <v>0</v>
       </c>
       <c r="U397" s="4" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="V397" s="4" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="W397" s="4">
         <v>3</v>
@@ -35749,13 +35758,13 @@
         <v>33</v>
       </c>
       <c r="C398" s="4">
-        <v>163568548</v>
+        <v>163568551</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E398" s="4">
-        <v>7742088</v>
+        <v>7949838</v>
       </c>
       <c r="F398" s="4" t="s">
         <v>51</v>
@@ -35770,24 +35779,24 @@
         <v>133</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="K398" s="4"/>
       <c r="L398" s="4" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="M398" s="4" t="s">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="N398" s="4">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="O398" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="P398" s="5"/>
       <c r="Q398" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="R398" s="4" t="s">
         <v>43</v>
@@ -35799,10 +35808,10 @@
         <v>0</v>
       </c>
       <c r="U398" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="V398" s="4" t="s">
-        <v>131</v>
+        <v>266</v>
       </c>
       <c r="W398" s="4">
         <v>3</v>
@@ -35812,7 +35821,7 @@
       </c>
       <c r="Y398" s="4"/>
       <c r="Z398" s="4" t="s">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="AA398" s="4" t="s">
         <v>48</v>
@@ -35829,13 +35838,13 @@
         <v>33</v>
       </c>
       <c r="C399" s="4">
-        <v>163568549</v>
+        <v>163568548</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E399" s="4">
-        <v>7730020</v>
+        <v>7742088</v>
       </c>
       <c r="F399" s="4" t="s">
         <v>51</v>
@@ -35850,24 +35859,24 @@
         <v>133</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="K399" s="4"/>
       <c r="L399" s="4" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="M399" s="4" t="s">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="N399" s="4">
         <v>76</v>
       </c>
       <c r="O399" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="P399" s="5"/>
       <c r="Q399" s="4" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="R399" s="4" t="s">
         <v>43</v>
@@ -35879,7 +35888,7 @@
         <v>0</v>
       </c>
       <c r="U399" s="4" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="V399" s="4" t="s">
         <v>131</v>
@@ -35892,7 +35901,7 @@
       </c>
       <c r="Y399" s="4"/>
       <c r="Z399" s="4" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="AA399" s="4" t="s">
         <v>48</v>
@@ -35909,13 +35918,13 @@
         <v>33</v>
       </c>
       <c r="C400" s="4">
-        <v>163568552</v>
+        <v>163568549</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E400" s="4">
-        <v>7258875</v>
+        <v>7730020</v>
       </c>
       <c r="F400" s="4" t="s">
         <v>51</v>
@@ -35930,24 +35939,24 @@
         <v>133</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="K400" s="4"/>
       <c r="L400" s="4" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="M400" s="4" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="N400" s="4">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="O400" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="P400" s="5"/>
       <c r="Q400" s="4" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="R400" s="4" t="s">
         <v>43</v>
@@ -35959,10 +35968,10 @@
         <v>0</v>
       </c>
       <c r="U400" s="4" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="V400" s="4" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="W400" s="4">
         <v>3</v>
@@ -35972,9 +35981,11 @@
       </c>
       <c r="Y400" s="4"/>
       <c r="Z400" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="AA400" s="4"/>
+        <v>334</v>
+      </c>
+      <c r="AA400" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB400" s="4" t="s">
         <v>49</v>
       </c>
@@ -35987,13 +35998,13 @@
         <v>33</v>
       </c>
       <c r="C401" s="4">
-        <v>163568560</v>
+        <v>163568552</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E401" s="4">
-        <v>7949883</v>
+        <v>7258875</v>
       </c>
       <c r="F401" s="4" t="s">
         <v>51</v>
@@ -36008,24 +36019,24 @@
         <v>133</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1676</v>
+        <v>1681</v>
       </c>
       <c r="K401" s="4"/>
       <c r="L401" s="4" t="s">
-        <v>1677</v>
+        <v>1682</v>
       </c>
       <c r="M401" s="4" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="N401" s="4">
         <v>51</v>
       </c>
       <c r="O401" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="P401" s="5"/>
       <c r="Q401" s="4" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="R401" s="4" t="s">
         <v>43</v>
@@ -36037,10 +36048,10 @@
         <v>0</v>
       </c>
       <c r="U401" s="4" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="V401" s="4" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="W401" s="4">
         <v>3</v>
@@ -36065,13 +36076,13 @@
         <v>33</v>
       </c>
       <c r="C402" s="4">
-        <v>163342542</v>
+        <v>163568560</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E402" s="4">
-        <v>1108684</v>
+        <v>7949883</v>
       </c>
       <c r="F402" s="4" t="s">
         <v>51</v>
@@ -36083,26 +36094,30 @@
         <v>133</v>
       </c>
       <c r="I402" s="4" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1698</v>
+        <v>1681</v>
       </c>
       <c r="K402" s="4"/>
       <c r="L402" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M402" s="4"/>
-      <c r="N402" s="4"/>
+        <v>1682</v>
+      </c>
+      <c r="M402" s="4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="N402" s="4">
+        <v>51</v>
+      </c>
       <c r="O402" s="4" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="P402" s="5"/>
       <c r="Q402" s="4" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="R402" s="4" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="S402" s="4">
         <v>0</v>
@@ -36111,24 +36126,22 @@
         <v>0</v>
       </c>
       <c r="U402" s="4" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="V402" s="4" t="s">
-        <v>333</v>
+        <v>266</v>
       </c>
       <c r="W402" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X402" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y402" s="4"/>
       <c r="Z402" s="4" t="s">
-        <v>1702</v>
-      </c>
-      <c r="AA402" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AA402" s="4"/>
       <c r="AB402" s="4" t="s">
         <v>49</v>
       </c>
@@ -36138,16 +36151,16 @@
         <v>1000</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1136</v>
+        <v>33</v>
       </c>
       <c r="C403" s="4">
-        <v>163569111</v>
+        <v>163342542</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="E403" s="4">
-        <v>8161103</v>
+        <v>1108684</v>
       </c>
       <c r="F403" s="4" t="s">
         <v>51</v>
@@ -36159,13 +36172,15 @@
         <v>133</v>
       </c>
       <c r="I403" s="4" t="s">
-        <v>133</v>
+        <v>287</v>
       </c>
       <c r="J403" s="4" t="s">
         <v>1703</v>
       </c>
       <c r="K403" s="4"/>
-      <c r="L403" s="4"/>
+      <c r="L403" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M403" s="4"/>
       <c r="N403" s="4"/>
       <c r="O403" s="4" t="s">
@@ -36176,7 +36191,7 @@
         <v>1705</v>
       </c>
       <c r="R403" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S403" s="4">
         <v>0</v>
@@ -36184,20 +36199,24 @@
       <c r="T403" s="4">
         <v>0</v>
       </c>
-      <c r="U403" s="4"/>
-      <c r="V403" s="4"/>
+      <c r="U403" s="4" t="s">
+        <v>1706</v>
+      </c>
+      <c r="V403" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="W403" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X403" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y403" s="4"/>
       <c r="Z403" s="4" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="AA403" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB403" s="4" t="s">
         <v>49</v>
@@ -36208,16 +36227,16 @@
         <v>1000</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>33</v>
+        <v>1136</v>
       </c>
       <c r="C404" s="4">
-        <v>163529880</v>
+        <v>163569111</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E404" s="4">
-        <v>1052016</v>
+        <v>8161103</v>
       </c>
       <c r="F404" s="4" t="s">
         <v>51</v>
@@ -36232,22 +36251,18 @@
         <v>133</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="K404" s="4"/>
-      <c r="L404" s="4" t="s">
-        <v>982</v>
-      </c>
-      <c r="M404" s="4" t="s">
-        <v>1707</v>
-      </c>
+      <c r="L404" s="4"/>
+      <c r="M404" s="4"/>
       <c r="N404" s="4"/>
       <c r="O404" s="4" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="P404" s="5"/>
       <c r="Q404" s="4" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="R404" s="4" t="s">
         <v>92</v>
@@ -36261,17 +36276,17 @@
       <c r="U404" s="4"/>
       <c r="V404" s="4"/>
       <c r="W404" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X404" s="4" t="s">
-        <v>1710</v>
+        <v>178</v>
       </c>
       <c r="Y404" s="4"/>
       <c r="Z404" s="4" t="s">
         <v>1711</v>
       </c>
       <c r="AA404" s="4" t="s">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="AB404" s="4" t="s">
         <v>49</v>
@@ -36285,13 +36300,13 @@
         <v>33</v>
       </c>
       <c r="C405" s="4">
-        <v>163585693</v>
+        <v>163529880</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E405" s="4">
-        <v>6765644</v>
+        <v>1052016</v>
       </c>
       <c r="F405" s="4" t="s">
         <v>51</v>
@@ -36306,13 +36321,15 @@
         <v>133</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="K405" s="4"/>
       <c r="L405" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M405" s="4"/>
+        <v>982</v>
+      </c>
+      <c r="M405" s="4" t="s">
+        <v>1712</v>
+      </c>
       <c r="N405" s="4"/>
       <c r="O405" s="4" t="s">
         <v>1713</v>
@@ -36322,7 +36339,7 @@
         <v>1714</v>
       </c>
       <c r="R405" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S405" s="4">
         <v>0</v>
@@ -36333,17 +36350,17 @@
       <c r="U405" s="4"/>
       <c r="V405" s="4"/>
       <c r="W405" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X405" s="4" t="s">
-        <v>46</v>
+        <v>1715</v>
       </c>
       <c r="Y405" s="4"/>
       <c r="Z405" s="4" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="AA405" s="4" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="AB405" s="4" t="s">
         <v>49</v>
@@ -36357,13 +36374,13 @@
         <v>33</v>
       </c>
       <c r="C406" s="4">
-        <v>163568562</v>
+        <v>163585693</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E406" s="4">
-        <v>1030230</v>
+        <v>6765644</v>
       </c>
       <c r="F406" s="4" t="s">
         <v>51</v>
@@ -36378,15 +36395,13 @@
         <v>133</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="K406" s="4"/>
       <c r="L406" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="M406" s="4" t="s">
-        <v>1717</v>
-      </c>
+      <c r="M406" s="4"/>
       <c r="N406" s="4"/>
       <c r="O406" s="4" t="s">
         <v>1718</v>
@@ -36396,10 +36411,10 @@
         <v>1719</v>
       </c>
       <c r="R406" s="4" t="s">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="S406" s="4">
-        <v>2968256.09</v>
+        <v>0</v>
       </c>
       <c r="T406" s="4">
         <v>0</v>
@@ -36407,17 +36422,17 @@
       <c r="U406" s="4"/>
       <c r="V406" s="4"/>
       <c r="W406" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X406" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y406" s="4"/>
       <c r="Z406" s="4" t="s">
-        <v>1628</v>
+        <v>1720</v>
       </c>
       <c r="AA406" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB406" s="4" t="s">
         <v>49</v>
@@ -36431,13 +36446,13 @@
         <v>33</v>
       </c>
       <c r="C407" s="4">
-        <v>163568564</v>
+        <v>163568562</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E407" s="4">
-        <v>1024682</v>
+        <v>1030230</v>
       </c>
       <c r="F407" s="4" t="s">
         <v>51</v>
@@ -36452,28 +36467,28 @@
         <v>133</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K407" s="4"/>
       <c r="L407" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M407" s="4" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="N407" s="4"/>
       <c r="O407" s="4" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="P407" s="5"/>
       <c r="Q407" s="4" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="R407" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S407" s="4">
-        <v>0</v>
+        <v>2968256.09</v>
       </c>
       <c r="T407" s="4">
         <v>0</v>
@@ -36488,10 +36503,10 @@
       </c>
       <c r="Y407" s="4"/>
       <c r="Z407" s="4" t="s">
-        <v>461</v>
+        <v>1633</v>
       </c>
       <c r="AA407" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB407" s="4" t="s">
         <v>49</v>
@@ -36505,13 +36520,13 @@
         <v>33</v>
       </c>
       <c r="C408" s="4">
-        <v>163568569</v>
+        <v>163568564</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E408" s="4">
-        <v>1024675</v>
+        <v>1024682</v>
       </c>
       <c r="F408" s="4" t="s">
         <v>51</v>
@@ -36526,31 +36541,31 @@
         <v>133</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K408" s="4"/>
       <c r="L408" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M408" s="4" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="N408" s="4"/>
       <c r="O408" s="4" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="P408" s="5"/>
       <c r="Q408" s="4" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="R408" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S408" s="4">
-        <v>806727.6800000001</v>
+        <v>0</v>
       </c>
       <c r="T408" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U408" s="4"/>
       <c r="V408" s="4"/>
@@ -36562,13 +36577,13 @@
       </c>
       <c r="Y408" s="4"/>
       <c r="Z408" s="4" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="AA408" s="4" t="s">
         <v>66</v>
       </c>
       <c r="AB408" s="4" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
     </row>
     <row r="409" spans="1:28">
@@ -36579,13 +36594,13 @@
         <v>33</v>
       </c>
       <c r="C409" s="4">
-        <v>163568570</v>
+        <v>163568569</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E409" s="4">
-        <v>1024679</v>
+        <v>1024675</v>
       </c>
       <c r="F409" s="4" t="s">
         <v>51</v>
@@ -36600,38 +36615,34 @@
         <v>133</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K409" s="4"/>
       <c r="L409" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M409" s="4" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="N409" s="4"/>
       <c r="O409" s="4" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="P409" s="5"/>
       <c r="Q409" s="4" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
       <c r="R409" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S409" s="4">
-        <v>255459.04</v>
+        <v>806727.6800000001</v>
       </c>
       <c r="T409" s="4">
-        <v>1</v>
-      </c>
-      <c r="U409" s="4" t="s">
-        <v>1726</v>
-      </c>
-      <c r="V409" s="4" t="s">
-        <v>610</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="U409" s="4"/>
+      <c r="V409" s="4"/>
       <c r="W409" s="4">
         <v>3</v>
       </c>
@@ -36640,13 +36651,13 @@
       </c>
       <c r="Y409" s="4"/>
       <c r="Z409" s="4" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="AA409" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB409" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="410" spans="1:28">
@@ -36657,13 +36668,13 @@
         <v>33</v>
       </c>
       <c r="C410" s="4">
-        <v>163568574</v>
+        <v>163568570</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E410" s="4">
-        <v>1024684</v>
+        <v>1024679</v>
       </c>
       <c r="F410" s="4" t="s">
         <v>51</v>
@@ -36678,34 +36689,34 @@
         <v>133</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K410" s="4"/>
       <c r="L410" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M410" s="4" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="N410" s="4"/>
       <c r="O410" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="P410" s="5"/>
       <c r="Q410" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="R410" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S410" s="4">
-        <v>6432996.49</v>
+        <v>255459.04</v>
       </c>
       <c r="T410" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="U410" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="V410" s="4" t="s">
         <v>610</v>
@@ -36718,13 +36729,13 @@
       </c>
       <c r="Y410" s="4"/>
       <c r="Z410" s="4" t="s">
-        <v>1730</v>
+        <v>424</v>
       </c>
       <c r="AA410" s="4" t="s">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="AB410" s="4" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
     </row>
     <row r="411" spans="1:28">
@@ -36735,13 +36746,13 @@
         <v>33</v>
       </c>
       <c r="C411" s="4">
-        <v>163568546</v>
+        <v>163568574</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E411" s="4">
-        <v>1024712</v>
+        <v>1024684</v>
       </c>
       <c r="F411" s="4" t="s">
         <v>51</v>
@@ -36756,14 +36767,14 @@
         <v>133</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K411" s="4"/>
       <c r="L411" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M411" s="4" t="s">
-        <v>1731</v>
+        <v>1722</v>
       </c>
       <c r="N411" s="4"/>
       <c r="O411" s="4" t="s">
@@ -36777,13 +36788,17 @@
         <v>167</v>
       </c>
       <c r="S411" s="4">
-        <v>0</v>
+        <v>6432996.49</v>
       </c>
       <c r="T411" s="4">
-        <v>0</v>
-      </c>
-      <c r="U411" s="4"/>
-      <c r="V411" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="U411" s="4" t="s">
+        <v>1734</v>
+      </c>
+      <c r="V411" s="4" t="s">
+        <v>610</v>
+      </c>
       <c r="W411" s="4">
         <v>3</v>
       </c>
@@ -36792,13 +36807,13 @@
       </c>
       <c r="Y411" s="4"/>
       <c r="Z411" s="4" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="AA411" s="4" t="s">
-        <v>642</v>
+        <v>280</v>
       </c>
       <c r="AB411" s="4" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="412" spans="1:28">
@@ -36806,16 +36821,16 @@
         <v>1000</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>418</v>
+        <v>33</v>
       </c>
       <c r="C412" s="4">
-        <v>163568554</v>
+        <v>163568546</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E412" s="4">
-        <v>1024719</v>
+        <v>1024712</v>
       </c>
       <c r="F412" s="4" t="s">
         <v>51</v>
@@ -36830,22 +36845,22 @@
         <v>133</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K412" s="4"/>
       <c r="L412" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M412" s="4" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="N412" s="4"/>
       <c r="O412" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="P412" s="5"/>
       <c r="Q412" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="R412" s="4" t="s">
         <v>167</v>
@@ -36856,23 +36871,21 @@
       <c r="T412" s="4">
         <v>0</v>
       </c>
-      <c r="U412" s="4" t="s">
-        <v>1737</v>
-      </c>
-      <c r="V412" s="4" t="s">
-        <v>1738</v>
-      </c>
+      <c r="U412" s="4"/>
+      <c r="V412" s="4"/>
       <c r="W412" s="4">
         <v>3</v>
       </c>
       <c r="X412" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y412" s="4"/>
       <c r="Z412" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="AA412" s="4"/>
+        <v>1739</v>
+      </c>
+      <c r="AA412" s="4" t="s">
+        <v>642</v>
+      </c>
       <c r="AB412" s="4" t="s">
         <v>49</v>
       </c>
@@ -36885,13 +36898,13 @@
         <v>418</v>
       </c>
       <c r="C413" s="4">
-        <v>163568555</v>
+        <v>163568554</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E413" s="4">
-        <v>1024710</v>
+        <v>1024719</v>
       </c>
       <c r="F413" s="4" t="s">
         <v>51</v>
@@ -36906,34 +36919,38 @@
         <v>133</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K413" s="4"/>
       <c r="L413" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M413" s="4" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="N413" s="4"/>
       <c r="O413" s="4" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="P413" s="5"/>
       <c r="Q413" s="4" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="R413" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S413" s="4">
-        <v>208021.49</v>
+        <v>0</v>
       </c>
       <c r="T413" s="4">
-        <v>1</v>
-      </c>
-      <c r="U413" s="4"/>
-      <c r="V413" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U413" s="4" t="s">
+        <v>1742</v>
+      </c>
+      <c r="V413" s="4" t="s">
+        <v>1743</v>
+      </c>
       <c r="W413" s="4">
         <v>3</v>
       </c>
@@ -36942,11 +36959,9 @@
       </c>
       <c r="Y413" s="4"/>
       <c r="Z413" s="4" t="s">
-        <v>1628</v>
-      </c>
-      <c r="AA413" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="AA413" s="4"/>
       <c r="AB413" s="4" t="s">
         <v>49</v>
       </c>
@@ -36956,16 +36971,16 @@
         <v>1000</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1136</v>
+        <v>418</v>
       </c>
       <c r="C414" s="4">
-        <v>163568559</v>
+        <v>163568555</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E414" s="4">
-        <v>1024718</v>
+        <v>1024710</v>
       </c>
       <c r="F414" s="4" t="s">
         <v>51</v>
@@ -36980,38 +36995,34 @@
         <v>133</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K414" s="4"/>
       <c r="L414" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M414" s="4" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="N414" s="4"/>
       <c r="O414" s="4" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="P414" s="5"/>
       <c r="Q414" s="4" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="R414" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S414" s="4">
-        <v>0</v>
+        <v>208021.49</v>
       </c>
       <c r="T414" s="4">
-        <v>0</v>
-      </c>
-      <c r="U414" s="4" t="s">
-        <v>1743</v>
-      </c>
-      <c r="V414" s="4" t="s">
-        <v>581</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U414" s="4"/>
+      <c r="V414" s="4"/>
       <c r="W414" s="4">
         <v>3</v>
       </c>
@@ -37020,10 +37031,10 @@
       </c>
       <c r="Y414" s="4"/>
       <c r="Z414" s="4" t="s">
-        <v>494</v>
+        <v>1633</v>
       </c>
       <c r="AA414" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB414" s="4" t="s">
         <v>49</v>
@@ -37037,13 +37048,13 @@
         <v>1136</v>
       </c>
       <c r="C415" s="4">
-        <v>163568561</v>
+        <v>163568559</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E415" s="4">
-        <v>1024748</v>
+        <v>1024718</v>
       </c>
       <c r="F415" s="4" t="s">
         <v>51</v>
@@ -37058,22 +37069,22 @@
         <v>133</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K415" s="4"/>
       <c r="L415" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M415" s="4" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="N415" s="4"/>
       <c r="O415" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="P415" s="5"/>
       <c r="Q415" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="R415" s="4" t="s">
         <v>167</v>
@@ -37085,10 +37096,10 @@
         <v>0</v>
       </c>
       <c r="U415" s="4" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="V415" s="4" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="W415" s="4">
         <v>3</v>
@@ -37098,10 +37109,10 @@
       </c>
       <c r="Y415" s="4"/>
       <c r="Z415" s="4" t="s">
-        <v>1628</v>
+        <v>494</v>
       </c>
       <c r="AA415" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB415" s="4" t="s">
         <v>49</v>
@@ -37115,13 +37126,13 @@
         <v>1136</v>
       </c>
       <c r="C416" s="4">
-        <v>163568571</v>
+        <v>163568561</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E416" s="4">
-        <v>1024704</v>
+        <v>1024748</v>
       </c>
       <c r="F416" s="4" t="s">
         <v>51</v>
@@ -37136,37 +37147,37 @@
         <v>133</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K416" s="4"/>
       <c r="L416" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M416" s="4" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="N416" s="4"/>
       <c r="O416" s="4" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="P416" s="5"/>
       <c r="Q416" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="R416" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S416" s="4">
-        <v>178233.87</v>
+        <v>0</v>
       </c>
       <c r="T416" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U416" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="V416" s="4" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="W416" s="4">
         <v>3</v>
@@ -37176,7 +37187,7 @@
       </c>
       <c r="Y416" s="4"/>
       <c r="Z416" s="4" t="s">
-        <v>424</v>
+        <v>1633</v>
       </c>
       <c r="AA416" s="4" t="s">
         <v>48</v>
@@ -37193,13 +37204,13 @@
         <v>1136</v>
       </c>
       <c r="C417" s="4">
-        <v>163568589</v>
+        <v>163568571</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E417" s="4">
-        <v>1024701</v>
+        <v>1024704</v>
       </c>
       <c r="F417" s="4" t="s">
         <v>51</v>
@@ -37214,34 +37225,34 @@
         <v>133</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="K417" s="4"/>
       <c r="L417" s="4" t="s">
         <v>296</v>
       </c>
       <c r="M417" s="4" t="s">
-        <v>1731</v>
+        <v>1736</v>
       </c>
       <c r="N417" s="4"/>
       <c r="O417" s="4" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="P417" s="5"/>
       <c r="Q417" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="R417" s="4" t="s">
         <v>167</v>
       </c>
       <c r="S417" s="4">
-        <v>0</v>
+        <v>178233.87</v>
       </c>
       <c r="T417" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U417" s="4" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="V417" s="4" t="s">
         <v>610</v>
@@ -37254,10 +37265,10 @@
       </c>
       <c r="Y417" s="4"/>
       <c r="Z417" s="4" t="s">
-        <v>490</v>
+        <v>424</v>
       </c>
       <c r="AA417" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="AB417" s="4" t="s">
         <v>49</v>
@@ -37268,16 +37279,16 @@
         <v>1000</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>536</v>
+        <v>1136</v>
       </c>
       <c r="C418" s="4">
-        <v>163568435</v>
+        <v>163568589</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E418" s="4">
-        <v>7870323</v>
+        <v>1024701</v>
       </c>
       <c r="F418" s="4" t="s">
         <v>51</v>
@@ -37292,34 +37303,38 @@
         <v>133</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1753</v>
+        <v>1721</v>
       </c>
       <c r="K418" s="4"/>
       <c r="L418" s="4" t="s">
-        <v>1754</v>
+        <v>296</v>
       </c>
       <c r="M418" s="4" t="s">
-        <v>1755</v>
+        <v>1736</v>
       </c>
       <c r="N418" s="4"/>
       <c r="O418" s="4" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="P418" s="5"/>
       <c r="Q418" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="R418" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="S418" s="4">
+        <v>0</v>
+      </c>
+      <c r="T418" s="4">
+        <v>0</v>
+      </c>
+      <c r="U418" s="4" t="s">
         <v>1757</v>
       </c>
-      <c r="R418" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="S418" s="4">
-        <v>0</v>
-      </c>
-      <c r="T418" s="4">
-        <v>0</v>
-      </c>
-      <c r="U418" s="4"/>
-      <c r="V418" s="4"/>
+      <c r="V418" s="4" t="s">
+        <v>610</v>
+      </c>
       <c r="W418" s="4">
         <v>3</v>
       </c>
@@ -37328,7 +37343,7 @@
       </c>
       <c r="Y418" s="4"/>
       <c r="Z418" s="4" t="s">
-        <v>1758</v>
+        <v>490</v>
       </c>
       <c r="AA418" s="4" t="s">
         <v>66</v>
@@ -37342,16 +37357,16 @@
         <v>1000</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>33</v>
+        <v>536</v>
       </c>
       <c r="C419" s="4">
-        <v>163586934</v>
+        <v>163568435</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E419" s="4">
-        <v>7788272</v>
+        <v>7870323</v>
       </c>
       <c r="F419" s="4" t="s">
         <v>51</v>
@@ -37366,23 +37381,25 @@
         <v>133</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="K419" s="4"/>
       <c r="L419" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M419" s="4"/>
+        <v>1759</v>
+      </c>
+      <c r="M419" s="4" t="s">
+        <v>1760</v>
+      </c>
       <c r="N419" s="4"/>
       <c r="O419" s="4" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="P419" s="5"/>
       <c r="Q419" s="4" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="R419" s="4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="S419" s="4">
         <v>0</v>
@@ -37393,17 +37410,17 @@
       <c r="U419" s="4"/>
       <c r="V419" s="4"/>
       <c r="W419" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X419" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y419" s="4"/>
       <c r="Z419" s="4" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="AA419" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="AB419" s="4" t="s">
         <v>49</v>
@@ -37414,16 +37431,16 @@
         <v>1000</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="C420" s="4">
-        <v>163568415</v>
+        <v>163586934</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="E420" s="4">
-        <v>8370323</v>
+        <v>7788272</v>
       </c>
       <c r="F420" s="4" t="s">
         <v>51</v>
@@ -37435,24 +37452,26 @@
         <v>133</v>
       </c>
       <c r="I420" s="4" t="s">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="K420" s="4"/>
-      <c r="L420" s="4"/>
+      <c r="L420" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="M420" s="4"/>
       <c r="N420" s="4"/>
       <c r="O420" s="4" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="P420" s="5"/>
       <c r="Q420" s="4" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="R420" s="4" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="S420" s="4">
         <v>0</v>
@@ -37463,16 +37482,18 @@
       <c r="U420" s="4"/>
       <c r="V420" s="4"/>
       <c r="W420" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X420" s="4" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="Y420" s="4"/>
       <c r="Z420" s="4" t="s">
-        <v>1766</v>
-      </c>
-      <c r="AA420" s="4"/>
+        <v>1767</v>
+      </c>
+      <c r="AA420" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="AB420" s="4" t="s">
         <v>49</v>
       </c>
@@ -37482,16 +37503,16 @@
         <v>1000</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="C421" s="4">
-        <v>163581320</v>
+        <v>163568415</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="E421" s="4">
-        <v>8074238</v>
+        <v>8370323</v>
       </c>
       <c r="F421" s="4" t="s">
         <v>51</v>
@@ -37500,24 +37521,24 @@
         <v>36</v>
       </c>
       <c r="H421" s="4" t="s">
-        <v>1767</v>
+        <v>133</v>
       </c>
       <c r="I421" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="J421" s="4" t="s">
         <v>1768</v>
-      </c>
-      <c r="J421" s="4" t="s">
-        <v>1769</v>
       </c>
       <c r="K421" s="4"/>
       <c r="L421" s="4"/>
       <c r="M421" s="4"/>
       <c r="N421" s="4"/>
       <c r="O421" s="4" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="P421" s="5"/>
       <c r="Q421" s="4" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="R421" s="4" t="s">
         <v>43</v>
@@ -37534,15 +37555,13 @@
         <v>3</v>
       </c>
       <c r="X421" s="4" t="s">
-        <v>46</v>
+        <v>178</v>
       </c>
       <c r="Y421" s="4"/>
       <c r="Z421" s="4" t="s">
-        <v>1772</v>
-      </c>
-      <c r="AA421" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>1771</v>
+      </c>
+      <c r="AA421" s="4"/>
       <c r="AB421" s="4" t="s">
         <v>49</v>
       </c>
@@ -37555,13 +37574,13 @@
         <v>33</v>
       </c>
       <c r="C422" s="4">
-        <v>163584981</v>
+        <v>163581320</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E422" s="4">
-        <v>7362058</v>
+        <v>8074238</v>
       </c>
       <c r="F422" s="4" t="s">
         <v>51</v>
@@ -37570,7 +37589,7 @@
         <v>36</v>
       </c>
       <c r="H422" s="4" t="s">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="I422" s="4" t="s">
         <v>1773</v>
@@ -37601,7 +37620,7 @@
       <c r="U422" s="4"/>
       <c r="V422" s="4"/>
       <c r="W422" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X422" s="4" t="s">
         <v>46</v>
@@ -37610,8 +37629,78 @@
       <c r="Z422" s="4" t="s">
         <v>1777</v>
       </c>
-      <c r="AA422" s="4"/>
+      <c r="AA422" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="AB422" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="423" spans="1:28">
+      <c r="A423" s="4">
+        <v>1000</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C423" s="4">
+        <v>163584981</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E423" s="4">
+        <v>7362058</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H423" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="I423" s="4" t="s">
+        <v>1778</v>
+      </c>
+      <c r="J423" s="4" t="s">
+        <v>1779</v>
+      </c>
+      <c r="K423" s="4"/>
+      <c r="L423" s="4"/>
+      <c r="M423" s="4"/>
+      <c r="N423" s="4"/>
+      <c r="O423" s="4" t="s">
+        <v>1780</v>
+      </c>
+      <c r="P423" s="5"/>
+      <c r="Q423" s="4" t="s">
+        <v>1781</v>
+      </c>
+      <c r="R423" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S423" s="4">
+        <v>0</v>
+      </c>
+      <c r="T423" s="4">
+        <v>0</v>
+      </c>
+      <c r="U423" s="4"/>
+      <c r="V423" s="4"/>
+      <c r="W423" s="4">
+        <v>2</v>
+      </c>
+      <c r="X423" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y423" s="4"/>
+      <c r="Z423" s="4" t="s">
+        <v>1782</v>
+      </c>
+      <c r="AA423" s="4"/>
+      <c r="AB423" s="4" t="s">
         <v>49</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 19:00:52</t>
+    <t>09/08/2026 a las 20:00:51</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 21:00:53</t>
+    <t>09/08/2026 a las 22:00:48</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>09/08/2026 a las 22:00:48</t>
+    <t>09/08/2026 a las 23:00:59</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>10/08/2026 a las 20:01:03</t>
+    <t>10/08/2026 a las 21:00:52</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>11/08/2026 a las 07:54:25</t>
+    <t>11/08/2026 a las 08:01:14</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -17779,7 +17779,7 @@
         <v>5</v>
       </c>
       <c r="X171" s="4" t="s">
-        <v>543</v>
+        <v>148</v>
       </c>
       <c r="Y171" s="4"/>
       <c r="Z171" s="4" t="s">
@@ -20537,7 +20537,7 @@
         <v>8</v>
       </c>
       <c r="X207" s="4" t="s">
-        <v>543</v>
+        <v>148</v>
       </c>
       <c r="Y207" s="4"/>
       <c r="Z207" s="4" t="s">
@@ -25495,7 +25495,7 @@
         <v>7</v>
       </c>
       <c r="X272" s="4" t="s">
-        <v>543</v>
+        <v>148</v>
       </c>
       <c r="Y272" s="4"/>
       <c r="Z272" s="4" t="s">
@@ -28615,7 +28615,7 @@
         <v>7</v>
       </c>
       <c r="X316" s="4" t="s">
-        <v>543</v>
+        <v>148</v>
       </c>
       <c r="Y316" s="4"/>
       <c r="Z316" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>18/08/2026 a las 08:00:59</t>
+    <t>18/08/2026 a las 08:04:28</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -2006,37 +2006,37 @@
     <t>Inspeccion PQR Peticion SUSPENSION TENDIDO RETIRO ACOMETIDA SE GENERA ORDEN PARA VALIDAR INFORMACION, VALIDAR CONEXIONES, VALIDAR DESOCUPADO Y TIEMPO DE DESOCUPADO, VALIDAR SI EXISTE DOBLE FACTURACIO, VALIDAR PREDIO UNIFICADO TIEMPO DE UNIFICACION, VALIDAR SI ESTA HABITADO, SI ESTA CONECTADO DIRECTO, VALIDAR</t>
   </si>
   <si>
+    <t>EL REPOSO</t>
+  </si>
+  <si>
+    <t>CR 30</t>
+  </si>
+  <si>
+    <t>CL 14 CR 30 - 113 DPL AU519</t>
+  </si>
+  <si>
+    <t>CERVANTES  NORMA</t>
+  </si>
+  <si>
+    <t>13024597-MCA55</t>
+  </si>
+  <si>
+    <t>Revision Suministromedidor MD Camp.Dirigidas SUSPENSION AUTOSOPORTADA 060-09-Acciones Especiales-MAG</t>
+  </si>
+  <si>
+    <t>EL ROSARIO</t>
+  </si>
+  <si>
+    <t>CR 7 CL 10A - 26</t>
+  </si>
+  <si>
+    <t>Garcia Delgado  Marla Isabel</t>
+  </si>
+  <si>
+    <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Estefany Viloria acuna  tel3002157745 Soporte de reclamo, ver lectura actual, alto estimado, estado del medidor, corregir anomalias, Conexiones normalizar si es necesario.</t>
+  </si>
+  <si>
     <t>ERVER WILLIAM BARRERA APONTE</t>
-  </si>
-  <si>
-    <t>EL REPOSO</t>
-  </si>
-  <si>
-    <t>CR 30</t>
-  </si>
-  <si>
-    <t>CL 14 CR 30 - 113 DPL AU519</t>
-  </si>
-  <si>
-    <t>CERVANTES  NORMA</t>
-  </si>
-  <si>
-    <t>13024597-MCA55</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD Camp.Dirigidas SUSPENSION AUTOSOPORTADA 060-09-Acciones Especiales-MAG</t>
-  </si>
-  <si>
-    <t>EL ROSARIO</t>
-  </si>
-  <si>
-    <t>CR 7 CL 10A - 26</t>
-  </si>
-  <si>
-    <t>Garcia Delgado  Marla Isabel</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Estefany Viloria acuna  tel3002157745 Soporte de reclamo, ver lectura actual, alto estimado, estado del medidor, corregir anomalias, Conexiones normalizar si es necesario.</t>
   </si>
   <si>
     <t>EL TOTUMO</t>
@@ -15716,7 +15716,7 @@
         <v>1000</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>663</v>
+        <v>296</v>
       </c>
       <c r="C138" s="4">
         <v>163537217</v>
@@ -15740,24 +15740,24 @@
         <v>57</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K138" s="4"/>
       <c r="L138" s="4" t="s">
         <v>593</v>
       </c>
       <c r="M138" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="N138" s="4">
         <v>113</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P138" s="5"/>
       <c r="Q138" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="R138" s="4" t="s">
         <v>100</v>
@@ -15769,7 +15769,7 @@
         <v>0</v>
       </c>
       <c r="U138" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="V138" s="4" t="s">
         <v>71</v>
@@ -15778,11 +15778,11 @@
         <v>13</v>
       </c>
       <c r="X138" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="Y138" s="4"/>
       <c r="Z138" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AA138" s="4" t="s">
         <v>123</v>
@@ -15820,18 +15820,18 @@
         <v>636</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
       <c r="O139" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P139" s="5"/>
       <c r="Q139" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="R139" s="4" t="s">
         <v>51</v>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="Y139" s="4"/>
       <c r="Z139" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AA139" s="4" t="s">
         <v>84</v>
@@ -15866,7 +15866,7 @@
         <v>1000</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C140" s="4">
         <v>163568443</v>
@@ -25770,7 +25770,7 @@
       </c>
       <c r="K271" s="4"/>
       <c r="L271" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="M271" s="4" t="s">
         <v>1234</v>
@@ -26159,7 +26159,7 @@
         <v>305</v>
       </c>
       <c r="M276" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="N276" s="4">
         <v>15</v>
@@ -27668,7 +27668,7 @@
         <v>1000</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C297" s="4">
         <v>163836751</v>
@@ -27740,7 +27740,7 @@
         <v>1000</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C298" s="4">
         <v>163836752</v>
@@ -27812,7 +27812,7 @@
         <v>1000</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C299" s="4">
         <v>163836754</v>
@@ -33512,7 +33512,7 @@
         <v>1000</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C376" s="4">
         <v>163846526</v>
@@ -33586,7 +33586,7 @@
         <v>1000</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C377" s="4">
         <v>163846528</v>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="K378" s="4"/>
       <c r="L378" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="M378" s="4" t="s">
         <v>1214</v>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>30/08/2026 a las 20:00:58</t>
+    <t>30/08/2026 a las 21:00:56</t>
   </si>
   <si>
     <t>Num_Lote</t>
